--- a/Data/mcquarrie_real_nom_stock_bond_returns_1793_2024.xlsx
+++ b/Data/mcquarrie_real_nom_stock_bond_returns_1793_2024.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cherifarkam/Desktop/Data_Science/Projects/Repositories/Stocks_Bonds_Mcquarrie_Analysis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7F699A-2F04-F841-865C-86DEEF83DB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B9FD39-B334-6147-9B74-BBAC9C2CD4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="2760" windowWidth="29640" windowHeight="18180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="2540" windowWidth="29640" windowHeight="18180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stocks v Bonds Periods" sheetId="1" r:id="rId1"/>
     <sheet name="Rolling Returns" sheetId="2" r:id="rId2"/>
-    <sheet name="Real Returns 1792-2025" sheetId="3" r:id="rId3"/>
-    <sheet name="Nominal Returns 1792-2025" sheetId="4" r:id="rId4"/>
-    <sheet name="2019-2025 JanToJan" sheetId="5" r:id="rId5"/>
+    <sheet name="Real Returns 1792-2026" sheetId="3" r:id="rId3"/>
+    <sheet name="Nominal Returns 1792-2026" sheetId="4" r:id="rId4"/>
+    <sheet name="2019-2026 JanToJan" sheetId="5" r:id="rId5"/>
     <sheet name="VTI" sheetId="6" r:id="rId6"/>
     <sheet name="VCLT" sheetId="7" r:id="rId7"/>
   </sheets>
@@ -700,7 +700,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -759,7 +759,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:S235">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:S236">
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="To January of:"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Measuring Worth  inflation index (annual)"/>
@@ -1016,11 +1016,11 @@
         <v>1900</v>
       </c>
       <c r="C2" s="2">
-        <f>RATE(107,,'Real Returns 1792-2025'!J3,-'Real Returns 1792-2025'!J110)</f>
+        <f>RATE(107,,'Real Returns 1792-2026'!J3,-'Real Returns 1792-2026'!J110)</f>
         <v>5.7228768231625704E-2</v>
       </c>
       <c r="D2" s="2">
-        <f>RATE(107,,'Real Returns 1792-2025'!K3,-'Real Returns 1792-2025'!K110)</f>
+        <f>RATE(107,,'Real Returns 1792-2026'!K3,-'Real Returns 1792-2026'!K110)</f>
         <v>6.1299657808366236E-2</v>
       </c>
       <c r="E2" s="2">
@@ -1036,11 +1036,11 @@
         <v>2000</v>
       </c>
       <c r="C3" s="2">
-        <f>RATE(100,,'Real Returns 1792-2025'!J110,-'Real Returns 1792-2025'!J210)</f>
+        <f>RATE(100,,'Real Returns 1792-2026'!J110,-'Real Returns 1792-2026'!J210)</f>
         <v>6.9148077756872844E-2</v>
       </c>
       <c r="D3" s="2">
-        <f>RATE(100,,'Real Returns 1792-2025'!K110,-'Real Returns 1792-2025'!K210)</f>
+        <f>RATE(100,,'Real Returns 1792-2026'!K110,-'Real Returns 1792-2026'!K210)</f>
         <v>1.8370889850210365E-2</v>
       </c>
       <c r="E3" s="2">
@@ -1056,11 +1056,11 @@
         <v>2025</v>
       </c>
       <c r="C4" s="2">
-        <f>RATE(25,,'Real Returns 1792-2025'!J210,-'Real Returns 1792-2025'!J235)</f>
+        <f>RATE(25,,'Real Returns 1792-2026'!J210,-'Real Returns 1792-2026'!J235)</f>
         <v>5.1864136651233031E-2</v>
       </c>
       <c r="D4" s="2">
-        <f>RATE(25,,'Real Returns 1792-2025'!K210,-'Real Returns 1792-2025'!K235)</f>
+        <f>RATE(25,,'Real Returns 1792-2026'!K210,-'Real Returns 1792-2026'!K235)</f>
         <v>3.2667744646386471E-2</v>
       </c>
       <c r="E4" s="2">
@@ -1076,11 +1076,11 @@
         <v>2025</v>
       </c>
       <c r="C5" s="37">
-        <f>RATE(232,,'Real Returns 1792-2025'!J3,-'Real Returns 1792-2025'!J235)</f>
+        <f>RATE(232,,'Real Returns 1792-2026'!J3,-'Real Returns 1792-2026'!J235)</f>
         <v>6.1767815480094468E-2</v>
       </c>
       <c r="D5" s="37">
-        <f>RATE(232,,'Real Returns 1792-2025'!K3,-'Real Returns 1792-2025'!K235)</f>
+        <f>RATE(232,,'Real Returns 1792-2026'!K3,-'Real Returns 1792-2026'!K235)</f>
         <v>3.951030681644041E-2</v>
       </c>
       <c r="E5" s="37">
@@ -1096,11 +1096,11 @@
         <v>1942</v>
       </c>
       <c r="C6" s="2">
-        <f>RATE(149,,'Real Returns 1792-2025'!J3,-'Real Returns 1792-2025'!J152)</f>
+        <f>RATE(149,,'Real Returns 1792-2026'!J3,-'Real Returns 1792-2026'!J152)</f>
         <v>5.3550463589011325E-2</v>
       </c>
       <c r="D6" s="2">
-        <f>RATE(149,,'Real Returns 1792-2025'!K3,-'Real Returns 1792-2025'!K152)</f>
+        <f>RATE(149,,'Real Returns 1792-2026'!K3,-'Real Returns 1792-2026'!K152)</f>
         <v>5.1916700146403157E-2</v>
       </c>
       <c r="E6" s="2">
@@ -1116,11 +1116,11 @@
         <v>2025</v>
       </c>
       <c r="C7" s="2">
-        <f>RATE(83,,'Real Returns 1792-2025'!J152,-'Real Returns 1792-2025'!J235)</f>
+        <f>RATE(83,,'Real Returns 1792-2026'!J152,-'Real Returns 1792-2026'!J235)</f>
         <v>7.6680583370517433E-2</v>
       </c>
       <c r="D7" s="2">
-        <f>RATE(83,,'Real Returns 1792-2025'!K152,-'Real Returns 1792-2025'!K235)</f>
+        <f>RATE(83,,'Real Returns 1792-2026'!K152,-'Real Returns 1792-2026'!K235)</f>
         <v>1.7604551685094335E-2</v>
       </c>
       <c r="E7" s="2">
@@ -1136,11 +1136,11 @@
         <v>1982</v>
       </c>
       <c r="C8" s="19">
-        <f>RATE(40,,'Real Returns 1792-2025'!J152,-'Real Returns 1792-2025'!J192)</f>
+        <f>RATE(40,,'Real Returns 1792-2026'!J152,-'Real Returns 1792-2026'!J192)</f>
         <v>6.690855476577387E-2</v>
       </c>
       <c r="D8" s="19">
-        <f>RATE(40,,'Real Returns 1792-2025'!K152,-'Real Returns 1792-2025'!K192)</f>
+        <f>RATE(40,,'Real Returns 1792-2026'!K152,-'Real Returns 1792-2026'!K192)</f>
         <v>-2.1045299583573766E-2</v>
       </c>
       <c r="E8" s="2">
@@ -1156,11 +1156,11 @@
         <v>2025</v>
       </c>
       <c r="C9" s="19">
-        <f>RATE(43,,'Real Returns 1792-2025'!J192,-'Real Returns 1792-2025'!J235)</f>
+        <f>RATE(43,,'Real Returns 1792-2026'!J192,-'Real Returns 1792-2026'!J235)</f>
         <v>8.5851180562127774E-2</v>
       </c>
       <c r="D9" s="19">
-        <f>RATE(43,,'Real Returns 1792-2025'!K192,-'Real Returns 1792-2025'!K235)</f>
+        <f>RATE(43,,'Real Returns 1792-2026'!K192,-'Real Returns 1792-2026'!K235)</f>
         <v>5.4926605424079983E-2</v>
       </c>
       <c r="E9" s="2">
@@ -2226,19 +2226,19 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <f>MAX('Real Returns 1792-2025'!$L:$L)</f>
+        <f>MAX('Real Returns 1792-2026'!$L:$L)</f>
         <v>0.17486097763558114</v>
       </c>
       <c r="C3" s="2">
-        <f>MAX('Real Returns 1792-2025'!$M:$M)</f>
+        <f>MAX('Real Returns 1792-2026'!$M:$M)</f>
         <v>0.13879258114992307</v>
       </c>
       <c r="D3" s="2">
-        <f>MIN('Real Returns 1792-2025'!L:L)</f>
+        <f>MIN('Real Returns 1792-2026'!L:L)</f>
         <v>-3.8984943726188541E-2</v>
       </c>
       <c r="E3" s="2">
-        <f>MIN('Real Returns 1792-2025'!M:M)</f>
+        <f>MIN('Real Returns 1792-2026'!M:M)</f>
         <v>-5.4105372090264746E-2</v>
       </c>
       <c r="F3" s="2">
@@ -2250,20 +2250,20 @@
         <v>0.19289795324018782</v>
       </c>
       <c r="H3" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$L:$L)</f>
-        <v>6.4836396173182778E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$L:$L)</f>
+        <v>6.5355033627492023E-2</v>
       </c>
       <c r="I3" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$M:$M)</f>
-        <v>5.1126104130944192E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$M:$M)</f>
+        <v>5.0774329840545016E-2</v>
       </c>
       <c r="J3" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$L:$L)</f>
-        <v>6.2785760901891377E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$L:$L)</f>
+        <v>6.3012328994997882E-2</v>
       </c>
       <c r="K3" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$M:$M)</f>
-        <v>4.2883213667721874E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$M:$M)</f>
+        <v>4.2684542962664489E-2</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -2271,19 +2271,19 @@
         <v>30</v>
       </c>
       <c r="B4" s="2">
-        <f>MAX('Real Returns 1792-2025'!$N:$N)</f>
+        <f>MAX('Real Returns 1792-2026'!$N:$N)</f>
         <v>0.10433815215021479</v>
       </c>
       <c r="C4" s="2">
-        <f>MAX('Real Returns 1792-2025'!$O:$O)</f>
+        <f>MAX('Real Returns 1792-2026'!$O:$O)</f>
         <v>8.7917715231416893E-2</v>
       </c>
       <c r="D4" s="2">
-        <f>MIN('Real Returns 1792-2025'!N:N)</f>
+        <f>MIN('Real Returns 1792-2026'!N:N)</f>
         <v>2.0015465104470501E-2</v>
       </c>
       <c r="E4" s="2">
-        <f>MIN('Real Returns 1792-2025'!O:O)</f>
+        <f>MIN('Real Returns 1792-2026'!O:O)</f>
         <v>-2.1255628917577086E-2</v>
       </c>
       <c r="F4" s="2">
@@ -2295,20 +2295,20 @@
         <v>0.10917334414899398</v>
       </c>
       <c r="H4" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$N:$N)</f>
-        <v>6.1753522826289653E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$N:$N)</f>
+        <v>6.1766451066070788E-2</v>
       </c>
       <c r="I4" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$O:$O)</f>
-        <v>4.7806211830209736E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$O:$O)</f>
+        <v>4.7778581254152602E-2</v>
       </c>
       <c r="J4" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$N:$N)</f>
-        <v>6.1847353925529619E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$N:$N)</f>
+        <v>6.1901411569454438E-2</v>
       </c>
       <c r="K4" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$O:$O)</f>
-        <v>4.1826987906128932E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$O:$O)</f>
+        <v>4.1774208916408505E-2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -2316,19 +2316,19 @@
         <v>50</v>
       </c>
       <c r="B5" s="2">
-        <f>MAX('Real Returns 1792-2025'!$P:$P)</f>
+        <f>MAX('Real Returns 1792-2026'!$P:$P)</f>
         <v>8.9078877682734883E-2</v>
       </c>
       <c r="C5" s="2">
-        <f>MAX('Real Returns 1792-2025'!$Q:$Q)</f>
+        <f>MAX('Real Returns 1792-2026'!$Q:$Q)</f>
         <v>7.3672054611964258E-2</v>
       </c>
       <c r="D5" s="2">
-        <f>MIN('Real Returns 1792-2025'!P:P)</f>
+        <f>MIN('Real Returns 1792-2026'!P:P)</f>
         <v>3.8001385483236776E-2</v>
       </c>
       <c r="E5" s="2">
-        <f>MIN('Real Returns 1792-2025'!Q:Q)</f>
+        <f>MIN('Real Returns 1792-2026'!Q:Q)</f>
         <v>-6.3890743262199796E-3</v>
       </c>
       <c r="F5" s="2">
@@ -2340,20 +2340,20 @@
         <v>8.0061128938184234E-2</v>
       </c>
       <c r="H5" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$P:$P)</f>
-        <v>5.9309912220267401E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$P:$P)</f>
+        <v>5.9328789111964139E-2</v>
       </c>
       <c r="I5" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$Q:$Q)</f>
-        <v>4.0815900618379773E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$Q:$Q)</f>
+        <v>4.0547335343232641E-2</v>
       </c>
       <c r="J5" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$P:$P)</f>
-        <v>6.081996089239422E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$P:$P)</f>
+        <v>6.0911775414574411E-2</v>
       </c>
       <c r="K5" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$Q:$Q)</f>
-        <v>3.9474192014525733E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$Q:$Q)</f>
+        <v>3.9468975709983173E-2</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -2361,19 +2361,19 @@
         <v>100</v>
       </c>
       <c r="B6" s="2">
-        <f>MAX('Real Returns 1792-2025'!$R:$R)</f>
+        <f>MAX('Real Returns 1792-2026'!$R:$R)</f>
         <v>7.5086449057128454E-2</v>
       </c>
       <c r="C6" s="2">
-        <f>MAX('Real Returns 1792-2025'!$S:$S)</f>
+        <f>MAX('Real Returns 1792-2026'!$S:$S)</f>
         <v>6.6300153673099091E-2</v>
       </c>
       <c r="D6" s="2">
-        <f>MIN('Real Returns 1792-2025'!$R:$R)</f>
+        <f>MIN('Real Returns 1792-2026'!$R:$R)</f>
         <v>4.9569754821905405E-2</v>
       </c>
       <c r="E6" s="2">
-        <f>MIN('Real Returns 1792-2025'!$S:$S)</f>
+        <f>MIN('Real Returns 1792-2026'!$S:$S)</f>
         <v>1.5147549885746672E-2</v>
       </c>
       <c r="F6" s="2">
@@ -2385,20 +2385,20 @@
         <v>5.1152603787352417E-2</v>
       </c>
       <c r="H6" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$R:$R)</f>
-        <v>6.0704080151793398E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$R:$R)</f>
+        <v>6.0794448934403431E-2</v>
       </c>
       <c r="I6" s="2">
-        <f>MEDIAN('Real Returns 1792-2025'!$S:$S)</f>
-        <v>3.9112818737744914E-2</v>
+        <f>MEDIAN('Real Returns 1792-2026'!$S:$S)</f>
+        <v>3.8837604507258358E-2</v>
       </c>
       <c r="J6" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$R:$R)</f>
-        <v>6.1973269856479725E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$R:$R)</f>
+        <v>6.2029965718630051E-2</v>
       </c>
       <c r="K6" s="2">
-        <f>AVERAGE('Real Returns 1792-2025'!$S:$S)</f>
-        <v>3.9312114753779721E-2</v>
+        <f>AVERAGE('Real Returns 1792-2026'!$S:$S)</f>
+        <v>3.9194783837259439E-2</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3922,11 +3922,11 @@
         <v>1.5931994938116616</v>
       </c>
       <c r="L13" s="2">
-        <f>RATE(10,,J3,-'Real Returns 1792-2025'!$J13)</f>
+        <f>RATE(10,,J3,-'Real Returns 1792-2026'!$J13)</f>
         <v>7.1099818815955534E-2</v>
       </c>
       <c r="M13" s="2">
-        <f>RATE(10,,K3,-'Real Returns 1792-2025'!$K13)</f>
+        <f>RATE(10,,K3,-'Real Returns 1792-2026'!$K13)</f>
         <v>4.7676049939700635E-2</v>
       </c>
       <c r="N13" s="2"/>
@@ -3969,11 +3969,11 @@
         <v>1.5584926809468853</v>
       </c>
       <c r="L14" s="2">
-        <f>RATE(10,,J4,-'Real Returns 1792-2025'!$J14)</f>
+        <f>RATE(10,,J4,-'Real Returns 1792-2026'!$J14)</f>
         <v>8.6624521425889306E-2</v>
       </c>
       <c r="M14" s="2">
-        <f>RATE(10,,K4,-'Real Returns 1792-2025'!$K14)</f>
+        <f>RATE(10,,K4,-'Real Returns 1792-2026'!$K14)</f>
         <v>6.0668297790944514E-2</v>
       </c>
       <c r="N14" s="2"/>
@@ -4016,11 +4016,11 @@
         <v>1.5465953821180198</v>
       </c>
       <c r="L15" s="2">
-        <f>RATE(10,,J5,-'Real Returns 1792-2025'!$J15)</f>
+        <f>RATE(10,,J5,-'Real Returns 1792-2026'!$J15)</f>
         <v>7.847643110689953E-2</v>
       </c>
       <c r="M15" s="2">
-        <f>RATE(10,,K5,-'Real Returns 1792-2025'!$K15)</f>
+        <f>RATE(10,,K5,-'Real Returns 1792-2026'!$K15)</f>
         <v>5.7472506783978729E-2</v>
       </c>
       <c r="N15" s="2"/>
@@ -4063,11 +4063,11 @@
         <v>1.6120495291818451</v>
       </c>
       <c r="L16" s="2">
-        <f>RATE(10,,J6,-'Real Returns 1792-2025'!$J16)</f>
+        <f>RATE(10,,J6,-'Real Returns 1792-2026'!$J16)</f>
         <v>7.6543985522509836E-2</v>
       </c>
       <c r="M16" s="2">
-        <f>RATE(10,,K6,-'Real Returns 1792-2025'!$K16)</f>
+        <f>RATE(10,,K6,-'Real Returns 1792-2026'!$K16)</f>
         <v>7.2668558508405284E-2</v>
       </c>
       <c r="N16" s="2"/>
@@ -4110,11 +4110,11 @@
         <v>1.8084228411568388</v>
       </c>
       <c r="L17" s="2">
-        <f>RATE(10,,J7,-'Real Returns 1792-2025'!$J17)</f>
+        <f>RATE(10,,J7,-'Real Returns 1792-2026'!$J17)</f>
         <v>9.28102844226011E-2</v>
       </c>
       <c r="M17" s="2">
-        <f>RATE(10,,K7,-'Real Returns 1792-2025'!$K17)</f>
+        <f>RATE(10,,K7,-'Real Returns 1792-2026'!$K17)</f>
         <v>9.2613773069113031E-2</v>
       </c>
       <c r="N17" s="2"/>
@@ -4157,11 +4157,11 @@
         <v>1.8678606955030765</v>
       </c>
       <c r="L18" s="2">
-        <f>RATE(10,,J8,-'Real Returns 1792-2025'!$J18)</f>
+        <f>RATE(10,,J8,-'Real Returns 1792-2026'!$J18)</f>
         <v>7.4341063016121672E-2</v>
       </c>
       <c r="M18" s="2">
-        <f>RATE(10,,K8,-'Real Returns 1792-2025'!$K18)</f>
+        <f>RATE(10,,K8,-'Real Returns 1792-2026'!$K18)</f>
         <v>7.6620289399531E-2</v>
       </c>
       <c r="N18" s="2"/>
@@ -4204,11 +4204,11 @@
         <v>1.9944117017504586</v>
       </c>
       <c r="L19" s="2">
-        <f>RATE(10,,J9,-'Real Returns 1792-2025'!$J19)</f>
+        <f>RATE(10,,J9,-'Real Returns 1792-2026'!$J19)</f>
         <v>7.5258089495934558E-2</v>
       </c>
       <c r="M19" s="2">
-        <f>RATE(10,,K9,-'Real Returns 1792-2025'!$K19)</f>
+        <f>RATE(10,,K9,-'Real Returns 1792-2026'!$K19)</f>
         <v>7.8424619974650195E-2</v>
       </c>
       <c r="N19" s="2"/>
@@ -4251,11 +4251,11 @@
         <v>2.1201856341795349</v>
       </c>
       <c r="L20" s="2">
-        <f>RATE(10,,J10,-'Real Returns 1792-2025'!$J20)</f>
+        <f>RATE(10,,J10,-'Real Returns 1792-2026'!$J20)</f>
         <v>7.8907157895240693E-2</v>
       </c>
       <c r="M20" s="2">
-        <f>RATE(10,,K10,-'Real Returns 1792-2025'!$K20)</f>
+        <f>RATE(10,,K10,-'Real Returns 1792-2026'!$K20)</f>
         <v>8.025447074624488E-2</v>
       </c>
       <c r="N20" s="2"/>
@@ -4298,11 +4298,11 @@
         <v>2.1313991373404417</v>
       </c>
       <c r="L21" s="2">
-        <f>RATE(10,,J11,-'Real Returns 1792-2025'!$J21)</f>
+        <f>RATE(10,,J11,-'Real Returns 1792-2026'!$J21)</f>
         <v>6.1175522849825359E-2</v>
       </c>
       <c r="M21" s="2">
-        <f>RATE(10,,K11,-'Real Returns 1792-2025'!$K21)</f>
+        <f>RATE(10,,K11,-'Real Returns 1792-2026'!$K21)</f>
         <v>6.4179180145916934E-2</v>
       </c>
       <c r="N21" s="2"/>
@@ -4345,11 +4345,11 @@
         <v>2.0201880994886685</v>
       </c>
       <c r="L22" s="2">
-        <f>RATE(10,,J12,-'Real Returns 1792-2025'!$J22)</f>
+        <f>RATE(10,,J12,-'Real Returns 1792-2026'!$J22)</f>
         <v>3.9081853383676056E-2</v>
       </c>
       <c r="M22" s="2">
-        <f>RATE(10,,K12,-'Real Returns 1792-2025'!$K22)</f>
+        <f>RATE(10,,K12,-'Real Returns 1792-2026'!$K22)</f>
         <v>3.5955078579087404E-2</v>
       </c>
       <c r="N22" s="2"/>
@@ -4392,11 +4392,11 @@
         <v>1.8844361224548367</v>
       </c>
       <c r="L23" s="2">
-        <f>RATE(10,,J13,-'Real Returns 1792-2025'!$J23)</f>
+        <f>RATE(10,,J13,-'Real Returns 1792-2026'!$J23)</f>
         <v>1.8649199053284233E-2</v>
       </c>
       <c r="M23" s="2">
-        <f>RATE(10,,K13,-'Real Returns 1792-2025'!$K23)</f>
+        <f>RATE(10,,K13,-'Real Returns 1792-2026'!$K23)</f>
         <v>1.6930156023153436E-2</v>
       </c>
       <c r="N23" s="2"/>
@@ -4439,11 +4439,11 @@
         <v>1.6005085465101239</v>
       </c>
       <c r="L24" s="2">
-        <f>RATE(10,,J14,-'Real Returns 1792-2025'!$J24)</f>
+        <f>RATE(10,,J14,-'Real Returns 1792-2026'!$J24)</f>
         <v>1.2715843463067214E-2</v>
       </c>
       <c r="M24" s="2">
-        <f>RATE(10,,K14,-'Real Returns 1792-2025'!$K24)</f>
+        <f>RATE(10,,K14,-'Real Returns 1792-2026'!$K24)</f>
         <v>2.6637711821674683E-3</v>
       </c>
       <c r="N24" s="2"/>
@@ -4486,11 +4486,11 @@
         <v>1.6258863656635549</v>
       </c>
       <c r="L25" s="2">
-        <f>RATE(10,,J15,-'Real Returns 1792-2025'!$J25)</f>
+        <f>RATE(10,,J15,-'Real Returns 1792-2026'!$J25)</f>
         <v>8.1316348684056915E-3</v>
       </c>
       <c r="M25" s="2">
-        <f>RATE(10,,K15,-'Real Returns 1792-2025'!$K25)</f>
+        <f>RATE(10,,K15,-'Real Returns 1792-2026'!$K25)</f>
         <v>5.0122329743731058E-3</v>
       </c>
       <c r="N25" s="2"/>
@@ -4533,11 +4533,11 @@
         <v>2.0855317640982838</v>
       </c>
       <c r="L26" s="2">
-        <f>RATE(10,,J16,-'Real Returns 1792-2025'!$J26)</f>
+        <f>RATE(10,,J16,-'Real Returns 1792-2026'!$J26)</f>
         <v>3.3408092441310794E-2</v>
       </c>
       <c r="M26" s="2">
-        <f>RATE(10,,K16,-'Real Returns 1792-2025'!$K26)</f>
+        <f>RATE(10,,K16,-'Real Returns 1792-2026'!$K26)</f>
         <v>2.6086190603105221E-2</v>
       </c>
       <c r="N26" s="2"/>
@@ -4580,11 +4580,11 @@
         <v>2.4609931405897552</v>
       </c>
       <c r="L27" s="2">
-        <f>RATE(10,,J17,-'Real Returns 1792-2025'!$J27)</f>
+        <f>RATE(10,,J17,-'Real Returns 1792-2026'!$J27)</f>
         <v>3.4622237396273209E-2</v>
       </c>
       <c r="M27" s="2">
-        <f>RATE(10,,K17,-'Real Returns 1792-2025'!$K27)</f>
+        <f>RATE(10,,K17,-'Real Returns 1792-2026'!$K27)</f>
         <v>3.1290558885156076E-2</v>
       </c>
       <c r="N27" s="2"/>
@@ -4627,11 +4627,11 @@
         <v>2.9920583061003283</v>
       </c>
       <c r="L28" s="2">
-        <f>RATE(10,,J18,-'Real Returns 1792-2025'!$J28)</f>
+        <f>RATE(10,,J18,-'Real Returns 1792-2026'!$J28)</f>
         <v>6.4106825156501859E-2</v>
       </c>
       <c r="M28" s="2">
-        <f>RATE(10,,K18,-'Real Returns 1792-2025'!$K28)</f>
+        <f>RATE(10,,K18,-'Real Returns 1792-2026'!$K28)</f>
         <v>4.8244414276803982E-2</v>
       </c>
       <c r="N28" s="2"/>
@@ -4674,11 +4674,11 @@
         <v>3.0563694227998499</v>
       </c>
       <c r="L29" s="2">
-        <f>RATE(10,,J19,-'Real Returns 1792-2025'!$J29)</f>
+        <f>RATE(10,,J19,-'Real Returns 1792-2026'!$J29)</f>
         <v>3.9683616969350806E-2</v>
       </c>
       <c r="M29" s="2">
-        <f>RATE(10,,K19,-'Real Returns 1792-2025'!$K29)</f>
+        <f>RATE(10,,K19,-'Real Returns 1792-2026'!$K29)</f>
         <v>4.3612093839565755E-2</v>
       </c>
       <c r="N29" s="2"/>
@@ -4721,11 +4721,11 @@
         <v>3.4580826101114543</v>
       </c>
       <c r="L30" s="2">
-        <f>RATE(10,,J20,-'Real Returns 1792-2025'!$J30)</f>
+        <f>RATE(10,,J20,-'Real Returns 1792-2026'!$J30)</f>
         <v>2.9802534373180842E-2</v>
       </c>
       <c r="M30" s="2">
-        <f>RATE(10,,K20,-'Real Returns 1792-2025'!$K30)</f>
+        <f>RATE(10,,K20,-'Real Returns 1792-2026'!$K30)</f>
         <v>5.0137452599744302E-2</v>
       </c>
       <c r="N30" s="2"/>
@@ -4768,11 +4768,11 @@
         <v>4.0522441633169377</v>
       </c>
       <c r="L31" s="2">
-        <f>RATE(10,,J21,-'Real Returns 1792-2025'!$J31)</f>
+        <f>RATE(10,,J21,-'Real Returns 1792-2026'!$J31)</f>
         <v>4.8120565542747358E-2</v>
       </c>
       <c r="M31" s="2">
-        <f>RATE(10,,K21,-'Real Returns 1792-2025'!$K31)</f>
+        <f>RATE(10,,K21,-'Real Returns 1792-2026'!$K31)</f>
         <v>6.635812405893983E-2</v>
       </c>
       <c r="N31" s="2"/>
@@ -4815,11 +4815,11 @@
         <v>4.3107524304189075</v>
       </c>
       <c r="L32" s="2">
-        <f>RATE(10,,J22,-'Real Returns 1792-2025'!$J32)</f>
+        <f>RATE(10,,J22,-'Real Returns 1792-2026'!$J32)</f>
         <v>6.1108598408014754E-2</v>
       </c>
       <c r="M32" s="2">
-        <f>RATE(10,,K22,-'Real Returns 1792-2025'!$K32)</f>
+        <f>RATE(10,,K22,-'Real Returns 1792-2026'!$K32)</f>
         <v>7.8738371883147307E-2</v>
       </c>
       <c r="N32" s="2"/>
@@ -4862,19 +4862,19 @@
         <v>4.6000905621773995</v>
       </c>
       <c r="L33" s="2">
-        <f>RATE(10,,J23,-'Real Returns 1792-2025'!$J33)</f>
+        <f>RATE(10,,J23,-'Real Returns 1792-2026'!$J33)</f>
         <v>6.1118431104181643E-2</v>
       </c>
       <c r="M33" s="2">
-        <f>RATE(10,,K23,-'Real Returns 1792-2025'!$K33)</f>
+        <f>RATE(10,,K23,-'Real Returns 1792-2026'!$K33)</f>
         <v>9.3348204581024746E-2</v>
       </c>
       <c r="N33" s="2">
-        <f>RATE(30,,J3,-'Real Returns 1792-2025'!$J33)</f>
+        <f>RATE(30,,J3,-'Real Returns 1792-2026'!$J33)</f>
         <v>5.004074312778832E-2</v>
       </c>
       <c r="O33" s="2">
-        <f>RATE(30,,K3,-'Real Returns 1792-2025'!$K33)</f>
+        <f>RATE(30,,K3,-'Real Returns 1792-2026'!$K33)</f>
         <v>5.2185258130263326E-2</v>
       </c>
       <c r="P33" s="2"/>
@@ -4915,19 +4915,19 @@
         <v>5.3709194086662642</v>
       </c>
       <c r="L34" s="2">
-        <f>RATE(10,,J24,-'Real Returns 1792-2025'!$J34)</f>
+        <f>RATE(10,,J24,-'Real Returns 1792-2026'!$J34)</f>
         <v>8.6049330910363195E-2</v>
       </c>
       <c r="M34" s="2">
-        <f>RATE(10,,K24,-'Real Returns 1792-2025'!$K34)</f>
+        <f>RATE(10,,K24,-'Real Returns 1792-2026'!$K34)</f>
         <v>0.12870140024329027</v>
       </c>
       <c r="N34" s="2">
-        <f>RATE(30,,J4,-'Real Returns 1792-2025'!$J34)</f>
+        <f>RATE(30,,J4,-'Real Returns 1792-2026'!$J34)</f>
         <v>6.122030909972221E-2</v>
       </c>
       <c r="O34" s="2">
-        <f>RATE(30,,K4,-'Real Returns 1792-2025'!$K34)</f>
+        <f>RATE(30,,K4,-'Real Returns 1792-2026'!$K34)</f>
         <v>6.2766831433068479E-2</v>
       </c>
       <c r="P34" s="2"/>
@@ -4968,19 +4968,19 @@
         <v>5.9639841582251849</v>
       </c>
       <c r="L35" s="2">
-        <f>RATE(10,,J25,-'Real Returns 1792-2025'!$J35)</f>
+        <f>RATE(10,,J25,-'Real Returns 1792-2026'!$J35)</f>
         <v>0.1105551689857559</v>
       </c>
       <c r="M35" s="2">
-        <f>RATE(10,,K25,-'Real Returns 1792-2025'!$K35)</f>
+        <f>RATE(10,,K25,-'Real Returns 1792-2026'!$K35)</f>
         <v>0.13879258114992307</v>
       </c>
       <c r="N35" s="2">
-        <f>RATE(30,,J5,-'Real Returns 1792-2025'!$J35)</f>
+        <f>RATE(30,,J5,-'Real Returns 1792-2026'!$J35)</f>
         <v>6.4852234231860872E-2</v>
       </c>
       <c r="O35" s="2">
-        <f>RATE(30,,K5,-'Real Returns 1792-2025'!$K35)</f>
+        <f>RATE(30,,K5,-'Real Returns 1792-2026'!$K35)</f>
         <v>6.568377586533547E-2</v>
       </c>
       <c r="P35" s="2"/>
@@ -5021,19 +5021,19 @@
         <v>5.9248299339793276</v>
       </c>
       <c r="L36" s="2">
-        <f>RATE(10,,J26,-'Real Returns 1792-2025'!$J36)</f>
+        <f>RATE(10,,J26,-'Real Returns 1792-2026'!$J36)</f>
         <v>8.6054835730008258E-2</v>
       </c>
       <c r="M36" s="2">
-        <f>RATE(10,,K26,-'Real Returns 1792-2025'!$K36)</f>
+        <f>RATE(10,,K26,-'Real Returns 1792-2026'!$K36)</f>
         <v>0.11005860563837047</v>
       </c>
       <c r="N36" s="2">
-        <f>RATE(30,,J6,-'Real Returns 1792-2025'!$J36)</f>
+        <f>RATE(30,,J6,-'Real Returns 1792-2026'!$J36)</f>
         <v>6.50871136498513E-2</v>
       </c>
       <c r="O36" s="2">
-        <f>RATE(30,,K6,-'Real Returns 1792-2025'!$K36)</f>
+        <f>RATE(30,,K6,-'Real Returns 1792-2026'!$K36)</f>
         <v>6.9051024220016036E-2</v>
       </c>
       <c r="P36" s="2"/>
@@ -5074,19 +5074,19 @@
         <v>6.2242369051054478</v>
       </c>
       <c r="L37" s="2">
-        <f>RATE(10,,J27,-'Real Returns 1792-2025'!$J37)</f>
+        <f>RATE(10,,J27,-'Real Returns 1792-2026'!$J37)</f>
         <v>7.8241742835943928E-2</v>
       </c>
       <c r="M37" s="2">
-        <f>RATE(10,,K27,-'Real Returns 1792-2025'!$K37)</f>
+        <f>RATE(10,,K27,-'Real Returns 1792-2026'!$K37)</f>
         <v>9.7229741582290405E-2</v>
       </c>
       <c r="N37" s="2">
-        <f>RATE(30,,J7,-'Real Returns 1792-2025'!$J37)</f>
+        <f>RATE(30,,J7,-'Real Returns 1792-2026'!$J37)</f>
         <v>6.8269693332691714E-2</v>
       </c>
       <c r="O37" s="2">
-        <f>RATE(30,,K7,-'Real Returns 1792-2025'!$K37)</f>
+        <f>RATE(30,,K7,-'Real Returns 1792-2026'!$K37)</f>
         <v>7.3285086027152516E-2</v>
       </c>
       <c r="P37" s="2"/>
@@ -5127,19 +5127,19 @@
         <v>6.7457753955399449</v>
       </c>
       <c r="L38" s="2">
-        <f>RATE(10,,J28,-'Real Returns 1792-2025'!$J38)</f>
+        <f>RATE(10,,J28,-'Real Returns 1792-2026'!$J38)</f>
         <v>5.5609578566605887E-2</v>
       </c>
       <c r="M38" s="2">
-        <f>RATE(10,,K28,-'Real Returns 1792-2025'!$K38)</f>
+        <f>RATE(10,,K28,-'Real Returns 1792-2026'!$K38)</f>
         <v>8.4691364056986393E-2</v>
       </c>
       <c r="N38" s="2">
-        <f>RATE(30,,J8,-'Real Returns 1792-2025'!$J38)</f>
+        <f>RATE(30,,J8,-'Real Returns 1792-2026'!$J38)</f>
         <v>6.4658295135488292E-2</v>
       </c>
       <c r="O38" s="2">
-        <f>RATE(30,,K8,-'Real Returns 1792-2025'!$K38)</f>
+        <f>RATE(30,,K8,-'Real Returns 1792-2026'!$K38)</f>
         <v>6.9737202923114208E-2</v>
       </c>
       <c r="P38" s="2"/>
@@ -5180,19 +5180,19 @@
         <v>7.1973076066307442</v>
       </c>
       <c r="L39" s="2">
-        <f>RATE(10,,J29,-'Real Returns 1792-2025'!$J39)</f>
+        <f>RATE(10,,J29,-'Real Returns 1792-2026'!$J39)</f>
         <v>7.7003608791382044E-2</v>
       </c>
       <c r="M39" s="2">
-        <f>RATE(10,,K29,-'Real Returns 1792-2025'!$K39)</f>
+        <f>RATE(10,,K29,-'Real Returns 1792-2026'!$K39)</f>
         <v>8.9422703820970187E-2</v>
       </c>
       <c r="N39" s="2">
-        <f>RATE(30,,J9,-'Real Returns 1792-2025'!$J39)</f>
+        <f>RATE(30,,J9,-'Real Returns 1792-2026'!$J39)</f>
         <v>6.3841739865017094E-2</v>
       </c>
       <c r="O39" s="2">
-        <f>RATE(30,,K9,-'Real Returns 1792-2025'!$K39)</f>
+        <f>RATE(30,,K9,-'Real Returns 1792-2026'!$K39)</f>
         <v>7.0307182171689242E-2</v>
       </c>
       <c r="P39" s="2"/>
@@ -5233,19 +5233,19 @@
         <v>7.7896709825442194</v>
       </c>
       <c r="L40" s="2">
-        <f>RATE(10,,J30,-'Real Returns 1792-2025'!$J40)</f>
+        <f>RATE(10,,J30,-'Real Returns 1792-2026'!$J40)</f>
         <v>8.528579311091776E-2</v>
       </c>
       <c r="M40" s="2">
-        <f>RATE(10,,K30,-'Real Returns 1792-2025'!$K40)</f>
+        <f>RATE(10,,K30,-'Real Returns 1792-2026'!$K40)</f>
         <v>8.4596940600351722E-2</v>
       </c>
       <c r="N40" s="2">
-        <f>RATE(30,,J10,-'Real Returns 1792-2025'!$J40)</f>
+        <f>RATE(30,,J10,-'Real Returns 1792-2026'!$J40)</f>
         <v>6.4373490874993333E-2</v>
       </c>
       <c r="O40" s="2">
-        <f>RATE(30,,K10,-'Real Returns 1792-2025'!$K40)</f>
+        <f>RATE(30,,K10,-'Real Returns 1792-2026'!$K40)</f>
         <v>7.1552692007449167E-2</v>
       </c>
       <c r="P40" s="2"/>
@@ -5286,19 +5286,19 @@
         <v>8.5631150458631922</v>
       </c>
       <c r="L41" s="2">
-        <f>RATE(10,,J31,-'Real Returns 1792-2025'!$J41)</f>
+        <f>RATE(10,,J31,-'Real Returns 1792-2026'!$J41)</f>
         <v>8.8719326334750992E-2</v>
       </c>
       <c r="M41" s="2">
-        <f>RATE(10,,K31,-'Real Returns 1792-2025'!$K41)</f>
+        <f>RATE(10,,K31,-'Real Returns 1792-2026'!$K41)</f>
         <v>7.7689415197596076E-2</v>
       </c>
       <c r="N41" s="2">
-        <f>RATE(30,,J11,-'Real Returns 1792-2025'!$J41)</f>
+        <f>RATE(30,,J11,-'Real Returns 1792-2026'!$J41)</f>
         <v>6.5871376552986069E-2</v>
       </c>
       <c r="O41" s="2">
-        <f>RATE(30,,K11,-'Real Returns 1792-2025'!$K41)</f>
+        <f>RATE(30,,K11,-'Real Returns 1792-2026'!$K41)</f>
         <v>6.9392545628599506E-2</v>
       </c>
       <c r="P41" s="2"/>
@@ -5339,19 +5339,19 @@
         <v>9.657061714239477</v>
       </c>
       <c r="L42" s="2">
-        <f>RATE(10,,J32,-'Real Returns 1792-2025'!$J42)</f>
+        <f>RATE(10,,J32,-'Real Returns 1792-2026'!$J42)</f>
         <v>8.5820057790168061E-2</v>
       </c>
       <c r="M42" s="2">
-        <f>RATE(10,,K32,-'Real Returns 1792-2025'!$K42)</f>
+        <f>RATE(10,,K32,-'Real Returns 1792-2026'!$K42)</f>
         <v>8.399977612258426E-2</v>
       </c>
       <c r="N42" s="2">
-        <f>RATE(30,,J12,-'Real Returns 1792-2025'!$J42)</f>
+        <f>RATE(30,,J12,-'Real Returns 1792-2026'!$J42)</f>
         <v>6.1832021092014522E-2</v>
       </c>
       <c r="O42" s="2">
-        <f>RATE(30,,K12,-'Real Returns 1792-2025'!$K42)</f>
+        <f>RATE(30,,K12,-'Real Returns 1792-2026'!$K42)</f>
         <v>6.601196976060035E-2</v>
       </c>
       <c r="P42" s="2"/>
@@ -5392,19 +5392,19 @@
         <v>10.395958562994652</v>
       </c>
       <c r="L43" s="2">
-        <f>RATE(10,,J33,-'Real Returns 1792-2025'!$J43)</f>
+        <f>RATE(10,,J33,-'Real Returns 1792-2026'!$J43)</f>
         <v>8.941571292065921E-2</v>
       </c>
       <c r="M43" s="2">
-        <f>RATE(10,,K33,-'Real Returns 1792-2025'!$K43)</f>
+        <f>RATE(10,,K33,-'Real Returns 1792-2026'!$K43)</f>
         <v>8.495022896430178E-2</v>
       </c>
       <c r="N43" s="2">
-        <f>RATE(30,,J13,-'Real Returns 1792-2025'!$J43)</f>
+        <f>RATE(30,,J13,-'Real Returns 1792-2026'!$J43)</f>
         <v>5.5992208151150288E-2</v>
       </c>
       <c r="O43" s="2">
-        <f>RATE(30,,K13,-'Real Returns 1792-2025'!$K43)</f>
+        <f>RATE(30,,K13,-'Real Returns 1792-2026'!$K43)</f>
         <v>6.4518334955508919E-2</v>
       </c>
       <c r="P43" s="2"/>
@@ -5445,19 +5445,19 @@
         <v>10.310481107200793</v>
       </c>
       <c r="L44" s="2">
-        <f>RATE(10,,J34,-'Real Returns 1792-2025'!$J44)</f>
+        <f>RATE(10,,J34,-'Real Returns 1792-2026'!$J44)</f>
         <v>7.2469743621967425E-2</v>
       </c>
       <c r="M44" s="2">
-        <f>RATE(10,,K34,-'Real Returns 1792-2025'!$K44)</f>
+        <f>RATE(10,,K34,-'Real Returns 1792-2026'!$K44)</f>
         <v>6.7389753648815678E-2</v>
       </c>
       <c r="N44" s="2">
-        <f>RATE(30,,J14,-'Real Returns 1792-2025'!$J44)</f>
+        <f>RATE(30,,J14,-'Real Returns 1792-2026'!$J44)</f>
         <v>5.6592203730643512E-2</v>
       </c>
       <c r="O44" s="2">
-        <f>RATE(30,,K14,-'Real Returns 1792-2025'!$K44)</f>
+        <f>RATE(30,,K14,-'Real Returns 1792-2026'!$K44)</f>
         <v>6.5007024132419752E-2</v>
       </c>
       <c r="P44" s="2"/>
@@ -5498,19 +5498,19 @@
         <v>10.931402582827348</v>
       </c>
       <c r="L45" s="2">
-        <f>RATE(10,,J35,-'Real Returns 1792-2025'!$J45)</f>
+        <f>RATE(10,,J35,-'Real Returns 1792-2026'!$J45)</f>
         <v>6.2852924867545165E-2</v>
       </c>
       <c r="M45" s="2">
-        <f>RATE(10,,K35,-'Real Returns 1792-2025'!$K45)</f>
+        <f>RATE(10,,K35,-'Real Returns 1792-2026'!$K45)</f>
         <v>6.2463308183666882E-2</v>
       </c>
       <c r="N45" s="2">
-        <f>RATE(30,,J15,-'Real Returns 1792-2025'!$J45)</f>
+        <f>RATE(30,,J15,-'Real Returns 1792-2026'!$J45)</f>
         <v>5.9685156335856325E-2</v>
       </c>
       <c r="O45" s="2">
-        <f>RATE(30,,K15,-'Real Returns 1792-2025'!$K45)</f>
+        <f>RATE(30,,K15,-'Real Returns 1792-2026'!$K45)</f>
         <v>6.735766359995364E-2</v>
       </c>
       <c r="P45" s="2"/>
@@ -5551,19 +5551,19 @@
         <v>10.601335002677279</v>
       </c>
       <c r="L46" s="2">
-        <f>RATE(10,,J36,-'Real Returns 1792-2025'!$J46)</f>
+        <f>RATE(10,,J36,-'Real Returns 1792-2026'!$J46)</f>
         <v>6.829632383298434E-2</v>
       </c>
       <c r="M46" s="2">
-        <f>RATE(10,,K36,-'Real Returns 1792-2025'!$K46)</f>
+        <f>RATE(10,,K36,-'Real Returns 1792-2026'!$K46)</f>
         <v>5.9908724381849097E-2</v>
       </c>
       <c r="N46" s="2">
-        <f>RATE(30,,J16,-'Real Returns 1792-2025'!$J46)</f>
+        <f>RATE(30,,J16,-'Real Returns 1792-2026'!$J46)</f>
         <v>6.2360175222900695E-2</v>
       </c>
       <c r="O46" s="2">
-        <f>RATE(30,,K16,-'Real Returns 1792-2025'!$K46)</f>
+        <f>RATE(30,,K16,-'Real Returns 1792-2026'!$K46)</f>
         <v>6.4795170254283371E-2</v>
       </c>
       <c r="P46" s="2"/>
@@ -5604,19 +5604,19 @@
         <v>10.349298602403078</v>
       </c>
       <c r="L47" s="2">
-        <f>RATE(10,,J37,-'Real Returns 1792-2025'!$J47)</f>
+        <f>RATE(10,,J37,-'Real Returns 1792-2026'!$J47)</f>
         <v>6.1130850122844853E-2</v>
       </c>
       <c r="M47" s="2">
-        <f>RATE(10,,K37,-'Real Returns 1792-2025'!$K47)</f>
+        <f>RATE(10,,K37,-'Real Returns 1792-2026'!$K47)</f>
         <v>5.2161679265983196E-2</v>
       </c>
       <c r="N47" s="2">
-        <f>RATE(30,,J17,-'Real Returns 1792-2025'!$J47)</f>
+        <f>RATE(30,,J17,-'Real Returns 1792-2026'!$J47)</f>
         <v>5.7845631265866969E-2</v>
       </c>
       <c r="O47" s="2">
-        <f>RATE(30,,K17,-'Real Returns 1792-2025'!$K47)</f>
+        <f>RATE(30,,K17,-'Real Returns 1792-2026'!$K47)</f>
         <v>5.9872680406898283E-2</v>
       </c>
       <c r="P47" s="2"/>
@@ -5657,19 +5657,19 @@
         <v>11.180048011185338</v>
       </c>
       <c r="L48" s="2">
-        <f>RATE(10,,J38,-'Real Returns 1792-2025'!$J48)</f>
+        <f>RATE(10,,J38,-'Real Returns 1792-2026'!$J48)</f>
         <v>5.2164221427860695E-2</v>
       </c>
       <c r="M48" s="2">
-        <f>RATE(10,,K38,-'Real Returns 1792-2025'!$K48)</f>
+        <f>RATE(10,,K38,-'Real Returns 1792-2026'!$K48)</f>
         <v>5.1819405757317388E-2</v>
       </c>
       <c r="N48" s="2">
-        <f>RATE(30,,J18,-'Real Returns 1792-2025'!$J48)</f>
+        <f>RATE(30,,J18,-'Real Returns 1792-2026'!$J48)</f>
         <v>5.7281647193303246E-2</v>
       </c>
       <c r="O48" s="2">
-        <f>RATE(30,,K18,-'Real Returns 1792-2025'!$K48)</f>
+        <f>RATE(30,,K18,-'Real Returns 1792-2026'!$K48)</f>
         <v>6.1459201478888024E-2</v>
       </c>
       <c r="P48" s="2"/>
@@ -5710,19 +5710,19 @@
         <v>11.77092117991895</v>
       </c>
       <c r="L49" s="2">
-        <f>RATE(10,,J39,-'Real Returns 1792-2025'!$J49)</f>
+        <f>RATE(10,,J39,-'Real Returns 1792-2026'!$J49)</f>
         <v>5.4518050919077597E-2</v>
       </c>
       <c r="M49" s="2">
-        <f>RATE(10,,K39,-'Real Returns 1792-2025'!$K49)</f>
+        <f>RATE(10,,K39,-'Real Returns 1792-2026'!$K49)</f>
         <v>5.0422555550145839E-2</v>
       </c>
       <c r="N49" s="2">
-        <f>RATE(30,,J19,-'Real Returns 1792-2025'!$J49)</f>
+        <f>RATE(30,,J19,-'Real Returns 1792-2026'!$J49)</f>
         <v>5.6957340158878607E-2</v>
       </c>
       <c r="O49" s="2">
-        <f>RATE(30,,K19,-'Real Returns 1792-2025'!$K49)</f>
+        <f>RATE(30,,K19,-'Real Returns 1792-2026'!$K49)</f>
         <v>6.0962061928880228E-2</v>
       </c>
       <c r="P49" s="2"/>
@@ -5763,19 +5763,19 @@
         <v>11.4238557341916</v>
       </c>
       <c r="L50" s="2">
-        <f>RATE(10,,J40,-'Real Returns 1792-2025'!$J50)</f>
+        <f>RATE(10,,J40,-'Real Returns 1792-2026'!$J50)</f>
         <v>3.4146169008617E-2</v>
       </c>
       <c r="M50" s="2">
-        <f>RATE(10,,K40,-'Real Returns 1792-2025'!$K50)</f>
+        <f>RATE(10,,K40,-'Real Returns 1792-2026'!$K50)</f>
         <v>3.9033044145853187E-2</v>
       </c>
       <c r="N50" s="2">
-        <f>RATE(30,,J20,-'Real Returns 1792-2025'!$J50)</f>
+        <f>RATE(30,,J20,-'Real Returns 1792-2026'!$J50)</f>
         <v>4.9445768053650647E-2</v>
       </c>
       <c r="O50" s="2">
-        <f>RATE(30,,K20,-'Real Returns 1792-2025'!$K50)</f>
+        <f>RATE(30,,K20,-'Real Returns 1792-2026'!$K50)</f>
         <v>5.7745762328067218E-2</v>
       </c>
       <c r="P50" s="2"/>
@@ -5816,19 +5816,19 @@
         <v>12.331276393658575</v>
       </c>
       <c r="L51" s="2">
-        <f>RATE(10,,J41,-'Real Returns 1792-2025'!$J51)</f>
+        <f>RATE(10,,J41,-'Real Returns 1792-2026'!$J51)</f>
         <v>1.6953112637593439E-2</v>
       </c>
       <c r="M51" s="2">
-        <f>RATE(10,,K41,-'Real Returns 1792-2025'!$K51)</f>
+        <f>RATE(10,,K41,-'Real Returns 1792-2026'!$K51)</f>
         <v>3.7140575656996619E-2</v>
       </c>
       <c r="N51" s="2">
-        <f>RATE(30,,J21,-'Real Returns 1792-2025'!$J51)</f>
+        <f>RATE(30,,J21,-'Real Returns 1792-2026'!$J51)</f>
         <v>5.0854774089106901E-2</v>
       </c>
       <c r="O51" s="2">
-        <f>RATE(30,,K21,-'Real Returns 1792-2025'!$K51)</f>
+        <f>RATE(30,,K21,-'Real Returns 1792-2026'!$K51)</f>
         <v>6.0257715606298508E-2</v>
       </c>
       <c r="P51" s="2"/>
@@ -5869,19 +5869,19 @@
         <v>9.7893401550042309</v>
       </c>
       <c r="L52" s="2">
-        <f>RATE(10,,J42,-'Real Returns 1792-2025'!$J52)</f>
+        <f>RATE(10,,J42,-'Real Returns 1792-2026'!$J52)</f>
         <v>-2.4006301510994709E-2</v>
       </c>
       <c r="M52" s="2">
-        <f>RATE(10,,K42,-'Real Returns 1792-2025'!$K52)</f>
+        <f>RATE(10,,K42,-'Real Returns 1792-2026'!$K52)</f>
         <v>1.3613881273059601E-3</v>
       </c>
       <c r="N52" s="2">
-        <f>RATE(30,,J22,-'Real Returns 1792-2025'!$J52)</f>
+        <f>RATE(30,,J22,-'Real Returns 1792-2026'!$J52)</f>
         <v>3.9891996679085211E-2</v>
       </c>
       <c r="O52" s="2">
-        <f>RATE(30,,K22,-'Real Returns 1792-2025'!$K52)</f>
+        <f>RATE(30,,K22,-'Real Returns 1792-2026'!$K52)</f>
         <v>5.4011591436240486E-2</v>
       </c>
       <c r="P52" s="2"/>
@@ -5922,27 +5922,27 @@
         <v>9.8879879320724875</v>
       </c>
       <c r="L53" s="2">
-        <f>RATE(10,,J43,-'Real Returns 1792-2025'!$J53)</f>
+        <f>RATE(10,,J43,-'Real Returns 1792-2026'!$J53)</f>
         <v>-2.4366067319954287E-2</v>
       </c>
       <c r="M53" s="2">
-        <f>RATE(10,,K43,-'Real Returns 1792-2025'!$K53)</f>
+        <f>RATE(10,,K43,-'Real Returns 1792-2026'!$K53)</f>
         <v>-4.9971177218854157E-3</v>
       </c>
       <c r="N53" s="2">
-        <f>RATE(30,,J23,-'Real Returns 1792-2025'!$J53)</f>
+        <f>RATE(30,,J23,-'Real Returns 1792-2026'!$J53)</f>
         <v>4.0913872637547338E-2</v>
       </c>
       <c r="O53" s="2">
-        <f>RATE(30,,K23,-'Real Returns 1792-2025'!$K53)</f>
+        <f>RATE(30,,K23,-'Real Returns 1792-2026'!$K53)</f>
         <v>5.6811547949725844E-2</v>
       </c>
       <c r="P53" s="2">
-        <f>RATE(50,,J3,-'Real Returns 1792-2025'!$J53)</f>
+        <f>RATE(50,,J3,-'Real Returns 1792-2026'!$J53)</f>
         <v>4.2364943111917346E-2</v>
       </c>
       <c r="Q53" s="2">
-        <f>RATE(50,,K3,-'Real Returns 1792-2025'!$K53)</f>
+        <f>RATE(50,,K3,-'Real Returns 1792-2026'!$K53)</f>
         <v>4.6892668859485211E-2</v>
       </c>
       <c r="R53" s="2"/>
@@ -5981,27 +5981,27 @@
         <v>15.491848692643842</v>
       </c>
       <c r="L54" s="2">
-        <f>RATE(10,,J44,-'Real Returns 1792-2025'!$J54)</f>
+        <f>RATE(10,,J44,-'Real Returns 1792-2026'!$J54)</f>
         <v>1.1060039907549363E-2</v>
       </c>
       <c r="M54" s="2">
-        <f>RATE(10,,K44,-'Real Returns 1792-2025'!$K54)</f>
+        <f>RATE(10,,K44,-'Real Returns 1792-2026'!$K54)</f>
         <v>4.1555535983054954E-2</v>
       </c>
       <c r="N54" s="2">
-        <f>RATE(30,,J24,-'Real Returns 1792-2025'!$J54)</f>
+        <f>RATE(30,,J24,-'Real Returns 1792-2026'!$J54)</f>
         <v>5.601604228135771E-2</v>
       </c>
       <c r="O54" s="2">
-        <f>RATE(30,,K24,-'Real Returns 1792-2025'!$K54)</f>
+        <f>RATE(30,,K24,-'Real Returns 1792-2026'!$K54)</f>
         <v>7.8602712928913951E-2</v>
       </c>
       <c r="P54" s="2">
-        <f>RATE(50,,J4,-'Real Returns 1792-2025'!$J54)</f>
+        <f>RATE(50,,J4,-'Real Returns 1792-2026'!$J54)</f>
         <v>5.3211834866205662E-2</v>
       </c>
       <c r="Q54" s="2">
-        <f>RATE(50,,K4,-'Real Returns 1792-2025'!$K54)</f>
+        <f>RATE(50,,K4,-'Real Returns 1792-2026'!$K54)</f>
         <v>5.9409559118073996E-2</v>
       </c>
       <c r="R54" s="2"/>
@@ -6040,27 +6040,27 @@
         <v>16.312667524736156</v>
       </c>
       <c r="L55" s="2">
-        <f>RATE(10,,J45,-'Real Returns 1792-2025'!$J55)</f>
+        <f>RATE(10,,J45,-'Real Returns 1792-2026'!$J55)</f>
         <v>1.2059123005262193E-2</v>
       </c>
       <c r="M55" s="2">
-        <f>RATE(10,,K45,-'Real Returns 1792-2025'!$K55)</f>
+        <f>RATE(10,,K45,-'Real Returns 1792-2026'!$K55)</f>
         <v>4.08422421926029E-2</v>
       </c>
       <c r="N55" s="2">
-        <f>RATE(30,,J25,-'Real Returns 1792-2025'!$J55)</f>
+        <f>RATE(30,,J25,-'Real Returns 1792-2026'!$J55)</f>
         <v>6.1059483439882691E-2</v>
       </c>
       <c r="O55" s="2">
-        <f>RATE(30,,K25,-'Real Returns 1792-2025'!$K55)</f>
+        <f>RATE(30,,K25,-'Real Returns 1792-2026'!$K55)</f>
         <v>7.9894078715066499E-2</v>
       </c>
       <c r="P55" s="2">
-        <f>RATE(50,,J5,-'Real Returns 1792-2025'!$J55)</f>
+        <f>RATE(50,,J5,-'Real Returns 1792-2026'!$J55)</f>
         <v>5.3681655501765367E-2</v>
       </c>
       <c r="Q55" s="2">
-        <f>RATE(50,,K5,-'Real Returns 1792-2025'!$K55)</f>
+        <f>RATE(50,,K5,-'Real Returns 1792-2026'!$K55)</f>
         <v>6.0026646489569908E-2</v>
       </c>
       <c r="R55" s="2"/>
@@ -6099,27 +6099,27 @@
         <v>16.442627354311334</v>
       </c>
       <c r="L56" s="2">
-        <f>RATE(10,,J46,-'Real Returns 1792-2025'!$J56)</f>
+        <f>RATE(10,,J46,-'Real Returns 1792-2026'!$J56)</f>
         <v>1.0890180209418183E-2</v>
       </c>
       <c r="M56" s="2">
-        <f>RATE(10,,K46,-'Real Returns 1792-2025'!$K56)</f>
+        <f>RATE(10,,K46,-'Real Returns 1792-2026'!$K56)</f>
         <v>4.4867126310340427E-2</v>
       </c>
       <c r="N56" s="2">
-        <f>RATE(30,,J26,-'Real Returns 1792-2025'!$J56)</f>
+        <f>RATE(30,,J26,-'Real Returns 1792-2026'!$J56)</f>
         <v>5.4587182206380674E-2</v>
       </c>
       <c r="O56" s="2">
-        <f>RATE(30,,K26,-'Real Returns 1792-2025'!$K56)</f>
+        <f>RATE(30,,K26,-'Real Returns 1792-2026'!$K56)</f>
         <v>7.1252413828409411E-2</v>
       </c>
       <c r="P56" s="2">
-        <f>RATE(50,,J6,-'Real Returns 1792-2025'!$J56)</f>
+        <f>RATE(50,,J6,-'Real Returns 1792-2026'!$J56)</f>
         <v>5.4654525387076103E-2</v>
       </c>
       <c r="Q56" s="2">
-        <f>RATE(50,,K6,-'Real Returns 1792-2025'!$K56)</f>
+        <f>RATE(50,,K6,-'Real Returns 1792-2026'!$K56)</f>
         <v>6.2343504589465686E-2</v>
       </c>
       <c r="R56" s="2"/>
@@ -6158,27 +6158,27 @@
         <v>17.052111742019452</v>
       </c>
       <c r="L57" s="2">
-        <f>RATE(10,,J47,-'Real Returns 1792-2025'!$J57)</f>
+        <f>RATE(10,,J47,-'Real Returns 1792-2026'!$J57)</f>
         <v>1.3039252318561775E-2</v>
       </c>
       <c r="M57" s="2">
-        <f>RATE(10,,K47,-'Real Returns 1792-2025'!$K57)</f>
+        <f>RATE(10,,K47,-'Real Returns 1792-2026'!$K57)</f>
         <v>5.120332336181576E-2</v>
       </c>
       <c r="N57" s="2">
-        <f>RATE(30,,J27,-'Real Returns 1792-2025'!$J57)</f>
+        <f>RATE(30,,J27,-'Real Returns 1792-2026'!$J57)</f>
         <v>5.0438066798592265E-2</v>
       </c>
       <c r="O57" s="2">
-        <f>RATE(30,,K27,-'Real Returns 1792-2025'!$K57)</f>
+        <f>RATE(30,,K27,-'Real Returns 1792-2026'!$K57)</f>
         <v>6.6650788868749519E-2</v>
       </c>
       <c r="P57" s="2">
-        <f>RATE(50,,J7,-'Real Returns 1792-2025'!$J57)</f>
+        <f>RATE(50,,J7,-'Real Returns 1792-2026'!$J57)</f>
         <v>5.5571333604583543E-2</v>
       </c>
       <c r="Q57" s="2">
-        <f>RATE(50,,K7,-'Real Returns 1792-2025'!$K57)</f>
+        <f>RATE(50,,K7,-'Real Returns 1792-2026'!$K57)</f>
         <v>6.4591263584752756E-2</v>
       </c>
       <c r="R57" s="2"/>
@@ -6217,27 +6217,27 @@
         <v>17.343670618965721</v>
       </c>
       <c r="L58" s="2">
-        <f>RATE(10,,J48,-'Real Returns 1792-2025'!$J58)</f>
+        <f>RATE(10,,J48,-'Real Returns 1792-2026'!$J58)</f>
         <v>1.9286732072950934E-2</v>
       </c>
       <c r="M58" s="2">
-        <f>RATE(10,,K48,-'Real Returns 1792-2025'!$K58)</f>
+        <f>RATE(10,,K48,-'Real Returns 1792-2026'!$K58)</f>
         <v>4.4887983858400614E-2</v>
       </c>
       <c r="N58" s="2">
-        <f>RATE(30,,J28,-'Real Returns 1792-2025'!$J58)</f>
+        <f>RATE(30,,J28,-'Real Returns 1792-2026'!$J58)</f>
         <v>4.2224011080374241E-2</v>
       </c>
       <c r="O58" s="2">
-        <f>RATE(30,,K28,-'Real Returns 1792-2025'!$K58)</f>
+        <f>RATE(30,,K28,-'Real Returns 1792-2026'!$K58)</f>
         <v>6.0325075623457333E-2</v>
       </c>
       <c r="P58" s="2">
-        <f>RATE(50,,J8,-'Real Returns 1792-2025'!$J58)</f>
+        <f>RATE(50,,J8,-'Real Returns 1792-2026'!$J58)</f>
         <v>5.2936365955353858E-2</v>
       </c>
       <c r="Q58" s="2">
-        <f>RATE(50,,K8,-'Real Returns 1792-2025'!$K58)</f>
+        <f>RATE(50,,K8,-'Real Returns 1792-2026'!$K58)</f>
         <v>6.112963277816344E-2</v>
       </c>
       <c r="R58" s="2"/>
@@ -6276,27 +6276,27 @@
         <v>21.827109512495706</v>
       </c>
       <c r="L59" s="2">
-        <f>RATE(10,,J49,-'Real Returns 1792-2025'!$J59)</f>
+        <f>RATE(10,,J49,-'Real Returns 1792-2026'!$J59)</f>
         <v>1.2687063501590564E-2</v>
       </c>
       <c r="M59" s="2">
-        <f>RATE(10,,K49,-'Real Returns 1792-2025'!$K59)</f>
+        <f>RATE(10,,K49,-'Real Returns 1792-2026'!$K59)</f>
         <v>6.3698575368571334E-2</v>
       </c>
       <c r="N59" s="2">
-        <f>RATE(30,,J29,-'Real Returns 1792-2025'!$J59)</f>
+        <f>RATE(30,,J29,-'Real Returns 1792-2026'!$J59)</f>
         <v>4.7728633546016648E-2</v>
       </c>
       <c r="O59" s="2">
-        <f>RATE(30,,K29,-'Real Returns 1792-2025'!$K59)</f>
+        <f>RATE(30,,K29,-'Real Returns 1792-2026'!$K59)</f>
         <v>6.7725658504295752E-2</v>
       </c>
       <c r="P59" s="2">
-        <f>RATE(50,,J9,-'Real Returns 1792-2025'!$J59)</f>
+        <f>RATE(50,,J9,-'Real Returns 1792-2026'!$J59)</f>
         <v>5.1555190975646828E-2</v>
       </c>
       <c r="Q59" s="2">
-        <f>RATE(50,,K9,-'Real Returns 1792-2025'!$K59)</f>
+        <f>RATE(50,,K9,-'Real Returns 1792-2026'!$K59)</f>
         <v>6.4980331428517307E-2</v>
       </c>
       <c r="R59" s="2"/>
@@ -6335,27 +6335,27 @@
         <v>25.085333236559766</v>
       </c>
       <c r="L60" s="2">
-        <f>RATE(10,,J50,-'Real Returns 1792-2025'!$J60)</f>
+        <f>RATE(10,,J50,-'Real Returns 1792-2026'!$J60)</f>
         <v>2.9646177484129534E-2</v>
       </c>
       <c r="M60" s="2">
-        <f>RATE(10,,K50,-'Real Returns 1792-2025'!$K60)</f>
+        <f>RATE(10,,K50,-'Real Returns 1792-2026'!$K60)</f>
         <v>8.1834224407694195E-2</v>
       </c>
       <c r="N60" s="2">
-        <f>RATE(30,,J30,-'Real Returns 1792-2025'!$J60)</f>
+        <f>RATE(30,,J30,-'Real Returns 1792-2026'!$J60)</f>
         <v>4.9392652246316088E-2</v>
       </c>
       <c r="O60" s="2">
-        <f>RATE(30,,K30,-'Real Returns 1792-2025'!$K60)</f>
+        <f>RATE(30,,K30,-'Real Returns 1792-2026'!$K60)</f>
         <v>6.828258922041143E-2</v>
       </c>
       <c r="P60" s="2">
-        <f>RATE(50,,J10,-'Real Returns 1792-2025'!$J60)</f>
+        <f>RATE(50,,J10,-'Real Returns 1792-2026'!$J60)</f>
         <v>5.1260671759025205E-2</v>
       </c>
       <c r="Q60" s="2">
-        <f>RATE(50,,K10,-'Real Returns 1792-2025'!$K60)</f>
+        <f>RATE(50,,K10,-'Real Returns 1792-2026'!$K60)</f>
         <v>6.7004213003444987E-2</v>
       </c>
       <c r="R60" s="2"/>
@@ -6394,27 +6394,27 @@
         <v>27.843381029740087</v>
       </c>
       <c r="L61" s="2">
-        <f>RATE(10,,J51,-'Real Returns 1792-2025'!$J61)</f>
+        <f>RATE(10,,J51,-'Real Returns 1792-2026'!$J61)</f>
         <v>5.1837991152362713E-2</v>
       </c>
       <c r="M61" s="2">
-        <f>RATE(10,,K51,-'Real Returns 1792-2025'!$K61)</f>
+        <f>RATE(10,,K51,-'Real Returns 1792-2026'!$K61)</f>
         <v>8.4854247855576853E-2</v>
       </c>
       <c r="N61" s="2">
-        <f>RATE(30,,J31,-'Real Returns 1792-2025'!$J61)</f>
+        <f>RATE(30,,J31,-'Real Returns 1792-2026'!$J61)</f>
         <v>5.2095682564079544E-2</v>
       </c>
       <c r="O61" s="2">
-        <f>RATE(30,,K31,-'Real Returns 1792-2025'!$K61)</f>
+        <f>RATE(30,,K31,-'Real Returns 1792-2026'!$K61)</f>
         <v>6.6352714547707123E-2</v>
       </c>
       <c r="P61" s="2">
-        <f>RATE(50,,J11,-'Real Returns 1792-2025'!$J61)</f>
+        <f>RATE(50,,J11,-'Real Returns 1792-2026'!$J61)</f>
         <v>5.3107816713145677E-2</v>
       </c>
       <c r="Q61" s="2">
-        <f>RATE(50,,K11,-'Real Returns 1792-2025'!$K61)</f>
+        <f>RATE(50,,K11,-'Real Returns 1792-2026'!$K61)</f>
         <v>6.5918734268187451E-2</v>
       </c>
       <c r="R61" s="2"/>
@@ -6453,27 +6453,27 @@
         <v>29.094390808028507</v>
       </c>
       <c r="L62" s="2">
-        <f>RATE(10,,J52,-'Real Returns 1792-2025'!$J62)</f>
+        <f>RATE(10,,J52,-'Real Returns 1792-2026'!$J62)</f>
         <v>8.3311832892681625E-2</v>
       </c>
       <c r="M62" s="2">
-        <f>RATE(10,,K52,-'Real Returns 1792-2025'!$K62)</f>
+        <f>RATE(10,,K52,-'Real Returns 1792-2026'!$K62)</f>
         <v>0.1150788663338114</v>
       </c>
       <c r="N62" s="2">
-        <f>RATE(30,,J32,-'Real Returns 1792-2025'!$J62)</f>
+        <f>RATE(30,,J32,-'Real Returns 1792-2026'!$J62)</f>
         <v>4.7095082853147778E-2</v>
       </c>
       <c r="O62" s="2">
-        <f>RATE(30,,K32,-'Real Returns 1792-2025'!$K62)</f>
+        <f>RATE(30,,K32,-'Real Returns 1792-2026'!$K62)</f>
         <v>6.5716949234131961E-2</v>
       </c>
       <c r="P62" s="2">
-        <f>RATE(50,,J12,-'Real Returns 1792-2025'!$J62)</f>
+        <f>RATE(50,,J12,-'Real Returns 1792-2026'!$J62)</f>
         <v>4.8271047133044795E-2</v>
       </c>
       <c r="Q62" s="2">
-        <f>RATE(50,,K12,-'Real Returns 1792-2025'!$K62)</f>
+        <f>RATE(50,,K12,-'Real Returns 1792-2026'!$K62)</f>
         <v>6.2273956091974933E-2</v>
       </c>
       <c r="R62" s="2"/>
@@ -6512,27 +6512,27 @@
         <v>32.238911455742219</v>
       </c>
       <c r="L63" s="2">
-        <f>RATE(10,,J53,-'Real Returns 1792-2025'!$J63)</f>
+        <f>RATE(10,,J53,-'Real Returns 1792-2026'!$J63)</f>
         <v>9.9488881290510228E-2</v>
       </c>
       <c r="M63" s="2">
-        <f>RATE(10,,K53,-'Real Returns 1792-2025'!$K63)</f>
+        <f>RATE(10,,K53,-'Real Returns 1792-2026'!$K63)</f>
         <v>0.12545269165854303</v>
       </c>
       <c r="N63" s="2">
-        <f>RATE(30,,J33,-'Real Returns 1792-2025'!$J63)</f>
+        <f>RATE(30,,J33,-'Real Returns 1792-2026'!$J63)</f>
         <v>5.3312224424320799E-2</v>
       </c>
       <c r="O63" s="2">
-        <f>RATE(30,,K33,-'Real Returns 1792-2025'!$K63)</f>
+        <f>RATE(30,,K33,-'Real Returns 1792-2026'!$K63)</f>
         <v>6.7055805309223837E-2</v>
       </c>
       <c r="P63" s="2">
-        <f>RATE(50,,J13,-'Real Returns 1792-2025'!$J63)</f>
+        <f>RATE(50,,J13,-'Real Returns 1792-2026'!$J63)</f>
         <v>4.7832768659814118E-2</v>
       </c>
       <c r="Q63" s="2">
-        <f>RATE(50,,K13,-'Real Returns 1792-2025'!$K63)</f>
+        <f>RATE(50,,K13,-'Real Returns 1792-2026'!$K63)</f>
         <v>6.1994345028569771E-2</v>
       </c>
       <c r="R63" s="2"/>
@@ -6571,27 +6571,27 @@
         <v>32.133615055603258</v>
       </c>
       <c r="L64" s="2">
-        <f>RATE(10,,J54,-'Real Returns 1792-2025'!$J64)</f>
+        <f>RATE(10,,J54,-'Real Returns 1792-2026'!$J64)</f>
         <v>4.4738544450495035E-2</v>
       </c>
       <c r="M64" s="2">
-        <f>RATE(10,,K54,-'Real Returns 1792-2025'!$K64)</f>
+        <f>RATE(10,,K54,-'Real Returns 1792-2026'!$K64)</f>
         <v>7.5686291457279189E-2</v>
       </c>
       <c r="N64" s="2">
-        <f>RATE(30,,J34,-'Real Returns 1792-2025'!$J64)</f>
+        <f>RATE(30,,J34,-'Real Returns 1792-2026'!$J64)</f>
         <v>4.2453129773464694E-2</v>
       </c>
       <c r="O64" s="2">
-        <f>RATE(30,,K34,-'Real Returns 1792-2025'!$K64)</f>
+        <f>RATE(30,,K34,-'Real Returns 1792-2026'!$K64)</f>
         <v>6.1443866160595877E-2</v>
       </c>
       <c r="P64" s="2">
-        <f>RATE(50,,J14,-'Real Returns 1792-2025'!$J64)</f>
+        <f>RATE(50,,J14,-'Real Returns 1792-2026'!$J64)</f>
         <v>4.4964060249608896E-2</v>
       </c>
       <c r="Q64" s="2">
-        <f>RATE(50,,K14,-'Real Returns 1792-2025'!$K64)</f>
+        <f>RATE(50,,K14,-'Real Returns 1792-2026'!$K64)</f>
         <v>6.2392745303214321E-2</v>
       </c>
       <c r="R64" s="2"/>
@@ -6630,27 +6630,27 @@
         <v>29.924526284095133</v>
       </c>
       <c r="L65" s="2">
-        <f>RATE(10,,J55,-'Real Returns 1792-2025'!$J65)</f>
+        <f>RATE(10,,J55,-'Real Returns 1792-2026'!$J65)</f>
         <v>1.8134819981104437E-2</v>
       </c>
       <c r="M65" s="2">
-        <f>RATE(10,,K55,-'Real Returns 1792-2025'!$K65)</f>
+        <f>RATE(10,,K55,-'Real Returns 1792-2026'!$K65)</f>
         <v>6.2552090162323104E-2</v>
       </c>
       <c r="N65" s="2">
-        <f>RATE(30,,J35,-'Real Returns 1792-2025'!$J65)</f>
+        <f>RATE(30,,J35,-'Real Returns 1792-2026'!$J65)</f>
         <v>3.0769237419721426E-2</v>
       </c>
       <c r="O65" s="2">
-        <f>RATE(30,,K35,-'Real Returns 1792-2025'!$K65)</f>
+        <f>RATE(30,,K35,-'Real Returns 1792-2026'!$K65)</f>
         <v>5.5236229434678631E-2</v>
       </c>
       <c r="P65" s="2">
-        <f>RATE(50,,J15,-'Real Returns 1792-2025'!$J65)</f>
+        <f>RATE(50,,J15,-'Real Returns 1792-2026'!$J65)</f>
         <v>4.1617686389348311E-2</v>
       </c>
       <c r="Q65" s="2">
-        <f>RATE(50,,K15,-'Real Returns 1792-2025'!$K65)</f>
+        <f>RATE(50,,K15,-'Real Returns 1792-2026'!$K65)</f>
         <v>6.1043065851199896E-2</v>
       </c>
       <c r="R65" s="2"/>
@@ -6689,27 +6689,27 @@
         <v>32.491721127247295</v>
       </c>
       <c r="L66" s="2">
-        <f>RATE(10,,J56,-'Real Returns 1792-2025'!$J66)</f>
+        <f>RATE(10,,J56,-'Real Returns 1792-2026'!$J66)</f>
         <v>1.082891494055848E-2</v>
       </c>
       <c r="M66" s="2">
-        <f>RATE(10,,K56,-'Real Returns 1792-2025'!$K66)</f>
+        <f>RATE(10,,K56,-'Real Returns 1792-2026'!$K66)</f>
         <v>7.0483925521203944E-2</v>
       </c>
       <c r="N66" s="2">
-        <f>RATE(30,,J36,-'Real Returns 1792-2025'!$J66)</f>
+        <f>RATE(30,,J36,-'Real Returns 1792-2026'!$J66)</f>
         <v>2.9653553734711083E-2</v>
       </c>
       <c r="O66" s="2">
-        <f>RATE(30,,K36,-'Real Returns 1792-2025'!$K66)</f>
+        <f>RATE(30,,K36,-'Real Returns 1792-2026'!$K66)</f>
         <v>5.8367660175425266E-2</v>
       </c>
       <c r="P66" s="2">
-        <f>RATE(50,,J16,-'Real Returns 1792-2025'!$J66)</f>
+        <f>RATE(50,,J16,-'Real Returns 1792-2026'!$J66)</f>
         <v>4.1452330173054809E-2</v>
       </c>
       <c r="Q66" s="2">
-        <f>RATE(50,,K16,-'Real Returns 1792-2025'!$K66)</f>
+        <f>RATE(50,,K16,-'Real Returns 1792-2026'!$K66)</f>
         <v>6.1910430713691851E-2</v>
       </c>
       <c r="R66" s="2"/>
@@ -6748,27 +6748,27 @@
         <v>34.917816446030379</v>
       </c>
       <c r="L67" s="2">
-        <f>RATE(10,,J57,-'Real Returns 1792-2025'!$J67)</f>
+        <f>RATE(10,,J57,-'Real Returns 1792-2026'!$J67)</f>
         <v>2.3391100788585868E-2</v>
       </c>
       <c r="M67" s="2">
-        <f>RATE(10,,K57,-'Real Returns 1792-2025'!$K67)</f>
+        <f>RATE(10,,K57,-'Real Returns 1792-2026'!$K67)</f>
         <v>7.4303252988934754E-2</v>
       </c>
       <c r="N67" s="2">
-        <f>RATE(30,,J37,-'Real Returns 1792-2025'!$J67)</f>
+        <f>RATE(30,,J37,-'Real Returns 1792-2026'!$J67)</f>
         <v>3.2315108319371802E-2</v>
       </c>
       <c r="O67" s="2">
-        <f>RATE(30,,K37,-'Real Returns 1792-2025'!$K67)</f>
+        <f>RATE(30,,K37,-'Real Returns 1792-2026'!$K67)</f>
         <v>5.9169254112446626E-2</v>
       </c>
       <c r="P67" s="2">
-        <f>RATE(50,,J17,-'Real Returns 1792-2025'!$J67)</f>
+        <f>RATE(50,,J17,-'Real Returns 1792-2026'!$J67)</f>
         <v>4.180625353221866E-2</v>
       </c>
       <c r="Q67" s="2">
-        <f>RATE(50,,K17,-'Real Returns 1792-2025'!$K67)</f>
+        <f>RATE(50,,K17,-'Real Returns 1792-2026'!$K67)</f>
         <v>6.0998920121230718E-2</v>
       </c>
       <c r="R67" s="2"/>
@@ -6807,27 +6807,27 @@
         <v>36.857579340170517</v>
       </c>
       <c r="L68" s="2">
-        <f>RATE(10,,J58,-'Real Returns 1792-2025'!$J68)</f>
+        <f>RATE(10,,J58,-'Real Returns 1792-2026'!$J68)</f>
         <v>6.1374146567356978E-3</v>
       </c>
       <c r="M68" s="2">
-        <f>RATE(10,,K58,-'Real Returns 1792-2025'!$K68)</f>
+        <f>RATE(10,,K58,-'Real Returns 1792-2026'!$K68)</f>
         <v>7.8297452550351268E-2</v>
       </c>
       <c r="N68" s="2">
-        <f>RATE(30,,J38,-'Real Returns 1792-2025'!$J68)</f>
+        <f>RATE(30,,J38,-'Real Returns 1792-2026'!$J68)</f>
         <v>2.5681211055220247E-2</v>
       </c>
       <c r="O68" s="2">
-        <f>RATE(30,,K38,-'Real Returns 1792-2025'!$K68)</f>
+        <f>RATE(30,,K38,-'Real Returns 1792-2026'!$K68)</f>
         <v>5.8237541796125891E-2</v>
       </c>
       <c r="P68" s="2">
-        <f>RATE(50,,J18,-'Real Returns 1792-2025'!$J68)</f>
+        <f>RATE(50,,J18,-'Real Returns 1792-2026'!$J68)</f>
         <v>3.9214386209065651E-2</v>
       </c>
       <c r="Q68" s="2">
-        <f>RATE(50,,K18,-'Real Returns 1792-2025'!$K68)</f>
+        <f>RATE(50,,K18,-'Real Returns 1792-2026'!$K68)</f>
         <v>6.1460033312014745E-2</v>
       </c>
       <c r="R68" s="2"/>
@@ -6866,27 +6866,27 @@
         <v>41.867199516249961</v>
       </c>
       <c r="L69" s="2">
-        <f>RATE(10,,J59,-'Real Returns 1792-2025'!$J69)</f>
+        <f>RATE(10,,J59,-'Real Returns 1792-2026'!$J69)</f>
         <v>1.5719044994778362E-2</v>
       </c>
       <c r="M69" s="2">
-        <f>RATE(10,,K59,-'Real Returns 1792-2025'!$K69)</f>
+        <f>RATE(10,,K59,-'Real Returns 1792-2026'!$K69)</f>
         <v>6.7303094146919734E-2</v>
       </c>
       <c r="N69" s="2">
-        <f>RATE(30,,J39,-'Real Returns 1792-2025'!$J69)</f>
+        <f>RATE(30,,J39,-'Real Returns 1792-2026'!$J69)</f>
         <v>2.7466392399464391E-2</v>
       </c>
       <c r="O69" s="2">
-        <f>RATE(30,,K39,-'Real Returns 1792-2025'!$K69)</f>
+        <f>RATE(30,,K39,-'Real Returns 1792-2026'!$K69)</f>
         <v>6.044983350385124E-2</v>
       </c>
       <c r="P69" s="2">
-        <f>RATE(50,,J19,-'Real Returns 1792-2025'!$J69)</f>
+        <f>RATE(50,,J19,-'Real Returns 1792-2026'!$J69)</f>
         <v>3.9643031727021098E-2</v>
       </c>
       <c r="Q69" s="2">
-        <f>RATE(50,,K19,-'Real Returns 1792-2025'!$K69)</f>
+        <f>RATE(50,,K19,-'Real Returns 1792-2026'!$K69)</f>
         <v>6.2774638215117029E-2</v>
       </c>
       <c r="R69" s="2"/>
@@ -6925,27 +6925,27 @@
         <v>43.621353455159394</v>
       </c>
       <c r="L70" s="2">
-        <f>RATE(10,,J60,-'Real Returns 1792-2025'!$J70)</f>
+        <f>RATE(10,,J60,-'Real Returns 1792-2026'!$J70)</f>
         <v>1.2562064887904902E-2</v>
       </c>
       <c r="M70" s="2">
-        <f>RATE(10,,K60,-'Real Returns 1792-2025'!$K70)</f>
+        <f>RATE(10,,K60,-'Real Returns 1792-2026'!$K70)</f>
         <v>5.6885467316218248E-2</v>
       </c>
       <c r="N70" s="2">
-        <f>RATE(30,,J40,-'Real Returns 1792-2025'!$J70)</f>
+        <f>RATE(30,,J40,-'Real Returns 1792-2026'!$J70)</f>
         <v>2.5409170762426835E-2</v>
       </c>
       <c r="O70" s="2">
-        <f>RATE(30,,K40,-'Real Returns 1792-2025'!$K70)</f>
+        <f>RATE(30,,K40,-'Real Returns 1792-2026'!$K70)</f>
         <v>5.9105769973770442E-2</v>
       </c>
       <c r="P70" s="2">
-        <f>RATE(50,,J20,-'Real Returns 1792-2025'!$J70)</f>
+        <f>RATE(50,,J20,-'Real Returns 1792-2026'!$J70)</f>
         <v>3.8001385483236776E-2</v>
       </c>
       <c r="Q70" s="2">
-        <f>RATE(50,,K20,-'Real Returns 1792-2025'!$K70)</f>
+        <f>RATE(50,,K20,-'Real Returns 1792-2026'!$K70)</f>
         <v>6.2347267033633094E-2</v>
       </c>
       <c r="R70" s="2"/>
@@ -6984,27 +6984,27 @@
         <v>43.305154889334304</v>
       </c>
       <c r="L71" s="2">
-        <f>RATE(10,,J61,-'Real Returns 1792-2025'!$J71)</f>
+        <f>RATE(10,,J61,-'Real Returns 1792-2026'!$J71)</f>
         <v>6.2034786580012794E-3</v>
       </c>
       <c r="M71" s="2">
-        <f>RATE(10,,K61,-'Real Returns 1792-2025'!$K71)</f>
+        <f>RATE(10,,K61,-'Real Returns 1792-2026'!$K71)</f>
         <v>4.5157550974929239E-2</v>
       </c>
       <c r="N71" s="2">
-        <f>RATE(30,,J41,-'Real Returns 1792-2025'!$J71)</f>
+        <f>RATE(30,,J41,-'Real Returns 1792-2026'!$J71)</f>
         <v>2.4814352608542367E-2</v>
       </c>
       <c r="O71" s="2">
-        <f>RATE(30,,K41,-'Real Returns 1792-2025'!$K71)</f>
+        <f>RATE(30,,K41,-'Real Returns 1792-2026'!$K71)</f>
         <v>5.551301784803276E-2</v>
       </c>
       <c r="P71" s="2">
-        <f>RATE(50,,J21,-'Real Returns 1792-2025'!$J71)</f>
+        <f>RATE(50,,J21,-'Real Returns 1792-2026'!$J71)</f>
         <v>4.1963616498650186E-2</v>
       </c>
       <c r="Q71" s="2">
-        <f>RATE(50,,K21,-'Real Returns 1792-2025'!$K71)</f>
+        <f>RATE(50,,K21,-'Real Returns 1792-2026'!$K71)</f>
         <v>6.2080649248611681E-2</v>
       </c>
       <c r="R71" s="2"/>
@@ -7043,27 +7043,27 @@
         <v>41.579640611764745</v>
       </c>
       <c r="L72" s="2">
-        <f>RATE(10,,J62,-'Real Returns 1792-2025'!$J72)</f>
+        <f>RATE(10,,J62,-'Real Returns 1792-2026'!$J72)</f>
         <v>3.736619104531188E-3</v>
       </c>
       <c r="M72" s="2">
-        <f>RATE(10,,K62,-'Real Returns 1792-2025'!$K72)</f>
+        <f>RATE(10,,K62,-'Real Returns 1792-2026'!$K72)</f>
         <v>3.6351657438939707E-2</v>
       </c>
       <c r="N72" s="2">
-        <f>RATE(30,,J42,-'Real Returns 1792-2025'!$J72)</f>
+        <f>RATE(30,,J42,-'Real Returns 1792-2026'!$J72)</f>
         <v>2.0015465104470501E-2</v>
       </c>
       <c r="O72" s="2">
-        <f>RATE(30,,K42,-'Real Returns 1792-2025'!$K72)</f>
+        <f>RATE(30,,K42,-'Real Returns 1792-2026'!$K72)</f>
         <v>4.9867578253206729E-2</v>
       </c>
       <c r="P72" s="2">
-        <f>RATE(50,,J22,-'Real Returns 1792-2025'!$J72)</f>
+        <f>RATE(50,,J22,-'Real Returns 1792-2026'!$J72)</f>
         <v>4.1040421415175894E-2</v>
       </c>
       <c r="Q72" s="2">
-        <f>RATE(50,,K22,-'Real Returns 1792-2025'!$K72)</f>
+        <f>RATE(50,,K22,-'Real Returns 1792-2026'!$K72)</f>
         <v>6.2355274463724082E-2</v>
       </c>
       <c r="R72" s="2"/>
@@ -7102,27 +7102,27 @@
         <v>41.629453453180233</v>
       </c>
       <c r="L73" s="2">
-        <f>RATE(10,,J63,-'Real Returns 1792-2025'!$J73)</f>
+        <f>RATE(10,,J63,-'Real Returns 1792-2026'!$J73)</f>
         <v>2.1924613348390781E-2</v>
       </c>
       <c r="M73" s="2">
-        <f>RATE(10,,K63,-'Real Returns 1792-2025'!$K73)</f>
+        <f>RATE(10,,K63,-'Real Returns 1792-2026'!$K73)</f>
         <v>2.5892923165708886E-2</v>
       </c>
       <c r="N73" s="2">
-        <f>RATE(30,,J43,-'Real Returns 1792-2025'!$J73)</f>
+        <f>RATE(30,,J43,-'Real Returns 1792-2026'!$J73)</f>
         <v>3.1095439504923567E-2</v>
       </c>
       <c r="O73" s="2">
-        <f>RATE(30,,K43,-'Real Returns 1792-2025'!$K73)</f>
+        <f>RATE(30,,K43,-'Real Returns 1792-2026'!$K73)</f>
         <v>4.7332400040121576E-2</v>
       </c>
       <c r="P73" s="2">
-        <f>RATE(50,,J23,-'Real Returns 1792-2025'!$J73)</f>
+        <f>RATE(50,,J23,-'Real Returns 1792-2026'!$J73)</f>
         <v>4.8505754149275243E-2</v>
       </c>
       <c r="Q73" s="2">
-        <f>RATE(50,,K23,-'Real Returns 1792-2025'!$K73)</f>
+        <f>RATE(50,,K23,-'Real Returns 1792-2026'!$K73)</f>
         <v>6.3859768713372705E-2</v>
       </c>
       <c r="R73" s="2"/>
@@ -7161,27 +7161,27 @@
         <v>35.956898384916066</v>
       </c>
       <c r="L74" s="2">
-        <f>RATE(10,,J64,-'Real Returns 1792-2025'!$J74)</f>
+        <f>RATE(10,,J64,-'Real Returns 1792-2026'!$J74)</f>
         <v>3.8188932955027982E-2</v>
       </c>
       <c r="M74" s="2">
-        <f>RATE(10,,K64,-'Real Returns 1792-2025'!$K74)</f>
+        <f>RATE(10,,K64,-'Real Returns 1792-2026'!$K74)</f>
         <v>1.1305254183684809E-2</v>
       </c>
       <c r="N74" s="2">
-        <f>RATE(30,,J44,-'Real Returns 1792-2025'!$J74)</f>
+        <f>RATE(30,,J44,-'Real Returns 1792-2026'!$J74)</f>
         <v>3.122552215204388E-2</v>
       </c>
       <c r="O74" s="2">
-        <f>RATE(30,,K44,-'Real Returns 1792-2025'!$K74)</f>
+        <f>RATE(30,,K44,-'Real Returns 1792-2026'!$K74)</f>
         <v>4.2517714042123601E-2</v>
       </c>
       <c r="P74" s="2">
-        <f>RATE(50,,J24,-'Real Returns 1792-2025'!$J74)</f>
+        <f>RATE(50,,J24,-'Real Returns 1792-2026'!$J74)</f>
         <v>5.0168801329489601E-2</v>
       </c>
       <c r="Q74" s="2">
-        <f>RATE(50,,K24,-'Real Returns 1792-2025'!$K74)</f>
+        <f>RATE(50,,K24,-'Real Returns 1792-2026'!$K74)</f>
         <v>6.421771641172723E-2</v>
       </c>
       <c r="R74" s="2"/>
@@ -7220,27 +7220,27 @@
         <v>33.909987399927587</v>
       </c>
       <c r="L75" s="2">
-        <f>RATE(10,,J65,-'Real Returns 1792-2025'!$J75)</f>
+        <f>RATE(10,,J65,-'Real Returns 1792-2026'!$J75)</f>
         <v>4.9347366540029171E-2</v>
       </c>
       <c r="M75" s="2">
-        <f>RATE(10,,K65,-'Real Returns 1792-2025'!$K75)</f>
+        <f>RATE(10,,K65,-'Real Returns 1792-2026'!$K75)</f>
         <v>1.258160707924252E-2</v>
       </c>
       <c r="N75" s="2">
-        <f>RATE(30,,J45,-'Real Returns 1792-2025'!$J75)</f>
+        <f>RATE(30,,J45,-'Real Returns 1792-2026'!$J75)</f>
         <v>2.6384655050323579E-2</v>
       </c>
       <c r="O75" s="2">
-        <f>RATE(30,,K45,-'Real Returns 1792-2025'!$K75)</f>
+        <f>RATE(30,,K45,-'Real Returns 1792-2026'!$K75)</f>
         <v>3.8456696714668372E-2</v>
       </c>
       <c r="P75" s="2">
-        <f>RATE(50,,J25,-'Real Returns 1792-2025'!$J75)</f>
+        <f>RATE(50,,J25,-'Real Returns 1792-2026'!$J75)</f>
         <v>4.999867799943427E-2</v>
       </c>
       <c r="Q75" s="2">
-        <f>RATE(50,,K25,-'Real Returns 1792-2025'!$K75)</f>
+        <f>RATE(50,,K25,-'Real Returns 1792-2026'!$K75)</f>
         <v>6.2636547904644083E-2</v>
       </c>
       <c r="R75" s="2"/>
@@ -7279,27 +7279,27 @@
         <v>34.279923297409674</v>
       </c>
       <c r="L76" s="2">
-        <f>RATE(10,,J66,-'Real Returns 1792-2025'!$J76)</f>
+        <f>RATE(10,,J66,-'Real Returns 1792-2026'!$J76)</f>
         <v>5.5581200343456726E-2</v>
       </c>
       <c r="M76" s="2">
-        <f>RATE(10,,K66,-'Real Returns 1792-2025'!$K76)</f>
+        <f>RATE(10,,K66,-'Real Returns 1792-2026'!$K76)</f>
         <v>5.3718302019143769E-3</v>
       </c>
       <c r="N76" s="2">
-        <f>RATE(30,,J46,-'Real Returns 1792-2025'!$J76)</f>
+        <f>RATE(30,,J46,-'Real Returns 1792-2026'!$J76)</f>
         <v>2.5552175959716563E-2</v>
       </c>
       <c r="O76" s="2">
-        <f>RATE(30,,K46,-'Real Returns 1792-2025'!$K76)</f>
+        <f>RATE(30,,K46,-'Real Returns 1792-2026'!$K76)</f>
         <v>3.9894567536310231E-2</v>
       </c>
       <c r="P76" s="2">
-        <f>RATE(50,,J26,-'Real Returns 1792-2025'!$J76)</f>
+        <f>RATE(50,,J26,-'Real Returns 1792-2026'!$J76)</f>
         <v>4.5883601642364782E-2</v>
       </c>
       <c r="Q76" s="2">
-        <f>RATE(50,,K26,-'Real Returns 1792-2025'!$K76)</f>
+        <f>RATE(50,,K26,-'Real Returns 1792-2026'!$K76)</f>
         <v>5.7587869084245215E-2</v>
       </c>
       <c r="R76" s="2"/>
@@ -7338,27 +7338,27 @@
         <v>39.551760548075514</v>
       </c>
       <c r="L77" s="2">
-        <f>RATE(10,,J67,-'Real Returns 1792-2025'!$J77)</f>
+        <f>RATE(10,,J67,-'Real Returns 1792-2026'!$J77)</f>
         <v>5.3133529741349807E-2</v>
       </c>
       <c r="M77" s="2">
-        <f>RATE(10,,K67,-'Real Returns 1792-2025'!$K77)</f>
+        <f>RATE(10,,K67,-'Real Returns 1792-2026'!$K77)</f>
         <v>1.2539266411839774E-2</v>
       </c>
       <c r="N77" s="2">
-        <f>RATE(30,,J47,-'Real Returns 1792-2025'!$J77)</f>
+        <f>RATE(30,,J47,-'Real Returns 1792-2026'!$J77)</f>
         <v>2.9715183274532542E-2</v>
       </c>
       <c r="O77" s="2">
-        <f>RATE(30,,K47,-'Real Returns 1792-2025'!$K77)</f>
+        <f>RATE(30,,K47,-'Real Returns 1792-2026'!$K77)</f>
         <v>4.5703343788278138E-2</v>
       </c>
       <c r="P77" s="2">
-        <f>RATE(50,,J27,-'Real Returns 1792-2025'!$J77)</f>
+        <f>RATE(50,,J27,-'Real Returns 1792-2026'!$J77)</f>
         <v>4.5507821843759524E-2</v>
       </c>
       <c r="Q77" s="2">
-        <f>RATE(50,,K27,-'Real Returns 1792-2025'!$K77)</f>
+        <f>RATE(50,,K27,-'Real Returns 1792-2026'!$K77)</f>
         <v>5.7112256812669807E-2</v>
       </c>
       <c r="R77" s="2"/>
@@ -7397,27 +7397,27 @@
         <v>45.380861115833703</v>
       </c>
       <c r="L78" s="2">
-        <f>RATE(10,,J68,-'Real Returns 1792-2025'!$J78)</f>
+        <f>RATE(10,,J68,-'Real Returns 1792-2026'!$J78)</f>
         <v>8.4549117503487231E-2</v>
       </c>
       <c r="M78" s="2">
-        <f>RATE(10,,K68,-'Real Returns 1792-2025'!$K78)</f>
+        <f>RATE(10,,K68,-'Real Returns 1792-2026'!$K78)</f>
         <v>2.1020806627416618E-2</v>
       </c>
       <c r="N78" s="2">
-        <f>RATE(30,,J48,-'Real Returns 1792-2025'!$J78)</f>
+        <f>RATE(30,,J48,-'Real Returns 1792-2026'!$J78)</f>
         <v>3.6098309683065294E-2</v>
       </c>
       <c r="O78" s="2">
-        <f>RATE(30,,K48,-'Real Returns 1792-2025'!$K78)</f>
+        <f>RATE(30,,K48,-'Real Returns 1792-2026'!$K78)</f>
         <v>4.7806211830209736E-2</v>
       </c>
       <c r="P78" s="2">
-        <f>RATE(50,,J28,-'Real Returns 1792-2025'!$J78)</f>
+        <f>RATE(50,,J28,-'Real Returns 1792-2026'!$J78)</f>
         <v>4.3176871144979118E-2</v>
       </c>
       <c r="Q78" s="2">
-        <f>RATE(50,,K28,-'Real Returns 1792-2025'!$K78)</f>
+        <f>RATE(50,,K28,-'Real Returns 1792-2026'!$K78)</f>
         <v>5.5888484774656494E-2</v>
       </c>
       <c r="R78" s="2"/>
@@ -7456,27 +7456,27 @@
         <v>50.321019717361587</v>
       </c>
       <c r="L79" s="2">
-        <f>RATE(10,,J69,-'Real Returns 1792-2025'!$J79)</f>
+        <f>RATE(10,,J69,-'Real Returns 1792-2026'!$J79)</f>
         <v>9.6703391114442053E-2</v>
       </c>
       <c r="M79" s="2">
-        <f>RATE(10,,K69,-'Real Returns 1792-2025'!$K79)</f>
+        <f>RATE(10,,K69,-'Real Returns 1792-2026'!$K79)</f>
         <v>1.8562193285607004E-2</v>
       </c>
       <c r="N79" s="2">
-        <f>RATE(30,,J49,-'Real Returns 1792-2025'!$J79)</f>
+        <f>RATE(30,,J49,-'Real Returns 1792-2026'!$J79)</f>
         <v>4.098869875312381E-2</v>
       </c>
       <c r="O79" s="2">
-        <f>RATE(30,,K49,-'Real Returns 1792-2025'!$K79)</f>
+        <f>RATE(30,,K49,-'Real Returns 1792-2026'!$K79)</f>
         <v>4.9618071394742926E-2</v>
       </c>
       <c r="P79" s="2">
-        <f>RATE(50,,J29,-'Real Returns 1792-2025'!$J79)</f>
+        <f>RATE(50,,J29,-'Real Returns 1792-2026'!$J79)</f>
         <v>5.0804307000421135E-2</v>
       </c>
       <c r="Q79" s="2">
-        <f>RATE(50,,K29,-'Real Returns 1792-2025'!$K79)</f>
+        <f>RATE(50,,K29,-'Real Returns 1792-2026'!$K79)</f>
         <v>5.7622963344222476E-2</v>
       </c>
       <c r="R79" s="2"/>
@@ -7515,27 +7515,27 @@
         <v>56.517509911776138</v>
       </c>
       <c r="L80" s="2">
-        <f>RATE(10,,J70,-'Real Returns 1792-2025'!$J80)</f>
+        <f>RATE(10,,J70,-'Real Returns 1792-2026'!$J80)</f>
         <v>0.1035856334374661</v>
       </c>
       <c r="M80" s="2">
-        <f>RATE(10,,K70,-'Real Returns 1792-2025'!$K80)</f>
+        <f>RATE(10,,K70,-'Real Returns 1792-2026'!$K80)</f>
         <v>2.623870039650195E-2</v>
       </c>
       <c r="N80" s="2">
-        <f>RATE(30,,J50,-'Real Returns 1792-2025'!$J80)</f>
+        <f>RATE(30,,J50,-'Real Returns 1792-2026'!$J80)</f>
         <v>4.7864757573521113E-2</v>
       </c>
       <c r="O80" s="2">
-        <f>RATE(30,,K50,-'Real Returns 1792-2025'!$K80)</f>
+        <f>RATE(30,,K50,-'Real Returns 1792-2026'!$K80)</f>
         <v>5.4740632534007995E-2</v>
       </c>
       <c r="P80" s="2">
-        <f>RATE(50,,J30,-'Real Returns 1792-2025'!$J80)</f>
+        <f>RATE(50,,J30,-'Real Returns 1792-2026'!$J80)</f>
         <v>5.2466665823930177E-2</v>
       </c>
       <c r="Q80" s="2">
-        <f>RATE(50,,K30,-'Real Returns 1792-2025'!$K80)</f>
+        <f>RATE(50,,K30,-'Real Returns 1792-2026'!$K80)</f>
         <v>5.7467315863468343E-2</v>
       </c>
       <c r="R80" s="2"/>
@@ -7574,27 +7574,27 @@
         <v>63.453680172908904</v>
       </c>
       <c r="L81" s="2">
-        <f>RATE(10,,J71,-'Real Returns 1792-2025'!$J81)</f>
+        <f>RATE(10,,J71,-'Real Returns 1792-2026'!$J81)</f>
         <v>9.5981716866020736E-2</v>
       </c>
       <c r="M81" s="2">
-        <f>RATE(10,,K71,-'Real Returns 1792-2025'!$K81)</f>
+        <f>RATE(10,,K71,-'Real Returns 1792-2026'!$K81)</f>
         <v>3.8943001397216376E-2</v>
       </c>
       <c r="N81" s="2">
-        <f>RATE(30,,J51,-'Real Returns 1792-2025'!$J81)</f>
+        <f>RATE(30,,J51,-'Real Returns 1792-2026'!$J81)</f>
         <v>5.0701435443555772E-2</v>
       </c>
       <c r="O81" s="2">
-        <f>RATE(30,,K51,-'Real Returns 1792-2025'!$K81)</f>
+        <f>RATE(30,,K51,-'Real Returns 1792-2026'!$K81)</f>
         <v>5.6124115592197169E-2</v>
       </c>
       <c r="P81" s="2">
-        <f>RATE(50,,J31,-'Real Returns 1792-2025'!$J81)</f>
+        <f>RATE(50,,J31,-'Real Returns 1792-2026'!$J81)</f>
         <v>5.1310417285684931E-2</v>
       </c>
       <c r="Q81" s="2">
-        <f>RATE(50,,K31,-'Real Returns 1792-2025'!$K81)</f>
+        <f>RATE(50,,K31,-'Real Returns 1792-2026'!$K81)</f>
         <v>5.6562577257437387E-2</v>
       </c>
       <c r="R81" s="2"/>
@@ -7633,27 +7633,27 @@
         <v>71.052257494878219</v>
       </c>
       <c r="L82" s="2">
-        <f>RATE(10,,J72,-'Real Returns 1792-2025'!$J82)</f>
+        <f>RATE(10,,J72,-'Real Returns 1792-2026'!$J82)</f>
         <v>0.12280163163765122</v>
       </c>
       <c r="M82" s="2">
-        <f>RATE(10,,K72,-'Real Returns 1792-2025'!$K82)</f>
+        <f>RATE(10,,K72,-'Real Returns 1792-2026'!$K82)</f>
         <v>5.504191798598649E-2</v>
       </c>
       <c r="N82" s="2">
-        <f>RATE(30,,J52,-'Real Returns 1792-2025'!$J82)</f>
+        <f>RATE(30,,J52,-'Real Returns 1792-2026'!$J82)</f>
         <v>6.878929907108472E-2</v>
       </c>
       <c r="O82" s="2">
-        <f>RATE(30,,K52,-'Real Returns 1792-2025'!$K82)</f>
+        <f>RATE(30,,K52,-'Real Returns 1792-2026'!$K82)</f>
         <v>6.8302263868999763E-2</v>
       </c>
       <c r="P82" s="2">
-        <f>RATE(50,,J32,-'Real Returns 1792-2025'!$J82)</f>
+        <f>RATE(50,,J32,-'Real Returns 1792-2026'!$J82)</f>
         <v>5.287359182478104E-2</v>
       </c>
       <c r="Q82" s="2">
-        <f>RATE(50,,K32,-'Real Returns 1792-2025'!$K82)</f>
+        <f>RATE(50,,K32,-'Real Returns 1792-2026'!$K82)</f>
         <v>5.7646401210767216E-2</v>
       </c>
       <c r="R82" s="2"/>
@@ -7692,27 +7692,27 @@
         <v>76.513253484805404</v>
       </c>
       <c r="L83" s="2">
-        <f>RATE(10,,J73,-'Real Returns 1792-2025'!$J83)</f>
+        <f>RATE(10,,J73,-'Real Returns 1792-2026'!$J83)</f>
         <v>0.10088371974477081</v>
       </c>
       <c r="M83" s="2">
-        <f>RATE(10,,K73,-'Real Returns 1792-2025'!$K83)</f>
+        <f>RATE(10,,K73,-'Real Returns 1792-2026'!$K83)</f>
         <v>6.2756074591298533E-2</v>
       </c>
       <c r="N83" s="2">
-        <f>RATE(30,,J53,-'Real Returns 1792-2025'!$J83)</f>
+        <f>RATE(30,,J53,-'Real Returns 1792-2026'!$J83)</f>
         <v>7.3454687628531523E-2</v>
       </c>
       <c r="O83" s="2">
-        <f>RATE(30,,K53,-'Real Returns 1792-2025'!$K83)</f>
+        <f>RATE(30,,K53,-'Real Returns 1792-2026'!$K83)</f>
         <v>7.0584516547173959E-2</v>
       </c>
       <c r="P83" s="2">
-        <f>RATE(50,,J33,-'Real Returns 1792-2025'!$J83)</f>
+        <f>RATE(50,,J33,-'Real Returns 1792-2026'!$J83)</f>
         <v>5.6249062378722126E-2</v>
       </c>
       <c r="Q83" s="2">
-        <f>RATE(50,,K33,-'Real Returns 1792-2025'!$K83)</f>
+        <f>RATE(50,,K33,-'Real Returns 1792-2026'!$K83)</f>
         <v>5.7838589268097311E-2</v>
       </c>
       <c r="R83" s="2"/>
@@ -7751,27 +7751,27 @@
         <v>84.746554196901243</v>
       </c>
       <c r="L84" s="2">
-        <f>RATE(10,,J74,-'Real Returns 1792-2025'!$J84)</f>
+        <f>RATE(10,,J74,-'Real Returns 1792-2026'!$J84)</f>
         <v>9.720905556037579E-2</v>
       </c>
       <c r="M84" s="2">
-        <f>RATE(10,,K74,-'Real Returns 1792-2025'!$K84)</f>
+        <f>RATE(10,,K74,-'Real Returns 1792-2026'!$K84)</f>
         <v>8.9516928663314052E-2</v>
       </c>
       <c r="N84" s="2">
-        <f>RATE(30,,J54,-'Real Returns 1792-2025'!$J84)</f>
+        <f>RATE(30,,J54,-'Real Returns 1792-2026'!$J84)</f>
         <v>5.9720002985967476E-2</v>
       </c>
       <c r="O84" s="2">
-        <f>RATE(30,,K54,-'Real Returns 1792-2025'!$K84)</f>
+        <f>RATE(30,,K54,-'Real Returns 1792-2026'!$K84)</f>
         <v>5.8280092811742457E-2</v>
       </c>
       <c r="P84" s="2">
-        <f>RATE(50,,J34,-'Real Returns 1792-2025'!$J84)</f>
+        <f>RATE(50,,J34,-'Real Returns 1792-2026'!$J84)</f>
         <v>5.2318191638981638E-2</v>
       </c>
       <c r="Q84" s="2">
-        <f>RATE(50,,K34,-'Real Returns 1792-2025'!$K84)</f>
+        <f>RATE(50,,K34,-'Real Returns 1792-2026'!$K84)</f>
         <v>5.6723749774463213E-2</v>
       </c>
       <c r="R84" s="2"/>
@@ -7810,27 +7810,27 @@
         <v>97.475941818469039</v>
       </c>
       <c r="L85" s="2">
-        <f>RATE(10,,J75,-'Real Returns 1792-2025'!$J85)</f>
+        <f>RATE(10,,J75,-'Real Returns 1792-2026'!$J85)</f>
         <v>0.11384854385615108</v>
       </c>
       <c r="M85" s="2">
-        <f>RATE(10,,K75,-'Real Returns 1792-2025'!$K85)</f>
+        <f>RATE(10,,K75,-'Real Returns 1792-2026'!$K85)</f>
         <v>0.11136567980975536</v>
       </c>
       <c r="N85" s="2">
-        <f>RATE(30,,J55,-'Real Returns 1792-2025'!$J85)</f>
+        <f>RATE(30,,J55,-'Real Returns 1792-2026'!$J85)</f>
         <v>5.9701550115727822E-2</v>
       </c>
       <c r="O85" s="2">
-        <f>RATE(30,,K55,-'Real Returns 1792-2025'!$K85)</f>
+        <f>RATE(30,,K55,-'Real Returns 1792-2026'!$K85)</f>
         <v>6.1399996457788229E-2</v>
       </c>
       <c r="P85" s="2">
-        <f>RATE(50,,J35,-'Real Returns 1792-2025'!$J85)</f>
+        <f>RATE(50,,J35,-'Real Returns 1792-2026'!$J85)</f>
         <v>5.0620699252690846E-2</v>
       </c>
       <c r="Q85" s="2">
-        <f>RATE(50,,K35,-'Real Returns 1792-2025'!$K85)</f>
+        <f>RATE(50,,K35,-'Real Returns 1792-2026'!$K85)</f>
         <v>5.7467963726654289E-2</v>
       </c>
       <c r="R85" s="2"/>
@@ -7869,27 +7869,27 @@
         <v>110.43092313672487</v>
       </c>
       <c r="L86" s="2">
-        <f>RATE(10,,J76,-'Real Returns 1792-2025'!$J86)</f>
+        <f>RATE(10,,J76,-'Real Returns 1792-2026'!$J86)</f>
         <v>0.11958064226576232</v>
       </c>
       <c r="M86" s="2">
-        <f>RATE(10,,K76,-'Real Returns 1792-2025'!$K86)</f>
+        <f>RATE(10,,K76,-'Real Returns 1792-2026'!$K86)</f>
         <v>0.12410035796370217</v>
       </c>
       <c r="N86" s="2">
-        <f>RATE(30,,J56,-'Real Returns 1792-2025'!$J86)</f>
+        <f>RATE(30,,J56,-'Real Returns 1792-2026'!$J86)</f>
         <v>6.1063954729463805E-2</v>
       </c>
       <c r="O86" s="2">
-        <f>RATE(30,,K56,-'Real Returns 1792-2025'!$K86)</f>
+        <f>RATE(30,,K56,-'Real Returns 1792-2026'!$K86)</f>
         <v>6.5542188498068046E-2</v>
       </c>
       <c r="P86" s="2">
-        <f>RATE(50,,J36,-'Real Returns 1792-2025'!$J86)</f>
+        <f>RATE(50,,J36,-'Real Returns 1792-2026'!$J86)</f>
         <v>5.2262465343954762E-2</v>
       </c>
       <c r="Q86" s="2">
-        <f>RATE(50,,K36,-'Real Returns 1792-2025'!$K86)</f>
+        <f>RATE(50,,K36,-'Real Returns 1792-2026'!$K86)</f>
         <v>6.025003696898866E-2</v>
       </c>
       <c r="R86" s="2"/>
@@ -7928,27 +7928,27 @@
         <v>119.19299072361633</v>
       </c>
       <c r="L87" s="2">
-        <f>RATE(10,,J77,-'Real Returns 1792-2025'!$J87)</f>
+        <f>RATE(10,,J77,-'Real Returns 1792-2026'!$J87)</f>
         <v>9.731350779771146E-2</v>
       </c>
       <c r="M87" s="2">
-        <f>RATE(10,,K77,-'Real Returns 1792-2025'!$K87)</f>
+        <f>RATE(10,,K77,-'Real Returns 1792-2026'!$K87)</f>
         <v>0.1166279380828181</v>
       </c>
       <c r="N87" s="2">
-        <f>RATE(30,,J57,-'Real Returns 1792-2025'!$J87)</f>
+        <f>RATE(30,,J57,-'Real Returns 1792-2026'!$J87)</f>
         <v>5.7511909899362758E-2</v>
       </c>
       <c r="O87" s="2">
-        <f>RATE(30,,K57,-'Real Returns 1792-2025'!$K87)</f>
+        <f>RATE(30,,K57,-'Real Returns 1792-2026'!$K87)</f>
         <v>6.6962325918113449E-2</v>
       </c>
       <c r="P87" s="2">
-        <f>RATE(50,,J37,-'Real Returns 1792-2025'!$J87)</f>
+        <f>RATE(50,,J37,-'Real Returns 1792-2026'!$J87)</f>
         <v>4.918048292349033E-2</v>
       </c>
       <c r="Q87" s="2">
-        <f>RATE(50,,K37,-'Real Returns 1792-2025'!$K87)</f>
+        <f>RATE(50,,K37,-'Real Returns 1792-2026'!$K87)</f>
         <v>6.0823891149998005E-2</v>
       </c>
       <c r="R87" s="2"/>
@@ -7987,27 +7987,27 @@
         <v>128.98298808637003</v>
       </c>
       <c r="L88" s="2">
-        <f>RATE(10,,J78,-'Real Returns 1792-2025'!$J88)</f>
+        <f>RATE(10,,J78,-'Real Returns 1792-2026'!$J88)</f>
         <v>8.2894602364716741E-2</v>
       </c>
       <c r="M88" s="2">
-        <f>RATE(10,,K78,-'Real Returns 1792-2025'!$K88)</f>
+        <f>RATE(10,,K78,-'Real Returns 1792-2026'!$K88)</f>
         <v>0.11010988570354595</v>
       </c>
       <c r="N88" s="2">
-        <f>RATE(30,,J58,-'Real Returns 1792-2025'!$J88)</f>
+        <f>RATE(30,,J58,-'Real Returns 1792-2026'!$J88)</f>
         <v>5.7217243116507742E-2</v>
       </c>
       <c r="O88" s="2">
-        <f>RATE(30,,K58,-'Real Returns 1792-2025'!$K88)</f>
+        <f>RATE(30,,K58,-'Real Returns 1792-2026'!$K88)</f>
         <v>6.9169055248670383E-2</v>
       </c>
       <c r="P88" s="2">
-        <f>RATE(50,,J38,-'Real Returns 1792-2025'!$J88)</f>
+        <f>RATE(50,,J38,-'Real Returns 1792-2026'!$J88)</f>
         <v>4.8514698210935001E-2</v>
       </c>
       <c r="Q88" s="2">
-        <f>RATE(50,,K38,-'Real Returns 1792-2025'!$K88)</f>
+        <f>RATE(50,,K38,-'Real Returns 1792-2026'!$K88)</f>
         <v>6.0791451180613611E-2</v>
       </c>
       <c r="R88" s="2"/>
@@ -8046,27 +8046,27 @@
         <v>142.21728989734447</v>
       </c>
       <c r="L89" s="2">
-        <f>RATE(10,,J79,-'Real Returns 1792-2025'!$J89)</f>
+        <f>RATE(10,,J79,-'Real Returns 1792-2026'!$J89)</f>
         <v>7.4583278092404559E-2</v>
       </c>
       <c r="M89" s="2">
-        <f>RATE(10,,K79,-'Real Returns 1792-2025'!$K89)</f>
+        <f>RATE(10,,K79,-'Real Returns 1792-2026'!$K89)</f>
         <v>0.10948209146407037</v>
       </c>
       <c r="N89" s="2">
-        <f>RATE(30,,J59,-'Real Returns 1792-2025'!$J89)</f>
+        <f>RATE(30,,J59,-'Real Returns 1792-2026'!$J89)</f>
         <v>6.1779379305851929E-2</v>
       </c>
       <c r="O89" s="2">
-        <f>RATE(30,,K59,-'Real Returns 1792-2025'!$K89)</f>
+        <f>RATE(30,,K59,-'Real Returns 1792-2026'!$K89)</f>
         <v>6.4466191491227634E-2</v>
       </c>
       <c r="P89" s="2">
-        <f>RATE(50,,J39,-'Real Returns 1792-2025'!$J89)</f>
+        <f>RATE(50,,J39,-'Real Returns 1792-2026'!$J89)</f>
         <v>5.0331591182404857E-2</v>
       </c>
       <c r="Q89" s="2">
-        <f>RATE(50,,K39,-'Real Returns 1792-2025'!$K89)</f>
+        <f>RATE(50,,K39,-'Real Returns 1792-2026'!$K89)</f>
         <v>6.1489363355190438E-2</v>
       </c>
       <c r="R89" s="2"/>
@@ -8105,27 +8105,27 @@
         <v>152.4833557960082</v>
       </c>
       <c r="L90" s="2">
-        <f>RATE(10,,J80,-'Real Returns 1792-2025'!$J90)</f>
+        <f>RATE(10,,J80,-'Real Returns 1792-2026'!$J90)</f>
         <v>0.1070717656387551</v>
       </c>
       <c r="M90" s="2">
-        <f>RATE(10,,K80,-'Real Returns 1792-2025'!$K90)</f>
+        <f>RATE(10,,K80,-'Real Returns 1792-2026'!$K90)</f>
         <v>0.10434289703283792</v>
       </c>
       <c r="N90" s="2">
-        <f>RATE(30,,J60,-'Real Returns 1792-2025'!$J90)</f>
+        <f>RATE(30,,J60,-'Real Returns 1792-2026'!$J90)</f>
         <v>7.3497791348935609E-2</v>
       </c>
       <c r="O90" s="2">
-        <f>RATE(30,,K60,-'Real Returns 1792-2025'!$K90)</f>
+        <f>RATE(30,,K60,-'Real Returns 1792-2026'!$K90)</f>
         <v>6.2005466518667306E-2</v>
       </c>
       <c r="P90" s="2">
-        <f>RATE(50,,J40,-'Real Returns 1792-2025'!$J90)</f>
+        <f>RATE(50,,J40,-'Real Returns 1792-2026'!$J90)</f>
         <v>5.6658572978662794E-2</v>
       </c>
       <c r="Q90" s="2">
-        <f>RATE(50,,K40,-'Real Returns 1792-2025'!$K90)</f>
+        <f>RATE(50,,K40,-'Real Returns 1792-2026'!$K90)</f>
         <v>6.1289986371400602E-2</v>
       </c>
       <c r="R90" s="2"/>
@@ -8164,27 +8164,27 @@
         <v>168.95494776314925</v>
       </c>
       <c r="L91" s="2">
-        <f>RATE(10,,J81,-'Real Returns 1792-2025'!$J91)</f>
+        <f>RATE(10,,J81,-'Real Returns 1792-2026'!$J91)</f>
         <v>0.12394584886115874</v>
       </c>
       <c r="M91" s="2">
-        <f>RATE(10,,K81,-'Real Returns 1792-2025'!$K91)</f>
+        <f>RATE(10,,K81,-'Real Returns 1792-2026'!$K91)</f>
         <v>0.10288799623117274</v>
       </c>
       <c r="N91" s="2">
-        <f>RATE(30,,J61,-'Real Returns 1792-2025'!$J91)</f>
+        <f>RATE(30,,J61,-'Real Returns 1792-2026'!$J91)</f>
         <v>7.4182741562666479E-2</v>
       </c>
       <c r="O91" s="2">
-        <f>RATE(30,,K61,-'Real Returns 1792-2025'!$K91)</f>
+        <f>RATE(30,,K61,-'Real Returns 1792-2026'!$K91)</f>
         <v>6.1944039043995924E-2</v>
       </c>
       <c r="P91" s="2">
-        <f>RATE(50,,J41,-'Real Returns 1792-2025'!$J91)</f>
+        <f>RATE(50,,J41,-'Real Returns 1792-2026'!$J91)</f>
         <v>5.8027263532413463E-2</v>
       </c>
       <c r="Q91" s="2">
-        <f>RATE(50,,K41,-'Real Returns 1792-2025'!$K91)</f>
+        <f>RATE(50,,K41,-'Real Returns 1792-2026'!$K91)</f>
         <v>6.1457922100751419E-2</v>
       </c>
       <c r="R91" s="2"/>
@@ -8223,27 +8223,27 @@
         <v>178.98140417827727</v>
       </c>
       <c r="L92" s="2">
-        <f>RATE(10,,J82,-'Real Returns 1792-2025'!$J92)</f>
+        <f>RATE(10,,J82,-'Real Returns 1792-2026'!$J92)</f>
         <v>0.10375764001449397</v>
       </c>
       <c r="M92" s="2">
-        <f>RATE(10,,K82,-'Real Returns 1792-2025'!$K92)</f>
+        <f>RATE(10,,K82,-'Real Returns 1792-2026'!$K92)</f>
         <v>9.6788790009644785E-2</v>
       </c>
       <c r="N92" s="2">
-        <f>RATE(30,,J62,-'Real Returns 1792-2025'!$J92)</f>
+        <f>RATE(30,,J62,-'Real Returns 1792-2026'!$J92)</f>
         <v>7.5471341742195691E-2</v>
       </c>
       <c r="O92" s="2">
-        <f>RATE(30,,K62,-'Real Returns 1792-2025'!$K92)</f>
+        <f>RATE(30,,K62,-'Real Returns 1792-2026'!$K92)</f>
         <v>6.2429093199298041E-2</v>
       </c>
       <c r="P92" s="2">
-        <f>RATE(50,,J42,-'Real Returns 1792-2025'!$J92)</f>
+        <f>RATE(50,,J42,-'Real Returns 1792-2026'!$J92)</f>
         <v>5.6329492612791875E-2</v>
       </c>
       <c r="Q92" s="2">
-        <f>RATE(50,,K42,-'Real Returns 1792-2025'!$K92)</f>
+        <f>RATE(50,,K42,-'Real Returns 1792-2026'!$K92)</f>
         <v>6.0130326009795357E-2</v>
       </c>
       <c r="R92" s="2"/>
@@ -8282,27 +8282,27 @@
         <v>189.63778849835876</v>
       </c>
       <c r="L93" s="2">
-        <f>RATE(10,,J83,-'Real Returns 1792-2025'!$J93)</f>
+        <f>RATE(10,,J83,-'Real Returns 1792-2026'!$J93)</f>
         <v>9.0014177475550267E-2</v>
       </c>
       <c r="M93" s="2">
-        <f>RATE(10,,K83,-'Real Returns 1792-2025'!$K93)</f>
+        <f>RATE(10,,K83,-'Real Returns 1792-2026'!$K93)</f>
         <v>9.5011855597338116E-2</v>
       </c>
       <c r="N93" s="2">
-        <f>RATE(30,,J63,-'Real Returns 1792-2025'!$J93)</f>
+        <f>RATE(30,,J63,-'Real Returns 1792-2026'!$J93)</f>
         <v>7.0362335402162149E-2</v>
       </c>
       <c r="O93" s="2">
-        <f>RATE(30,,K63,-'Real Returns 1792-2025'!$K93)</f>
+        <f>RATE(30,,K63,-'Real Returns 1792-2026'!$K93)</f>
         <v>6.0843900688403597E-2</v>
       </c>
       <c r="P93" s="2">
-        <f>RATE(50,,J43,-'Real Returns 1792-2025'!$J93)</f>
+        <f>RATE(50,,J43,-'Real Returns 1792-2026'!$J93)</f>
         <v>5.6365085813160347E-2</v>
       </c>
       <c r="Q93" s="2">
-        <f>RATE(50,,K43,-'Real Returns 1792-2025'!$K93)</f>
+        <f>RATE(50,,K43,-'Real Returns 1792-2026'!$K93)</f>
         <v>5.979339093155505E-2</v>
       </c>
       <c r="R93" s="2"/>
@@ -8341,27 +8341,27 @@
         <v>205.72676346012975</v>
       </c>
       <c r="L94" s="2">
-        <f>RATE(10,,J84,-'Real Returns 1792-2025'!$J94)</f>
+        <f>RATE(10,,J84,-'Real Returns 1792-2026'!$J94)</f>
         <v>8.4535802344108943E-2</v>
       </c>
       <c r="M94" s="2">
-        <f>RATE(10,,K84,-'Real Returns 1792-2025'!$K94)</f>
+        <f>RATE(10,,K84,-'Real Returns 1792-2026'!$K94)</f>
         <v>9.2740084735446274E-2</v>
       </c>
       <c r="N94" s="2">
-        <f>RATE(30,,J64,-'Real Returns 1792-2025'!$J94)</f>
+        <f>RATE(30,,J64,-'Real Returns 1792-2026'!$J94)</f>
         <v>7.300865215700561E-2</v>
       </c>
       <c r="O94" s="2">
-        <f>RATE(30,,K64,-'Real Returns 1792-2025'!$K94)</f>
+        <f>RATE(30,,K64,-'Real Returns 1792-2026'!$K94)</f>
         <v>6.3843408088656184E-2</v>
       </c>
       <c r="P94" s="2">
-        <f>RATE(50,,J44,-'Real Returns 1792-2025'!$J94)</f>
+        <f>RATE(50,,J44,-'Real Returns 1792-2026'!$J94)</f>
         <v>5.467547476495084E-2</v>
       </c>
       <c r="Q94" s="2">
-        <f>RATE(50,,K44,-'Real Returns 1792-2025'!$K94)</f>
+        <f>RATE(50,,K44,-'Real Returns 1792-2026'!$K94)</f>
         <v>6.1696137212203281E-2</v>
       </c>
       <c r="R94" s="2"/>
@@ -8400,27 +8400,27 @@
         <v>219.89807094153491</v>
       </c>
       <c r="L95" s="2">
-        <f>RATE(10,,J85,-'Real Returns 1792-2025'!$J95)</f>
+        <f>RATE(10,,J85,-'Real Returns 1792-2026'!$J95)</f>
         <v>6.2122059988327108E-2</v>
       </c>
       <c r="M95" s="2">
-        <f>RATE(10,,K85,-'Real Returns 1792-2025'!$K95)</f>
+        <f>RATE(10,,K85,-'Real Returns 1792-2026'!$K95)</f>
         <v>8.475684166434444E-2</v>
       </c>
       <c r="N95" s="2">
-        <f>RATE(30,,J65,-'Real Returns 1792-2025'!$J95)</f>
+        <f>RATE(30,,J65,-'Real Returns 1792-2026'!$J95)</f>
         <v>7.4747926298508169E-2</v>
       </c>
       <c r="O95" s="2">
-        <f>RATE(30,,K65,-'Real Returns 1792-2025'!$K95)</f>
+        <f>RATE(30,,K65,-'Real Returns 1792-2026'!$K95)</f>
         <v>6.8742642244769239E-2</v>
       </c>
       <c r="P95" s="2">
-        <f>RATE(50,,J45,-'Real Returns 1792-2025'!$J95)</f>
+        <f>RATE(50,,J45,-'Real Returns 1792-2026'!$J95)</f>
         <v>5.0476168801320755E-2</v>
       </c>
       <c r="Q95" s="2">
-        <f>RATE(50,,K45,-'Real Returns 1792-2025'!$K95)</f>
+        <f>RATE(50,,K45,-'Real Returns 1792-2026'!$K95)</f>
         <v>6.1868922583862826E-2</v>
       </c>
       <c r="R95" s="2"/>
@@ -8459,27 +8459,27 @@
         <v>241.16393900091037</v>
       </c>
       <c r="L96" s="2">
-        <f>RATE(10,,J86,-'Real Returns 1792-2025'!$J96)</f>
+        <f>RATE(10,,J86,-'Real Returns 1792-2026'!$J96)</f>
         <v>8.1744196636783978E-2</v>
       </c>
       <c r="M96" s="2">
-        <f>RATE(10,,K86,-'Real Returns 1792-2025'!$K96)</f>
+        <f>RATE(10,,K86,-'Real Returns 1792-2026'!$K96)</f>
         <v>8.1240156226775745E-2</v>
       </c>
       <c r="N96" s="2">
-        <f>RATE(30,,J66,-'Real Returns 1792-2025'!$J96)</f>
+        <f>RATE(30,,J66,-'Real Returns 1792-2026'!$J96)</f>
         <v>8.5318486657847567E-2</v>
       </c>
       <c r="O96" s="2">
-        <f>RATE(30,,K66,-'Real Returns 1792-2025'!$K96)</f>
+        <f>RATE(30,,K66,-'Real Returns 1792-2026'!$K96)</f>
         <v>6.909916017194169E-2</v>
       </c>
       <c r="P96" s="2">
-        <f>RATE(50,,J46,-'Real Returns 1792-2025'!$J96)</f>
+        <f>RATE(50,,J46,-'Real Returns 1792-2026'!$J96)</f>
         <v>5.4898433012605413E-2</v>
       </c>
       <c r="Q96" s="2">
-        <f>RATE(50,,K46,-'Real Returns 1792-2025'!$K96)</f>
+        <f>RATE(50,,K46,-'Real Returns 1792-2026'!$K96)</f>
         <v>6.4483750374831825E-2</v>
       </c>
       <c r="R96" s="2"/>
@@ -8518,27 +8518,27 @@
         <v>254.74963922233331</v>
       </c>
       <c r="L97" s="2">
-        <f>RATE(10,,J87,-'Real Returns 1792-2025'!$J97)</f>
+        <f>RATE(10,,J87,-'Real Returns 1792-2026'!$J97)</f>
         <v>0.1038968861673191</v>
       </c>
       <c r="M97" s="2">
-        <f>RATE(10,,K87,-'Real Returns 1792-2025'!$K97)</f>
+        <f>RATE(10,,K87,-'Real Returns 1792-2026'!$K97)</f>
         <v>7.8912652323631122E-2</v>
       </c>
       <c r="N97" s="2">
-        <f>RATE(30,,J67,-'Real Returns 1792-2025'!$J97)</f>
+        <f>RATE(30,,J67,-'Real Returns 1792-2026'!$J97)</f>
         <v>8.4544953594617833E-2</v>
       </c>
       <c r="O97" s="2">
-        <f>RATE(30,,K67,-'Real Returns 1792-2025'!$K97)</f>
+        <f>RATE(30,,K67,-'Real Returns 1792-2026'!$K97)</f>
         <v>6.8486116134877775E-2</v>
       </c>
       <c r="P97" s="2">
-        <f>RATE(50,,J47,-'Real Returns 1792-2025'!$J97)</f>
+        <f>RATE(50,,J47,-'Real Returns 1792-2026'!$J97)</f>
         <v>5.7504238318256642E-2</v>
       </c>
       <c r="Q97" s="2">
-        <f>RATE(50,,K47,-'Real Returns 1792-2025'!$K97)</f>
+        <f>RATE(50,,K47,-'Real Returns 1792-2026'!$K97)</f>
         <v>6.6164096021893118E-2</v>
       </c>
       <c r="R97" s="2"/>
@@ -8577,27 +8577,27 @@
         <v>263.49900789971878</v>
       </c>
       <c r="L98" s="2">
-        <f>RATE(10,,J88,-'Real Returns 1792-2025'!$J98)</f>
+        <f>RATE(10,,J88,-'Real Returns 1792-2026'!$J98)</f>
         <v>9.7822474921243963E-2</v>
       </c>
       <c r="M98" s="2">
-        <f>RATE(10,,K88,-'Real Returns 1792-2025'!$K98)</f>
+        <f>RATE(10,,K88,-'Real Returns 1792-2026'!$K98)</f>
         <v>7.4050384847623829E-2</v>
       </c>
       <c r="N98" s="2">
-        <f>RATE(30,,J68,-'Real Returns 1792-2025'!$J98)</f>
+        <f>RATE(30,,J68,-'Real Returns 1792-2026'!$J98)</f>
         <v>8.8401614376646551E-2</v>
       </c>
       <c r="O98" s="2">
-        <f>RATE(30,,K68,-'Real Returns 1792-2025'!$K98)</f>
+        <f>RATE(30,,K68,-'Real Returns 1792-2026'!$K98)</f>
         <v>6.7763503647211357E-2</v>
       </c>
       <c r="P98" s="2">
-        <f>RATE(50,,J48,-'Real Returns 1792-2025'!$J98)</f>
+        <f>RATE(50,,J48,-'Real Returns 1792-2026'!$J98)</f>
         <v>5.7460710737557472E-2</v>
       </c>
       <c r="Q98" s="2">
-        <f>RATE(50,,K48,-'Real Returns 1792-2025'!$K98)</f>
+        <f>RATE(50,,K48,-'Real Returns 1792-2026'!$K98)</f>
         <v>6.5238136821966289E-2</v>
       </c>
       <c r="R98" s="2"/>
@@ -8636,27 +8636,27 @@
         <v>285.61543123088575</v>
       </c>
       <c r="L99" s="2">
-        <f>RATE(10,,J89,-'Real Returns 1792-2025'!$J99)</f>
+        <f>RATE(10,,J89,-'Real Returns 1792-2026'!$J99)</f>
         <v>8.395422699091587E-2</v>
       </c>
       <c r="M99" s="2">
-        <f>RATE(10,,K89,-'Real Returns 1792-2025'!$K99)</f>
+        <f>RATE(10,,K89,-'Real Returns 1792-2026'!$K99)</f>
         <v>7.2217588217897213E-2</v>
       </c>
       <c r="N99" s="2">
-        <f>RATE(30,,J69,-'Real Returns 1792-2025'!$J99)</f>
+        <f>RATE(30,,J69,-'Real Returns 1792-2026'!$J99)</f>
         <v>8.5042466352749077E-2</v>
       </c>
       <c r="O99" s="2">
-        <f>RATE(30,,K69,-'Real Returns 1792-2025'!$K99)</f>
+        <f>RATE(30,,K69,-'Real Returns 1792-2026'!$K99)</f>
         <v>6.6097500642125204E-2</v>
       </c>
       <c r="P99" s="2">
-        <f>RATE(50,,J49,-'Real Returns 1792-2025'!$J99)</f>
+        <f>RATE(50,,J49,-'Real Returns 1792-2026'!$J99)</f>
         <v>5.6131055220007491E-2</v>
       </c>
       <c r="Q99" s="2">
-        <f>RATE(50,,K49,-'Real Returns 1792-2025'!$K99)</f>
+        <f>RATE(50,,K49,-'Real Returns 1792-2026'!$K99)</f>
         <v>6.5858184305380318E-2</v>
       </c>
       <c r="R99" s="2"/>
@@ -8695,27 +8695,27 @@
         <v>304.99778097308973</v>
       </c>
       <c r="L100" s="2">
-        <f>RATE(10,,J90,-'Real Returns 1792-2025'!$J100)</f>
+        <f>RATE(10,,J90,-'Real Returns 1792-2026'!$J100)</f>
         <v>5.5619382200072114E-2</v>
       </c>
       <c r="M100" s="2">
-        <f>RATE(10,,K90,-'Real Returns 1792-2025'!$K100)</f>
+        <f>RATE(10,,K90,-'Real Returns 1792-2026'!$K100)</f>
         <v>7.1784381043335885E-2</v>
       </c>
       <c r="N100" s="2">
-        <f>RATE(30,,J70,-'Real Returns 1792-2025'!$J100)</f>
+        <f>RATE(30,,J70,-'Real Returns 1792-2026'!$J100)</f>
         <v>8.8503231996974893E-2</v>
       </c>
       <c r="O100" s="2">
-        <f>RATE(30,,K70,-'Real Returns 1792-2025'!$K100)</f>
+        <f>RATE(30,,K70,-'Real Returns 1792-2026'!$K100)</f>
         <v>6.6972562194762331E-2</v>
       </c>
       <c r="P100" s="2">
-        <f>RATE(50,,J50,-'Real Returns 1792-2025'!$J100)</f>
+        <f>RATE(50,,J50,-'Real Returns 1792-2026'!$J100)</f>
         <v>6.1010707148743439E-2</v>
       </c>
       <c r="Q100" s="2">
-        <f>RATE(50,,K50,-'Real Returns 1792-2025'!$K100)</f>
+        <f>RATE(50,,K50,-'Real Returns 1792-2026'!$K100)</f>
         <v>6.7897769460523241E-2</v>
       </c>
       <c r="R100" s="2"/>
@@ -8754,27 +8754,27 @@
         <v>312.86229450877022</v>
       </c>
       <c r="L101" s="2">
-        <f>RATE(10,,J91,-'Real Returns 1792-2025'!$J101)</f>
+        <f>RATE(10,,J91,-'Real Returns 1792-2026'!$J101)</f>
         <v>2.7885049551538244E-2</v>
       </c>
       <c r="M101" s="2">
-        <f>RATE(10,,K91,-'Real Returns 1792-2025'!$K101)</f>
+        <f>RATE(10,,K91,-'Real Returns 1792-2026'!$K101)</f>
         <v>6.3550781787364757E-2</v>
       </c>
       <c r="N101" s="2">
-        <f>RATE(30,,J71,-'Real Returns 1792-2025'!$J101)</f>
+        <f>RATE(30,,J71,-'Real Returns 1792-2026'!$J101)</f>
         <v>8.1843438657465128E-2</v>
       </c>
       <c r="O101" s="2">
-        <f>RATE(30,,K71,-'Real Returns 1792-2025'!$K101)</f>
+        <f>RATE(30,,K71,-'Real Returns 1792-2026'!$K101)</f>
         <v>6.8137397975781042E-2</v>
       </c>
       <c r="P101" s="2">
-        <f>RATE(50,,J51,-'Real Returns 1792-2025'!$J101)</f>
+        <f>RATE(50,,J51,-'Real Returns 1792-2026'!$J101)</f>
         <v>6.029223954660496E-2</v>
       </c>
       <c r="Q101" s="2">
-        <f>RATE(50,,K51,-'Real Returns 1792-2025'!$K101)</f>
+        <f>RATE(50,,K51,-'Real Returns 1792-2026'!$K101)</f>
         <v>6.6809572282003918E-2</v>
       </c>
       <c r="R101" s="2"/>
@@ -8813,27 +8813,27 @@
         <v>329.57918273242825</v>
       </c>
       <c r="L102" s="2">
-        <f>RATE(10,,J92,-'Real Returns 1792-2025'!$J102)</f>
+        <f>RATE(10,,J92,-'Real Returns 1792-2026'!$J102)</f>
         <v>4.2922621062673354E-2</v>
       </c>
       <c r="M102" s="2">
-        <f>RATE(10,,K92,-'Real Returns 1792-2025'!$K102)</f>
+        <f>RATE(10,,K92,-'Real Returns 1792-2026'!$K102)</f>
         <v>6.2955751431864257E-2</v>
       </c>
       <c r="N102" s="2">
-        <f>RATE(30,,J72,-'Real Returns 1792-2025'!$J102)</f>
+        <f>RATE(30,,J72,-'Real Returns 1792-2026'!$J102)</f>
         <v>8.928857461134701E-2</v>
       </c>
       <c r="O102" s="2">
-        <f>RATE(30,,K72,-'Real Returns 1792-2025'!$K102)</f>
+        <f>RATE(30,,K72,-'Real Returns 1792-2026'!$K102)</f>
         <v>7.1443566293546146E-2</v>
       </c>
       <c r="P102" s="2">
-        <f>RATE(50,,J52,-'Real Returns 1792-2025'!$J102)</f>
+        <f>RATE(50,,J52,-'Real Returns 1792-2026'!$J102)</f>
         <v>7.0435294279623598E-2</v>
       </c>
       <c r="Q102" s="2">
-        <f>RATE(50,,K52,-'Real Returns 1792-2025'!$K102)</f>
+        <f>RATE(50,,K52,-'Real Returns 1792-2026'!$K102)</f>
         <v>7.2862651917032867E-2</v>
       </c>
       <c r="R102" s="2"/>
@@ -8872,35 +8872,35 @@
         <v>345.69285447145057</v>
       </c>
       <c r="L103" s="2">
-        <f>RATE(10,,J93,-'Real Returns 1792-2025'!$J103)</f>
+        <f>RATE(10,,J93,-'Real Returns 1792-2026'!$J103)</f>
         <v>4.5652017079692277E-2</v>
       </c>
       <c r="M103" s="2">
-        <f>RATE(10,,K93,-'Real Returns 1792-2025'!$K103)</f>
+        <f>RATE(10,,K93,-'Real Returns 1792-2026'!$K103)</f>
         <v>6.1882716268616453E-2</v>
       </c>
       <c r="N103" s="2">
-        <f>RATE(30,,J73,-'Real Returns 1792-2025'!$J103)</f>
+        <f>RATE(30,,J73,-'Real Returns 1792-2026'!$J103)</f>
         <v>7.8583051997719144E-2</v>
       </c>
       <c r="O103" s="2">
-        <f>RATE(30,,K73,-'Real Returns 1792-2025'!$K103)</f>
+        <f>RATE(30,,K73,-'Real Returns 1792-2026'!$K103)</f>
         <v>7.3106905994691704E-2</v>
       </c>
       <c r="P103" s="2">
-        <f>RATE(50,,J53,-'Real Returns 1792-2025'!$J103)</f>
+        <f>RATE(50,,J53,-'Real Returns 1792-2026'!$J103)</f>
         <v>7.1110052799302742E-2</v>
       </c>
       <c r="Q103" s="2">
-        <f>RATE(50,,K53,-'Real Returns 1792-2025'!$K103)</f>
+        <f>RATE(50,,K53,-'Real Returns 1792-2026'!$K103)</f>
         <v>7.3672054611964258E-2</v>
       </c>
       <c r="R103" s="2">
-        <f>RATE(100,,J3,-'Real Returns 1792-2025'!$J103)</f>
+        <f>RATE(100,,J3,-'Real Returns 1792-2026'!$J103)</f>
         <v>5.6639753767827455E-2</v>
       </c>
       <c r="S103" s="2">
-        <f>RATE(100,,K3,-'Real Returns 1792-2025'!$K103)</f>
+        <f>RATE(100,,K3,-'Real Returns 1792-2026'!$K103)</f>
         <v>6.0197813019783962E-2</v>
       </c>
     </row>
@@ -8937,35 +8937,35 @@
         <v>372.32918129575671</v>
       </c>
       <c r="L104" s="2">
-        <f>RATE(10,,J94,-'Real Returns 1792-2025'!$J104)</f>
+        <f>RATE(10,,J94,-'Real Returns 1792-2026'!$J104)</f>
         <v>3.4444530518967564E-2</v>
       </c>
       <c r="M104" s="2">
-        <f>RATE(10,,K94,-'Real Returns 1792-2025'!$K104)</f>
+        <f>RATE(10,,K94,-'Real Returns 1792-2026'!$K104)</f>
         <v>6.1117869353662133E-2</v>
       </c>
       <c r="N104" s="2">
-        <f>RATE(30,,J74,-'Real Returns 1792-2025'!$J104)</f>
+        <f>RATE(30,,J74,-'Real Returns 1792-2026'!$J104)</f>
         <v>7.1717102986085648E-2</v>
       </c>
       <c r="O104" s="2">
-        <f>RATE(30,,K74,-'Real Returns 1792-2025'!$K104)</f>
+        <f>RATE(30,,K74,-'Real Returns 1792-2026'!$K104)</f>
         <v>8.1031033979183972E-2</v>
       </c>
       <c r="P104" s="2">
-        <f>RATE(50,,J54,-'Real Returns 1792-2025'!$J104)</f>
+        <f>RATE(50,,J54,-'Real Returns 1792-2026'!$J104)</f>
         <v>5.9509608088036063E-2</v>
       </c>
       <c r="Q104" s="2">
-        <f>RATE(50,,K54,-'Real Returns 1792-2025'!$K104)</f>
+        <f>RATE(50,,K54,-'Real Returns 1792-2026'!$K104)</f>
         <v>6.5654630960200189E-2</v>
       </c>
       <c r="R104" s="2">
-        <f>RATE(100,,J4,-'Real Returns 1792-2025'!$J104)</f>
+        <f>RATE(100,,J4,-'Real Returns 1792-2026'!$J104)</f>
         <v>5.6356028236600901E-2</v>
       </c>
       <c r="S104" s="2">
-        <f>RATE(100,,K4,-'Real Returns 1792-2025'!$K104)</f>
+        <f>RATE(100,,K4,-'Real Returns 1792-2026'!$K104)</f>
         <v>6.2527506823521289E-2</v>
       </c>
     </row>
@@ -9002,35 +9002,35 @@
         <v>410.35427547013256</v>
       </c>
       <c r="L105" s="2">
-        <f>RATE(10,,J95,-'Real Returns 1792-2025'!$J105)</f>
+        <f>RATE(10,,J95,-'Real Returns 1792-2026'!$J105)</f>
         <v>5.3973383244579634E-2</v>
       </c>
       <c r="M105" s="2">
-        <f>RATE(10,,K95,-'Real Returns 1792-2025'!$K105)</f>
+        <f>RATE(10,,K95,-'Real Returns 1792-2026'!$K105)</f>
         <v>6.4372767335701228E-2</v>
       </c>
       <c r="N105" s="2">
-        <f>RATE(30,,J75,-'Real Returns 1792-2025'!$J105)</f>
+        <f>RATE(30,,J75,-'Real Returns 1792-2026'!$J105)</f>
         <v>7.6324942592949599E-2</v>
       </c>
       <c r="O105" s="2">
-        <f>RATE(30,,K75,-'Real Returns 1792-2025'!$K105)</f>
+        <f>RATE(30,,K75,-'Real Returns 1792-2026'!$K105)</f>
         <v>8.6661743618241749E-2</v>
       </c>
       <c r="P105" s="2">
-        <f>RATE(50,,J55,-'Real Returns 1792-2025'!$J105)</f>
+        <f>RATE(50,,J55,-'Real Returns 1792-2026'!$J105)</f>
         <v>5.9036567872509049E-2</v>
       </c>
       <c r="Q105" s="2">
-        <f>RATE(50,,K55,-'Real Returns 1792-2025'!$K105)</f>
+        <f>RATE(50,,K55,-'Real Returns 1792-2026'!$K105)</f>
         <v>6.6627261772746429E-2</v>
       </c>
       <c r="R105" s="2">
-        <f>RATE(100,,J5,-'Real Returns 1792-2025'!$J105)</f>
+        <f>RATE(100,,J5,-'Real Returns 1792-2026'!$J105)</f>
         <v>5.6355718530149937E-2</v>
       </c>
       <c r="S105" s="2">
-        <f>RATE(100,,K5,-'Real Returns 1792-2025'!$K105)</f>
+        <f>RATE(100,,K5,-'Real Returns 1792-2026'!$K105)</f>
         <v>6.3321832443356429E-2</v>
       </c>
     </row>
@@ -9067,35 +9067,35 @@
         <v>429.45859839790779</v>
       </c>
       <c r="L106" s="2">
-        <f>RATE(10,,J96,-'Real Returns 1792-2025'!$J106)</f>
+        <f>RATE(10,,J96,-'Real Returns 1792-2026'!$J106)</f>
         <v>3.2388865908097052E-2</v>
       </c>
       <c r="M106" s="2">
-        <f>RATE(10,,K96,-'Real Returns 1792-2025'!$K106)</f>
+        <f>RATE(10,,K96,-'Real Returns 1792-2026'!$K106)</f>
         <v>5.940225585193764E-2</v>
       </c>
       <c r="N106" s="2">
-        <f>RATE(30,,J76,-'Real Returns 1792-2025'!$J106)</f>
+        <f>RATE(30,,J76,-'Real Returns 1792-2026'!$J106)</f>
         <v>7.7310986843328058E-2</v>
       </c>
       <c r="O106" s="2">
-        <f>RATE(30,,K76,-'Real Returns 1792-2025'!$K106)</f>
+        <f>RATE(30,,K76,-'Real Returns 1792-2026'!$K106)</f>
         <v>8.7917715231416893E-2</v>
       </c>
       <c r="P106" s="2">
-        <f>RATE(50,,J56,-'Real Returns 1792-2025'!$J106)</f>
+        <f>RATE(50,,J56,-'Real Returns 1792-2026'!$J106)</f>
         <v>5.9347666003660884E-2</v>
       </c>
       <c r="Q106" s="2">
-        <f>RATE(50,,K56,-'Real Returns 1792-2025'!$K106)</f>
+        <f>RATE(50,,K56,-'Real Returns 1792-2026'!$K106)</f>
         <v>6.742901028560519E-2</v>
       </c>
       <c r="R106" s="2">
-        <f>RATE(100,,J6,-'Real Returns 1792-2025'!$J106)</f>
+        <f>RATE(100,,J6,-'Real Returns 1792-2026'!$J106)</f>
         <v>5.6998490969885122E-2</v>
       </c>
       <c r="S106" s="2">
-        <f>RATE(100,,K6,-'Real Returns 1792-2025'!$K106)</f>
+        <f>RATE(100,,K6,-'Real Returns 1792-2026'!$K106)</f>
         <v>6.4883221620585657E-2</v>
       </c>
     </row>
@@ -9132,35 +9132,35 @@
         <v>457.69951874809306</v>
       </c>
       <c r="L107" s="2">
-        <f>RATE(10,,J97,-'Real Returns 1792-2025'!$J107)</f>
+        <f>RATE(10,,J97,-'Real Returns 1792-2026'!$J107)</f>
         <v>2.2920778520154797E-2</v>
       </c>
       <c r="M107" s="2">
-        <f>RATE(10,,K97,-'Real Returns 1792-2025'!$K107)</f>
+        <f>RATE(10,,K97,-'Real Returns 1792-2026'!$K107)</f>
         <v>6.0343766998690679E-2</v>
       </c>
       <c r="N107" s="2">
-        <f>RATE(30,,J77,-'Real Returns 1792-2025'!$J107)</f>
+        <f>RATE(30,,J77,-'Real Returns 1792-2026'!$J107)</f>
         <v>7.4072864640880073E-2</v>
       </c>
       <c r="O107" s="2">
-        <f>RATE(30,,K77,-'Real Returns 1792-2025'!$K107)</f>
+        <f>RATE(30,,K77,-'Real Returns 1792-2026'!$K107)</f>
         <v>8.5043512219382916E-2</v>
       </c>
       <c r="P107" s="2">
-        <f>RATE(50,,J57,-'Real Returns 1792-2025'!$J107)</f>
+        <f>RATE(50,,J57,-'Real Returns 1792-2026'!$J107)</f>
         <v>5.9559286160334707E-2</v>
       </c>
       <c r="Q107" s="2">
-        <f>RATE(50,,K57,-'Real Returns 1792-2025'!$K107)</f>
+        <f>RATE(50,,K57,-'Real Returns 1792-2026'!$K107)</f>
         <v>6.8011786884810049E-2</v>
       </c>
       <c r="R107" s="2">
-        <f>RATE(100,,J7,-'Real Returns 1792-2025'!$J107)</f>
+        <f>RATE(100,,J7,-'Real Returns 1792-2026'!$J107)</f>
         <v>5.7563430108215762E-2</v>
       </c>
       <c r="S107" s="2">
-        <f>RATE(100,,K7,-'Real Returns 1792-2025'!$K107)</f>
+        <f>RATE(100,,K7,-'Real Returns 1792-2026'!$K107)</f>
         <v>6.6300153673099091E-2</v>
       </c>
     </row>
@@ -9197,35 +9197,35 @@
         <v>511.05788654097267</v>
       </c>
       <c r="L108" s="2">
-        <f>RATE(10,,J98,-'Real Returns 1792-2025'!$J108)</f>
+        <f>RATE(10,,J98,-'Real Returns 1792-2026'!$J108)</f>
         <v>4.5486449607782573E-2</v>
       </c>
       <c r="M108" s="2">
-        <f>RATE(10,,K98,-'Real Returns 1792-2025'!$K108)</f>
+        <f>RATE(10,,K98,-'Real Returns 1792-2026'!$K108)</f>
         <v>6.8486676319193557E-2</v>
       </c>
       <c r="N108" s="2">
-        <f>RATE(30,,J78,-'Real Returns 1792-2025'!$J108)</f>
+        <f>RATE(30,,J78,-'Real Returns 1792-2026'!$J108)</f>
         <v>7.5174374558268822E-2</v>
       </c>
       <c r="O108" s="2">
-        <f>RATE(30,,K78,-'Real Returns 1792-2025'!$K108)</f>
+        <f>RATE(30,,K78,-'Real Returns 1792-2026'!$K108)</f>
         <v>8.405981385515808E-2</v>
       </c>
       <c r="P108" s="2">
-        <f>RATE(50,,J58,-'Real Returns 1792-2025'!$J108)</f>
+        <f>RATE(50,,J58,-'Real Returns 1792-2026'!$J108)</f>
         <v>6.2841852949780216E-2</v>
       </c>
       <c r="Q108" s="2">
-        <f>RATE(50,,K58,-'Real Returns 1792-2025'!$K108)</f>
+        <f>RATE(50,,K58,-'Real Returns 1792-2026'!$K108)</f>
         <v>7.0006908091833089E-2</v>
       </c>
       <c r="R108" s="2">
-        <f>RATE(100,,J8,-'Real Returns 1792-2025'!$J108)</f>
+        <f>RATE(100,,J8,-'Real Returns 1792-2026'!$J108)</f>
         <v>5.7877515703662279E-2</v>
       </c>
       <c r="S108" s="2">
-        <f>RATE(100,,K8,-'Real Returns 1792-2025'!$K108)</f>
+        <f>RATE(100,,K8,-'Real Returns 1792-2026'!$K108)</f>
         <v>6.5559025795366349E-2</v>
       </c>
     </row>
@@ -9262,35 +9262,35 @@
         <v>568.7155613691981</v>
       </c>
       <c r="L109" s="2">
-        <f>RATE(10,,J99,-'Real Returns 1792-2025'!$J109)</f>
+        <f>RATE(10,,J99,-'Real Returns 1792-2026'!$J109)</f>
         <v>6.9362647606215203E-2</v>
       </c>
       <c r="M109" s="2">
-        <f>RATE(10,,K99,-'Real Returns 1792-2025'!$K109)</f>
+        <f>RATE(10,,K99,-'Real Returns 1792-2026'!$K109)</f>
         <v>7.1300590736842237E-2</v>
       </c>
       <c r="N109" s="2">
-        <f>RATE(30,,J79,-'Real Returns 1792-2025'!$J109)</f>
+        <f>RATE(30,,J79,-'Real Returns 1792-2026'!$J109)</f>
         <v>7.5949803468243593E-2</v>
       </c>
       <c r="O109" s="2">
-        <f>RATE(30,,K79,-'Real Returns 1792-2025'!$K109)</f>
+        <f>RATE(30,,K79,-'Real Returns 1792-2026'!$K109)</f>
         <v>8.4188648659970527E-2</v>
       </c>
       <c r="P109" s="2">
-        <f>RATE(50,,J59,-'Real Returns 1792-2025'!$J109)</f>
+        <f>RATE(50,,J59,-'Real Returns 1792-2026'!$J109)</f>
         <v>6.769636151207005E-2</v>
       </c>
       <c r="Q109" s="2">
-        <f>RATE(50,,K59,-'Real Returns 1792-2025'!$K109)</f>
+        <f>RATE(50,,K59,-'Real Returns 1792-2026'!$K109)</f>
         <v>6.7377337593776065E-2</v>
       </c>
       <c r="R109" s="2">
-        <f>RATE(100,,J9,-'Real Returns 1792-2025'!$J109)</f>
+        <f>RATE(100,,J9,-'Real Returns 1792-2026'!$J109)</f>
         <v>5.9595041199178134E-2</v>
       </c>
       <c r="S109" s="2">
-        <f>RATE(100,,K9,-'Real Returns 1792-2025'!$K109)</f>
+        <f>RATE(100,,K9,-'Real Returns 1792-2026'!$K109)</f>
         <v>6.6178160885935755E-2</v>
       </c>
     </row>
@@ -9327,35 +9327,35 @@
         <v>581.65918380592655</v>
       </c>
       <c r="L110" s="2">
-        <f>RATE(10,,J100,-'Real Returns 1792-2025'!$J110)</f>
+        <f>RATE(10,,J100,-'Real Returns 1792-2026'!$J110)</f>
         <v>6.2369160594815377E-2</v>
       </c>
       <c r="M110" s="2">
-        <f>RATE(10,,K100,-'Real Returns 1792-2025'!$K110)</f>
+        <f>RATE(10,,K100,-'Real Returns 1792-2026'!$K110)</f>
         <v>6.6687463553874546E-2</v>
       </c>
       <c r="N110" s="2">
-        <f>RATE(30,,J80,-'Real Returns 1792-2025'!$J110)</f>
+        <f>RATE(30,,J80,-'Real Returns 1792-2026'!$J110)</f>
         <v>7.4779881845885729E-2</v>
       </c>
       <c r="O110" s="2">
-        <f>RATE(30,,K80,-'Real Returns 1792-2025'!$K110)</f>
+        <f>RATE(30,,K80,-'Real Returns 1792-2026'!$K110)</f>
         <v>8.0810410004821823E-2</v>
       </c>
       <c r="P110" s="2">
-        <f>RATE(50,,J60,-'Real Returns 1792-2025'!$J110)</f>
+        <f>RATE(50,,J60,-'Real Returns 1792-2026'!$J110)</f>
         <v>6.7670529698049084E-2</v>
       </c>
       <c r="Q110" s="2">
-        <f>RATE(50,,K60,-'Real Returns 1792-2025'!$K110)</f>
+        <f>RATE(50,,K60,-'Real Returns 1792-2026'!$K110)</f>
         <v>6.4890553042773899E-2</v>
       </c>
       <c r="R110" s="2">
-        <f>RATE(100,,J10,-'Real Returns 1792-2025'!$J110)</f>
+        <f>RATE(100,,J10,-'Real Returns 1792-2026'!$J110)</f>
         <v>5.9433829112401262E-2</v>
       </c>
       <c r="S110" s="2">
-        <f>RATE(100,,K10,-'Real Returns 1792-2025'!$K110)</f>
+        <f>RATE(100,,K10,-'Real Returns 1792-2026'!$K110)</f>
         <v>6.5946859127846147E-2</v>
       </c>
     </row>
@@ -9392,35 +9392,35 @@
         <v>617.90635966293451</v>
       </c>
       <c r="L111" s="2">
-        <f>RATE(10,,J101,-'Real Returns 1792-2025'!$J111)</f>
+        <f>RATE(10,,J101,-'Real Returns 1792-2026'!$J111)</f>
         <v>8.6434430250589112E-2</v>
       </c>
       <c r="M111" s="2">
-        <f>RATE(10,,K101,-'Real Returns 1792-2025'!$K111)</f>
+        <f>RATE(10,,K101,-'Real Returns 1792-2026'!$K111)</f>
         <v>7.0426726122944996E-2</v>
       </c>
       <c r="N111" s="2">
-        <f>RATE(30,,J81,-'Real Returns 1792-2025'!$J111)</f>
+        <f>RATE(30,,J81,-'Real Returns 1792-2026'!$J111)</f>
         <v>7.8692897354090019E-2</v>
       </c>
       <c r="O111" s="2">
-        <f>RATE(30,,K81,-'Real Returns 1792-2025'!$K111)</f>
+        <f>RATE(30,,K81,-'Real Returns 1792-2026'!$K111)</f>
         <v>7.8819683326648002E-2</v>
       </c>
       <c r="P111" s="2">
-        <f>RATE(50,,J61,-'Real Returns 1792-2025'!$J111)</f>
+        <f>RATE(50,,J61,-'Real Returns 1792-2026'!$J111)</f>
         <v>6.717714634342474E-2</v>
       </c>
       <c r="Q111" s="2">
-        <f>RATE(50,,K61,-'Real Returns 1792-2025'!$K111)</f>
+        <f>RATE(50,,K61,-'Real Returns 1792-2026'!$K111)</f>
         <v>6.3956847275838044E-2</v>
       </c>
       <c r="R111" s="2">
-        <f>RATE(100,,J11,-'Real Returns 1792-2025'!$J111)</f>
+        <f>RATE(100,,J11,-'Real Returns 1792-2026'!$J111)</f>
         <v>6.0119141715643559E-2</v>
       </c>
       <c r="S111" s="2">
-        <f>RATE(100,,K11,-'Real Returns 1792-2025'!$K111)</f>
+        <f>RATE(100,,K11,-'Real Returns 1792-2026'!$K111)</f>
         <v>6.4937338985678883E-2</v>
       </c>
     </row>
@@ -9457,35 +9457,35 @@
         <v>642.74721744656267</v>
       </c>
       <c r="L112" s="2">
-        <f>RATE(10,,J102,-'Real Returns 1792-2025'!$J112)</f>
+        <f>RATE(10,,J102,-'Real Returns 1792-2026'!$J112)</f>
         <v>8.7860663494553182E-2</v>
       </c>
       <c r="M112" s="2">
-        <f>RATE(10,,K102,-'Real Returns 1792-2025'!$K112)</f>
+        <f>RATE(10,,K102,-'Real Returns 1792-2026'!$K112)</f>
         <v>6.9074678642102788E-2</v>
       </c>
       <c r="N112" s="2">
-        <f>RATE(30,,J82,-'Real Returns 1792-2025'!$J112)</f>
+        <f>RATE(30,,J82,-'Real Returns 1792-2026'!$J112)</f>
         <v>7.7869941884528157E-2</v>
       </c>
       <c r="O112" s="2">
-        <f>RATE(30,,K82,-'Real Returns 1792-2025'!$K112)</f>
+        <f>RATE(30,,K82,-'Real Returns 1792-2026'!$K112)</f>
         <v>7.6172964310167596E-2</v>
       </c>
       <c r="P112" s="2">
-        <f>RATE(50,,J62,-'Real Returns 1792-2025'!$J112)</f>
+        <f>RATE(50,,J62,-'Real Returns 1792-2026'!$J112)</f>
         <v>7.1332740579653373E-2</v>
       </c>
       <c r="Q112" s="2">
-        <f>RATE(50,,K62,-'Real Returns 1792-2025'!$K112)</f>
+        <f>RATE(50,,K62,-'Real Returns 1792-2026'!$K112)</f>
         <v>6.3860339401155028E-2</v>
       </c>
       <c r="R112" s="2">
-        <f>RATE(100,,J12,-'Real Returns 1792-2025'!$J112)</f>
+        <f>RATE(100,,J12,-'Real Returns 1792-2026'!$J112)</f>
         <v>5.9739163092796414E-2</v>
       </c>
       <c r="S112" s="2">
-        <f>RATE(100,,K12,-'Real Returns 1792-2025'!$K112)</f>
+        <f>RATE(100,,K12,-'Real Returns 1792-2026'!$K112)</f>
         <v>6.306685183243628E-2</v>
       </c>
     </row>
@@ -9522,35 +9522,35 @@
         <v>644.34826724269487</v>
       </c>
       <c r="L113" s="2">
-        <f>RATE(10,,J103,-'Real Returns 1792-2025'!$J113)</f>
+        <f>RATE(10,,J103,-'Real Returns 1792-2026'!$J113)</f>
         <v>8.840241520159503E-2</v>
       </c>
       <c r="M113" s="2">
-        <f>RATE(10,,K103,-'Real Returns 1792-2025'!$K113)</f>
+        <f>RATE(10,,K103,-'Real Returns 1792-2026'!$K113)</f>
         <v>6.4248449745988326E-2</v>
       </c>
       <c r="N113" s="2">
-        <f>RATE(30,,J83,-'Real Returns 1792-2025'!$J113)</f>
+        <f>RATE(30,,J83,-'Real Returns 1792-2026'!$J113)</f>
         <v>7.4491393042409731E-2</v>
       </c>
       <c r="O113" s="2">
-        <f>RATE(30,,K83,-'Real Returns 1792-2025'!$K113)</f>
+        <f>RATE(30,,K83,-'Real Returns 1792-2026'!$K113)</f>
         <v>7.3608974494407634E-2</v>
       </c>
       <c r="P113" s="2">
-        <f>RATE(50,,J63,-'Real Returns 1792-2025'!$J113)</f>
+        <f>RATE(50,,J63,-'Real Returns 1792-2026'!$J113)</f>
         <v>6.8941224673356796E-2</v>
       </c>
       <c r="Q113" s="2">
-        <f>RATE(50,,K63,-'Real Returns 1792-2025'!$K113)</f>
+        <f>RATE(50,,K63,-'Real Returns 1792-2026'!$K113)</f>
         <v>6.1731753000503604E-2</v>
       </c>
       <c r="R113" s="2">
-        <f>RATE(100,,J13,-'Real Returns 1792-2025'!$J113)</f>
+        <f>RATE(100,,J13,-'Real Returns 1792-2026'!$J113)</f>
         <v>5.8334372013165908E-2</v>
       </c>
       <c r="S113" s="2">
-        <f>RATE(100,,K13,-'Real Returns 1792-2025'!$K113)</f>
+        <f>RATE(100,,K13,-'Real Returns 1792-2026'!$K113)</f>
         <v>6.1863040897263119E-2</v>
       </c>
     </row>
@@ -9587,35 +9587,35 @@
         <v>638.85311660226091</v>
       </c>
       <c r="L114" s="2">
-        <f>RATE(10,,J104,-'Real Returns 1792-2025'!$J114)</f>
+        <f>RATE(10,,J104,-'Real Returns 1792-2026'!$J114)</f>
         <v>8.5222171774658809E-2</v>
       </c>
       <c r="M114" s="2">
-        <f>RATE(10,,K104,-'Real Returns 1792-2025'!$K114)</f>
+        <f>RATE(10,,K104,-'Real Returns 1792-2026'!$K114)</f>
         <v>5.5473646761227159E-2</v>
       </c>
       <c r="N114" s="2">
-        <f>RATE(30,,J84,-'Real Returns 1792-2025'!$J114)</f>
+        <f>RATE(30,,J84,-'Real Returns 1792-2026'!$J114)</f>
         <v>6.7800007851110414E-2</v>
       </c>
       <c r="O114" s="2">
-        <f>RATE(30,,K84,-'Real Returns 1792-2025'!$K114)</f>
+        <f>RATE(30,,K84,-'Real Returns 1792-2026'!$K114)</f>
         <v>6.9652307297565302E-2</v>
       </c>
       <c r="P114" s="2">
-        <f>RATE(50,,J64,-'Real Returns 1792-2025'!$J114)</f>
+        <f>RATE(50,,J64,-'Real Returns 1792-2026'!$J114)</f>
         <v>6.759641681306526E-2</v>
       </c>
       <c r="Q114" s="2">
-        <f>RATE(50,,K64,-'Real Returns 1792-2025'!$K114)</f>
+        <f>RATE(50,,K64,-'Real Returns 1792-2026'!$K114)</f>
         <v>6.1619356997977784E-2</v>
       </c>
       <c r="R114" s="2">
-        <f>RATE(100,,J14,-'Real Returns 1792-2025'!$J114)</f>
+        <f>RATE(100,,J14,-'Real Returns 1792-2026'!$J114)</f>
         <v>5.6219620353156252E-2</v>
       </c>
       <c r="S114" s="2">
-        <f>RATE(100,,K14,-'Real Returns 1792-2025'!$K114)</f>
+        <f>RATE(100,,K14,-'Real Returns 1792-2026'!$K114)</f>
         <v>6.2005980749594888E-2</v>
       </c>
     </row>
@@ -9652,35 +9652,35 @@
         <v>716.02929281031106</v>
       </c>
       <c r="L115" s="2">
-        <f>RATE(10,,J105,-'Real Returns 1792-2025'!$J115)</f>
+        <f>RATE(10,,J105,-'Real Returns 1792-2026'!$J115)</f>
         <v>0.10863375333784353</v>
       </c>
       <c r="M115" s="2">
-        <f>RATE(10,,K105,-'Real Returns 1792-2025'!$K115)</f>
+        <f>RATE(10,,K105,-'Real Returns 1792-2026'!$K115)</f>
         <v>5.7248755729802321E-2</v>
       </c>
       <c r="N115" s="2">
-        <f>RATE(30,,J85,-'Real Returns 1792-2025'!$J115)</f>
+        <f>RATE(30,,J85,-'Real Returns 1792-2026'!$J115)</f>
         <v>7.4642609958500195E-2</v>
       </c>
       <c r="O115" s="2">
-        <f>RATE(30,,K85,-'Real Returns 1792-2025'!$K115)</f>
+        <f>RATE(30,,K85,-'Real Returns 1792-2026'!$K115)</f>
         <v>6.872945322329134E-2</v>
       </c>
       <c r="P115" s="2">
-        <f>RATE(50,,J65,-'Real Returns 1792-2025'!$J115)</f>
+        <f>RATE(50,,J65,-'Real Returns 1792-2026'!$J115)</f>
         <v>7.7227712844162841E-2</v>
       </c>
       <c r="Q115" s="2">
-        <f>RATE(50,,K65,-'Real Returns 1792-2025'!$K115)</f>
+        <f>RATE(50,,K65,-'Real Returns 1792-2026'!$K115)</f>
         <v>6.5560394865960672E-2</v>
       </c>
       <c r="R115" s="2">
-        <f>RATE(100,,J15,-'Real Returns 1792-2025'!$J115)</f>
+        <f>RATE(100,,J15,-'Real Returns 1792-2026'!$J115)</f>
         <v>5.9273070525719701E-2</v>
       </c>
       <c r="S115" s="2">
-        <f>RATE(100,,K15,-'Real Returns 1792-2025'!$K115)</f>
+        <f>RATE(100,,K15,-'Real Returns 1792-2026'!$K115)</f>
         <v>6.3299331429277572E-2</v>
       </c>
     </row>
@@ -9717,35 +9717,35 @@
         <v>741.06878883565548</v>
       </c>
       <c r="L116" s="2">
-        <f>RATE(10,,J106,-'Real Returns 1792-2025'!$J116)</f>
+        <f>RATE(10,,J106,-'Real Returns 1792-2026'!$J116)</f>
         <v>0.12281043072665071</v>
       </c>
       <c r="M116" s="2">
-        <f>RATE(10,,K106,-'Real Returns 1792-2025'!$K116)</f>
+        <f>RATE(10,,K106,-'Real Returns 1792-2026'!$K116)</f>
         <v>5.6072471404143592E-2</v>
       </c>
       <c r="N116" s="2">
-        <f>RATE(30,,J86,-'Real Returns 1792-2025'!$J116)</f>
+        <f>RATE(30,,J86,-'Real Returns 1792-2026'!$J116)</f>
         <v>7.8345941634293731E-2</v>
       </c>
       <c r="O116" s="2">
-        <f>RATE(30,,K86,-'Real Returns 1792-2025'!$K116)</f>
+        <f>RATE(30,,K86,-'Real Returns 1792-2026'!$K116)</f>
         <v>6.5513428269634189E-2</v>
       </c>
       <c r="P116" s="2">
-        <f>RATE(50,,J66,-'Real Returns 1792-2025'!$J116)</f>
+        <f>RATE(50,,J66,-'Real Returns 1792-2026'!$J116)</f>
         <v>8.1843077537304132E-2</v>
       </c>
       <c r="Q116" s="2">
-        <f>RATE(50,,K66,-'Real Returns 1792-2025'!$K116)</f>
+        <f>RATE(50,,K66,-'Real Returns 1792-2026'!$K116)</f>
         <v>6.4539341741223458E-2</v>
       </c>
       <c r="R116" s="2">
-        <f>RATE(100,,J16,-'Real Returns 1792-2025'!$J116)</f>
+        <f>RATE(100,,J16,-'Real Returns 1792-2026'!$J116)</f>
         <v>6.1455601498700864E-2</v>
       </c>
       <c r="S116" s="2">
-        <f>RATE(100,,K16,-'Real Returns 1792-2025'!$K116)</f>
+        <f>RATE(100,,K16,-'Real Returns 1792-2026'!$K116)</f>
         <v>6.3224073702236927E-2</v>
       </c>
     </row>
@@ -9782,35 +9782,35 @@
         <v>721.37931387328615</v>
       </c>
       <c r="L117" s="2">
-        <f>RATE(10,,J107,-'Real Returns 1792-2025'!$J117)</f>
+        <f>RATE(10,,J107,-'Real Returns 1792-2026'!$J117)</f>
         <v>0.11850979945698994</v>
       </c>
       <c r="M117" s="2">
-        <f>RATE(10,,K107,-'Real Returns 1792-2025'!$K117)</f>
+        <f>RATE(10,,K107,-'Real Returns 1792-2026'!$K117)</f>
         <v>4.6546001785758274E-2</v>
       </c>
       <c r="N117" s="2">
-        <f>RATE(30,,J87,-'Real Returns 1792-2025'!$J117)</f>
+        <f>RATE(30,,J87,-'Real Returns 1792-2026'!$J117)</f>
         <v>8.094459443606393E-2</v>
       </c>
       <c r="O117" s="2">
-        <f>RATE(30,,K87,-'Real Returns 1792-2025'!$K117)</f>
+        <f>RATE(30,,K87,-'Real Returns 1792-2026'!$K117)</f>
         <v>6.1851452811802231E-2</v>
       </c>
       <c r="P117" s="2">
-        <f>RATE(50,,J67,-'Real Returns 1792-2025'!$J117)</f>
+        <f>RATE(50,,J67,-'Real Returns 1792-2026'!$J117)</f>
         <v>7.8561449671365052E-2</v>
       </c>
       <c r="Q117" s="2">
-        <f>RATE(50,,K67,-'Real Returns 1792-2025'!$K117)</f>
+        <f>RATE(50,,K67,-'Real Returns 1792-2026'!$K117)</f>
         <v>6.2434909066788287E-2</v>
       </c>
       <c r="R117" s="2">
-        <f>RATE(100,,J17,-'Real Returns 1792-2025'!$J117)</f>
+        <f>RATE(100,,J17,-'Real Returns 1792-2026'!$J117)</f>
         <v>6.0024557764325678E-2</v>
       </c>
       <c r="S117" s="2">
-        <f>RATE(100,,K17,-'Real Returns 1792-2025'!$K117)</f>
+        <f>RATE(100,,K17,-'Real Returns 1792-2026'!$K117)</f>
         <v>6.1716671819109017E-2</v>
       </c>
     </row>
@@ -9847,35 +9847,35 @@
         <v>685.40497183152138</v>
       </c>
       <c r="L118" s="2">
-        <f>RATE(10,,J108,-'Real Returns 1792-2025'!$J118)</f>
+        <f>RATE(10,,J108,-'Real Returns 1792-2026'!$J118)</f>
         <v>6.5873671081801269E-2</v>
       </c>
       <c r="M118" s="2">
-        <f>RATE(10,,K108,-'Real Returns 1792-2025'!$K118)</f>
+        <f>RATE(10,,K108,-'Real Returns 1792-2026'!$K118)</f>
         <v>2.9787736425747089E-2</v>
       </c>
       <c r="N118" s="2">
-        <f>RATE(30,,J88,-'Real Returns 1792-2025'!$J118)</f>
+        <f>RATE(30,,J88,-'Real Returns 1792-2026'!$J118)</f>
         <v>6.9511404997285989E-2</v>
       </c>
       <c r="O118" s="2">
-        <f>RATE(30,,K88,-'Real Returns 1792-2025'!$K118)</f>
+        <f>RATE(30,,K88,-'Real Returns 1792-2026'!$K118)</f>
         <v>5.7256816530479954E-2</v>
       </c>
       <c r="P118" s="2">
-        <f>RATE(50,,J68,-'Real Returns 1792-2025'!$J118)</f>
+        <f>RATE(50,,J68,-'Real Returns 1792-2026'!$J118)</f>
         <v>7.5172963366416823E-2</v>
       </c>
       <c r="Q118" s="2">
-        <f>RATE(50,,K68,-'Real Returns 1792-2025'!$K118)</f>
+        <f>RATE(50,,K68,-'Real Returns 1792-2026'!$K118)</f>
         <v>6.0201486537413321E-2</v>
       </c>
       <c r="R118" s="2">
-        <f>RATE(100,,J18,-'Real Returns 1792-2025'!$J118)</f>
+        <f>RATE(100,,J18,-'Real Returns 1792-2026'!$J118)</f>
         <v>5.7040780288706315E-2</v>
       </c>
       <c r="S118" s="2">
-        <f>RATE(100,,K18,-'Real Returns 1792-2025'!$K118)</f>
+        <f>RATE(100,,K18,-'Real Returns 1792-2026'!$K118)</f>
         <v>6.0830573285276177E-2</v>
       </c>
     </row>
@@ -9912,35 +9912,35 @@
         <v>782.51683936568077</v>
       </c>
       <c r="L119" s="2">
-        <f>RATE(10,,J109,-'Real Returns 1792-2025'!$J119)</f>
+        <f>RATE(10,,J109,-'Real Returns 1792-2026'!$J119)</f>
         <v>7.5086451140691304E-2</v>
       </c>
       <c r="M119" s="2">
-        <f>RATE(10,,K109,-'Real Returns 1792-2025'!$K119)</f>
+        <f>RATE(10,,K109,-'Real Returns 1792-2026'!$K119)</f>
         <v>3.2428198999799741E-2</v>
       </c>
       <c r="N119" s="2">
-        <f>RATE(30,,J89,-'Real Returns 1792-2025'!$J119)</f>
+        <f>RATE(30,,J89,-'Real Returns 1792-2026'!$J119)</f>
         <v>7.611771490382431E-2</v>
       </c>
       <c r="O119" s="2">
-        <f>RATE(30,,K89,-'Real Returns 1792-2025'!$K119)</f>
+        <f>RATE(30,,K89,-'Real Returns 1792-2026'!$K119)</f>
         <v>5.8485004541076309E-2</v>
       </c>
       <c r="P119" s="2">
-        <f>RATE(50,,J69,-'Real Returns 1792-2025'!$J119)</f>
+        <f>RATE(50,,J69,-'Real Returns 1792-2026'!$J119)</f>
         <v>7.9895474885960535E-2</v>
       </c>
       <c r="Q119" s="2">
-        <f>RATE(50,,K69,-'Real Returns 1792-2025'!$K119)</f>
+        <f>RATE(50,,K69,-'Real Returns 1792-2026'!$K119)</f>
         <v>6.0308872671957447E-2</v>
       </c>
       <c r="R119" s="2">
-        <f>RATE(100,,J19,-'Real Returns 1792-2025'!$J119)</f>
+        <f>RATE(100,,J19,-'Real Returns 1792-2026'!$J119)</f>
         <v>5.9578126170409806E-2</v>
       </c>
       <c r="S119" s="2">
-        <f>RATE(100,,K19,-'Real Returns 1792-2025'!$K119)</f>
+        <f>RATE(100,,K19,-'Real Returns 1792-2026'!$K119)</f>
         <v>6.1541039503276718E-2</v>
       </c>
     </row>
@@ -9977,35 +9977,35 @@
         <v>796.32777174704404</v>
       </c>
       <c r="L120" s="2">
-        <f>RATE(10,,J110,-'Real Returns 1792-2025'!$J120)</f>
+        <f>RATE(10,,J110,-'Real Returns 1792-2026'!$J120)</f>
         <v>8.6673934543889247E-2</v>
       </c>
       <c r="M120" s="2">
-        <f>RATE(10,,K110,-'Real Returns 1792-2025'!$K120)</f>
+        <f>RATE(10,,K110,-'Real Returns 1792-2026'!$K120)</f>
         <v>3.1911202560962457E-2</v>
       </c>
       <c r="N120" s="2">
-        <f>RATE(30,,J90,-'Real Returns 1792-2025'!$J120)</f>
+        <f>RATE(30,,J90,-'Real Returns 1792-2026'!$J120)</f>
         <v>6.8137970069672982E-2</v>
       </c>
       <c r="O120" s="2">
-        <f>RATE(30,,K90,-'Real Returns 1792-2025'!$K120)</f>
+        <f>RATE(30,,K90,-'Real Returns 1792-2026'!$K120)</f>
         <v>5.6644704087015711E-2</v>
       </c>
       <c r="P120" s="2">
-        <f>RATE(50,,J70,-'Real Returns 1792-2025'!$J120)</f>
+        <f>RATE(50,,J70,-'Real Returns 1792-2026'!$J120)</f>
         <v>8.2861155047535731E-2</v>
       </c>
       <c r="Q120" s="2">
-        <f>RATE(50,,K70,-'Real Returns 1792-2025'!$K120)</f>
+        <f>RATE(50,,K70,-'Real Returns 1792-2026'!$K120)</f>
         <v>5.9809613112936734E-2</v>
       </c>
       <c r="R120" s="2">
-        <f>RATE(100,,J20,-'Real Returns 1792-2025'!$J120)</f>
+        <f>RATE(100,,J20,-'Real Returns 1792-2026'!$J120)</f>
         <v>6.0194029045066828E-2</v>
       </c>
       <c r="S120" s="2">
-        <f>RATE(100,,K20,-'Real Returns 1792-2025'!$K120)</f>
+        <f>RATE(100,,K20,-'Real Returns 1792-2026'!$K120)</f>
         <v>6.1077681447351477E-2</v>
       </c>
     </row>
@@ -10042,35 +10042,35 @@
         <v>803.61120472830555</v>
       </c>
       <c r="L121" s="2">
-        <f>RATE(10,,J111,-'Real Returns 1792-2025'!$J121)</f>
+        <f>RATE(10,,J111,-'Real Returns 1792-2026'!$J121)</f>
         <v>6.1339280121288871E-2</v>
       </c>
       <c r="M121" s="2">
-        <f>RATE(10,,K111,-'Real Returns 1792-2025'!$K121)</f>
+        <f>RATE(10,,K111,-'Real Returns 1792-2026'!$K121)</f>
         <v>2.6626172492265968E-2</v>
       </c>
       <c r="N121" s="2">
-        <f>RATE(30,,J91,-'Real Returns 1792-2025'!$J121)</f>
+        <f>RATE(30,,J91,-'Real Returns 1792-2026'!$J121)</f>
         <v>5.8280439873439172E-2</v>
       </c>
       <c r="O121" s="2">
-        <f>RATE(30,,K91,-'Real Returns 1792-2025'!$K121)</f>
+        <f>RATE(30,,K91,-'Real Returns 1792-2026'!$K121)</f>
         <v>5.3357606277427444E-2</v>
       </c>
       <c r="P121" s="2">
-        <f>RATE(50,,J71,-'Real Returns 1792-2025'!$J121)</f>
+        <f>RATE(50,,J71,-'Real Returns 1792-2026'!$J121)</f>
         <v>7.8624301842936978E-2</v>
       </c>
       <c r="Q121" s="2">
-        <f>RATE(50,,K71,-'Real Returns 1792-2025'!$K121)</f>
+        <f>RATE(50,,K71,-'Real Returns 1792-2026'!$K121)</f>
         <v>6.0156859621595608E-2</v>
       </c>
       <c r="R121" s="2">
-        <f>RATE(100,,J21,-'Real Returns 1792-2025'!$J121)</f>
+        <f>RATE(100,,J21,-'Real Returns 1792-2026'!$J121)</f>
         <v>6.0135500005145302E-2</v>
       </c>
       <c r="S121" s="2">
-        <f>RATE(100,,K21,-'Real Returns 1792-2025'!$K121)</f>
+        <f>RATE(100,,K21,-'Real Returns 1792-2026'!$K121)</f>
         <v>6.1118318460123368E-2</v>
       </c>
     </row>
@@ -10107,35 +10107,35 @@
         <v>829.75122624829851</v>
       </c>
       <c r="L122" s="2">
-        <f>RATE(10,,J112,-'Real Returns 1792-2025'!$J122)</f>
+        <f>RATE(10,,J112,-'Real Returns 1792-2026'!$J122)</f>
         <v>4.6645623607023047E-2</v>
       </c>
       <c r="M122" s="2">
-        <f>RATE(10,,K112,-'Real Returns 1792-2025'!$K122)</f>
+        <f>RATE(10,,K112,-'Real Returns 1792-2026'!$K122)</f>
         <v>2.5866315161778321E-2</v>
       </c>
       <c r="N122" s="2">
-        <f>RATE(30,,J92,-'Real Returns 1792-2025'!$J122)</f>
+        <f>RATE(30,,J92,-'Real Returns 1792-2026'!$J122)</f>
         <v>5.8948909563231976E-2</v>
       </c>
       <c r="O122" s="2">
-        <f>RATE(30,,K92,-'Real Returns 1792-2025'!$K122)</f>
+        <f>RATE(30,,K92,-'Real Returns 1792-2026'!$K122)</f>
         <v>5.2457740098275606E-2</v>
       </c>
       <c r="P122" s="2">
-        <f>RATE(50,,J72,-'Real Returns 1792-2025'!$J122)</f>
+        <f>RATE(50,,J72,-'Real Returns 1792-2026'!$J122)</f>
         <v>8.0339750590223871E-2</v>
       </c>
       <c r="Q122" s="2">
-        <f>RATE(50,,K72,-'Real Returns 1792-2025'!$K122)</f>
+        <f>RATE(50,,K72,-'Real Returns 1792-2026'!$K122)</f>
         <v>6.1698841420319166E-2</v>
       </c>
       <c r="R122" s="2">
-        <f>RATE(100,,J22,-'Real Returns 1792-2025'!$J122)</f>
+        <f>RATE(100,,J22,-'Real Returns 1792-2026'!$J122)</f>
         <v>6.0508061839241227E-2</v>
       </c>
       <c r="S122" s="2">
-        <f>RATE(100,,K22,-'Real Returns 1792-2025'!$K122)</f>
+        <f>RATE(100,,K22,-'Real Returns 1792-2026'!$K122)</f>
         <v>6.2027007224723686E-2</v>
       </c>
     </row>
@@ -10174,35 +10174,35 @@
         <v>834.46350340241509</v>
       </c>
       <c r="L123" s="2">
-        <f>RATE(10,,J113,-'Real Returns 1792-2025'!$J123)</f>
+        <f>RATE(10,,J113,-'Real Returns 1792-2026'!$J123)</f>
         <v>4.5105333086488758E-2</v>
       </c>
       <c r="M123" s="2">
-        <f>RATE(10,,K113,-'Real Returns 1792-2025'!$K123)</f>
+        <f>RATE(10,,K113,-'Real Returns 1792-2026'!$K123)</f>
         <v>2.6192102870289939E-2</v>
       </c>
       <c r="N123" s="2">
-        <f>RATE(30,,J93,-'Real Returns 1792-2025'!$J123)</f>
+        <f>RATE(30,,J93,-'Real Returns 1792-2026'!$J123)</f>
         <v>5.9527532866127997E-2</v>
       </c>
       <c r="O123" s="2">
-        <f>RATE(30,,K93,-'Real Returns 1792-2025'!$K123)</f>
+        <f>RATE(30,,K93,-'Real Returns 1792-2026'!$K123)</f>
         <v>5.0629075580031872E-2</v>
       </c>
       <c r="P123" s="2">
-        <f>RATE(50,,J73,-'Real Returns 1792-2025'!$J123)</f>
+        <f>RATE(50,,J73,-'Real Returns 1792-2026'!$J123)</f>
         <v>7.3747256664741814E-2</v>
       </c>
       <c r="Q123" s="2">
-        <f>RATE(50,,K73,-'Real Returns 1792-2025'!$K123)</f>
+        <f>RATE(50,,K73,-'Real Returns 1792-2026'!$K123)</f>
         <v>6.1793672044366053E-2</v>
       </c>
       <c r="R123" s="2">
-        <f>RATE(100,,J23,-'Real Returns 1792-2025'!$J123)</f>
+        <f>RATE(100,,J23,-'Real Returns 1792-2026'!$J123)</f>
         <v>6.1051448853749628E-2</v>
       </c>
       <c r="S123" s="2">
-        <f>RATE(100,,K23,-'Real Returns 1792-2025'!$K123)</f>
+        <f>RATE(100,,K23,-'Real Returns 1792-2026'!$K123)</f>
         <v>6.282621832654689E-2</v>
       </c>
     </row>
@@ -10241,35 +10241,35 @@
         <v>825.9514426428392</v>
       </c>
       <c r="L124" s="2">
-        <f>RATE(10,,J114,-'Real Returns 1792-2025'!$J124)</f>
+        <f>RATE(10,,J114,-'Real Returns 1792-2026'!$J124)</f>
         <v>5.9346867295697693E-2</v>
       </c>
       <c r="M124" s="2">
-        <f>RATE(10,,K114,-'Real Returns 1792-2025'!$K124)</f>
+        <f>RATE(10,,K114,-'Real Returns 1792-2026'!$K124)</f>
         <v>2.601887392414946E-2</v>
       </c>
       <c r="N124" s="2">
-        <f>RATE(30,,J94,-'Real Returns 1792-2025'!$J124)</f>
+        <f>RATE(30,,J94,-'Real Returns 1792-2026'!$J124)</f>
         <v>5.9468423452559843E-2</v>
       </c>
       <c r="O124" s="2">
-        <f>RATE(30,,K94,-'Real Returns 1792-2025'!$K124)</f>
+        <f>RATE(30,,K94,-'Real Returns 1792-2026'!$K124)</f>
         <v>4.7423043136030803E-2</v>
       </c>
       <c r="P124" s="2">
-        <f>RATE(50,,J74,-'Real Returns 1792-2025'!$J124)</f>
+        <f>RATE(50,,J74,-'Real Returns 1792-2026'!$J124)</f>
         <v>7.1912821802230881E-2</v>
       </c>
       <c r="Q124" s="2">
-        <f>RATE(50,,K74,-'Real Returns 1792-2025'!$K124)</f>
+        <f>RATE(50,,K74,-'Real Returns 1792-2026'!$K124)</f>
         <v>6.4690663998627759E-2</v>
       </c>
       <c r="R124" s="2">
-        <f>RATE(100,,J24,-'Real Returns 1792-2025'!$J124)</f>
+        <f>RATE(100,,J24,-'Real Returns 1792-2026'!$J124)</f>
         <v>6.0985109791925993E-2</v>
       </c>
       <c r="S124" s="2">
-        <f>RATE(100,,K24,-'Real Returns 1792-2025'!$K124)</f>
+        <f>RATE(100,,K24,-'Real Returns 1792-2026'!$K124)</f>
         <v>6.4454163938254802E-2</v>
       </c>
     </row>
@@ -10304,35 +10304,35 @@
         <v>829.41278346742774</v>
       </c>
       <c r="L125" s="2">
-        <f>RATE(10,,J115,-'Real Returns 1792-2025'!$J125)</f>
+        <f>RATE(10,,J115,-'Real Returns 1792-2026'!$J125)</f>
         <v>2.3576415248334391E-2</v>
       </c>
       <c r="M125" s="2">
-        <f>RATE(10,,K115,-'Real Returns 1792-2025'!$K125)</f>
+        <f>RATE(10,,K115,-'Real Returns 1792-2026'!$K125)</f>
         <v>1.4808260037740861E-2</v>
       </c>
       <c r="N125" s="2">
-        <f>RATE(30,,J95,-'Real Returns 1792-2025'!$J125)</f>
+        <f>RATE(30,,J95,-'Real Returns 1792-2026'!$J125)</f>
         <v>6.1482088624578997E-2</v>
       </c>
       <c r="O125" s="2">
-        <f>RATE(30,,K95,-'Real Returns 1792-2025'!$K125)</f>
+        <f>RATE(30,,K95,-'Real Returns 1792-2026'!$K125)</f>
         <v>4.5245508844952799E-2</v>
       </c>
       <c r="P125" s="2">
-        <f>RATE(50,,J75,-'Real Returns 1792-2025'!$J125)</f>
+        <f>RATE(50,,J75,-'Real Returns 1792-2026'!$J125)</f>
         <v>7.1883822376285489E-2</v>
       </c>
       <c r="Q125" s="2">
-        <f>RATE(50,,K75,-'Real Returns 1792-2025'!$K125)</f>
+        <f>RATE(50,,K75,-'Real Returns 1792-2026'!$K125)</f>
         <v>6.6028613718456183E-2</v>
       </c>
       <c r="R125" s="2">
-        <f>RATE(100,,J25,-'Real Returns 1792-2025'!$J125)</f>
+        <f>RATE(100,,J25,-'Real Returns 1792-2026'!$J125)</f>
         <v>6.088481771701347E-2</v>
       </c>
       <c r="S125" s="2">
-        <f>RATE(100,,K25,-'Real Returns 1792-2025'!$K125)</f>
+        <f>RATE(100,,K25,-'Real Returns 1792-2026'!$K125)</f>
         <v>6.4331229481358582E-2</v>
       </c>
     </row>
@@ -10367,35 +10367,35 @@
         <v>867.74079490344025</v>
       </c>
       <c r="L126" s="2">
-        <f>RATE(10,,J116,-'Real Returns 1792-2025'!$J126)</f>
+        <f>RATE(10,,J116,-'Real Returns 1792-2026'!$J126)</f>
         <v>2.898410645884256E-2</v>
       </c>
       <c r="M126" s="2">
-        <f>RATE(10,,K116,-'Real Returns 1792-2025'!$K126)</f>
+        <f>RATE(10,,K116,-'Real Returns 1792-2026'!$K126)</f>
         <v>1.5905120369324149E-2</v>
       </c>
       <c r="N126" s="2">
-        <f>RATE(30,,J96,-'Real Returns 1792-2025'!$J126)</f>
+        <f>RATE(30,,J96,-'Real Returns 1792-2026'!$J126)</f>
         <v>6.0521487916081515E-2</v>
       </c>
       <c r="O126" s="2">
-        <f>RATE(30,,K96,-'Real Returns 1792-2025'!$K126)</f>
+        <f>RATE(30,,K96,-'Real Returns 1792-2026'!$K126)</f>
         <v>4.3604448223030882E-2</v>
       </c>
       <c r="P126" s="2">
-        <f>RATE(50,,J76,-'Real Returns 1792-2025'!$J126)</f>
+        <f>RATE(50,,J76,-'Real Returns 1792-2026'!$J126)</f>
         <v>7.6335524547092221E-2</v>
       </c>
       <c r="Q126" s="2">
-        <f>RATE(50,,K76,-'Real Returns 1792-2025'!$K126)</f>
+        <f>RATE(50,,K76,-'Real Returns 1792-2026'!$K126)</f>
         <v>6.6760689660598421E-2</v>
       </c>
       <c r="R126" s="2">
-        <f>RATE(100,,J26,-'Real Returns 1792-2025'!$J126)</f>
+        <f>RATE(100,,J26,-'Real Returns 1792-2026'!$J126)</f>
         <v>6.1000318090440785E-2</v>
       </c>
       <c r="S126" s="2">
-        <f>RATE(100,,K26,-'Real Returns 1792-2025'!$K126)</f>
+        <f>RATE(100,,K26,-'Real Returns 1792-2026'!$K126)</f>
         <v>6.2164377389860095E-2</v>
       </c>
     </row>
@@ -10430,35 +10430,35 @@
         <v>817.27108909665355</v>
       </c>
       <c r="L127" s="2">
-        <f>RATE(10,,J117,-'Real Returns 1792-2025'!$J127)</f>
+        <f>RATE(10,,J117,-'Real Returns 1792-2026'!$J127)</f>
         <v>2.8704188857687999E-2</v>
       </c>
       <c r="M127" s="2">
-        <f>RATE(10,,K117,-'Real Returns 1792-2025'!$K127)</f>
+        <f>RATE(10,,K117,-'Real Returns 1792-2026'!$K127)</f>
         <v>1.2558783118144071E-2</v>
       </c>
       <c r="N127" s="2">
-        <f>RATE(30,,J97,-'Real Returns 1792-2025'!$J127)</f>
+        <f>RATE(30,,J97,-'Real Returns 1792-2026'!$J127)</f>
         <v>5.5822146585350875E-2</v>
       </c>
       <c r="O127" s="2">
-        <f>RATE(30,,K97,-'Real Returns 1792-2025'!$K127)</f>
+        <f>RATE(30,,K97,-'Real Returns 1792-2026'!$K127)</f>
         <v>3.9621099962367422E-2</v>
       </c>
       <c r="P127" s="2">
-        <f>RATE(50,,J77,-'Real Returns 1792-2025'!$J127)</f>
+        <f>RATE(50,,J77,-'Real Returns 1792-2026'!$J127)</f>
         <v>7.351052603789128E-2</v>
       </c>
       <c r="Q127" s="2">
-        <f>RATE(50,,K77,-'Real Returns 1792-2025'!$K127)</f>
+        <f>RATE(50,,K77,-'Real Returns 1792-2026'!$K127)</f>
         <v>6.2439004724291716E-2</v>
       </c>
       <c r="R127" s="2">
-        <f>RATE(100,,J27,-'Real Returns 1792-2025'!$J127)</f>
+        <f>RATE(100,,J27,-'Real Returns 1792-2026'!$J127)</f>
         <v>5.9416656374035232E-2</v>
       </c>
       <c r="S127" s="2">
-        <f>RATE(100,,K27,-'Real Returns 1792-2025'!$K127)</f>
+        <f>RATE(100,,K27,-'Real Returns 1792-2026'!$K127)</f>
         <v>5.9772284032078363E-2</v>
       </c>
     </row>
@@ -10493,35 +10493,35 @@
         <v>618.17888319869894</v>
       </c>
       <c r="L128" s="2">
-        <f>RATE(10,,J118,-'Real Returns 1792-2025'!$J128)</f>
+        <f>RATE(10,,J118,-'Real Returns 1792-2026'!$J128)</f>
         <v>2.0583986662395342E-2</v>
       </c>
       <c r="M128" s="2">
-        <f>RATE(10,,K118,-'Real Returns 1792-2025'!$K128)</f>
+        <f>RATE(10,,K118,-'Real Returns 1792-2026'!$K128)</f>
         <v>-1.0270097934568012E-2</v>
       </c>
       <c r="N128" s="2">
-        <f>RATE(30,,J98,-'Real Returns 1792-2025'!$J128)</f>
+        <f>RATE(30,,J98,-'Real Returns 1792-2026'!$J128)</f>
         <v>4.3816836328234562E-2</v>
       </c>
       <c r="O128" s="2">
-        <f>RATE(30,,K98,-'Real Returns 1792-2025'!$K128)</f>
+        <f>RATE(30,,K98,-'Real Returns 1792-2026'!$K128)</f>
         <v>2.8832100180912514E-2</v>
       </c>
       <c r="P128" s="2">
-        <f>RATE(50,,J78,-'Real Returns 1792-2025'!$J128)</f>
+        <f>RATE(50,,J78,-'Real Returns 1792-2026'!$J128)</f>
         <v>6.2180293741076725E-2</v>
       </c>
       <c r="Q128" s="2">
-        <f>RATE(50,,K78,-'Real Returns 1792-2025'!$K128)</f>
+        <f>RATE(50,,K78,-'Real Returns 1792-2026'!$K128)</f>
         <v>5.3621996097748981E-2</v>
       </c>
       <c r="R128" s="2">
-        <f>RATE(100,,J28,-'Real Returns 1792-2025'!$J128)</f>
+        <f>RATE(100,,J28,-'Real Returns 1792-2026'!$J128)</f>
         <v>5.263569928469021E-2</v>
       </c>
       <c r="S128" s="2">
-        <f>RATE(100,,K28,-'Real Returns 1792-2025'!$K128)</f>
+        <f>RATE(100,,K28,-'Real Returns 1792-2026'!$K128)</f>
         <v>5.4754631639985465E-2</v>
       </c>
     </row>
@@ -10556,35 +10556,35 @@
         <v>566.07323752012428</v>
       </c>
       <c r="L129" s="2">
-        <f>RATE(10,,J119,-'Real Returns 1792-2025'!$J129)</f>
+        <f>RATE(10,,J119,-'Real Returns 1792-2026'!$J129)</f>
         <v>-1.4999092482643306E-2</v>
       </c>
       <c r="M129" s="2">
-        <f>RATE(10,,K119,-'Real Returns 1792-2025'!$K129)</f>
+        <f>RATE(10,,K119,-'Real Returns 1792-2026'!$K129)</f>
         <v>-3.1860603803641772E-2</v>
       </c>
       <c r="N129" s="2">
-        <f>RATE(30,,J99,-'Real Returns 1792-2025'!$J129)</f>
+        <f>RATE(30,,J99,-'Real Returns 1792-2026'!$J129)</f>
         <v>4.2321453119550309E-2</v>
       </c>
       <c r="O129" s="2">
-        <f>RATE(30,,K99,-'Real Returns 1792-2025'!$K129)</f>
+        <f>RATE(30,,K99,-'Real Returns 1792-2026'!$K129)</f>
         <v>2.3064539550273027E-2</v>
       </c>
       <c r="P129" s="2">
-        <f>RATE(50,,J79,-'Real Returns 1792-2025'!$J129)</f>
+        <f>RATE(50,,J79,-'Real Returns 1792-2026'!$J129)</f>
         <v>5.6942132080641361E-2</v>
       </c>
       <c r="Q129" s="2">
-        <f>RATE(50,,K79,-'Real Returns 1792-2025'!$K129)</f>
+        <f>RATE(50,,K79,-'Real Returns 1792-2026'!$K129)</f>
         <v>4.9596717434052723E-2</v>
       </c>
       <c r="R129" s="2">
-        <f>RATE(100,,J29,-'Real Returns 1792-2025'!$J129)</f>
+        <f>RATE(100,,J29,-'Real Returns 1792-2026'!$J129)</f>
         <v>5.3868751145293374E-2</v>
       </c>
       <c r="S129" s="2">
-        <f>RATE(100,,K29,-'Real Returns 1792-2025'!$K129)</f>
+        <f>RATE(100,,K29,-'Real Returns 1792-2026'!$K129)</f>
         <v>5.3602197512971829E-2</v>
       </c>
     </row>
@@ -10619,35 +10619,35 @@
         <v>471.77744260895571</v>
       </c>
       <c r="L130" s="2">
-        <f>RATE(10,,J120,-'Real Returns 1792-2025'!$J130)</f>
+        <f>RATE(10,,J120,-'Real Returns 1792-2026'!$J130)</f>
         <v>-2.7051025683644682E-2</v>
       </c>
       <c r="M130" s="2">
-        <f>RATE(10,,K120,-'Real Returns 1792-2025'!$K130)</f>
+        <f>RATE(10,,K120,-'Real Returns 1792-2026'!$K130)</f>
         <v>-5.1003674182054363E-2</v>
       </c>
       <c r="N130" s="2">
-        <f>RATE(30,,J100,-'Real Returns 1792-2025'!$J130)</f>
+        <f>RATE(30,,J100,-'Real Returns 1792-2026'!$J130)</f>
         <v>3.9493049732976855E-2</v>
       </c>
       <c r="O130" s="2">
-        <f>RATE(30,,K100,-'Real Returns 1792-2025'!$K130)</f>
+        <f>RATE(30,,K100,-'Real Returns 1792-2026'!$K130)</f>
         <v>1.4646316495252422E-2</v>
       </c>
       <c r="P130" s="2">
-        <f>RATE(50,,J80,-'Real Returns 1792-2025'!$J130)</f>
+        <f>RATE(50,,J80,-'Real Returns 1792-2026'!$J130)</f>
         <v>5.591650904003645E-2</v>
       </c>
       <c r="Q130" s="2">
-        <f>RATE(50,,K80,-'Real Returns 1792-2025'!$K130)</f>
+        <f>RATE(50,,K80,-'Real Returns 1792-2026'!$K130)</f>
         <v>4.3352552966698175E-2</v>
       </c>
       <c r="R130" s="2">
-        <f>RATE(100,,J30,-'Real Returns 1792-2025'!$J130)</f>
+        <f>RATE(100,,J30,-'Real Returns 1792-2026'!$J130)</f>
         <v>5.4190176229038545E-2</v>
       </c>
       <c r="S130" s="2">
-        <f>RATE(100,,K30,-'Real Returns 1792-2025'!$K130)</f>
+        <f>RATE(100,,K30,-'Real Returns 1792-2026'!$K130)</f>
         <v>5.0386225957508142E-2</v>
       </c>
     </row>
@@ -10682,35 +10682,35 @@
         <v>501.53821111537911</v>
       </c>
       <c r="L131" s="2">
-        <f>RATE(10,,J121,-'Real Returns 1792-2025'!$J131)</f>
+        <f>RATE(10,,J121,-'Real Returns 1792-2026'!$J131)</f>
         <v>-3.4606715994855181E-2</v>
       </c>
       <c r="M131" s="2">
-        <f>RATE(10,,K121,-'Real Returns 1792-2025'!$K131)</f>
+        <f>RATE(10,,K121,-'Real Returns 1792-2026'!$K131)</f>
         <v>-4.6049578332287767E-2</v>
       </c>
       <c r="N131" s="2">
-        <f>RATE(30,,J101,-'Real Returns 1792-2025'!$J131)</f>
+        <f>RATE(30,,J101,-'Real Returns 1792-2026'!$J131)</f>
         <v>3.6383946354575439E-2</v>
       </c>
       <c r="O131" s="2">
-        <f>RATE(30,,K101,-'Real Returns 1792-2025'!$K131)</f>
+        <f>RATE(30,,K101,-'Real Returns 1792-2026'!$K131)</f>
         <v>1.5854931768041463E-2</v>
       </c>
       <c r="P131" s="2">
-        <f>RATE(50,,J81,-'Real Returns 1792-2025'!$J131)</f>
+        <f>RATE(50,,J81,-'Real Returns 1792-2026'!$J131)</f>
         <v>5.1599555038631499E-2</v>
       </c>
       <c r="Q131" s="2">
-        <f>RATE(50,,K81,-'Real Returns 1792-2025'!$K131)</f>
+        <f>RATE(50,,K81,-'Real Returns 1792-2026'!$K131)</f>
         <v>4.2214099599643957E-2</v>
       </c>
       <c r="R131" s="2">
-        <f>RATE(100,,J31,-'Real Returns 1792-2025'!$J131)</f>
+        <f>RATE(100,,J31,-'Real Returns 1792-2026'!$J131)</f>
         <v>5.1454976223605065E-2</v>
       </c>
       <c r="S131" s="2">
-        <f>RATE(100,,K31,-'Real Returns 1792-2025'!$K131)</f>
+        <f>RATE(100,,K31,-'Real Returns 1792-2026'!$K131)</f>
         <v>4.9363814468529048E-2</v>
       </c>
     </row>
@@ -10745,35 +10745,35 @@
         <v>656.17229508070545</v>
       </c>
       <c r="L132" s="2">
-        <f>RATE(10,,J122,-'Real Returns 1792-2025'!$J132)</f>
+        <f>RATE(10,,J122,-'Real Returns 1792-2026'!$J132)</f>
         <v>-1.6919973566029128E-2</v>
       </c>
       <c r="M132" s="2">
-        <f>RATE(10,,K122,-'Real Returns 1792-2025'!$K132)</f>
+        <f>RATE(10,,K122,-'Real Returns 1792-2026'!$K132)</f>
         <v>-2.3196968710836024E-2</v>
       </c>
       <c r="N132" s="2">
-        <f>RATE(30,,J102,-'Real Returns 1792-2025'!$J132)</f>
+        <f>RATE(30,,J102,-'Real Returns 1792-2026'!$J132)</f>
         <v>3.8294617149406164E-2</v>
       </c>
       <c r="O132" s="2">
-        <f>RATE(30,,K102,-'Real Returns 1792-2025'!$K132)</f>
+        <f>RATE(30,,K102,-'Real Returns 1792-2026'!$K132)</f>
         <v>2.3219018875005736E-2</v>
       </c>
       <c r="P132" s="2">
-        <f>RATE(50,,J82,-'Real Returns 1792-2025'!$J132)</f>
+        <f>RATE(50,,J82,-'Real Returns 1792-2026'!$J132)</f>
         <v>5.2004320723933163E-2</v>
       </c>
       <c r="Q132" s="2">
-        <f>RATE(50,,K82,-'Real Returns 1792-2025'!$K132)</f>
+        <f>RATE(50,,K82,-'Real Returns 1792-2026'!$K132)</f>
         <v>4.5463319856497639E-2</v>
       </c>
       <c r="R132" s="2">
-        <f>RATE(100,,J32,-'Real Returns 1792-2025'!$J132)</f>
+        <f>RATE(100,,J32,-'Real Returns 1792-2026'!$J132)</f>
         <v>5.2438866526623384E-2</v>
       </c>
       <c r="S132" s="2">
-        <f>RATE(100,,K32,-'Real Returns 1792-2025'!$K132)</f>
+        <f>RATE(100,,K32,-'Real Returns 1792-2026'!$K132)</f>
         <v>5.1537216573139789E-2</v>
       </c>
     </row>
@@ -10808,35 +10808,35 @@
         <v>713.88403557402683</v>
       </c>
       <c r="L133" s="2">
-        <f>RATE(10,,J123,-'Real Returns 1792-2025'!$J133)</f>
+        <f>RATE(10,,J123,-'Real Returns 1792-2026'!$J133)</f>
         <v>4.4618100049484107E-3</v>
       </c>
       <c r="M133" s="2">
-        <f>RATE(10,,K123,-'Real Returns 1792-2025'!$K133)</f>
+        <f>RATE(10,,K123,-'Real Returns 1792-2026'!$K133)</f>
         <v>-1.5485691610212281E-2</v>
       </c>
       <c r="N133" s="2">
-        <f>RATE(30,,J103,-'Real Returns 1792-2025'!$J133)</f>
+        <f>RATE(30,,J103,-'Real Returns 1792-2026'!$J133)</f>
         <v>4.5428486931374593E-2</v>
       </c>
       <c r="O133" s="2">
-        <f>RATE(30,,K103,-'Real Returns 1792-2025'!$K133)</f>
+        <f>RATE(30,,K103,-'Real Returns 1792-2026'!$K133)</f>
         <v>2.4466847583440393E-2</v>
       </c>
       <c r="P133" s="2">
-        <f>RATE(50,,J83,-'Real Returns 1792-2025'!$J133)</f>
+        <f>RATE(50,,J83,-'Real Returns 1792-2026'!$J133)</f>
         <v>5.4242362107961559E-2</v>
       </c>
       <c r="Q133" s="2">
-        <f>RATE(50,,K83,-'Real Returns 1792-2025'!$K133)</f>
+        <f>RATE(50,,K83,-'Real Returns 1792-2026'!$K133)</f>
         <v>4.5677636458073448E-2</v>
       </c>
       <c r="R133" s="2">
-        <f>RATE(100,,J33,-'Real Returns 1792-2025'!$J133)</f>
+        <f>RATE(100,,J33,-'Real Returns 1792-2026'!$J133)</f>
         <v>5.5245235233086436E-2</v>
       </c>
       <c r="S133" s="2">
-        <f>RATE(100,,K33,-'Real Returns 1792-2025'!$K133)</f>
+        <f>RATE(100,,K33,-'Real Returns 1792-2026'!$K133)</f>
         <v>5.1740536337325317E-2</v>
       </c>
     </row>
@@ -10871,35 +10871,35 @@
         <v>720.52533493038197</v>
       </c>
       <c r="L134" s="2">
-        <f>RATE(10,,J124,-'Real Returns 1792-2025'!$J134)</f>
+        <f>RATE(10,,J124,-'Real Returns 1792-2026'!$J134)</f>
         <v>1.3971442117605969E-2</v>
       </c>
       <c r="M134" s="2">
-        <f>RATE(10,,K124,-'Real Returns 1792-2025'!$K134)</f>
+        <f>RATE(10,,K124,-'Real Returns 1792-2026'!$K134)</f>
         <v>-1.356272684214584E-2</v>
       </c>
       <c r="N134" s="2">
-        <f>RATE(30,,J104,-'Real Returns 1792-2025'!$J134)</f>
+        <f>RATE(30,,J104,-'Real Returns 1792-2026'!$J134)</f>
         <v>5.2432350761527004E-2</v>
       </c>
       <c r="O134" s="2">
-        <f>RATE(30,,K104,-'Real Returns 1792-2025'!$K134)</f>
+        <f>RATE(30,,K104,-'Real Returns 1792-2026'!$K134)</f>
         <v>2.2250675059627936E-2</v>
       </c>
       <c r="P134" s="2">
-        <f>RATE(50,,J84,-'Real Returns 1792-2025'!$J134)</f>
+        <f>RATE(50,,J84,-'Real Returns 1792-2026'!$J134)</f>
         <v>5.5131852668960764E-2</v>
       </c>
       <c r="Q134" s="2">
-        <f>RATE(50,,K84,-'Real Returns 1792-2025'!$K134)</f>
+        <f>RATE(50,,K84,-'Real Returns 1792-2026'!$K134)</f>
         <v>4.3735713908864077E-2</v>
       </c>
       <c r="R134" s="2">
-        <f>RATE(100,,J34,-'Real Returns 1792-2025'!$J134)</f>
+        <f>RATE(100,,J34,-'Real Returns 1792-2026'!$J134)</f>
         <v>5.3724083022349593E-2</v>
       </c>
       <c r="S134" s="2">
-        <f>RATE(100,,K34,-'Real Returns 1792-2025'!$K134)</f>
+        <f>RATE(100,,K34,-'Real Returns 1792-2026'!$K134)</f>
         <v>5.0209654006145431E-2</v>
       </c>
     </row>
@@ -10934,35 +10934,35 @@
         <v>781.38246562414713</v>
       </c>
       <c r="L135" s="2">
-        <f>RATE(10,,J125,-'Real Returns 1792-2025'!$J135)</f>
+        <f>RATE(10,,J125,-'Real Returns 1792-2026'!$J135)</f>
         <v>4.5626009316679136E-2</v>
       </c>
       <c r="M135" s="2">
-        <f>RATE(10,,K125,-'Real Returns 1792-2025'!$K135)</f>
+        <f>RATE(10,,K125,-'Real Returns 1792-2026'!$K135)</f>
         <v>-5.9475645873286794E-3</v>
       </c>
       <c r="N135" s="2">
-        <f>RATE(30,,J105,-'Real Returns 1792-2025'!$J135)</f>
+        <f>RATE(30,,J105,-'Real Returns 1792-2026'!$J135)</f>
         <v>5.8672377232609554E-2</v>
       </c>
       <c r="O135" s="2">
-        <f>RATE(30,,K105,-'Real Returns 1792-2025'!$K135)</f>
+        <f>RATE(30,,K105,-'Real Returns 1792-2026'!$K135)</f>
         <v>2.1700227196010276E-2</v>
       </c>
       <c r="P135" s="2">
-        <f>RATE(50,,J85,-'Real Returns 1792-2025'!$J135)</f>
+        <f>RATE(50,,J85,-'Real Returns 1792-2026'!$J135)</f>
         <v>5.8419331714248082E-2</v>
       </c>
       <c r="Q135" s="2">
-        <f>RATE(50,,K85,-'Real Returns 1792-2025'!$K135)</f>
+        <f>RATE(50,,K85,-'Real Returns 1792-2026'!$K135)</f>
         <v>4.2507827352060094E-2</v>
       </c>
       <c r="R135" s="2">
-        <f>RATE(100,,J35,-'Real Returns 1792-2025'!$J135)</f>
+        <f>RATE(100,,J35,-'Real Returns 1792-2026'!$J135)</f>
         <v>5.4512806175524169E-2</v>
       </c>
       <c r="S135" s="2">
-        <f>RATE(100,,K35,-'Real Returns 1792-2025'!$K135)</f>
+        <f>RATE(100,,K35,-'Real Returns 1792-2026'!$K135)</f>
         <v>4.9961251358206622E-2</v>
       </c>
     </row>
@@ -10997,35 +10997,35 @@
         <v>816.18126248123826</v>
       </c>
       <c r="L136" s="2">
-        <f>RATE(10,,J126,-'Real Returns 1792-2025'!$J136)</f>
+        <f>RATE(10,,J126,-'Real Returns 1792-2026'!$J136)</f>
         <v>4.0537283677427559E-2</v>
       </c>
       <c r="M136" s="2">
-        <f>RATE(10,,K126,-'Real Returns 1792-2025'!$K136)</f>
+        <f>RATE(10,,K126,-'Real Returns 1792-2026'!$K136)</f>
         <v>-6.106934506475154E-3</v>
       </c>
       <c r="N136" s="2">
-        <f>RATE(30,,J106,-'Real Returns 1792-2025'!$J136)</f>
+        <f>RATE(30,,J106,-'Real Returns 1792-2026'!$J136)</f>
         <v>6.330433336327014E-2</v>
       </c>
       <c r="O136" s="2">
-        <f>RATE(30,,K106,-'Real Returns 1792-2025'!$K136)</f>
+        <f>RATE(30,,K106,-'Real Returns 1792-2026'!$K136)</f>
         <v>2.1634406422878949E-2</v>
       </c>
       <c r="P136" s="2">
-        <f>RATE(50,,J86,-'Real Returns 1792-2025'!$J136)</f>
+        <f>RATE(50,,J86,-'Real Returns 1792-2026'!$J136)</f>
         <v>6.0689152696663778E-2</v>
       </c>
       <c r="Q136" s="2">
-        <f>RATE(50,,K86,-'Real Returns 1792-2025'!$K136)</f>
+        <f>RATE(50,,K86,-'Real Returns 1792-2026'!$K136)</f>
         <v>4.0815900618379773E-2</v>
       </c>
       <c r="R136" s="2">
-        <f>RATE(100,,J36,-'Real Returns 1792-2025'!$J136)</f>
+        <f>RATE(100,,J36,-'Real Returns 1792-2026'!$J136)</f>
         <v>5.6467407343854789E-2</v>
       </c>
       <c r="S136" s="2">
-        <f>RATE(100,,K36,-'Real Returns 1792-2025'!$K136)</f>
+        <f>RATE(100,,K36,-'Real Returns 1792-2026'!$K136)</f>
         <v>5.0488028065750479E-2</v>
       </c>
     </row>
@@ -11060,35 +11060,35 @@
         <v>908.16557078092285</v>
       </c>
       <c r="L137" s="2">
-        <f>RATE(10,,J127,-'Real Returns 1792-2025'!$J137)</f>
+        <f>RATE(10,,J127,-'Real Returns 1792-2026'!$J137)</f>
         <v>5.605948512439151E-2</v>
       </c>
       <c r="M137" s="2">
-        <f>RATE(10,,K127,-'Real Returns 1792-2025'!$K137)</f>
+        <f>RATE(10,,K127,-'Real Returns 1792-2026'!$K137)</f>
         <v>1.0601386511159579E-2</v>
       </c>
       <c r="N137" s="2">
-        <f>RATE(30,,J107,-'Real Returns 1792-2025'!$J137)</f>
+        <f>RATE(30,,J107,-'Real Returns 1792-2026'!$J137)</f>
         <v>6.7102722062850548E-2</v>
       </c>
       <c r="O137" s="2">
-        <f>RATE(30,,K107,-'Real Returns 1792-2025'!$K137)</f>
+        <f>RATE(30,,K107,-'Real Returns 1792-2026'!$K137)</f>
         <v>2.3103301050043615E-2</v>
       </c>
       <c r="P137" s="2">
-        <f>RATE(50,,J87,-'Real Returns 1792-2025'!$J137)</f>
+        <f>RATE(50,,J87,-'Real Returns 1792-2026'!$J137)</f>
         <v>6.5314500393219038E-2</v>
       </c>
       <c r="Q137" s="2">
-        <f>RATE(50,,K87,-'Real Returns 1792-2025'!$K137)</f>
+        <f>RATE(50,,K87,-'Real Returns 1792-2026'!$K137)</f>
         <v>4.1449669113523741E-2</v>
       </c>
       <c r="R137" s="2">
-        <f>RATE(100,,J37,-'Real Returns 1792-2025'!$J137)</f>
+        <f>RATE(100,,J37,-'Real Returns 1792-2026'!$J137)</f>
         <v>5.7216714769448611E-2</v>
       </c>
       <c r="S137" s="2">
-        <f>RATE(100,,K37,-'Real Returns 1792-2025'!$K137)</f>
+        <f>RATE(100,,K37,-'Real Returns 1792-2026'!$K137)</f>
         <v>5.1092141739306686E-2</v>
       </c>
     </row>
@@ -11123,35 +11123,35 @@
         <v>996.6069489126611</v>
       </c>
       <c r="L138" s="2">
-        <f>RATE(10,,J128,-'Real Returns 1792-2025'!$J138)</f>
+        <f>RATE(10,,J128,-'Real Returns 1792-2026'!$J138)</f>
         <v>0.12814584065716575</v>
       </c>
       <c r="M138" s="2">
-        <f>RATE(10,,K128,-'Real Returns 1792-2025'!$K138)</f>
+        <f>RATE(10,,K128,-'Real Returns 1792-2026'!$K138)</f>
         <v>4.8916638622951127E-2</v>
       </c>
       <c r="N138" s="2">
-        <f>RATE(30,,J108,-'Real Returns 1792-2025'!$J138)</f>
+        <f>RATE(30,,J108,-'Real Returns 1792-2026'!$J138)</f>
         <v>7.0631236939138822E-2</v>
       </c>
       <c r="O138" s="2">
-        <f>RATE(30,,K108,-'Real Returns 1792-2025'!$K138)</f>
+        <f>RATE(30,,K108,-'Real Returns 1792-2026'!$K138)</f>
         <v>2.2512110756268695E-2</v>
       </c>
       <c r="P138" s="2">
-        <f>RATE(50,,J88,-'Real Returns 1792-2025'!$J138)</f>
+        <f>RATE(50,,J88,-'Real Returns 1792-2026'!$J138)</f>
         <v>7.0912656696377127E-2</v>
       </c>
       <c r="Q138" s="2">
-        <f>RATE(50,,K88,-'Real Returns 1792-2025'!$K138)</f>
+        <f>RATE(50,,K88,-'Real Returns 1792-2026'!$K138)</f>
         <v>4.1741173749164112E-2</v>
       </c>
       <c r="R138" s="2">
-        <f>RATE(100,,J38,-'Real Returns 1792-2025'!$J138)</f>
+        <f>RATE(100,,J38,-'Real Returns 1792-2026'!$J138)</f>
         <v>5.9654500790820783E-2</v>
       </c>
       <c r="S138" s="2">
-        <f>RATE(100,,K38,-'Real Returns 1792-2025'!$K138)</f>
+        <f>RATE(100,,K38,-'Real Returns 1792-2026'!$K138)</f>
         <v>5.1223159684039621E-2</v>
       </c>
     </row>
@@ -11186,35 +11186,35 @@
         <v>1014.5606254023119</v>
       </c>
       <c r="L139" s="2">
-        <f>RATE(10,,J129,-'Real Returns 1792-2025'!$J139)</f>
+        <f>RATE(10,,J129,-'Real Returns 1792-2026'!$J139)</f>
         <v>0.17486097763558114</v>
       </c>
       <c r="M139" s="2">
-        <f>RATE(10,,K129,-'Real Returns 1792-2025'!$K139)</f>
+        <f>RATE(10,,K129,-'Real Returns 1792-2026'!$K139)</f>
         <v>6.0084630647465824E-2</v>
       </c>
       <c r="N139" s="2">
-        <f>RATE(30,,J109,-'Real Returns 1792-2025'!$J139)</f>
+        <f>RATE(30,,J109,-'Real Returns 1792-2026'!$J139)</f>
         <v>7.552910200865845E-2</v>
       </c>
       <c r="O139" s="2">
-        <f>RATE(30,,K109,-'Real Returns 1792-2025'!$K139)</f>
+        <f>RATE(30,,K109,-'Real Returns 1792-2026'!$K139)</f>
         <v>1.9481688871069613E-2</v>
       </c>
       <c r="P139" s="2">
-        <f>RATE(50,,J89,-'Real Returns 1792-2025'!$J139)</f>
+        <f>RATE(50,,J89,-'Real Returns 1792-2026'!$J139)</f>
         <v>7.5970812215377881E-2</v>
       </c>
       <c r="Q139" s="2">
-        <f>RATE(50,,K89,-'Real Returns 1792-2025'!$K139)</f>
+        <f>RATE(50,,K89,-'Real Returns 1792-2026'!$K139)</f>
         <v>4.0079441565037212E-2</v>
       </c>
       <c r="R139" s="2">
-        <f>RATE(100,,J39,-'Real Returns 1792-2025'!$J139)</f>
+        <f>RATE(100,,J39,-'Real Returns 1792-2026'!$J139)</f>
         <v>6.3073908653563479E-2</v>
       </c>
       <c r="S139" s="2">
-        <f>RATE(100,,K39,-'Real Returns 1792-2025'!$K139)</f>
+        <f>RATE(100,,K39,-'Real Returns 1792-2026'!$K139)</f>
         <v>5.0729872168149295E-2</v>
       </c>
     </row>
@@ -11249,35 +11249,35 @@
         <v>1058.663616406438</v>
       </c>
       <c r="L140" s="2">
-        <f>RATE(10,,J130,-'Real Returns 1792-2025'!$J140)</f>
+        <f>RATE(10,,J130,-'Real Returns 1792-2026'!$J140)</f>
         <v>0.15424197628915717</v>
       </c>
       <c r="M140" s="2">
-        <f>RATE(10,,K130,-'Real Returns 1792-2025'!$K140)</f>
+        <f>RATE(10,,K130,-'Real Returns 1792-2026'!$K140)</f>
         <v>8.4181722660237338E-2</v>
       </c>
       <c r="N140" s="2">
-        <f>RATE(30,,J110,-'Real Returns 1792-2025'!$J140)</f>
+        <f>RATE(30,,J110,-'Real Returns 1792-2026'!$J140)</f>
         <v>6.8633356668556827E-2</v>
       </c>
       <c r="O140" s="2">
-        <f>RATE(30,,K110,-'Real Returns 1792-2025'!$K140)</f>
+        <f>RATE(30,,K110,-'Real Returns 1792-2026'!$K140)</f>
         <v>2.0163184227317471E-2</v>
       </c>
       <c r="P140" s="2">
-        <f>RATE(50,,J90,-'Real Returns 1792-2025'!$J140)</f>
+        <f>RATE(50,,J90,-'Real Returns 1792-2026'!$J140)</f>
         <v>6.476507590299295E-2</v>
       </c>
       <c r="Q140" s="2">
-        <f>RATE(50,,K90,-'Real Returns 1792-2025'!$K140)</f>
+        <f>RATE(50,,K90,-'Real Returns 1792-2026'!$K140)</f>
         <v>3.9514881357756819E-2</v>
       </c>
       <c r="R140" s="2">
-        <f>RATE(100,,J40,-'Real Returns 1792-2025'!$J140)</f>
+        <f>RATE(100,,J40,-'Real Returns 1792-2026'!$J140)</f>
         <v>6.0704080151793398E-2</v>
       </c>
       <c r="S140" s="2">
-        <f>RATE(100,,K40,-'Real Returns 1792-2025'!$K140)</f>
+        <f>RATE(100,,K40,-'Real Returns 1792-2026'!$K140)</f>
         <v>5.034600692849129E-2</v>
       </c>
     </row>
@@ -11312,35 +11312,35 @@
         <v>1216.907844913977</v>
       </c>
       <c r="L141" s="2">
-        <f>RATE(10,,J131,-'Real Returns 1792-2025'!$J141)</f>
+        <f>RATE(10,,J131,-'Real Returns 1792-2026'!$J141)</f>
         <v>0.13989597768034165</v>
       </c>
       <c r="M141" s="2">
-        <f>RATE(10,,K131,-'Real Returns 1792-2025'!$K141)</f>
+        <f>RATE(10,,K131,-'Real Returns 1792-2026'!$K141)</f>
         <v>9.2685969042547237E-2</v>
       </c>
       <c r="N141" s="2">
-        <f>RATE(30,,J111,-'Real Returns 1792-2025'!$J141)</f>
+        <f>RATE(30,,J111,-'Real Returns 1792-2026'!$J141)</f>
         <v>5.311203852008526E-2</v>
       </c>
       <c r="O141" s="2">
-        <f>RATE(30,,K111,-'Real Returns 1792-2025'!$K141)</f>
+        <f>RATE(30,,K111,-'Real Returns 1792-2026'!$K141)</f>
         <v>2.2848158291531865E-2</v>
       </c>
       <c r="P141" s="2">
-        <f>RATE(50,,J91,-'Real Returns 1792-2025'!$J141)</f>
+        <f>RATE(50,,J91,-'Real Returns 1792-2026'!$J141)</f>
         <v>5.4567445129058298E-2</v>
       </c>
       <c r="Q141" s="2">
-        <f>RATE(50,,K91,-'Real Returns 1792-2025'!$K141)</f>
+        <f>RATE(50,,K91,-'Real Returns 1792-2026'!$K141)</f>
         <v>4.0278770068085515E-2</v>
       </c>
       <c r="R141" s="2">
-        <f>RATE(100,,J41,-'Real Returns 1792-2025'!$J141)</f>
+        <f>RATE(100,,J41,-'Real Returns 1792-2026'!$J141)</f>
         <v>5.6295937782978388E-2</v>
       </c>
       <c r="S141" s="2">
-        <f>RATE(100,,K41,-'Real Returns 1792-2025'!$K141)</f>
+        <f>RATE(100,,K41,-'Real Returns 1792-2026'!$K141)</f>
         <v>5.0814989273882151E-2</v>
       </c>
     </row>
@@ -11375,35 +11375,35 @@
         <v>1105.0315513070029</v>
       </c>
       <c r="L142" s="2">
-        <f>RATE(10,,J132,-'Real Returns 1792-2025'!$J142)</f>
+        <f>RATE(10,,J132,-'Real Returns 1792-2026'!$J142)</f>
         <v>5.6579428151059478E-2</v>
       </c>
       <c r="M142" s="2">
-        <f>RATE(10,,K132,-'Real Returns 1792-2025'!$K142)</f>
+        <f>RATE(10,,K132,-'Real Returns 1792-2026'!$K142)</f>
         <v>5.3502762780309639E-2</v>
       </c>
       <c r="N142" s="2">
-        <f>RATE(30,,J112,-'Real Returns 1792-2025'!$J142)</f>
+        <f>RATE(30,,J112,-'Real Returns 1792-2026'!$J142)</f>
         <v>2.8245683345776259E-2</v>
       </c>
       <c r="O142" s="2">
-        <f>RATE(30,,K112,-'Real Returns 1792-2025'!$K142)</f>
+        <f>RATE(30,,K112,-'Real Returns 1792-2026'!$K142)</f>
         <v>1.8226703499844003E-2</v>
       </c>
       <c r="P142" s="2">
-        <f>RATE(50,,J92,-'Real Returns 1792-2025'!$J142)</f>
+        <f>RATE(50,,J92,-'Real Returns 1792-2026'!$J142)</f>
         <v>4.2853274431896994E-2</v>
       </c>
       <c r="Q142" s="2">
-        <f>RATE(50,,K92,-'Real Returns 1792-2025'!$K142)</f>
+        <f>RATE(50,,K92,-'Real Returns 1792-2026'!$K142)</f>
         <v>3.7077794327813267E-2</v>
       </c>
       <c r="R142" s="2">
-        <f>RATE(100,,J42,-'Real Returns 1792-2025'!$J142)</f>
+        <f>RATE(100,,J42,-'Real Returns 1792-2026'!$J142)</f>
         <v>4.9569754821905405E-2</v>
       </c>
       <c r="S142" s="2">
-        <f>RATE(100,,K42,-'Real Returns 1792-2025'!$K142)</f>
+        <f>RATE(100,,K42,-'Real Returns 1792-2026'!$K142)</f>
         <v>4.8540709842831702E-2</v>
       </c>
     </row>
@@ -11438,35 +11438,35 @@
         <v>1308.7456699887462</v>
       </c>
       <c r="L143" s="2">
-        <f>RATE(10,,J133,-'Real Returns 1792-2025'!$J143)</f>
+        <f>RATE(10,,J133,-'Real Returns 1792-2026'!$J143)</f>
         <v>3.3356064131394685E-2</v>
       </c>
       <c r="M143" s="2">
-        <f>RATE(10,,K133,-'Real Returns 1792-2025'!$K143)</f>
+        <f>RATE(10,,K133,-'Real Returns 1792-2026'!$K143)</f>
         <v>6.2484880897357119E-2</v>
       </c>
       <c r="N143" s="2">
-        <f>RATE(30,,J113,-'Real Returns 1792-2025'!$J143)</f>
+        <f>RATE(30,,J113,-'Real Returns 1792-2026'!$J143)</f>
         <v>2.7498418045748034E-2</v>
       </c>
       <c r="O143" s="2">
-        <f>RATE(30,,K113,-'Real Returns 1792-2025'!$K143)</f>
+        <f>RATE(30,,K113,-'Real Returns 1792-2026'!$K143)</f>
         <v>2.3900652502184167E-2</v>
       </c>
       <c r="P143" s="2">
-        <f>RATE(50,,J93,-'Real Returns 1792-2025'!$J143)</f>
+        <f>RATE(50,,J93,-'Real Returns 1792-2026'!$J143)</f>
         <v>4.3047370134648093E-2</v>
       </c>
       <c r="Q143" s="2">
-        <f>RATE(50,,K93,-'Real Returns 1792-2025'!$K143)</f>
+        <f>RATE(50,,K93,-'Real Returns 1792-2026'!$K143)</f>
         <v>3.9390175589236652E-2</v>
       </c>
       <c r="R143" s="2">
-        <f>RATE(100,,J43,-'Real Returns 1792-2025'!$J143)</f>
+        <f>RATE(100,,J43,-'Real Returns 1792-2026'!$J143)</f>
         <v>4.9685107375788073E-2</v>
       </c>
       <c r="S143" s="2">
-        <f>RATE(100,,K43,-'Real Returns 1792-2025'!$K143)</f>
+        <f>RATE(100,,K43,-'Real Returns 1792-2026'!$K143)</f>
         <v>4.9542204338595373E-2</v>
       </c>
     </row>
@@ -11501,35 +11501,35 @@
         <v>1476.1776877293437</v>
       </c>
       <c r="L144" s="2">
-        <f>RATE(10,,J134,-'Real Returns 1792-2025'!$J144)</f>
+        <f>RATE(10,,J134,-'Real Returns 1792-2026'!$J144)</f>
         <v>8.8127590352309854E-2</v>
       </c>
       <c r="M144" s="2">
-        <f>RATE(10,,K134,-'Real Returns 1792-2025'!$K144)</f>
+        <f>RATE(10,,K134,-'Real Returns 1792-2026'!$K144)</f>
         <v>7.4357792217206259E-2</v>
       </c>
       <c r="N144" s="2">
-        <f>RATE(30,,J114,-'Real Returns 1792-2025'!$J144)</f>
+        <f>RATE(30,,J114,-'Real Returns 1792-2026'!$J144)</f>
         <v>5.3370724435877696E-2</v>
       </c>
       <c r="O144" s="2">
-        <f>RATE(30,,K114,-'Real Returns 1792-2025'!$K144)</f>
+        <f>RATE(30,,K114,-'Real Returns 1792-2026'!$K144)</f>
         <v>2.8311250399894339E-2</v>
       </c>
       <c r="P144" s="2">
-        <f>RATE(50,,J94,-'Real Returns 1792-2025'!$J144)</f>
+        <f>RATE(50,,J94,-'Real Returns 1792-2026'!$J144)</f>
         <v>5.5829810155911354E-2</v>
       </c>
       <c r="Q144" s="2">
-        <f>RATE(50,,K94,-'Real Returns 1792-2025'!$K144)</f>
+        <f>RATE(50,,K94,-'Real Returns 1792-2026'!$K144)</f>
         <v>4.0200257289950352E-2</v>
       </c>
       <c r="R144" s="2">
-        <f>RATE(100,,J44,-'Real Returns 1792-2025'!$J144)</f>
+        <f>RATE(100,,J44,-'Real Returns 1792-2026'!$J144)</f>
         <v>5.5252484620232328E-2</v>
       </c>
       <c r="S144" s="2">
-        <f>RATE(100,,K44,-'Real Returns 1792-2025'!$K144)</f>
+        <f>RATE(100,,K44,-'Real Returns 1792-2026'!$K144)</f>
         <v>5.0893236771693544E-2</v>
       </c>
     </row>
@@ -11564,35 +11564,35 @@
         <v>1691.7709189711688</v>
       </c>
       <c r="L145" s="2">
-        <f>RATE(10,,J135,-'Real Returns 1792-2025'!$J145)</f>
+        <f>RATE(10,,J135,-'Real Returns 1792-2026'!$J145)</f>
         <v>4.6521628859054663E-2</v>
       </c>
       <c r="M145" s="2">
-        <f>RATE(10,,K135,-'Real Returns 1792-2025'!$K145)</f>
+        <f>RATE(10,,K135,-'Real Returns 1792-2026'!$K145)</f>
         <v>8.0308490568735041E-2</v>
       </c>
       <c r="N145" s="2">
-        <f>RATE(30,,J115,-'Real Returns 1792-2025'!$J145)</f>
+        <f>RATE(30,,J115,-'Real Returns 1792-2026'!$J145)</f>
         <v>3.8520209261768176E-2</v>
       </c>
       <c r="O145" s="2">
-        <f>RATE(30,,K115,-'Real Returns 1792-2025'!$K145)</f>
+        <f>RATE(30,,K115,-'Real Returns 1792-2026'!$K145)</f>
         <v>2.9074994774174474E-2</v>
       </c>
       <c r="P145" s="2">
-        <f>RATE(50,,J95,-'Real Returns 1792-2025'!$J145)</f>
+        <f>RATE(50,,J95,-'Real Returns 1792-2026'!$J145)</f>
         <v>5.5291692747859063E-2</v>
       </c>
       <c r="Q145" s="2">
-        <f>RATE(50,,K95,-'Real Returns 1792-2025'!$K145)</f>
+        <f>RATE(50,,K95,-'Real Returns 1792-2026'!$K145)</f>
         <v>4.1651401970619097E-2</v>
       </c>
       <c r="R145" s="2">
-        <f>RATE(100,,J45,-'Real Returns 1792-2025'!$J145)</f>
+        <f>RATE(100,,J45,-'Real Returns 1792-2026'!$J145)</f>
         <v>5.2881177705082237E-2</v>
       </c>
       <c r="S145" s="2">
-        <f>RATE(100,,K45,-'Real Returns 1792-2025'!$K145)</f>
+        <f>RATE(100,,K45,-'Real Returns 1792-2026'!$K145)</f>
         <v>5.1711582097766932E-2</v>
       </c>
     </row>
@@ -11627,35 +11627,35 @@
         <v>1816.2036926934259</v>
       </c>
       <c r="L146" s="2">
-        <f>RATE(10,,J136,-'Real Returns 1792-2025'!$J146)</f>
+        <f>RATE(10,,J136,-'Real Returns 1792-2026'!$J146)</f>
         <v>7.4729369117518804E-2</v>
       </c>
       <c r="M146" s="2">
-        <f>RATE(10,,K136,-'Real Returns 1792-2025'!$K146)</f>
+        <f>RATE(10,,K136,-'Real Returns 1792-2026'!$K146)</f>
         <v>8.3272687433771447E-2</v>
       </c>
       <c r="N146" s="2">
-        <f>RATE(30,,J116,-'Real Returns 1792-2025'!$J146)</f>
+        <f>RATE(30,,J116,-'Real Returns 1792-2026'!$J146)</f>
         <v>4.790475241798841E-2</v>
       </c>
       <c r="O146" s="2">
-        <f>RATE(30,,K116,-'Real Returns 1792-2025'!$K146)</f>
+        <f>RATE(30,,K116,-'Real Returns 1792-2026'!$K146)</f>
         <v>3.0331239374291913E-2</v>
       </c>
       <c r="P146" s="2">
-        <f>RATE(50,,J96,-'Real Returns 1792-2025'!$J146)</f>
+        <f>RATE(50,,J96,-'Real Returns 1792-2026'!$J146)</f>
         <v>5.9309912220267401E-2</v>
       </c>
       <c r="Q146" s="2">
-        <f>RATE(50,,K96,-'Real Returns 1792-2025'!$K146)</f>
+        <f>RATE(50,,K96,-'Real Returns 1792-2026'!$K146)</f>
         <v>4.120691493393297E-2</v>
       </c>
       <c r="R146" s="2">
-        <f>RATE(100,,J46,-'Real Returns 1792-2025'!$J146)</f>
+        <f>RATE(100,,J46,-'Real Returns 1792-2026'!$J146)</f>
         <v>5.7101871380370234E-2</v>
       </c>
       <c r="S146" s="2">
-        <f>RATE(100,,K46,-'Real Returns 1792-2025'!$K146)</f>
+        <f>RATE(100,,K46,-'Real Returns 1792-2026'!$K146)</f>
         <v>5.2781003687424631E-2</v>
       </c>
     </row>
@@ -11690,35 +11690,35 @@
         <v>1939.9086383213</v>
       </c>
       <c r="L147" s="2">
-        <f>RATE(10,,J137,-'Real Returns 1792-2025'!$J147)</f>
+        <f>RATE(10,,J137,-'Real Returns 1792-2026'!$J147)</f>
         <v>8.6139003584796064E-2</v>
       </c>
       <c r="M147" s="2">
-        <f>RATE(10,,K137,-'Real Returns 1792-2025'!$K147)</f>
+        <f>RATE(10,,K137,-'Real Returns 1792-2026'!$K147)</f>
         <v>7.8851387252450653E-2</v>
       </c>
       <c r="N147" s="2">
-        <f>RATE(30,,J117,-'Real Returns 1792-2025'!$J147)</f>
+        <f>RATE(30,,J117,-'Real Returns 1792-2026'!$J147)</f>
         <v>5.6707443177080943E-2</v>
       </c>
       <c r="O147" s="2">
-        <f>RATE(30,,K117,-'Real Returns 1792-2025'!$K147)</f>
+        <f>RATE(30,,K117,-'Real Returns 1792-2026'!$K147)</f>
         <v>3.3524048448835247E-2</v>
       </c>
       <c r="P147" s="2">
-        <f>RATE(50,,J97,-'Real Returns 1792-2025'!$J147)</f>
+        <f>RATE(50,,J97,-'Real Returns 1792-2026'!$J147)</f>
         <v>6.186478571584688E-2</v>
       </c>
       <c r="Q147" s="2">
-        <f>RATE(50,,K97,-'Real Returns 1792-2025'!$K147)</f>
+        <f>RATE(50,,K97,-'Real Returns 1792-2026'!$K147)</f>
         <v>4.1437841290900029E-2</v>
       </c>
       <c r="R147" s="2">
-        <f>RATE(100,,J47,-'Real Returns 1792-2025'!$J147)</f>
+        <f>RATE(100,,J47,-'Real Returns 1792-2026'!$J147)</f>
         <v>5.9682269083535043E-2</v>
       </c>
       <c r="S147" s="2">
-        <f>RATE(100,,K47,-'Real Returns 1792-2025'!$K147)</f>
+        <f>RATE(100,,K47,-'Real Returns 1792-2026'!$K147)</f>
         <v>5.3728444440457962E-2</v>
       </c>
     </row>
@@ -11753,35 +11753,35 @@
         <v>1795.030889992848</v>
       </c>
       <c r="L148" s="2">
-        <f>RATE(10,,J138,-'Real Returns 1792-2025'!$J148)</f>
+        <f>RATE(10,,J138,-'Real Returns 1792-2026'!$J148)</f>
         <v>7.8909244467620116E-3</v>
       </c>
       <c r="M148" s="2">
-        <f>RATE(10,,K138,-'Real Returns 1792-2025'!$K148)</f>
+        <f>RATE(10,,K138,-'Real Returns 1792-2026'!$K148)</f>
         <v>6.0607762987495338E-2</v>
       </c>
       <c r="N148" s="2">
-        <f>RATE(30,,J118,-'Real Returns 1792-2025'!$J148)</f>
+        <f>RATE(30,,J118,-'Real Returns 1792-2026'!$J148)</f>
         <v>5.0854311271098677E-2</v>
       </c>
       <c r="O148" s="2">
-        <f>RATE(30,,K118,-'Real Returns 1792-2025'!$K148)</f>
+        <f>RATE(30,,K118,-'Real Returns 1792-2026'!$K148)</f>
         <v>3.2612764478112587E-2</v>
       </c>
       <c r="P148" s="2">
-        <f>RATE(50,,J98,-'Real Returns 1792-2025'!$J148)</f>
+        <f>RATE(50,,J98,-'Real Returns 1792-2026'!$J148)</f>
         <v>5.2762325567350804E-2</v>
       </c>
       <c r="Q148" s="2">
-        <f>RATE(50,,K98,-'Real Returns 1792-2025'!$K148)</f>
+        <f>RATE(50,,K98,-'Real Returns 1792-2026'!$K148)</f>
         <v>3.912037098568194E-2</v>
       </c>
       <c r="R148" s="2">
-        <f>RATE(100,,J48,-'Real Returns 1792-2025'!$J148)</f>
+        <f>RATE(100,,J48,-'Real Returns 1792-2026'!$J148)</f>
         <v>5.5108902922678525E-2</v>
       </c>
       <c r="S148" s="2">
-        <f>RATE(100,,K48,-'Real Returns 1792-2025'!$K148)</f>
+        <f>RATE(100,,K48,-'Real Returns 1792-2026'!$K148)</f>
         <v>5.209821210884491E-2</v>
       </c>
     </row>
@@ -11816,35 +11816,35 @@
         <v>1892.3823687654008</v>
       </c>
       <c r="L149" s="2">
-        <f>RATE(10,,J139,-'Real Returns 1792-2025'!$J149)</f>
+        <f>RATE(10,,J139,-'Real Returns 1792-2026'!$J149)</f>
         <v>-1.2303761217175446E-2</v>
       </c>
       <c r="M149" s="2">
-        <f>RATE(10,,K139,-'Real Returns 1792-2025'!$K149)</f>
+        <f>RATE(10,,K139,-'Real Returns 1792-2026'!$K149)</f>
         <v>6.4322121688183936E-2</v>
       </c>
       <c r="N149" s="2">
-        <f>RATE(30,,J119,-'Real Returns 1792-2025'!$J149)</f>
+        <f>RATE(30,,J119,-'Real Returns 1792-2026'!$J149)</f>
         <v>4.5559702691011603E-2</v>
       </c>
       <c r="O149" s="2">
-        <f>RATE(30,,K119,-'Real Returns 1792-2025'!$K149)</f>
+        <f>RATE(30,,K119,-'Real Returns 1792-2026'!$K149)</f>
         <v>2.9873397347587805E-2</v>
       </c>
       <c r="P149" s="2">
-        <f>RATE(50,,J99,-'Real Returns 1792-2025'!$J149)</f>
+        <f>RATE(50,,J99,-'Real Returns 1792-2026'!$J149)</f>
         <v>5.6143624548410216E-2</v>
       </c>
       <c r="Q149" s="2">
-        <f>RATE(50,,K99,-'Real Returns 1792-2025'!$K149)</f>
+        <f>RATE(50,,K99,-'Real Returns 1792-2026'!$K149)</f>
         <v>3.8543147460413561E-2</v>
       </c>
       <c r="R149" s="2">
-        <f>RATE(100,,J49,-'Real Returns 1792-2025'!$J149)</f>
+        <f>RATE(100,,J49,-'Real Returns 1792-2026'!$J149)</f>
         <v>5.6137339865509998E-2</v>
       </c>
       <c r="S149" s="2">
-        <f>RATE(100,,K49,-'Real Returns 1792-2025'!$K149)</f>
+        <f>RATE(100,,K49,-'Real Returns 1792-2026'!$K149)</f>
         <v>5.2112025154659652E-2</v>
       </c>
     </row>
@@ -11879,35 +11879,35 @@
         <v>1953.3394810412135</v>
       </c>
       <c r="L150" s="2">
-        <f>RATE(10,,J140,-'Real Returns 1792-2025'!$J150)</f>
+        <f>RATE(10,,J140,-'Real Returns 1792-2026'!$J150)</f>
         <v>9.9300019978371453E-3</v>
       </c>
       <c r="M150" s="2">
-        <f>RATE(10,,K140,-'Real Returns 1792-2025'!$K150)</f>
+        <f>RATE(10,,K140,-'Real Returns 1792-2026'!$K150)</f>
         <v>6.3168190018607698E-2</v>
       </c>
       <c r="N150" s="2">
-        <f>RATE(30,,J120,-'Real Returns 1792-2025'!$J150)</f>
+        <f>RATE(30,,J120,-'Real Returns 1792-2026'!$J150)</f>
         <v>4.2860138417864638E-2</v>
       </c>
       <c r="O150" s="2">
-        <f>RATE(30,,K120,-'Real Returns 1792-2025'!$K150)</f>
+        <f>RATE(30,,K120,-'Real Returns 1792-2026'!$K150)</f>
         <v>3.0361277454455916E-2</v>
       </c>
       <c r="P150" s="2">
-        <f>RATE(50,,J100,-'Real Returns 1792-2025'!$J150)</f>
+        <f>RATE(50,,J100,-'Real Returns 1792-2026'!$J150)</f>
         <v>5.5384184078318514E-2</v>
       </c>
       <c r="Q150" s="2">
-        <f>RATE(50,,K100,-'Real Returns 1792-2025'!$K150)</f>
+        <f>RATE(50,,K100,-'Real Returns 1792-2026'!$K150)</f>
         <v>3.7838126203884999E-2</v>
       </c>
       <c r="R150" s="2">
-        <f>RATE(100,,J50,-'Real Returns 1792-2025'!$J150)</f>
+        <f>RATE(100,,J50,-'Real Returns 1792-2026'!$J150)</f>
         <v>5.8193706021258416E-2</v>
       </c>
       <c r="S150" s="2">
-        <f>RATE(100,,K50,-'Real Returns 1792-2025'!$K150)</f>
+        <f>RATE(100,,K50,-'Real Returns 1792-2026'!$K150)</f>
         <v>5.2760666074793315E-2</v>
       </c>
     </row>
@@ -11942,35 +11942,35 @@
         <v>2027.014232112288</v>
       </c>
       <c r="L151" s="2">
-        <f>RATE(10,,J141,-'Real Returns 1792-2025'!$J151)</f>
+        <f>RATE(10,,J141,-'Real Returns 1792-2026'!$J151)</f>
         <v>2.5532186346165192E-2</v>
       </c>
       <c r="M151" s="2">
-        <f>RATE(10,,K141,-'Real Returns 1792-2025'!$K151)</f>
+        <f>RATE(10,,K141,-'Real Returns 1792-2026'!$K151)</f>
         <v>5.234928594980625E-2</v>
       </c>
       <c r="N151" s="2">
-        <f>RATE(30,,J121,-'Real Returns 1792-2025'!$J151)</f>
+        <f>RATE(30,,J121,-'Real Returns 1792-2026'!$J151)</f>
         <v>4.1133122311276957E-2</v>
       </c>
       <c r="O151" s="2">
-        <f>RATE(30,,K121,-'Real Returns 1792-2025'!$K151)</f>
+        <f>RATE(30,,K121,-'Real Returns 1792-2026'!$K151)</f>
         <v>3.1320602880885416E-2</v>
       </c>
       <c r="P151" s="2">
-        <f>RATE(50,,J101,-'Real Returns 1792-2025'!$J151)</f>
+        <f>RATE(50,,J101,-'Real Returns 1792-2026'!$J151)</f>
         <v>5.4084214453758724E-2</v>
       </c>
       <c r="Q151" s="2">
-        <f>RATE(50,,K101,-'Real Returns 1792-2025'!$K151)</f>
+        <f>RATE(50,,K101,-'Real Returns 1792-2026'!$K151)</f>
         <v>3.8078201514885446E-2</v>
       </c>
       <c r="R151" s="2">
-        <f>RATE(100,,J51,-'Real Returns 1792-2025'!$J151)</f>
+        <f>RATE(100,,J51,-'Real Returns 1792-2026'!$J151)</f>
         <v>5.7183670141294933E-2</v>
       </c>
       <c r="S151" s="2">
-        <f>RATE(100,,K51,-'Real Returns 1792-2025'!$K151)</f>
+        <f>RATE(100,,K51,-'Real Returns 1792-2026'!$K151)</f>
         <v>5.2345837713735563E-2</v>
       </c>
     </row>
@@ -12005,35 +12005,35 @@
         <v>1884.6085125711641</v>
       </c>
       <c r="L152" s="2">
-        <f>RATE(10,,J142,-'Real Returns 1792-2025'!$J152)</f>
+        <f>RATE(10,,J142,-'Real Returns 1792-2026'!$J152)</f>
         <v>6.6413283829411029E-2</v>
       </c>
       <c r="M152" s="2">
-        <f>RATE(10,,K142,-'Real Returns 1792-2025'!$K152)</f>
+        <f>RATE(10,,K142,-'Real Returns 1792-2026'!$K152)</f>
         <v>5.4835280584833231E-2</v>
       </c>
       <c r="N152" s="2">
-        <f>RATE(30,,J122,-'Real Returns 1792-2025'!$J152)</f>
+        <f>RATE(30,,J122,-'Real Returns 1792-2026'!$J152)</f>
         <v>3.4678734232739969E-2</v>
       </c>
       <c r="O152" s="2">
-        <f>RATE(30,,K122,-'Real Returns 1792-2025'!$K152)</f>
+        <f>RATE(30,,K122,-'Real Returns 1792-2026'!$K152)</f>
         <v>2.7722287449338193E-2</v>
       </c>
       <c r="P152" s="2">
-        <f>RATE(50,,J102,-'Real Returns 1792-2025'!$J152)</f>
+        <f>RATE(50,,J102,-'Real Returns 1792-2026'!$J152)</f>
         <v>4.7509332471840207E-2</v>
       </c>
       <c r="Q152" s="2">
-        <f>RATE(50,,K102,-'Real Returns 1792-2025'!$K152)</f>
+        <f>RATE(50,,K102,-'Real Returns 1792-2026'!$K152)</f>
         <v>3.5488374778993817E-2</v>
       </c>
       <c r="R152" s="2">
-        <f>RATE(100,,J52,-'Real Returns 1792-2025'!$J152)</f>
+        <f>RATE(100,,J52,-'Real Returns 1792-2026'!$J152)</f>
         <v>5.8910270305842262E-2</v>
       </c>
       <c r="S152" s="2">
-        <f>RATE(100,,K52,-'Real Returns 1792-2025'!$K152)</f>
+        <f>RATE(100,,K52,-'Real Returns 1792-2026'!$K152)</f>
         <v>5.4009868926283192E-2</v>
       </c>
     </row>
@@ -12068,35 +12068,35 @@
         <v>1841.0744658836504</v>
       </c>
       <c r="L153" s="2">
-        <f>RATE(10,,J143,-'Real Returns 1792-2025'!$J153)</f>
+        <f>RATE(10,,J143,-'Real Returns 1792-2026'!$J153)</f>
         <v>7.7372619901783013E-2</v>
       </c>
       <c r="M153" s="2">
-        <f>RATE(10,,K143,-'Real Returns 1792-2025'!$K153)</f>
+        <f>RATE(10,,K143,-'Real Returns 1792-2026'!$K153)</f>
         <v>3.4717060177360454E-2</v>
       </c>
       <c r="N153" s="2">
-        <f>RATE(30,,J123,-'Real Returns 1792-2025'!$J153)</f>
+        <f>RATE(30,,J123,-'Real Returns 1792-2026'!$J153)</f>
         <v>3.7965978154626122E-2</v>
       </c>
       <c r="O153" s="2">
-        <f>RATE(30,,K123,-'Real Returns 1792-2025'!$K153)</f>
+        <f>RATE(30,,K123,-'Real Returns 1792-2026'!$K153)</f>
         <v>2.6728144350507212E-2</v>
       </c>
       <c r="P153" s="2">
-        <f>RATE(50,,J103,-'Real Returns 1792-2025'!$J153)</f>
+        <f>RATE(50,,J103,-'Real Returns 1792-2026'!$J153)</f>
         <v>4.9300266981138971E-2</v>
       </c>
       <c r="Q153" s="2">
-        <f>RATE(50,,K103,-'Real Returns 1792-2025'!$K153)</f>
+        <f>RATE(50,,K103,-'Real Returns 1792-2026'!$K153)</f>
         <v>3.4016857392669436E-2</v>
       </c>
       <c r="R153" s="2">
-        <f>RATE(100,,J53,-'Real Returns 1792-2025'!$J153)</f>
+        <f>RATE(100,,J53,-'Real Returns 1792-2026'!$J153)</f>
         <v>6.0149076481794586E-2</v>
       </c>
       <c r="S153" s="2">
-        <f>RATE(100,,K53,-'Real Returns 1792-2025'!$K153)</f>
+        <f>RATE(100,,K53,-'Real Returns 1792-2026'!$K153)</f>
         <v>5.3657915919483948E-2</v>
       </c>
     </row>
@@ -12131,35 +12131,35 @@
         <v>1928.1669217694248</v>
       </c>
       <c r="L154" s="2">
-        <f>RATE(10,,J144,-'Real Returns 1792-2025'!$J154)</f>
+        <f>RATE(10,,J144,-'Real Returns 1792-2026'!$J154)</f>
         <v>3.763629430235186E-2</v>
       </c>
       <c r="M154" s="2">
-        <f>RATE(10,,K144,-'Real Returns 1792-2025'!$K154)</f>
+        <f>RATE(10,,K144,-'Real Returns 1792-2026'!$K154)</f>
         <v>2.7071312948835025E-2</v>
       </c>
       <c r="N154" s="2">
-        <f>RATE(30,,J124,-'Real Returns 1792-2025'!$J154)</f>
+        <f>RATE(30,,J124,-'Real Returns 1792-2026'!$J154)</f>
         <v>4.6124965705409977E-2</v>
       </c>
       <c r="O154" s="2">
-        <f>RATE(30,,K124,-'Real Returns 1792-2025'!$K154)</f>
+        <f>RATE(30,,K124,-'Real Returns 1792-2026'!$K154)</f>
         <v>2.8662727061648165E-2</v>
       </c>
       <c r="P154" s="2">
-        <f>RATE(50,,J104,-'Real Returns 1792-2025'!$J154)</f>
+        <f>RATE(50,,J104,-'Real Returns 1792-2026'!$J154)</f>
         <v>5.6480557054165687E-2</v>
       </c>
       <c r="Q154" s="2">
-        <f>RATE(50,,K104,-'Real Returns 1792-2025'!$K154)</f>
+        <f>RATE(50,,K104,-'Real Returns 1792-2026'!$K154)</f>
         <v>3.3437819962133311E-2</v>
       </c>
       <c r="R154" s="2">
-        <f>RATE(100,,J54,-'Real Returns 1792-2025'!$J154)</f>
+        <f>RATE(100,,J54,-'Real Returns 1792-2026'!$J154)</f>
         <v>5.7993998544471105E-2</v>
       </c>
       <c r="S154" s="2">
-        <f>RATE(100,,K54,-'Real Returns 1792-2025'!$K154)</f>
+        <f>RATE(100,,K54,-'Real Returns 1792-2026'!$K154)</f>
         <v>4.942260250665087E-2</v>
       </c>
     </row>
@@ -12194,35 +12194,35 @@
         <v>2013.1108499088846</v>
       </c>
       <c r="L155" s="2">
-        <f>RATE(10,,J145,-'Real Returns 1792-2025'!$J155)</f>
+        <f>RATE(10,,J145,-'Real Returns 1792-2026'!$J155)</f>
         <v>7.1902612084040349E-2</v>
       </c>
       <c r="M155" s="2">
-        <f>RATE(10,,K145,-'Real Returns 1792-2025'!$K155)</f>
+        <f>RATE(10,,K145,-'Real Returns 1792-2026'!$K155)</f>
         <v>1.7542630838338829E-2</v>
       </c>
       <c r="N155" s="2">
-        <f>RATE(30,,J125,-'Real Returns 1792-2025'!$J155)</f>
+        <f>RATE(30,,J125,-'Real Returns 1792-2026'!$J155)</f>
         <v>5.4613448265265048E-2</v>
       </c>
       <c r="O155" s="2">
-        <f>RATE(30,,K125,-'Real Returns 1792-2025'!$K155)</f>
+        <f>RATE(30,,K125,-'Real Returns 1792-2026'!$K155)</f>
         <v>2.999843657423925E-2</v>
       </c>
       <c r="P155" s="2">
-        <f>RATE(50,,J105,-'Real Returns 1792-2025'!$J155)</f>
+        <f>RATE(50,,J105,-'Real Returns 1792-2026'!$J155)</f>
         <v>5.8857839941828763E-2</v>
       </c>
       <c r="Q155" s="2">
-        <f>RATE(50,,K105,-'Real Returns 1792-2025'!$K155)</f>
+        <f>RATE(50,,K105,-'Real Returns 1792-2026'!$K155)</f>
         <v>3.2319603430923133E-2</v>
       </c>
       <c r="R155" s="2">
-        <f>RATE(100,,J55,-'Real Returns 1792-2025'!$J155)</f>
+        <f>RATE(100,,J55,-'Real Returns 1792-2026'!$J155)</f>
         <v>5.8947200135881936E-2</v>
       </c>
       <c r="S155" s="2">
-        <f>RATE(100,,K55,-'Real Returns 1792-2025'!$K155)</f>
+        <f>RATE(100,,K55,-'Real Returns 1792-2026'!$K155)</f>
         <v>4.9333232048452469E-2</v>
       </c>
     </row>
@@ -12257,35 +12257,35 @@
         <v>2094.6838447533792</v>
       </c>
       <c r="L156" s="2">
-        <f>RATE(10,,J146,-'Real Returns 1792-2025'!$J156)</f>
+        <f>RATE(10,,J146,-'Real Returns 1792-2026'!$J156)</f>
         <v>5.993017659567601E-2</v>
       </c>
       <c r="M156" s="2">
-        <f>RATE(10,,K146,-'Real Returns 1792-2025'!$K156)</f>
+        <f>RATE(10,,K146,-'Real Returns 1792-2026'!$K156)</f>
         <v>1.4367655974333045E-2</v>
       </c>
       <c r="N156" s="2">
-        <f>RATE(30,,J126,-'Real Returns 1792-2025'!$J156)</f>
+        <f>RATE(30,,J126,-'Real Returns 1792-2026'!$J156)</f>
         <v>5.8306198962939731E-2</v>
       </c>
       <c r="O156" s="2">
-        <f>RATE(30,,K126,-'Real Returns 1792-2025'!$K156)</f>
+        <f>RATE(30,,K126,-'Real Returns 1792-2026'!$K156)</f>
         <v>2.9811211355126068E-2</v>
       </c>
       <c r="P156" s="2">
-        <f>RATE(50,,J106,-'Real Returns 1792-2025'!$J156)</f>
+        <f>RATE(50,,J106,-'Real Returns 1792-2026'!$J156)</f>
         <v>6.4902447147761555E-2</v>
       </c>
       <c r="Q156" s="2">
-        <f>RATE(50,,K106,-'Real Returns 1792-2025'!$K156)</f>
+        <f>RATE(50,,K106,-'Real Returns 1792-2026'!$K156)</f>
         <v>3.2200211251167961E-2</v>
       </c>
       <c r="R156" s="2">
-        <f>RATE(100,,J56,-'Real Returns 1792-2025'!$J156)</f>
+        <f>RATE(100,,J56,-'Real Returns 1792-2026'!$J156)</f>
         <v>6.2121425217679715E-2</v>
       </c>
       <c r="S156" s="2">
-        <f>RATE(100,,K56,-'Real Returns 1792-2025'!$K156)</f>
+        <f>RATE(100,,K56,-'Real Returns 1792-2026'!$K156)</f>
         <v>4.9666828051530103E-2</v>
       </c>
     </row>
@@ -12320,35 +12320,35 @@
         <v>1766.1715558466726</v>
       </c>
       <c r="L157" s="2">
-        <f>RATE(10,,J147,-'Real Returns 1792-2025'!$J157)</f>
+        <f>RATE(10,,J147,-'Real Returns 1792-2026'!$J157)</f>
         <v>7.6872213608350712E-3</v>
       </c>
       <c r="M157" s="2">
-        <f>RATE(10,,K147,-'Real Returns 1792-2025'!$K157)</f>
+        <f>RATE(10,,K147,-'Real Returns 1792-2026'!$K157)</f>
         <v>-9.3387838659642133E-3</v>
       </c>
       <c r="N157" s="2">
-        <f>RATE(30,,J127,-'Real Returns 1792-2025'!$J157)</f>
+        <f>RATE(30,,J127,-'Real Returns 1792-2026'!$J157)</f>
         <v>4.9461507829118088E-2</v>
       </c>
       <c r="O157" s="2">
-        <f>RATE(30,,K127,-'Real Returns 1792-2025'!$K157)</f>
+        <f>RATE(30,,K127,-'Real Returns 1792-2026'!$K157)</f>
         <v>2.6019366531500304E-2</v>
       </c>
       <c r="P157" s="2">
-        <f>RATE(50,,J107,-'Real Returns 1792-2025'!$J157)</f>
+        <f>RATE(50,,J107,-'Real Returns 1792-2026'!$J157)</f>
         <v>5.8683071787432498E-2</v>
       </c>
       <c r="Q157" s="2">
-        <f>RATE(50,,K107,-'Real Returns 1792-2025'!$K157)</f>
+        <f>RATE(50,,K107,-'Real Returns 1792-2026'!$K157)</f>
         <v>2.7375130469615941E-2</v>
       </c>
       <c r="R157" s="2">
-        <f>RATE(100,,J57,-'Real Returns 1792-2025'!$J157)</f>
+        <f>RATE(100,,J57,-'Real Returns 1792-2026'!$J157)</f>
         <v>5.9121088361637784E-2</v>
       </c>
       <c r="S157" s="2">
-        <f>RATE(100,,K57,-'Real Returns 1792-2025'!$K157)</f>
+        <f>RATE(100,,K57,-'Real Returns 1792-2026'!$K157)</f>
         <v>4.7496419513627645E-2</v>
       </c>
     </row>
@@ -12383,35 +12383,35 @@
         <v>1510.4753920477731</v>
       </c>
       <c r="L158" s="2">
-        <f>RATE(10,,J148,-'Real Returns 1792-2025'!$J158)</f>
+        <f>RATE(10,,J148,-'Real Returns 1792-2026'!$J158)</f>
         <v>4.2650224825676375E-2</v>
       </c>
       <c r="M158" s="2">
-        <f>RATE(10,,K148,-'Real Returns 1792-2025'!$K158)</f>
+        <f>RATE(10,,K148,-'Real Returns 1792-2026'!$K158)</f>
         <v>-1.7111683285096074E-2</v>
       </c>
       <c r="N158" s="2">
-        <f>RATE(30,,J128,-'Real Returns 1792-2025'!$J158)</f>
+        <f>RATE(30,,J128,-'Real Returns 1792-2026'!$J158)</f>
         <v>5.8373947242715322E-2</v>
       </c>
       <c r="O158" s="2">
-        <f>RATE(30,,K128,-'Real Returns 1792-2025'!$K158)</f>
+        <f>RATE(30,,K128,-'Real Returns 1792-2026'!$K158)</f>
         <v>3.0227922038817967E-2</v>
       </c>
       <c r="P158" s="2">
-        <f>RATE(50,,J108,-'Real Returns 1792-2025'!$J158)</f>
+        <f>RATE(50,,J108,-'Real Returns 1792-2026'!$J158)</f>
         <v>5.21905121414327E-2</v>
       </c>
       <c r="Q158" s="2">
-        <f>RATE(50,,K108,-'Real Returns 1792-2025'!$K158)</f>
+        <f>RATE(50,,K108,-'Real Returns 1792-2026'!$K158)</f>
         <v>2.1910522822966245E-2</v>
       </c>
       <c r="R158" s="2">
-        <f>RATE(100,,J58,-'Real Returns 1792-2025'!$J158)</f>
+        <f>RATE(100,,J58,-'Real Returns 1792-2026'!$J158)</f>
         <v>5.7502772374869428E-2</v>
       </c>
       <c r="S158" s="2">
-        <f>RATE(100,,K58,-'Real Returns 1792-2025'!$K158)</f>
+        <f>RATE(100,,K58,-'Real Returns 1792-2026'!$K158)</f>
         <v>4.5682226525969677E-2</v>
       </c>
     </row>
@@ -12446,35 +12446,35 @@
         <v>1581.7082772378267</v>
       </c>
       <c r="L159" s="2">
-        <f>RATE(10,,J149,-'Real Returns 1792-2025'!$J159)</f>
+        <f>RATE(10,,J149,-'Real Returns 1792-2026'!$J159)</f>
         <v>2.7621774659751522E-2</v>
       </c>
       <c r="M159" s="2">
-        <f>RATE(10,,K149,-'Real Returns 1792-2025'!$K159)</f>
+        <f>RATE(10,,K149,-'Real Returns 1792-2026'!$K159)</f>
         <v>-1.7773268375233169E-2</v>
       </c>
       <c r="N159" s="2">
-        <f>RATE(30,,J129,-'Real Returns 1792-2025'!$J159)</f>
+        <f>RATE(30,,J129,-'Real Returns 1792-2026'!$J159)</f>
         <v>6.0427688858228419E-2</v>
       </c>
       <c r="O159" s="2">
-        <f>RATE(30,,K129,-'Real Returns 1792-2025'!$K159)</f>
+        <f>RATE(30,,K129,-'Real Returns 1792-2026'!$K159)</f>
         <v>3.4844570674156895E-2</v>
       </c>
       <c r="P159" s="2">
-        <f>RATE(50,,J109,-'Real Returns 1792-2025'!$J159)</f>
+        <f>RATE(50,,J109,-'Real Returns 1792-2026'!$J159)</f>
         <v>4.7766815020462046E-2</v>
       </c>
       <c r="Q159" s="2">
-        <f>RATE(50,,K109,-'Real Returns 1792-2025'!$K159)</f>
+        <f>RATE(50,,K109,-'Real Returns 1792-2026'!$K159)</f>
         <v>2.0668297381472415E-2</v>
       </c>
       <c r="R159" s="2">
-        <f>RATE(100,,J59,-'Real Returns 1792-2025'!$J159)</f>
+        <f>RATE(100,,J59,-'Real Returns 1792-2026'!$J159)</f>
         <v>5.7684648706912749E-2</v>
       </c>
       <c r="S159" s="2">
-        <f>RATE(100,,K59,-'Real Returns 1792-2025'!$K159)</f>
+        <f>RATE(100,,K59,-'Real Returns 1792-2026'!$K159)</f>
         <v>4.3761567517181861E-2</v>
       </c>
     </row>
@@ -12509,35 +12509,35 @@
         <v>1723.4316227337226</v>
       </c>
       <c r="L160" s="2">
-        <f>RATE(10,,J150,-'Real Returns 1792-2025'!$J160)</f>
+        <f>RATE(10,,J150,-'Real Returns 1792-2026'!$J160)</f>
         <v>4.3738930073538101E-2</v>
       </c>
       <c r="M160" s="2">
-        <f>RATE(10,,K150,-'Real Returns 1792-2025'!$K160)</f>
+        <f>RATE(10,,K150,-'Real Returns 1792-2026'!$K160)</f>
         <v>-1.2444225160020434E-2</v>
       </c>
       <c r="N160" s="2">
-        <f>RATE(30,,J130,-'Real Returns 1792-2025'!$J160)</f>
+        <f>RATE(30,,J130,-'Real Returns 1792-2026'!$J160)</f>
         <v>6.756257415666693E-2</v>
       </c>
       <c r="O160" s="2">
-        <f>RATE(30,,K130,-'Real Returns 1792-2025'!$K160)</f>
+        <f>RATE(30,,K130,-'Real Returns 1792-2026'!$K160)</f>
         <v>4.4131575723991748E-2</v>
       </c>
       <c r="P160" s="2">
-        <f>RATE(50,,J110,-'Real Returns 1792-2025'!$J160)</f>
+        <f>RATE(50,,J110,-'Real Returns 1792-2026'!$J160)</f>
         <v>5.1656394908198205E-2</v>
       </c>
       <c r="Q160" s="2">
-        <f>RATE(50,,K110,-'Real Returns 1792-2025'!$K160)</f>
+        <f>RATE(50,,K110,-'Real Returns 1792-2026'!$K160)</f>
         <v>2.1961439466272284E-2</v>
       </c>
       <c r="R160" s="2">
-        <f>RATE(100,,J60,-'Real Returns 1792-2025'!$J160)</f>
+        <f>RATE(100,,J60,-'Real Returns 1792-2026'!$J160)</f>
         <v>5.9633210225138317E-2</v>
       </c>
       <c r="S160" s="2">
-        <f>RATE(100,,K60,-'Real Returns 1792-2025'!$K160)</f>
+        <f>RATE(100,,K60,-'Real Returns 1792-2026'!$K160)</f>
         <v>4.3205196719036575E-2</v>
       </c>
     </row>
@@ -12572,35 +12572,35 @@
         <v>1649.1504602083944</v>
       </c>
       <c r="L161" s="2">
-        <f>RATE(10,,J151,-'Real Returns 1792-2025'!$J161)</f>
+        <f>RATE(10,,J151,-'Real Returns 1792-2026'!$J161)</f>
         <v>7.9584190849052674E-2</v>
       </c>
       <c r="M161" s="2">
-        <f>RATE(10,,K151,-'Real Returns 1792-2025'!$K161)</f>
+        <f>RATE(10,,K151,-'Real Returns 1792-2026'!$K161)</f>
         <v>-2.0419010614235945E-2</v>
       </c>
       <c r="N161" s="2">
-        <f>RATE(30,,J131,-'Real Returns 1792-2025'!$J161)</f>
+        <f>RATE(30,,J131,-'Real Returns 1792-2026'!$J161)</f>
         <v>8.0663154227110026E-2</v>
       </c>
       <c r="O161" s="2">
-        <f>RATE(30,,K131,-'Real Returns 1792-2025'!$K161)</f>
+        <f>RATE(30,,K131,-'Real Returns 1792-2026'!$K161)</f>
         <v>4.0475540144345179E-2</v>
       </c>
       <c r="P161" s="2">
-        <f>RATE(50,,J111,-'Real Returns 1792-2025'!$J161)</f>
+        <f>RATE(50,,J111,-'Real Returns 1792-2026'!$J161)</f>
         <v>5.2751596561300511E-2</v>
       </c>
       <c r="Q161" s="2">
-        <f>RATE(50,,K111,-'Real Returns 1792-2025'!$K161)</f>
+        <f>RATE(50,,K111,-'Real Returns 1792-2026'!$K161)</f>
         <v>1.98275789337506E-2</v>
       </c>
       <c r="R161" s="2">
-        <f>RATE(100,,J61,-'Real Returns 1792-2025'!$J161)</f>
+        <f>RATE(100,,J61,-'Real Returns 1792-2026'!$J161)</f>
         <v>5.993983066342299E-2</v>
       </c>
       <c r="S161" s="2">
-        <f>RATE(100,,K61,-'Real Returns 1792-2025'!$K161)</f>
+        <f>RATE(100,,K61,-'Real Returns 1792-2026'!$K161)</f>
         <v>4.1658550412344425E-2</v>
       </c>
     </row>
@@ -12635,35 +12635,35 @@
         <v>1533.3689552902222</v>
       </c>
       <c r="L162" s="2">
-        <f>RATE(10,,J152,-'Real Returns 1792-2025'!$J162)</f>
+        <f>RATE(10,,J152,-'Real Returns 1792-2026'!$J162)</f>
         <v>0.10910604939921242</v>
       </c>
       <c r="M162" s="2">
-        <f>RATE(10,,K152,-'Real Returns 1792-2025'!$K162)</f>
+        <f>RATE(10,,K152,-'Real Returns 1792-2026'!$K162)</f>
         <v>-2.0414040347616128E-2</v>
       </c>
       <c r="N162" s="2">
-        <f>RATE(30,,J132,-'Real Returns 1792-2025'!$J162)</f>
+        <f>RATE(30,,J132,-'Real Returns 1792-2026'!$J162)</f>
         <v>7.7127028021226993E-2</v>
       </c>
       <c r="O162" s="2">
-        <f>RATE(30,,K132,-'Real Returns 1792-2025'!$K162)</f>
+        <f>RATE(30,,K132,-'Real Returns 1792-2026'!$K162)</f>
         <v>2.8697361429230052E-2</v>
       </c>
       <c r="P162" s="2">
-        <f>RATE(50,,J112,-'Real Returns 1792-2025'!$J162)</f>
+        <f>RATE(50,,J112,-'Real Returns 1792-2026'!$J162)</f>
         <v>5.1569209027934874E-2</v>
       </c>
       <c r="Q162" s="2">
-        <f>RATE(50,,K112,-'Real Returns 1792-2025'!$K162)</f>
+        <f>RATE(50,,K112,-'Real Returns 1792-2026'!$K162)</f>
         <v>1.7541496359584151E-2</v>
       </c>
       <c r="R162" s="2">
-        <f>RATE(100,,J62,-'Real Returns 1792-2025'!$J162)</f>
+        <f>RATE(100,,J62,-'Real Returns 1792-2026'!$J162)</f>
         <v>6.1404975781815564E-2</v>
       </c>
       <c r="S162" s="2">
-        <f>RATE(100,,K62,-'Real Returns 1792-2025'!$K162)</f>
+        <f>RATE(100,,K62,-'Real Returns 1792-2026'!$K162)</f>
         <v>4.0443194831317697E-2</v>
       </c>
     </row>
@@ -12698,35 +12698,35 @@
         <v>1558.0647331831433</v>
       </c>
       <c r="L163" s="2">
-        <f>RATE(10,,J153,-'Real Returns 1792-2025'!$J163)</f>
+        <f>RATE(10,,J153,-'Real Returns 1792-2026'!$J163)</f>
         <v>0.1046824196431872</v>
       </c>
       <c r="M163" s="2">
-        <f>RATE(10,,K153,-'Real Returns 1792-2025'!$K163)</f>
+        <f>RATE(10,,K153,-'Real Returns 1792-2026'!$K163)</f>
         <v>-1.6551970998294738E-2</v>
       </c>
       <c r="N163" s="2">
-        <f>RATE(30,,J133,-'Real Returns 1792-2025'!$J163)</f>
+        <f>RATE(30,,J133,-'Real Returns 1792-2026'!$J163)</f>
         <v>7.1398719740572256E-2</v>
       </c>
       <c r="O163" s="2">
-        <f>RATE(30,,K133,-'Real Returns 1792-2025'!$K163)</f>
+        <f>RATE(30,,K133,-'Real Returns 1792-2026'!$K163)</f>
         <v>2.6357344075331725E-2</v>
       </c>
       <c r="P163" s="2">
-        <f>RATE(50,,J113,-'Real Returns 1792-2025'!$J163)</f>
+        <f>RATE(50,,J113,-'Real Returns 1792-2026'!$J163)</f>
         <v>5.2420677934980633E-2</v>
       </c>
       <c r="Q163" s="2">
-        <f>RATE(50,,K113,-'Real Returns 1792-2025'!$K163)</f>
+        <f>RATE(50,,K113,-'Real Returns 1792-2026'!$K163)</f>
         <v>1.781605385138493E-2</v>
       </c>
       <c r="R163" s="2">
-        <f>RATE(100,,J63,-'Real Returns 1792-2025'!$J163)</f>
+        <f>RATE(100,,J63,-'Real Returns 1792-2026'!$J163)</f>
         <v>6.0648786518605148E-2</v>
       </c>
       <c r="S163" s="2">
-        <f>RATE(100,,K63,-'Real Returns 1792-2025'!$K163)</f>
+        <f>RATE(100,,K63,-'Real Returns 1792-2026'!$K163)</f>
         <v>3.9542025647223471E-2</v>
       </c>
     </row>
@@ -12761,35 +12761,35 @@
         <v>1619.544758274139</v>
       </c>
       <c r="L164" s="2">
-        <f>RATE(10,,J154,-'Real Returns 1792-2025'!$J164)</f>
+        <f>RATE(10,,J154,-'Real Returns 1792-2026'!$J164)</f>
         <v>9.1629083787859458E-2</v>
       </c>
       <c r="M164" s="2">
-        <f>RATE(10,,K154,-'Real Returns 1792-2025'!$K164)</f>
+        <f>RATE(10,,K154,-'Real Returns 1792-2026'!$K164)</f>
         <v>-1.729122814896214E-2</v>
       </c>
       <c r="N164" s="2">
-        <f>RATE(30,,J134,-'Real Returns 1792-2025'!$J164)</f>
+        <f>RATE(30,,J134,-'Real Returns 1792-2026'!$J164)</f>
         <v>7.2177505523965541E-2</v>
       </c>
       <c r="O164" s="2">
-        <f>RATE(30,,K134,-'Real Returns 1792-2025'!$K164)</f>
+        <f>RATE(30,,K134,-'Real Returns 1792-2026'!$K164)</f>
         <v>2.736505618556347E-2</v>
       </c>
       <c r="P164" s="2">
-        <f>RATE(50,,J114,-'Real Returns 1792-2025'!$J164)</f>
+        <f>RATE(50,,J114,-'Real Returns 1792-2026'!$J164)</f>
         <v>5.7725067162532916E-2</v>
       </c>
       <c r="Q164" s="2">
-        <f>RATE(50,,K114,-'Real Returns 1792-2025'!$K164)</f>
+        <f>RATE(50,,K114,-'Real Returns 1792-2026'!$K164)</f>
         <v>1.8778658517272794E-2</v>
       </c>
       <c r="R164" s="2">
-        <f>RATE(100,,J64,-'Real Returns 1792-2025'!$J164)</f>
+        <f>RATE(100,,J64,-'Real Returns 1792-2026'!$J164)</f>
         <v>6.2649279713715839E-2</v>
       </c>
       <c r="S164" s="2">
-        <f>RATE(100,,K64,-'Real Returns 1792-2025'!$K164)</f>
+        <f>RATE(100,,K64,-'Real Returns 1792-2026'!$K164)</f>
         <v>3.997843457346268E-2</v>
       </c>
     </row>
@@ -12824,35 +12824,35 @@
         <v>1675.0809458211293</v>
       </c>
       <c r="L165" s="2">
-        <f>RATE(10,,J155,-'Real Returns 1792-2025'!$J165)</f>
+        <f>RATE(10,,J155,-'Real Returns 1792-2026'!$J165)</f>
         <v>0.11346607051320008</v>
       </c>
       <c r="M165" s="2">
-        <f>RATE(10,,K155,-'Real Returns 1792-2025'!$K165)</f>
+        <f>RATE(10,,K155,-'Real Returns 1792-2026'!$K165)</f>
         <v>-1.8214054229463077E-2</v>
       </c>
       <c r="N165" s="2">
-        <f>RATE(30,,J135,-'Real Returns 1792-2025'!$J165)</f>
+        <f>RATE(30,,J135,-'Real Returns 1792-2026'!$J165)</f>
         <v>7.6944960885107508E-2</v>
       </c>
       <c r="O165" s="2">
-        <f>RATE(30,,K135,-'Real Returns 1792-2025'!$K165)</f>
+        <f>RATE(30,,K135,-'Real Returns 1792-2026'!$K165)</f>
         <v>2.5744203026963754E-2</v>
       </c>
       <c r="P165" s="2">
-        <f>RATE(50,,J115,-'Real Returns 1792-2025'!$J165)</f>
+        <f>RATE(50,,J115,-'Real Returns 1792-2026'!$J165)</f>
         <v>5.9779305489906273E-2</v>
       </c>
       <c r="Q165" s="2">
-        <f>RATE(50,,K115,-'Real Returns 1792-2025'!$K165)</f>
+        <f>RATE(50,,K115,-'Real Returns 1792-2026'!$K165)</f>
         <v>1.7143200380951476E-2</v>
       </c>
       <c r="R165" s="2">
-        <f>RATE(100,,J65,-'Real Returns 1792-2025'!$J165)</f>
+        <f>RATE(100,,J65,-'Real Returns 1792-2026'!$J165)</f>
         <v>6.8467892532323563E-2</v>
       </c>
       <c r="S165" s="2">
-        <f>RATE(100,,K65,-'Real Returns 1792-2025'!$K165)</f>
+        <f>RATE(100,,K65,-'Real Returns 1792-2026'!$K165)</f>
         <v>4.1070367570392251E-2</v>
       </c>
     </row>
@@ -12887,35 +12887,35 @@
         <v>1700.627296826576</v>
       </c>
       <c r="L166" s="2">
-        <f>RATE(10,,J156,-'Real Returns 1792-2025'!$J166)</f>
+        <f>RATE(10,,J156,-'Real Returns 1792-2026'!$J166)</f>
         <v>9.561765944599411E-2</v>
       </c>
       <c r="M166" s="2">
-        <f>RATE(10,,K156,-'Real Returns 1792-2025'!$K166)</f>
+        <f>RATE(10,,K156,-'Real Returns 1792-2026'!$K166)</f>
         <v>-2.0624881760888829E-2</v>
       </c>
       <c r="N166" s="2">
-        <f>RATE(30,,J136,-'Real Returns 1792-2025'!$J166)</f>
+        <f>RATE(30,,J136,-'Real Returns 1792-2026'!$J166)</f>
         <v>7.6659720803444784E-2</v>
       </c>
       <c r="O166" s="2">
-        <f>RATE(30,,K136,-'Real Returns 1792-2025'!$K166)</f>
+        <f>RATE(30,,K136,-'Real Returns 1792-2026'!$K166)</f>
         <v>2.4772393845321612E-2</v>
       </c>
       <c r="P166" s="2">
-        <f>RATE(50,,J116,-'Real Returns 1792-2025'!$J166)</f>
+        <f>RATE(50,,J116,-'Real Returns 1792-2026'!$J166)</f>
         <v>5.9693674803384729E-2</v>
       </c>
       <c r="Q166" s="2">
-        <f>RATE(50,,K116,-'Real Returns 1792-2025'!$K166)</f>
+        <f>RATE(50,,K116,-'Real Returns 1792-2026'!$K166)</f>
         <v>1.6751946395476659E-2</v>
       </c>
       <c r="R166" s="2">
-        <f>RATE(100,,J66,-'Real Returns 1792-2025'!$J166)</f>
+        <f>RATE(100,,J66,-'Real Returns 1792-2026'!$J166)</f>
         <v>7.0711103144124862E-2</v>
       </c>
       <c r="S166" s="2">
-        <f>RATE(100,,K66,-'Real Returns 1792-2025'!$K166)</f>
+        <f>RATE(100,,K66,-'Real Returns 1792-2026'!$K166)</f>
         <v>4.0371302819307051E-2</v>
       </c>
     </row>
@@ -12950,35 +12950,35 @@
         <v>1535.6993852857631</v>
       </c>
       <c r="L167" s="2">
-        <f>RATE(10,,J157,-'Real Returns 1792-2025'!$J167)</f>
+        <f>RATE(10,,J157,-'Real Returns 1792-2026'!$J167)</f>
         <v>0.13240636715998588</v>
       </c>
       <c r="M167" s="2">
-        <f>RATE(10,,K157,-'Real Returns 1792-2025'!$K167)</f>
+        <f>RATE(10,,K157,-'Real Returns 1792-2026'!$K167)</f>
         <v>-1.3885528077492229E-2</v>
       </c>
       <c r="N167" s="2">
-        <f>RATE(30,,J137,-'Real Returns 1792-2025'!$J167)</f>
+        <f>RATE(30,,J137,-'Real Returns 1792-2026'!$J167)</f>
         <v>7.4165388390129899E-2</v>
       </c>
       <c r="O167" s="2">
-        <f>RATE(30,,K137,-'Real Returns 1792-2025'!$K167)</f>
+        <f>RATE(30,,K137,-'Real Returns 1792-2026'!$K167)</f>
         <v>1.7664689703780951E-2</v>
       </c>
       <c r="P167" s="2">
-        <f>RATE(50,,J117,-'Real Returns 1792-2025'!$J167)</f>
+        <f>RATE(50,,J117,-'Real Returns 1792-2026'!$J167)</f>
         <v>6.1300748843720207E-2</v>
       </c>
       <c r="Q167" s="2">
-        <f>RATE(50,,K117,-'Real Returns 1792-2025'!$K167)</f>
+        <f>RATE(50,,K117,-'Real Returns 1792-2026'!$K167)</f>
         <v>1.522627813958745E-2</v>
       </c>
       <c r="R167" s="2">
-        <f>RATE(100,,J67,-'Real Returns 1792-2025'!$J167)</f>
+        <f>RATE(100,,J67,-'Real Returns 1792-2026'!$J167)</f>
         <v>6.9896291333971988E-2</v>
       </c>
       <c r="S167" s="2">
-        <f>RATE(100,,K67,-'Real Returns 1792-2025'!$K167)</f>
+        <f>RATE(100,,K67,-'Real Returns 1792-2026'!$K167)</f>
         <v>3.8562390276771809E-2</v>
       </c>
     </row>
@@ -13013,35 +13013,35 @@
         <v>1560.3334560845637</v>
       </c>
       <c r="L168" s="2">
-        <f>RATE(10,,J158,-'Real Returns 1792-2025'!$J168)</f>
+        <f>RATE(10,,J158,-'Real Returns 1792-2026'!$J168)</f>
         <v>0.13841151505857774</v>
       </c>
       <c r="M168" s="2">
-        <f>RATE(10,,K158,-'Real Returns 1792-2025'!$K168)</f>
+        <f>RATE(10,,K158,-'Real Returns 1792-2026'!$K168)</f>
         <v>3.2527910676112678E-3</v>
       </c>
       <c r="N168" s="2">
-        <f>RATE(30,,J138,-'Real Returns 1792-2025'!$J168)</f>
+        <f>RATE(30,,J138,-'Real Returns 1792-2026'!$J168)</f>
         <v>6.157451820487931E-2</v>
       </c>
       <c r="O168" s="2">
-        <f>RATE(30,,K138,-'Real Returns 1792-2025'!$K168)</f>
+        <f>RATE(30,,K138,-'Real Returns 1792-2026'!$K168)</f>
         <v>1.505548811737655E-2</v>
       </c>
       <c r="P168" s="2">
-        <f>RATE(50,,J118,-'Real Returns 1792-2025'!$J168)</f>
+        <f>RATE(50,,J118,-'Real Returns 1792-2026'!$J168)</f>
         <v>6.6137183500031907E-2</v>
       </c>
       <c r="Q168" s="2">
-        <f>RATE(50,,K118,-'Real Returns 1792-2025'!$K168)</f>
+        <f>RATE(50,,K118,-'Real Returns 1792-2026'!$K168)</f>
         <v>1.6588993665680517E-2</v>
       </c>
       <c r="R168" s="2">
-        <f>RATE(100,,J68,-'Real Returns 1792-2025'!$J168)</f>
+        <f>RATE(100,,J68,-'Real Returns 1792-2026'!$J168)</f>
         <v>7.0645541222115554E-2</v>
       </c>
       <c r="S168" s="2">
-        <f>RATE(100,,K68,-'Real Returns 1792-2025'!$K168)</f>
+        <f>RATE(100,,K68,-'Real Returns 1792-2026'!$K168)</f>
         <v>3.8166249827770213E-2</v>
       </c>
     </row>
@@ -13076,35 +13076,35 @@
         <v>1468.2010747631061</v>
       </c>
       <c r="L169" s="2">
-        <f>RATE(10,,J159,-'Real Returns 1792-2025'!$J169)</f>
+        <f>RATE(10,,J159,-'Real Returns 1792-2026'!$J169)</f>
         <v>0.1691669526015831</v>
       </c>
       <c r="M169" s="2">
-        <f>RATE(10,,K159,-'Real Returns 1792-2025'!$K169)</f>
+        <f>RATE(10,,K159,-'Real Returns 1792-2026'!$K169)</f>
         <v>-7.4190974493292252E-3</v>
       </c>
       <c r="N169" s="2">
-        <f>RATE(30,,J139,-'Real Returns 1792-2025'!$J169)</f>
+        <f>RATE(30,,J139,-'Real Returns 1792-2026'!$J169)</f>
         <v>5.8711774399596038E-2</v>
       </c>
       <c r="O169" s="2">
-        <f>RATE(30,,K139,-'Real Returns 1792-2025'!$K169)</f>
+        <f>RATE(30,,K139,-'Real Returns 1792-2026'!$K169)</f>
         <v>1.2395605001546833E-2</v>
       </c>
       <c r="P169" s="2">
-        <f>RATE(50,,J119,-'Real Returns 1792-2025'!$J169)</f>
+        <f>RATE(50,,J119,-'Real Returns 1792-2026'!$J169)</f>
         <v>6.5494636295381339E-2</v>
       </c>
       <c r="Q169" s="2">
-        <f>RATE(50,,K119,-'Real Returns 1792-2025'!$K169)</f>
+        <f>RATE(50,,K119,-'Real Returns 1792-2026'!$K169)</f>
         <v>1.2665085982154357E-2</v>
       </c>
       <c r="R169" s="2">
-        <f>RATE(100,,J69,-'Real Returns 1792-2025'!$J169)</f>
+        <f>RATE(100,,J69,-'Real Returns 1792-2026'!$J169)</f>
         <v>7.2670889066465696E-2</v>
       </c>
       <c r="S169" s="2">
-        <f>RATE(100,,K69,-'Real Returns 1792-2025'!$K169)</f>
+        <f>RATE(100,,K69,-'Real Returns 1792-2026'!$K169)</f>
         <v>3.6213190281087583E-2</v>
       </c>
     </row>
@@ -13139,35 +13139,35 @@
         <v>1422.8851060110555</v>
       </c>
       <c r="L170" s="2">
-        <f>RATE(10,,J160,-'Real Returns 1792-2025'!$J170)</f>
+        <f>RATE(10,,J160,-'Real Returns 1792-2026'!$J170)</f>
         <v>0.14743177644477359</v>
       </c>
       <c r="M170" s="2">
-        <f>RATE(10,,K160,-'Real Returns 1792-2025'!$K170)</f>
+        <f>RATE(10,,K160,-'Real Returns 1792-2026'!$K170)</f>
         <v>-1.8980641084467162E-2</v>
       </c>
       <c r="N170" s="2">
-        <f>RATE(30,,J140,-'Real Returns 1792-2025'!$J170)</f>
+        <f>RATE(30,,J140,-'Real Returns 1792-2026'!$J170)</f>
         <v>6.5458838450514131E-2</v>
       </c>
       <c r="O170" s="2">
-        <f>RATE(30,,K140,-'Real Returns 1792-2025'!$K170)</f>
+        <f>RATE(30,,K140,-'Real Returns 1792-2026'!$K170)</f>
         <v>9.9047034598773731E-3</v>
       </c>
       <c r="P170" s="2">
-        <f>RATE(50,,J120,-'Real Returns 1792-2025'!$J170)</f>
+        <f>RATE(50,,J120,-'Real Returns 1792-2026'!$J170)</f>
         <v>6.3161868140252E-2</v>
       </c>
       <c r="Q170" s="2">
-        <f>RATE(50,,K120,-'Real Returns 1792-2025'!$K170)</f>
+        <f>RATE(50,,K120,-'Real Returns 1792-2026'!$K170)</f>
         <v>1.1676261102698576E-2</v>
       </c>
       <c r="R170" s="2">
-        <f>RATE(100,,J70,-'Real Returns 1792-2025'!$J170)</f>
+        <f>RATE(100,,J70,-'Real Returns 1792-2026'!$J170)</f>
         <v>7.2966303540903374E-2</v>
       </c>
       <c r="S170" s="2">
-        <f>RATE(100,,K70,-'Real Returns 1792-2025'!$K170)</f>
+        <f>RATE(100,,K70,-'Real Returns 1792-2026'!$K170)</f>
         <v>3.5463290935067546E-2</v>
       </c>
     </row>
@@ -13202,35 +13202,35 @@
         <v>1529.9421596648524</v>
       </c>
       <c r="L171" s="2">
-        <f>RATE(10,,J161,-'Real Returns 1792-2025'!$J171)</f>
+        <f>RATE(10,,J161,-'Real Returns 1792-2026'!$J171)</f>
         <v>0.13577695045815466</v>
       </c>
       <c r="M171" s="2">
-        <f>RATE(10,,K161,-'Real Returns 1792-2025'!$K171)</f>
+        <f>RATE(10,,K161,-'Real Returns 1792-2026'!$K171)</f>
         <v>-7.4749577143085914E-3</v>
       </c>
       <c r="N171" s="2">
-        <f>RATE(30,,J141,-'Real Returns 1792-2025'!$J171)</f>
+        <f>RATE(30,,J141,-'Real Returns 1792-2026'!$J171)</f>
         <v>7.9359920302875947E-2</v>
       </c>
       <c r="O171" s="2">
-        <f>RATE(30,,K141,-'Real Returns 1792-2025'!$K171)</f>
+        <f>RATE(30,,K141,-'Real Returns 1792-2026'!$K171)</f>
         <v>7.659748343131486E-3</v>
       </c>
       <c r="P171" s="2">
-        <f>RATE(50,,J121,-'Real Returns 1792-2025'!$J171)</f>
+        <f>RATE(50,,J121,-'Real Returns 1792-2026'!$J171)</f>
         <v>6.7121011848642609E-2</v>
       </c>
       <c r="Q171" s="2">
-        <f>RATE(50,,K121,-'Real Returns 1792-2025'!$K171)</f>
+        <f>RATE(50,,K121,-'Real Returns 1792-2026'!$K171)</f>
         <v>1.2960663343912575E-2</v>
       </c>
       <c r="R171" s="2">
-        <f>RATE(100,,J71,-'Real Returns 1792-2025'!$J171)</f>
+        <f>RATE(100,,J71,-'Real Returns 1792-2026'!$J171)</f>
         <v>7.2857239518459585E-2</v>
       </c>
       <c r="S171" s="2">
-        <f>RATE(100,,K71,-'Real Returns 1792-2025'!$K171)</f>
+        <f>RATE(100,,K71,-'Real Returns 1792-2026'!$K171)</f>
         <v>3.6290111779142653E-2</v>
       </c>
     </row>
@@ -13265,35 +13265,35 @@
         <v>1560.2622394610089</v>
       </c>
       <c r="L172" s="2">
-        <f>RATE(10,,J162,-'Real Returns 1792-2025'!$J172)</f>
+        <f>RATE(10,,J162,-'Real Returns 1792-2026'!$J172)</f>
         <v>0.13869551044664127</v>
       </c>
       <c r="M172" s="2">
-        <f>RATE(10,,K162,-'Real Returns 1792-2025'!$K172)</f>
+        <f>RATE(10,,K162,-'Real Returns 1792-2026'!$K172)</f>
         <v>1.7401786650683162E-3</v>
       </c>
       <c r="N172" s="2">
-        <f>RATE(30,,J142,-'Real Returns 1792-2025'!$J172)</f>
+        <f>RATE(30,,J142,-'Real Returns 1792-2026'!$J172)</f>
         <v>0.10433815215021479</v>
       </c>
       <c r="O172" s="2">
-        <f>RATE(30,,K142,-'Real Returns 1792-2025'!$K172)</f>
+        <f>RATE(30,,K142,-'Real Returns 1792-2026'!$K172)</f>
         <v>1.1565705560530999E-2</v>
       </c>
       <c r="P172" s="2">
-        <f>RATE(50,,J122,-'Real Returns 1792-2025'!$J172)</f>
+        <f>RATE(50,,J122,-'Real Returns 1792-2026'!$J172)</f>
         <v>6.9447452658267739E-2</v>
       </c>
       <c r="Q172" s="2">
-        <f>RATE(50,,K122,-'Real Returns 1792-2025'!$K172)</f>
+        <f>RATE(50,,K122,-'Real Returns 1792-2026'!$K172)</f>
         <v>1.2709756238337928E-2</v>
       </c>
       <c r="R172" s="2">
-        <f>RATE(100,,J72,-'Real Returns 1792-2025'!$J172)</f>
+        <f>RATE(100,,J72,-'Real Returns 1792-2026'!$J172)</f>
         <v>7.4879804570815625E-2</v>
       </c>
       <c r="S172" s="2">
-        <f>RATE(100,,K72,-'Real Returns 1792-2025'!$K172)</f>
+        <f>RATE(100,,K72,-'Real Returns 1792-2026'!$K172)</f>
         <v>3.6915027807715182E-2</v>
       </c>
     </row>
@@ -13328,35 +13328,35 @@
         <v>1664.4318631140488</v>
       </c>
       <c r="L173" s="2">
-        <f>RATE(10,,J163,-'Real Returns 1792-2025'!$J173)</f>
+        <f>RATE(10,,J163,-'Real Returns 1792-2026'!$J173)</f>
         <v>0.12313457692459877</v>
       </c>
       <c r="M173" s="2">
-        <f>RATE(10,,K163,-'Real Returns 1792-2025'!$K173)</f>
+        <f>RATE(10,,K163,-'Real Returns 1792-2026'!$K173)</f>
         <v>6.6257886938517864E-3</v>
       </c>
       <c r="N173" s="2">
-        <f>RATE(30,,J143,-'Real Returns 1792-2025'!$J173)</f>
+        <f>RATE(30,,J143,-'Real Returns 1792-2026'!$J173)</f>
         <v>0.1015690486689316</v>
       </c>
       <c r="O173" s="2">
-        <f>RATE(30,,K143,-'Real Returns 1792-2025'!$K173)</f>
+        <f>RATE(30,,K143,-'Real Returns 1792-2026'!$K173)</f>
         <v>8.0460188606205178E-3</v>
       </c>
       <c r="P173" s="2">
-        <f>RATE(50,,J123,-'Real Returns 1792-2025'!$J173)</f>
+        <f>RATE(50,,J123,-'Real Returns 1792-2026'!$J173)</f>
         <v>6.7686420811365638E-2</v>
       </c>
       <c r="Q173" s="2">
-        <f>RATE(50,,K123,-'Real Returns 1792-2025'!$K173)</f>
+        <f>RATE(50,,K123,-'Real Returns 1792-2026'!$K173)</f>
         <v>1.390478692830327E-2</v>
       </c>
       <c r="R173" s="2">
-        <f>RATE(100,,J73,-'Real Returns 1792-2025'!$J173)</f>
+        <f>RATE(100,,J73,-'Real Returns 1792-2026'!$J173)</f>
         <v>7.0712550278617073E-2</v>
       </c>
       <c r="S173" s="2">
-        <f>RATE(100,,K73,-'Real Returns 1792-2025'!$K173)</f>
+        <f>RATE(100,,K73,-'Real Returns 1792-2026'!$K173)</f>
         <v>3.7572979031328446E-2</v>
       </c>
     </row>
@@ -13391,35 +13391,35 @@
         <v>1667.4486331694166</v>
       </c>
       <c r="L174" s="2">
-        <f>RATE(10,,J164,-'Real Returns 1792-2025'!$J174)</f>
+        <f>RATE(10,,J164,-'Real Returns 1792-2026'!$J174)</f>
         <v>0.13472258981204616</v>
       </c>
       <c r="M174" s="2">
-        <f>RATE(10,,K164,-'Real Returns 1792-2025'!$K174)</f>
+        <f>RATE(10,,K164,-'Real Returns 1792-2026'!$K174)</f>
         <v>2.9192123557432552E-3</v>
       </c>
       <c r="N174" s="2">
-        <f>RATE(30,,J144,-'Real Returns 1792-2025'!$J174)</f>
+        <f>RATE(30,,J144,-'Real Returns 1792-2026'!$J174)</f>
         <v>8.7268111767438941E-2</v>
       </c>
       <c r="O174" s="2">
-        <f>RATE(30,,K144,-'Real Returns 1792-2025'!$K174)</f>
+        <f>RATE(30,,K144,-'Real Returns 1792-2026'!$K174)</f>
         <v>4.0695445346704429E-3</v>
       </c>
       <c r="P174" s="2">
-        <f>RATE(50,,J124,-'Real Returns 1792-2025'!$J174)</f>
+        <f>RATE(50,,J124,-'Real Returns 1792-2026'!$J174)</f>
         <v>7.2366157397090888E-2</v>
       </c>
       <c r="Q174" s="2">
-        <f>RATE(50,,K124,-'Real Returns 1792-2025'!$K174)</f>
+        <f>RATE(50,,K124,-'Real Returns 1792-2026'!$K174)</f>
         <v>1.4149448826662653E-2</v>
       </c>
       <c r="R174" s="2">
-        <f>RATE(100,,J74,-'Real Returns 1792-2025'!$J174)</f>
+        <f>RATE(100,,J74,-'Real Returns 1792-2026'!$J174)</f>
         <v>7.2139465638280095E-2</v>
       </c>
       <c r="S174" s="2">
-        <f>RATE(100,,K74,-'Real Returns 1792-2025'!$K174)</f>
+        <f>RATE(100,,K74,-'Real Returns 1792-2026'!$K174)</f>
         <v>3.9112818737744914E-2</v>
       </c>
     </row>
@@ -13454,35 +13454,35 @@
         <v>1709.0011191767403</v>
       </c>
       <c r="L175" s="2">
-        <f>RATE(10,,J165,-'Real Returns 1792-2025'!$J175)</f>
+        <f>RATE(10,,J165,-'Real Returns 1792-2026'!$J175)</f>
         <v>0.11033322778069971</v>
       </c>
       <c r="M175" s="2">
-        <f>RATE(10,,K165,-'Real Returns 1792-2025'!$K175)</f>
+        <f>RATE(10,,K165,-'Real Returns 1792-2026'!$K175)</f>
         <v>2.0067677719433161E-3</v>
       </c>
       <c r="N175" s="2">
-        <f>RATE(30,,J145,-'Real Returns 1792-2025'!$J175)</f>
+        <f>RATE(30,,J145,-'Real Returns 1792-2026'!$J175)</f>
         <v>9.8403440514712781E-2</v>
       </c>
       <c r="O175" s="2">
-        <f>RATE(30,,K145,-'Real Returns 1792-2025'!$K175)</f>
+        <f>RATE(30,,K145,-'Real Returns 1792-2026'!$K175)</f>
         <v>3.3783030736434042E-4</v>
       </c>
       <c r="P175" s="2">
-        <f>RATE(50,,J125,-'Real Returns 1792-2025'!$J175)</f>
+        <f>RATE(50,,J125,-'Real Returns 1792-2026'!$J175)</f>
         <v>7.7164539600174248E-2</v>
       </c>
       <c r="Q175" s="2">
-        <f>RATE(50,,K125,-'Real Returns 1792-2025'!$K175)</f>
+        <f>RATE(50,,K125,-'Real Returns 1792-2026'!$K175)</f>
         <v>1.4563963465620725E-2</v>
       </c>
       <c r="R175" s="2">
-        <f>RATE(100,,J75,-'Real Returns 1792-2025'!$J175)</f>
+        <f>RATE(100,,J75,-'Real Returns 1792-2026'!$J175)</f>
         <v>7.452093699155056E-2</v>
       </c>
       <c r="S175" s="2">
-        <f>RATE(100,,K75,-'Real Returns 1792-2025'!$K175)</f>
+        <f>RATE(100,,K75,-'Real Returns 1792-2026'!$K175)</f>
         <v>3.9977987989148631E-2</v>
       </c>
     </row>
@@ -13517,35 +13517,35 @@
         <v>1663.6113367468251</v>
       </c>
       <c r="L176" s="2">
-        <f>RATE(10,,J166,-'Real Returns 1792-2025'!$J176)</f>
+        <f>RATE(10,,J166,-'Real Returns 1792-2026'!$J176)</f>
         <v>9.9518300910836924E-2</v>
       </c>
       <c r="M176" s="2">
-        <f>RATE(10,,K166,-'Real Returns 1792-2025'!$K176)</f>
+        <f>RATE(10,,K166,-'Real Returns 1792-2026'!$K176)</f>
         <v>-2.1982241269549274E-3</v>
       </c>
       <c r="N176" s="2">
-        <f>RATE(30,,J146,-'Real Returns 1792-2025'!$J176)</f>
+        <f>RATE(30,,J146,-'Real Returns 1792-2026'!$J176)</f>
         <v>8.4874699235010551E-2</v>
       </c>
       <c r="O176" s="2">
-        <f>RATE(30,,K146,-'Real Returns 1792-2025'!$K176)</f>
+        <f>RATE(30,,K146,-'Real Returns 1792-2026'!$K176)</f>
         <v>-2.920982139971314E-3</v>
       </c>
       <c r="P176" s="2">
-        <f>RATE(50,,J126,-'Real Returns 1792-2025'!$J176)</f>
+        <f>RATE(50,,J126,-'Real Returns 1792-2026'!$J176)</f>
         <v>7.3838823105483703E-2</v>
       </c>
       <c r="Q176" s="2">
-        <f>RATE(50,,K126,-'Real Returns 1792-2025'!$K176)</f>
+        <f>RATE(50,,K126,-'Real Returns 1792-2026'!$K176)</f>
         <v>1.3102150243761117E-2</v>
       </c>
       <c r="R176" s="2">
-        <f>RATE(100,,J76,-'Real Returns 1792-2025'!$J176)</f>
+        <f>RATE(100,,J76,-'Real Returns 1792-2026'!$J176)</f>
         <v>7.5086449057128454E-2</v>
       </c>
       <c r="S176" s="2">
-        <f>RATE(100,,K76,-'Real Returns 1792-2025'!$K176)</f>
+        <f>RATE(100,,K76,-'Real Returns 1792-2026'!$K176)</f>
         <v>3.9585277161364549E-2</v>
       </c>
     </row>
@@ -13580,35 +13580,35 @@
         <v>1633.521090187161</v>
       </c>
       <c r="L177" s="2">
-        <f>RATE(10,,J167,-'Real Returns 1792-2025'!$J177)</f>
+        <f>RATE(10,,J167,-'Real Returns 1792-2026'!$J177)</f>
         <v>8.8177374723450191E-2</v>
       </c>
       <c r="M177" s="2">
-        <f>RATE(10,,K167,-'Real Returns 1792-2025'!$K177)</f>
+        <f>RATE(10,,K167,-'Real Returns 1792-2026'!$K177)</f>
         <v>6.1943018451821345E-3</v>
       </c>
       <c r="N177" s="2">
-        <f>RATE(30,,J147,-'Real Returns 1792-2025'!$J177)</f>
+        <f>RATE(30,,J147,-'Real Returns 1792-2026'!$J177)</f>
         <v>7.4836935164957916E-2</v>
       </c>
       <c r="O177" s="2">
-        <f>RATE(30,,K147,-'Real Returns 1792-2025'!$K177)</f>
+        <f>RATE(30,,K147,-'Real Returns 1792-2026'!$K177)</f>
         <v>-5.7137147962232617E-3</v>
       </c>
       <c r="P177" s="2">
-        <f>RATE(50,,J127,-'Real Returns 1792-2025'!$J177)</f>
+        <f>RATE(50,,J127,-'Real Returns 1792-2026'!$J177)</f>
         <v>7.3297968588897408E-2</v>
       </c>
       <c r="Q177" s="2">
-        <f>RATE(50,,K127,-'Real Returns 1792-2025'!$K177)</f>
+        <f>RATE(50,,K127,-'Real Returns 1792-2026'!$K177)</f>
         <v>1.3946807631108222E-2</v>
       </c>
       <c r="R177" s="2">
-        <f>RATE(100,,J77,-'Real Returns 1792-2025'!$J177)</f>
+        <f>RATE(100,,J77,-'Real Returns 1792-2026'!$J177)</f>
         <v>7.3404242051862453E-2</v>
       </c>
       <c r="S177" s="2">
-        <f>RATE(100,,K77,-'Real Returns 1792-2025'!$K177)</f>
+        <f>RATE(100,,K77,-'Real Returns 1792-2026'!$K177)</f>
         <v>3.790974421813726E-2</v>
       </c>
     </row>
@@ -13643,35 +13643,35 @@
         <v>1448.077128932706</v>
       </c>
       <c r="L178" s="2">
-        <f>RATE(10,,J168,-'Real Returns 1792-2025'!$J178)</f>
+        <f>RATE(10,,J168,-'Real Returns 1792-2026'!$J178)</f>
         <v>0.10574513513828374</v>
       </c>
       <c r="M178" s="2">
-        <f>RATE(10,,K168,-'Real Returns 1792-2025'!$K178)</f>
+        <f>RATE(10,,K168,-'Real Returns 1792-2026'!$K178)</f>
         <v>-7.4384958200363026E-3</v>
       </c>
       <c r="N178" s="2">
-        <f>RATE(30,,J148,-'Real Returns 1792-2025'!$J178)</f>
+        <f>RATE(30,,J148,-'Real Returns 1792-2026'!$J178)</f>
         <v>9.4874445766663887E-2</v>
       </c>
       <c r="O178" s="2">
-        <f>RATE(30,,K148,-'Real Returns 1792-2025'!$K178)</f>
+        <f>RATE(30,,K148,-'Real Returns 1792-2026'!$K178)</f>
         <v>-7.1339540853574716E-3</v>
       </c>
       <c r="P178" s="2">
-        <f>RATE(50,,J128,-'Real Returns 1792-2025'!$J178)</f>
+        <f>RATE(50,,J128,-'Real Returns 1792-2026'!$J178)</f>
         <v>8.3363870225418621E-2</v>
       </c>
       <c r="Q178" s="2">
-        <f>RATE(50,,K128,-'Real Returns 1792-2025'!$K178)</f>
+        <f>RATE(50,,K128,-'Real Returns 1792-2026'!$K178)</f>
         <v>1.7170018238957859E-2</v>
       </c>
       <c r="R178" s="2">
-        <f>RATE(100,,J78,-'Real Returns 1792-2025'!$J178)</f>
+        <f>RATE(100,,J78,-'Real Returns 1792-2026'!$J178)</f>
         <v>7.2719792818432993E-2</v>
       </c>
       <c r="S178" s="2">
-        <f>RATE(100,,K78,-'Real Returns 1792-2025'!$K178)</f>
+        <f>RATE(100,,K78,-'Real Returns 1792-2026'!$K178)</f>
         <v>3.5235579463096849E-2</v>
       </c>
     </row>
@@ -13706,35 +13706,35 @@
         <v>1382.1773417003628</v>
       </c>
       <c r="L179" s="2">
-        <f>RATE(10,,J169,-'Real Returns 1792-2025'!$J179)</f>
+        <f>RATE(10,,J169,-'Real Returns 1792-2026'!$J179)</f>
         <v>8.4167838019794133E-2</v>
       </c>
       <c r="M179" s="2">
-        <f>RATE(10,,K169,-'Real Returns 1792-2025'!$K179)</f>
+        <f>RATE(10,,K169,-'Real Returns 1792-2026'!$K179)</f>
         <v>-6.0195945139180813E-3</v>
       </c>
       <c r="N179" s="2">
-        <f>RATE(30,,J149,-'Real Returns 1792-2025'!$J179)</f>
+        <f>RATE(30,,J149,-'Real Returns 1792-2026'!$J179)</f>
         <v>9.2116033320763485E-2</v>
       </c>
       <c r="O179" s="2">
-        <f>RATE(30,,K149,-'Real Returns 1792-2025'!$K179)</f>
+        <f>RATE(30,,K149,-'Real Returns 1792-2026'!$K179)</f>
         <v>-1.0417904047887762E-2</v>
       </c>
       <c r="P179" s="2">
-        <f>RATE(50,,J129,-'Real Returns 1792-2025'!$J179)</f>
+        <f>RATE(50,,J129,-'Real Returns 1792-2026'!$J179)</f>
         <v>8.6133591622736844E-2</v>
       </c>
       <c r="Q179" s="2">
-        <f>RATE(50,,K129,-'Real Returns 1792-2025'!$K179)</f>
+        <f>RATE(50,,K129,-'Real Returns 1792-2026'!$K179)</f>
         <v>1.8014169589116367E-2</v>
       </c>
       <c r="R179" s="2">
-        <f>RATE(100,,J79,-'Real Returns 1792-2025'!$J179)</f>
+        <f>RATE(100,,J79,-'Real Returns 1792-2026'!$J179)</f>
         <v>7.1438450893982416E-2</v>
       </c>
       <c r="S179" s="2">
-        <f>RATE(100,,K79,-'Real Returns 1792-2025'!$K179)</f>
+        <f>RATE(100,,K79,-'Real Returns 1792-2026'!$K179)</f>
         <v>3.3684831416889237E-2</v>
       </c>
     </row>
@@ -13769,35 +13769,35 @@
         <v>1183.9263070117115</v>
       </c>
       <c r="L180" s="2">
-        <f>RATE(10,,J170,-'Real Returns 1792-2025'!$J180)</f>
+        <f>RATE(10,,J170,-'Real Returns 1792-2026'!$J180)</f>
         <v>5.4741430729842749E-2</v>
       </c>
       <c r="M180" s="2">
-        <f>RATE(10,,K170,-'Real Returns 1792-2025'!$K180)</f>
+        <f>RATE(10,,K170,-'Real Returns 1792-2026'!$K180)</f>
         <v>-1.82170544796968E-2</v>
       </c>
       <c r="N180" s="2">
-        <f>RATE(30,,J150,-'Real Returns 1792-2025'!$J180)</f>
+        <f>RATE(30,,J150,-'Real Returns 1792-2026'!$J180)</f>
         <v>8.098977734752974E-2</v>
       </c>
       <c r="O180" s="2">
-        <f>RATE(30,,K150,-'Real Returns 1792-2025'!$K180)</f>
+        <f>RATE(30,,K150,-'Real Returns 1792-2026'!$K180)</f>
         <v>-1.6551630224189113E-2</v>
       </c>
       <c r="P180" s="2">
-        <f>RATE(50,,J130,-'Real Returns 1792-2025'!$J180)</f>
+        <f>RATE(50,,J130,-'Real Returns 1792-2026'!$J180)</f>
         <v>8.0464693176602986E-2</v>
       </c>
       <c r="Q180" s="2">
-        <f>RATE(50,,K130,-'Real Returns 1792-2025'!$K180)</f>
+        <f>RATE(50,,K130,-'Real Returns 1792-2026'!$K180)</f>
         <v>1.8572038691704835E-2</v>
       </c>
       <c r="R180" s="2">
-        <f>RATE(100,,J80,-'Real Returns 1792-2025'!$J180)</f>
+        <f>RATE(100,,J80,-'Real Returns 1792-2026'!$J180)</f>
         <v>6.8120080777465064E-2</v>
       </c>
       <c r="S180" s="2">
-        <f>RATE(100,,K80,-'Real Returns 1792-2025'!$K180)</f>
+        <f>RATE(100,,K80,-'Real Returns 1792-2026'!$K180)</f>
         <v>3.0887839170242414E-2</v>
       </c>
     </row>
@@ -13832,35 +13832,35 @@
         <v>1364.6113095969802</v>
       </c>
       <c r="L181" s="2">
-        <f>RATE(10,,J171,-'Real Returns 1792-2025'!$J181)</f>
+        <f>RATE(10,,J171,-'Real Returns 1792-2026'!$J181)</f>
         <v>4.9517181360853202E-2</v>
       </c>
       <c r="M181" s="2">
-        <f>RATE(10,,K171,-'Real Returns 1792-2025'!$K181)</f>
+        <f>RATE(10,,K171,-'Real Returns 1792-2026'!$K181)</f>
         <v>-1.1370886907187443E-2</v>
       </c>
       <c r="N181" s="2">
-        <f>RATE(30,,J151,-'Real Returns 1792-2025'!$J181)</f>
+        <f>RATE(30,,J151,-'Real Returns 1792-2026'!$J181)</f>
         <v>8.7709796199923681E-2</v>
       </c>
       <c r="O181" s="2">
-        <f>RATE(30,,K151,-'Real Returns 1792-2025'!$K181)</f>
+        <f>RATE(30,,K151,-'Real Returns 1792-2026'!$K181)</f>
         <v>-1.3103204175411087E-2</v>
       </c>
       <c r="P181" s="2">
-        <f>RATE(50,,J131,-'Real Returns 1792-2025'!$J181)</f>
+        <f>RATE(50,,J131,-'Real Returns 1792-2026'!$J181)</f>
         <v>8.5102407986375792E-2</v>
       </c>
       <c r="Q181" s="2">
-        <f>RATE(50,,K131,-'Real Returns 1792-2025'!$K181)</f>
+        <f>RATE(50,,K131,-'Real Returns 1792-2026'!$K181)</f>
         <v>2.0220624341422595E-2</v>
       </c>
       <c r="R181" s="2">
-        <f>RATE(100,,J81,-'Real Returns 1792-2025'!$J181)</f>
+        <f>RATE(100,,J81,-'Real Returns 1792-2026'!$J181)</f>
         <v>6.8219644740640822E-2</v>
       </c>
       <c r="S181" s="2">
-        <f>RATE(100,,K81,-'Real Returns 1792-2025'!$K181)</f>
+        <f>RATE(100,,K81,-'Real Returns 1792-2026'!$K181)</f>
         <v>3.1158726574577991E-2</v>
       </c>
     </row>
@@ -13895,35 +13895,35 @@
         <v>1403.7746581157642</v>
       </c>
       <c r="L182" s="2">
-        <f>RATE(10,,J172,-'Real Returns 1792-2025'!$J182)</f>
+        <f>RATE(10,,J172,-'Real Returns 1792-2026'!$J182)</f>
         <v>4.5541598504174843E-2</v>
       </c>
       <c r="M182" s="2">
-        <f>RATE(10,,K172,-'Real Returns 1792-2025'!$K182)</f>
+        <f>RATE(10,,K172,-'Real Returns 1792-2026'!$K182)</f>
         <v>-1.0513256950444768E-2</v>
       </c>
       <c r="N182" s="2">
-        <f>RATE(30,,J152,-'Real Returns 1792-2025'!$J182)</f>
+        <f>RATE(30,,J152,-'Real Returns 1792-2026'!$J182)</f>
         <v>9.7085983095826014E-2</v>
       </c>
       <c r="O182" s="2">
-        <f>RATE(30,,K152,-'Real Returns 1792-2025'!$K182)</f>
+        <f>RATE(30,,K152,-'Real Returns 1792-2026'!$K182)</f>
         <v>-9.7704664890691049E-3</v>
       </c>
       <c r="P182" s="2">
-        <f>RATE(50,,J132,-'Real Returns 1792-2025'!$J182)</f>
+        <f>RATE(50,,J132,-'Real Returns 1792-2026'!$J182)</f>
         <v>8.2704493397834714E-2</v>
       </c>
       <c r="Q182" s="2">
-        <f>RATE(50,,K132,-'Real Returns 1792-2025'!$K182)</f>
+        <f>RATE(50,,K132,-'Real Returns 1792-2026'!$K182)</f>
         <v>1.532619317185681E-2</v>
       </c>
       <c r="R182" s="2">
-        <f>RATE(100,,J82,-'Real Returns 1792-2025'!$J182)</f>
+        <f>RATE(100,,J82,-'Real Returns 1792-2026'!$J182)</f>
         <v>6.7244023230754596E-2</v>
       </c>
       <c r="S182" s="2">
-        <f>RATE(100,,K82,-'Real Returns 1792-2025'!$K182)</f>
+        <f>RATE(100,,K82,-'Real Returns 1792-2026'!$K182)</f>
         <v>3.0284568771946744E-2</v>
       </c>
     </row>
@@ -13958,35 +13958,35 @@
         <v>1440.3469422544911</v>
       </c>
       <c r="L183" s="2">
-        <f>RATE(10,,J173,-'Real Returns 1792-2025'!$J183)</f>
+        <f>RATE(10,,J173,-'Real Returns 1792-2026'!$J183)</f>
         <v>5.6361573317587711E-2</v>
       </c>
       <c r="M183" s="2">
-        <f>RATE(10,,K173,-'Real Returns 1792-2025'!$K183)</f>
+        <f>RATE(10,,K173,-'Real Returns 1792-2026'!$K183)</f>
         <v>-1.4355939061148914E-2</v>
       </c>
       <c r="N183" s="2">
-        <f>RATE(30,,J153,-'Real Returns 1792-2025'!$J183)</f>
+        <f>RATE(30,,J153,-'Real Returns 1792-2026'!$J183)</f>
         <v>9.4361010203734483E-2</v>
       </c>
       <c r="O183" s="2">
-        <f>RATE(30,,K153,-'Real Returns 1792-2025'!$K183)</f>
+        <f>RATE(30,,K153,-'Real Returns 1792-2026'!$K183)</f>
         <v>-8.1487948718699729E-3</v>
       </c>
       <c r="P183" s="2">
-        <f>RATE(50,,J133,-'Real Returns 1792-2025'!$J183)</f>
+        <f>RATE(50,,J133,-'Real Returns 1792-2026'!$J183)</f>
         <v>7.8498517180321581E-2</v>
       </c>
       <c r="Q183" s="2">
-        <f>RATE(50,,K133,-'Real Returns 1792-2025'!$K183)</f>
+        <f>RATE(50,,K133,-'Real Returns 1792-2026'!$K183)</f>
         <v>1.413737595057607E-2</v>
       </c>
       <c r="R183" s="2">
-        <f>RATE(100,,J83,-'Real Returns 1792-2025'!$J183)</f>
+        <f>RATE(100,,J83,-'Real Returns 1792-2026'!$J183)</f>
         <v>6.6301469698938062E-2</v>
       </c>
       <c r="S183" s="2">
-        <f>RATE(100,,K83,-'Real Returns 1792-2025'!$K183)</f>
+        <f>RATE(100,,K83,-'Real Returns 1792-2026'!$K183)</f>
         <v>2.9786761580783295E-2</v>
       </c>
     </row>
@@ -14021,35 +14021,35 @@
         <v>1331.0641725151881</v>
       </c>
       <c r="L184" s="2">
-        <f>RATE(10,,J174,-'Real Returns 1792-2025'!$J184)</f>
+        <f>RATE(10,,J174,-'Real Returns 1792-2026'!$J184)</f>
         <v>1.3579495494436804E-2</v>
       </c>
       <c r="M184" s="2">
-        <f>RATE(10,,K174,-'Real Returns 1792-2025'!$K184)</f>
+        <f>RATE(10,,K174,-'Real Returns 1792-2026'!$K184)</f>
         <v>-2.2279653550090702E-2</v>
       </c>
       <c r="N184" s="2">
-        <f>RATE(30,,J154,-'Real Returns 1792-2025'!$J184)</f>
+        <f>RATE(30,,J154,-'Real Returns 1792-2026'!$J184)</f>
         <v>7.8799835714062585E-2</v>
       </c>
       <c r="O184" s="2">
-        <f>RATE(30,,K154,-'Real Returns 1792-2025'!$K184)</f>
+        <f>RATE(30,,K154,-'Real Returns 1792-2026'!$K184)</f>
         <v>-1.2277048417328797E-2</v>
       </c>
       <c r="P184" s="2">
-        <f>RATE(50,,J134,-'Real Returns 1792-2025'!$J184)</f>
+        <f>RATE(50,,J134,-'Real Returns 1792-2026'!$J184)</f>
         <v>7.2283240804327076E-2</v>
       </c>
       <c r="Q184" s="2">
-        <f>RATE(50,,K134,-'Real Returns 1792-2025'!$K184)</f>
+        <f>RATE(50,,K134,-'Real Returns 1792-2026'!$K184)</f>
         <v>1.2350716934739922E-2</v>
       </c>
       <c r="R184" s="2">
-        <f>RATE(100,,J84,-'Real Returns 1792-2025'!$J184)</f>
+        <f>RATE(100,,J84,-'Real Returns 1792-2026'!$J184)</f>
         <v>6.3672977214212598E-2</v>
       </c>
       <c r="S184" s="2">
-        <f>RATE(100,,K84,-'Real Returns 1792-2025'!$K184)</f>
+        <f>RATE(100,,K84,-'Real Returns 1792-2026'!$K184)</f>
         <v>2.7923439885496174E-2</v>
       </c>
     </row>
@@ -14084,35 +14084,35 @@
         <v>1229.3971122511548</v>
       </c>
       <c r="L185" s="2">
-        <f>RATE(10,,J175,-'Real Returns 1792-2025'!$J185)</f>
+        <f>RATE(10,,J175,-'Real Returns 1792-2026'!$J185)</f>
         <v>-3.2477659815280016E-2</v>
       </c>
       <c r="M185" s="2">
-        <f>RATE(10,,K175,-'Real Returns 1792-2025'!$K185)</f>
+        <f>RATE(10,,K175,-'Real Returns 1792-2026'!$K185)</f>
         <v>-3.2401950674674419E-2</v>
       </c>
       <c r="N185" s="2">
-        <f>RATE(30,,J155,-'Real Returns 1792-2025'!$J185)</f>
+        <f>RATE(30,,J155,-'Real Returns 1792-2026'!$J185)</f>
         <v>6.1525526376834498E-2</v>
       </c>
       <c r="O185" s="2">
-        <f>RATE(30,,K155,-'Real Returns 1792-2025'!$K185)</f>
+        <f>RATE(30,,K155,-'Real Returns 1792-2026'!$K185)</f>
         <v>-1.6304201100873161E-2</v>
       </c>
       <c r="P185" s="2">
-        <f>RATE(50,,J135,-'Real Returns 1792-2025'!$J185)</f>
+        <f>RATE(50,,J135,-'Real Returns 1792-2026'!$J185)</f>
         <v>6.0569107604436866E-2</v>
       </c>
       <c r="Q185" s="2">
-        <f>RATE(50,,K135,-'Real Returns 1792-2025'!$K185)</f>
+        <f>RATE(50,,K135,-'Real Returns 1792-2026'!$K185)</f>
         <v>9.1054937262455143E-3</v>
       </c>
       <c r="R185" s="2">
-        <f>RATE(100,,J85,-'Real Returns 1792-2025'!$J185)</f>
+        <f>RATE(100,,J85,-'Real Returns 1792-2026'!$J185)</f>
         <v>5.9493674406572994E-2</v>
       </c>
       <c r="S185" s="2">
-        <f>RATE(100,,K85,-'Real Returns 1792-2025'!$K185)</f>
+        <f>RATE(100,,K85,-'Real Returns 1792-2026'!$K185)</f>
         <v>2.5670695610228868E-2</v>
       </c>
     </row>
@@ -14147,35 +14147,35 @@
         <v>1269.8558046811831</v>
       </c>
       <c r="L186" s="2">
-        <f>RATE(10,,J176,-'Real Returns 1792-2025'!$J186)</f>
+        <f>RATE(10,,J176,-'Real Returns 1792-2026'!$J186)</f>
         <v>-1.7937615192520451E-2</v>
       </c>
       <c r="M186" s="2">
-        <f>RATE(10,,K176,-'Real Returns 1792-2025'!$K186)</f>
+        <f>RATE(10,,K176,-'Real Returns 1792-2026'!$K186)</f>
         <v>-2.664726454921169E-2</v>
       </c>
       <c r="N186" s="2">
-        <f>RATE(30,,J156,-'Real Returns 1792-2025'!$J186)</f>
+        <f>RATE(30,,J156,-'Real Returns 1792-2026'!$J186)</f>
         <v>5.7629414997242605E-2</v>
       </c>
       <c r="O186" s="2">
-        <f>RATE(30,,K156,-'Real Returns 1792-2025'!$K186)</f>
+        <f>RATE(30,,K156,-'Real Returns 1792-2026'!$K186)</f>
         <v>-1.6544913569356834E-2</v>
       </c>
       <c r="P186" s="2">
-        <f>RATE(50,,J136,-'Real Returns 1792-2025'!$J186)</f>
+        <f>RATE(50,,J136,-'Real Returns 1792-2026'!$J186)</f>
         <v>6.1488729548678608E-2</v>
       </c>
       <c r="Q186" s="2">
-        <f>RATE(50,,K136,-'Real Returns 1792-2025'!$K186)</f>
+        <f>RATE(50,,K136,-'Real Returns 1792-2026'!$K186)</f>
         <v>8.8796354800650019E-3</v>
       </c>
       <c r="R186" s="2">
-        <f>RATE(100,,J86,-'Real Returns 1792-2025'!$J186)</f>
+        <f>RATE(100,,J86,-'Real Returns 1792-2026'!$J186)</f>
         <v>6.108886580800231E-2</v>
       </c>
       <c r="S186" s="2">
-        <f>RATE(100,,K86,-'Real Returns 1792-2025'!$K186)</f>
+        <f>RATE(100,,K86,-'Real Returns 1792-2026'!$K186)</f>
         <v>2.4723360921241309E-2</v>
       </c>
     </row>
@@ -14210,35 +14210,35 @@
         <v>1362.9442028088156</v>
       </c>
       <c r="L187" s="2">
-        <f>RATE(10,,J177,-'Real Returns 1792-2025'!$J187)</f>
+        <f>RATE(10,,J177,-'Real Returns 1792-2026'!$J187)</f>
         <v>-9.4910684043178293E-3</v>
       </c>
       <c r="M187" s="2">
-        <f>RATE(10,,K177,-'Real Returns 1792-2025'!$K187)</f>
+        <f>RATE(10,,K177,-'Real Returns 1792-2026'!$K187)</f>
         <v>-1.7946081015157576E-2</v>
       </c>
       <c r="N187" s="2">
-        <f>RATE(30,,J157,-'Real Returns 1792-2025'!$J187)</f>
+        <f>RATE(30,,J157,-'Real Returns 1792-2026'!$J187)</f>
         <v>6.8694227278107256E-2</v>
       </c>
       <c r="O187" s="2">
-        <f>RATE(30,,K157,-'Real Returns 1792-2025'!$K187)</f>
+        <f>RATE(30,,K157,-'Real Returns 1792-2026'!$K187)</f>
         <v>-8.6016927973789296E-3</v>
       </c>
       <c r="P187" s="2">
-        <f>RATE(50,,J137,-'Real Returns 1792-2025'!$J187)</f>
+        <f>RATE(50,,J137,-'Real Returns 1792-2026'!$J187)</f>
         <v>5.9630158153499591E-2</v>
       </c>
       <c r="Q187" s="2">
-        <f>RATE(50,,K137,-'Real Returns 1792-2025'!$K187)</f>
+        <f>RATE(50,,K137,-'Real Returns 1792-2026'!$K187)</f>
         <v>8.1525683675136851E-3</v>
       </c>
       <c r="R187" s="2">
-        <f>RATE(100,,J87,-'Real Returns 1792-2025'!$J187)</f>
+        <f>RATE(100,,J87,-'Real Returns 1792-2026'!$J187)</f>
         <v>6.2468527785590665E-2</v>
       </c>
       <c r="S187" s="2">
-        <f>RATE(100,,K87,-'Real Returns 1792-2025'!$K187)</f>
+        <f>RATE(100,,K87,-'Real Returns 1792-2026'!$K187)</f>
         <v>2.4665876636031713E-2</v>
       </c>
     </row>
@@ -14273,35 +14273,35 @@
         <v>1326.1624101679138</v>
       </c>
       <c r="L188" s="2">
-        <f>RATE(10,,J178,-'Real Returns 1792-2025'!$J188)</f>
+        <f>RATE(10,,J178,-'Real Returns 1792-2026'!$J188)</f>
         <v>-3.0311563908482463E-2</v>
       </c>
       <c r="M188" s="2">
-        <f>RATE(10,,K178,-'Real Returns 1792-2025'!$K188)</f>
+        <f>RATE(10,,K178,-'Real Returns 1792-2026'!$K188)</f>
         <v>-8.7561588664380637E-3</v>
       </c>
       <c r="N188" s="2">
-        <f>RATE(30,,J158,-'Real Returns 1792-2025'!$J188)</f>
+        <f>RATE(30,,J158,-'Real Returns 1792-2026'!$J188)</f>
         <v>6.8715671670042139E-2</v>
       </c>
       <c r="O188" s="2">
-        <f>RATE(30,,K158,-'Real Returns 1792-2025'!$K188)</f>
+        <f>RATE(30,,K158,-'Real Returns 1792-2026'!$K188)</f>
         <v>-4.3284406779784028E-3</v>
       </c>
       <c r="P188" s="2">
-        <f>RATE(50,,J138,-'Real Returns 1792-2025'!$J188)</f>
+        <f>RATE(50,,J138,-'Real Returns 1792-2026'!$J188)</f>
         <v>5.1060564851030846E-2</v>
       </c>
       <c r="Q188" s="2">
-        <f>RATE(50,,K138,-'Real Returns 1792-2025'!$K188)</f>
+        <f>RATE(50,,K138,-'Real Returns 1792-2026'!$K188)</f>
         <v>5.7301184036854013E-3</v>
       </c>
       <c r="R188" s="2">
-        <f>RATE(100,,J88,-'Real Returns 1792-2025'!$J188)</f>
+        <f>RATE(100,,J88,-'Real Returns 1792-2026'!$J188)</f>
         <v>6.094017826332223E-2</v>
       </c>
       <c r="S188" s="2">
-        <f>RATE(100,,K88,-'Real Returns 1792-2025'!$K188)</f>
+        <f>RATE(100,,K88,-'Real Returns 1792-2026'!$K188)</f>
         <v>2.3577292646062526E-2</v>
       </c>
     </row>
@@ -14336,35 +14336,35 @@
         <v>1246.0953655691421</v>
       </c>
       <c r="L189" s="2">
-        <f>RATE(10,,J179,-'Real Returns 1792-2025'!$J189)</f>
+        <f>RATE(10,,J179,-'Real Returns 1792-2026'!$J189)</f>
         <v>-3.2379565157734387E-2</v>
       </c>
       <c r="M189" s="2">
-        <f>RATE(10,,K179,-'Real Returns 1792-2025'!$K189)</f>
+        <f>RATE(10,,K179,-'Real Returns 1792-2026'!$K189)</f>
         <v>-1.0310982047178395E-2</v>
       </c>
       <c r="N189" s="2">
-        <f>RATE(30,,J159,-'Real Returns 1792-2025'!$J189)</f>
+        <f>RATE(30,,J159,-'Real Returns 1792-2026'!$J189)</f>
         <v>7.0432683200386495E-2</v>
       </c>
       <c r="O189" s="2">
-        <f>RATE(30,,K159,-'Real Returns 1792-2025'!$K189)</f>
+        <f>RATE(30,,K159,-'Real Returns 1792-2026'!$K189)</f>
         <v>-7.9181680450872618E-3</v>
       </c>
       <c r="P189" s="2">
-        <f>RATE(50,,J139,-'Real Returns 1792-2025'!$J189)</f>
+        <f>RATE(50,,J139,-'Real Returns 1792-2026'!$J189)</f>
         <v>4.4785065671320179E-2</v>
       </c>
       <c r="Q189" s="2">
-        <f>RATE(50,,K139,-'Real Returns 1792-2025'!$K189)</f>
+        <f>RATE(50,,K139,-'Real Returns 1792-2026'!$K189)</f>
         <v>4.1196488684998979E-3</v>
       </c>
       <c r="R189" s="2">
-        <f>RATE(100,,J89,-'Real Returns 1792-2025'!$J189)</f>
+        <f>RATE(100,,J89,-'Real Returns 1792-2026'!$J189)</f>
         <v>6.0263286028929754E-2</v>
       </c>
       <c r="S189" s="2">
-        <f>RATE(100,,K89,-'Real Returns 1792-2025'!$K189)</f>
+        <f>RATE(100,,K89,-'Real Returns 1792-2026'!$K189)</f>
         <v>2.1941389542419348E-2</v>
       </c>
     </row>
@@ -14399,35 +14399,35 @@
         <v>962.67886355454607</v>
       </c>
       <c r="L190" s="2">
-        <f>RATE(10,,J180,-'Real Returns 1792-2025'!$J190)</f>
+        <f>RATE(10,,J180,-'Real Returns 1792-2026'!$J190)</f>
         <v>1.8281060326306652E-3</v>
       </c>
       <c r="M190" s="2">
-        <f>RATE(10,,K180,-'Real Returns 1792-2025'!$K190)</f>
+        <f>RATE(10,,K180,-'Real Returns 1792-2026'!$K190)</f>
         <v>-2.0474657623963801E-2</v>
       </c>
       <c r="N190" s="2">
-        <f>RATE(30,,J160,-'Real Returns 1792-2025'!$J190)</f>
+        <f>RATE(30,,J160,-'Real Returns 1792-2026'!$J190)</f>
         <v>6.6322803280491824E-2</v>
       </c>
       <c r="O190" s="2">
-        <f>RATE(30,,K160,-'Real Returns 1792-2025'!$K190)</f>
+        <f>RATE(30,,K160,-'Real Returns 1792-2026'!$K190)</f>
         <v>-1.922456600273938E-2</v>
       </c>
       <c r="P190" s="2">
-        <f>RATE(50,,J140,-'Real Returns 1792-2025'!$J190)</f>
+        <f>RATE(50,,J140,-'Real Returns 1792-2026'!$J190)</f>
         <v>5.0291496426497648E-2</v>
       </c>
       <c r="Q190" s="2">
-        <f>RATE(50,,K140,-'Real Returns 1792-2025'!$K190)</f>
+        <f>RATE(50,,K140,-'Real Returns 1792-2026'!$K190)</f>
         <v>-1.899049944589253E-3</v>
       </c>
       <c r="R190" s="2">
-        <f>RATE(100,,J90,-'Real Returns 1792-2025'!$J190)</f>
+        <f>RATE(100,,J90,-'Real Returns 1792-2026'!$J190)</f>
         <v>5.7503524775594582E-2</v>
       </c>
       <c r="S190" s="2">
-        <f>RATE(100,,K90,-'Real Returns 1792-2025'!$K190)</f>
+        <f>RATE(100,,K90,-'Real Returns 1792-2026'!$K190)</f>
         <v>1.8597462533612736E-2</v>
       </c>
     </row>
@@ -14462,35 +14462,35 @@
         <v>883.23365117188507</v>
       </c>
       <c r="L191" s="2">
-        <f>RATE(10,,J181,-'Real Returns 1792-2025'!$J191)</f>
+        <f>RATE(10,,J181,-'Real Returns 1792-2026'!$J191)</f>
         <v>1.3055410700319743E-3</v>
       </c>
       <c r="M191" s="2">
-        <f>RATE(10,,K181,-'Real Returns 1792-2025'!$K191)</f>
+        <f>RATE(10,,K181,-'Real Returns 1792-2026'!$K191)</f>
         <v>-4.2570809936254575E-2</v>
       </c>
       <c r="N191" s="2">
-        <f>RATE(30,,J161,-'Real Returns 1792-2025'!$J191)</f>
+        <f>RATE(30,,J161,-'Real Returns 1792-2026'!$J191)</f>
         <v>6.0758224389178259E-2</v>
       </c>
       <c r="O191" s="2">
-        <f>RATE(30,,K161,-'Real Returns 1792-2025'!$K191)</f>
+        <f>RATE(30,,K161,-'Real Returns 1792-2026'!$K191)</f>
         <v>-2.059907264060673E-2</v>
       </c>
       <c r="P191" s="2">
-        <f>RATE(50,,J141,-'Real Returns 1792-2025'!$J191)</f>
+        <f>RATE(50,,J141,-'Real Returns 1792-2026'!$J191)</f>
         <v>5.7331100749322822E-2</v>
       </c>
       <c r="Q191" s="2">
-        <f>RATE(50,,K141,-'Real Returns 1792-2025'!$K191)</f>
+        <f>RATE(50,,K141,-'Real Returns 1792-2026'!$K191)</f>
         <v>-6.3890743262199796E-3</v>
       </c>
       <c r="R191" s="2">
-        <f>RATE(100,,J91,-'Real Returns 1792-2025'!$J191)</f>
+        <f>RATE(100,,J91,-'Real Returns 1792-2026'!$J191)</f>
         <v>5.5948368800628506E-2</v>
       </c>
       <c r="S191" s="2">
-        <f>RATE(100,,K91,-'Real Returns 1792-2025'!$K191)</f>
+        <f>RATE(100,,K91,-'Real Returns 1792-2026'!$K191)</f>
         <v>1.6677112797439837E-2</v>
       </c>
     </row>
@@ -14525,35 +14525,35 @@
         <v>804.86860506005314</v>
       </c>
       <c r="L192" s="2">
-        <f>RATE(10,,J182,-'Real Returns 1792-2025'!$J192)</f>
+        <f>RATE(10,,J182,-'Real Returns 1792-2026'!$J192)</f>
         <v>-1.8733910641214026E-2</v>
       </c>
       <c r="M192" s="2">
-        <f>RATE(10,,K182,-'Real Returns 1792-2025'!$K192)</f>
+        <f>RATE(10,,K182,-'Real Returns 1792-2026'!$K192)</f>
         <v>-5.4105372090264746E-2</v>
       </c>
       <c r="N192" s="2">
-        <f>RATE(30,,J162,-'Real Returns 1792-2025'!$J192)</f>
+        <f>RATE(30,,J162,-'Real Returns 1792-2026'!$J192)</f>
         <v>5.3202557953214644E-2</v>
       </c>
       <c r="O192" s="2">
-        <f>RATE(30,,K162,-'Real Returns 1792-2025'!$K192)</f>
+        <f>RATE(30,,K162,-'Real Returns 1792-2026'!$K192)</f>
         <v>-2.1255628917577086E-2</v>
       </c>
       <c r="P192" s="2">
-        <f>RATE(50,,J142,-'Real Returns 1792-2025'!$J192)</f>
+        <f>RATE(50,,J142,-'Real Returns 1792-2026'!$J192)</f>
         <v>6.6809482180387944E-2</v>
       </c>
       <c r="Q192" s="2">
-        <f>RATE(50,,K142,-'Real Returns 1792-2025'!$K192)</f>
+        <f>RATE(50,,K142,-'Real Returns 1792-2026'!$K192)</f>
         <v>-6.318953433490408E-3</v>
       </c>
       <c r="R192" s="2">
-        <f>RATE(100,,J92,-'Real Returns 1792-2025'!$J192)</f>
+        <f>RATE(100,,J92,-'Real Returns 1792-2026'!$J192)</f>
         <v>5.4763367626508956E-2</v>
       </c>
       <c r="S192" s="2">
-        <f>RATE(100,,K92,-'Real Returns 1792-2025'!$K192)</f>
+        <f>RATE(100,,K92,-'Real Returns 1792-2026'!$K192)</f>
         <v>1.5147549885746672E-2</v>
       </c>
     </row>
@@ -14588,35 +14588,35 @@
         <v>1110.2952193675605</v>
       </c>
       <c r="L193" s="2">
-        <f>RATE(10,,J183,-'Real Returns 1792-2025'!$J193)</f>
+        <f>RATE(10,,J183,-'Real Returns 1792-2026'!$J193)</f>
         <v>-4.0329619673769032E-3</v>
       </c>
       <c r="M193" s="2">
-        <f>RATE(10,,K183,-'Real Returns 1792-2025'!$K193)</f>
+        <f>RATE(10,,K183,-'Real Returns 1792-2026'!$K193)</f>
         <v>-2.5690055056871816E-2</v>
       </c>
       <c r="N193" s="2">
-        <f>RATE(30,,J163,-'Real Returns 1792-2025'!$J193)</f>
+        <f>RATE(30,,J163,-'Real Returns 1792-2026'!$J193)</f>
         <v>5.7214520274050898E-2</v>
       </c>
       <c r="O193" s="2">
-        <f>RATE(30,,K163,-'Real Returns 1792-2025'!$K193)</f>
+        <f>RATE(30,,K163,-'Real Returns 1792-2026'!$K193)</f>
         <v>-1.123041448417149E-2</v>
       </c>
       <c r="P193" s="2">
-        <f>RATE(50,,J143,-'Real Returns 1792-2025'!$J193)</f>
+        <f>RATE(50,,J143,-'Real Returns 1792-2026'!$J193)</f>
         <v>7.0578572899221675E-2</v>
       </c>
       <c r="Q193" s="2">
-        <f>RATE(50,,K143,-'Real Returns 1792-2025'!$K193)</f>
+        <f>RATE(50,,K143,-'Real Returns 1792-2026'!$K193)</f>
         <v>-3.2834622355655371E-3</v>
       </c>
       <c r="R193" s="2">
-        <f>RATE(100,,J93,-'Real Returns 1792-2025'!$J193)</f>
+        <f>RATE(100,,J93,-'Real Returns 1792-2026'!$J193)</f>
         <v>5.6723315246255776E-2</v>
       </c>
       <c r="S193" s="2">
-        <f>RATE(100,,K93,-'Real Returns 1792-2025'!$K193)</f>
+        <f>RATE(100,,K93,-'Real Returns 1792-2026'!$K193)</f>
         <v>1.7829738806875984E-2</v>
       </c>
     </row>
@@ -14651,35 +14651,35 @@
         <v>1173.922032536336</v>
       </c>
       <c r="L194" s="2">
-        <f>RATE(10,,J184,-'Real Returns 1792-2025'!$J194)</f>
+        <f>RATE(10,,J184,-'Real Returns 1792-2026'!$J194)</f>
         <v>3.3929199955707458E-2</v>
       </c>
       <c r="M194" s="2">
-        <f>RATE(10,,K184,-'Real Returns 1792-2025'!$K194)</f>
+        <f>RATE(10,,K184,-'Real Returns 1792-2026'!$K194)</f>
         <v>-1.248426135147567E-2</v>
       </c>
       <c r="N194" s="2">
-        <f>RATE(30,,J164,-'Real Returns 1792-2025'!$J194)</f>
+        <f>RATE(30,,J164,-'Real Returns 1792-2026'!$J194)</f>
         <v>5.9447497000766007E-2</v>
       </c>
       <c r="O194" s="2">
-        <f>RATE(30,,K164,-'Real Returns 1792-2025'!$K194)</f>
+        <f>RATE(30,,K164,-'Real Returns 1792-2026'!$K194)</f>
         <v>-1.0669169282378486E-2</v>
       </c>
       <c r="P194" s="2">
-        <f>RATE(50,,J144,-'Real Returns 1792-2025'!$J194)</f>
+        <f>RATE(50,,J144,-'Real Returns 1792-2026'!$J194)</f>
         <v>6.1381989718315447E-2</v>
       </c>
       <c r="Q194" s="2">
-        <f>RATE(50,,K144,-'Real Returns 1792-2025'!$K194)</f>
+        <f>RATE(50,,K144,-'Real Returns 1792-2026'!$K194)</f>
         <v>-4.5716340462937221E-3</v>
       </c>
       <c r="R194" s="2">
-        <f>RATE(100,,J94,-'Real Returns 1792-2025'!$J194)</f>
+        <f>RATE(100,,J94,-'Real Returns 1792-2026'!$J194)</f>
         <v>5.8602259919745429E-2</v>
       </c>
       <c r="S194" s="2">
-        <f>RATE(100,,K94,-'Real Returns 1792-2025'!$K194)</f>
+        <f>RATE(100,,K94,-'Real Returns 1792-2026'!$K194)</f>
         <v>1.7568102083964351E-2</v>
       </c>
     </row>
@@ -14714,35 +14714,35 @@
         <v>1332.1313924300493</v>
       </c>
       <c r="L195" s="2">
-        <f>RATE(10,,J185,-'Real Returns 1792-2025'!$J195)</f>
+        <f>RATE(10,,J185,-'Real Returns 1792-2026'!$J195)</f>
         <v>7.6448643686403028E-2</v>
       </c>
       <c r="M195" s="2">
-        <f>RATE(10,,K185,-'Real Returns 1792-2025'!$K195)</f>
+        <f>RATE(10,,K185,-'Real Returns 1792-2026'!$K195)</f>
         <v>8.0579230726941023E-3</v>
       </c>
       <c r="N195" s="2">
-        <f>RATE(30,,J165,-'Real Returns 1792-2025'!$J195)</f>
+        <f>RATE(30,,J165,-'Real Returns 1792-2026'!$J195)</f>
         <v>4.9629152722526271E-2</v>
       </c>
       <c r="O195" s="2">
-        <f>RATE(30,,K165,-'Real Returns 1792-2025'!$K195)</f>
+        <f>RATE(30,,K165,-'Real Returns 1792-2026'!$K195)</f>
         <v>-7.6069621516643851E-3</v>
       </c>
       <c r="P195" s="2">
-        <f>RATE(50,,J145,-'Real Returns 1792-2025'!$J195)</f>
+        <f>RATE(50,,J145,-'Real Returns 1792-2026'!$J195)</f>
         <v>6.656663590661735E-2</v>
       </c>
       <c r="Q195" s="2">
-        <f>RATE(50,,K145,-'Real Returns 1792-2025'!$K195)</f>
+        <f>RATE(50,,K145,-'Real Returns 1792-2026'!$K195)</f>
         <v>-4.7685074179815339E-3</v>
       </c>
       <c r="R195" s="2">
-        <f>RATE(100,,J95,-'Real Returns 1792-2025'!$J195)</f>
+        <f>RATE(100,,J95,-'Real Returns 1792-2026'!$J195)</f>
         <v>6.0914186272522396E-2</v>
       </c>
       <c r="S195" s="2">
-        <f>RATE(100,,K95,-'Real Returns 1792-2025'!$K195)</f>
+        <f>RATE(100,,K95,-'Real Returns 1792-2026'!$K195)</f>
         <v>1.8176939207212479E-2</v>
       </c>
     </row>
@@ -14777,35 +14777,35 @@
         <v>1622.9148464918883</v>
       </c>
       <c r="L196" s="2">
-        <f>RATE(10,,J186,-'Real Returns 1792-2025'!$J196)</f>
+        <f>RATE(10,,J186,-'Real Returns 1792-2026'!$J196)</f>
         <v>6.8290133211900667E-2</v>
       </c>
       <c r="M196" s="2">
-        <f>RATE(10,,K186,-'Real Returns 1792-2025'!$K196)</f>
+        <f>RATE(10,,K186,-'Real Returns 1792-2026'!$K196)</f>
         <v>2.4835433074932783E-2</v>
       </c>
       <c r="N196" s="2">
-        <f>RATE(30,,J166,-'Real Returns 1792-2025'!$J196)</f>
+        <f>RATE(30,,J166,-'Real Returns 1792-2026'!$J196)</f>
         <v>4.8761941436549772E-2</v>
       </c>
       <c r="O196" s="2">
-        <f>RATE(30,,K166,-'Real Returns 1792-2025'!$K196)</f>
+        <f>RATE(30,,K166,-'Real Returns 1792-2026'!$K196)</f>
         <v>-1.5578972399100555E-3</v>
       </c>
       <c r="P196" s="2">
-        <f>RATE(50,,J146,-'Real Returns 1792-2025'!$J196)</f>
+        <f>RATE(50,,J146,-'Real Returns 1792-2026'!$J196)</f>
         <v>6.0213689181320029E-2</v>
       </c>
       <c r="Q196" s="2">
-        <f>RATE(50,,K146,-'Real Returns 1792-2025'!$K196)</f>
+        <f>RATE(50,,K146,-'Real Returns 1792-2026'!$K196)</f>
         <v>-2.2479619215640626E-3</v>
       </c>
       <c r="R196" s="2">
-        <f>RATE(100,,J96,-'Real Returns 1792-2025'!$J196)</f>
+        <f>RATE(100,,J96,-'Real Returns 1792-2026'!$J196)</f>
         <v>5.9761704356875923E-2</v>
       </c>
       <c r="S196" s="2">
-        <f>RATE(100,,K96,-'Real Returns 1792-2025'!$K196)</f>
+        <f>RATE(100,,K96,-'Real Returns 1792-2026'!$K196)</f>
         <v>1.9247919515508284E-2</v>
       </c>
     </row>
@@ -14840,35 +14840,35 @@
         <v>1949.6710362594847</v>
       </c>
       <c r="L197" s="2">
-        <f>RATE(10,,J187,-'Real Returns 1792-2025'!$J197)</f>
+        <f>RATE(10,,J187,-'Real Returns 1792-2026'!$J197)</f>
         <v>9.1015016332560733E-2</v>
       </c>
       <c r="M197" s="2">
-        <f>RATE(10,,K187,-'Real Returns 1792-2025'!$K197)</f>
+        <f>RATE(10,,K187,-'Real Returns 1792-2026'!$K197)</f>
         <v>3.6449929472105118E-2</v>
       </c>
       <c r="N197" s="2">
-        <f>RATE(30,,J167,-'Real Returns 1792-2025'!$J197)</f>
+        <f>RATE(30,,J167,-'Real Returns 1792-2026'!$J197)</f>
         <v>5.5511425294157514E-2</v>
       </c>
       <c r="O197" s="2">
-        <f>RATE(30,,K167,-'Real Returns 1792-2025'!$K197)</f>
+        <f>RATE(30,,K167,-'Real Returns 1792-2026'!$K197)</f>
         <v>7.9875568761826193E-3</v>
       </c>
       <c r="P197" s="2">
-        <f>RATE(50,,J147,-'Real Returns 1792-2025'!$J197)</f>
+        <f>RATE(50,,J147,-'Real Returns 1792-2026'!$J197)</f>
         <v>6.0579855561588722E-2</v>
       </c>
       <c r="Q197" s="2">
-        <f>RATE(50,,K147,-'Real Returns 1792-2025'!$K197)</f>
+        <f>RATE(50,,K147,-'Real Returns 1792-2026'!$K197)</f>
         <v>1.0040065326274614E-4</v>
       </c>
       <c r="R197" s="2">
-        <f>RATE(100,,J97,-'Real Returns 1792-2025'!$J197)</f>
+        <f>RATE(100,,J97,-'Real Returns 1792-2026'!$J197)</f>
         <v>6.1222126164142181E-2</v>
       </c>
       <c r="S197" s="2">
-        <f>RATE(100,,K97,-'Real Returns 1792-2025'!$K197)</f>
+        <f>RATE(100,,K97,-'Real Returns 1792-2026'!$K197)</f>
         <v>2.0559847500624565E-2</v>
       </c>
     </row>
@@ -14903,35 +14903,35 @@
         <v>1923.8892455474906</v>
       </c>
       <c r="L198" s="2">
-        <f>RATE(10,,J188,-'Real Returns 1792-2025'!$J198)</f>
+        <f>RATE(10,,J188,-'Real Returns 1792-2026'!$J198)</f>
         <v>9.2931629801092555E-2</v>
       </c>
       <c r="M198" s="2">
-        <f>RATE(10,,K188,-'Real Returns 1792-2025'!$K198)</f>
+        <f>RATE(10,,K188,-'Real Returns 1792-2026'!$K198)</f>
         <v>3.7906747459140966E-2</v>
       </c>
       <c r="N198" s="2">
-        <f>RATE(30,,J168,-'Real Returns 1792-2025'!$J198)</f>
+        <f>RATE(30,,J168,-'Real Returns 1792-2026'!$J198)</f>
         <v>5.4289989403286922E-2</v>
       </c>
       <c r="O198" s="2">
-        <f>RATE(30,,K168,-'Real Returns 1792-2025'!$K198)</f>
+        <f>RATE(30,,K168,-'Real Returns 1792-2026'!$K198)</f>
         <v>7.0060695929691913E-3</v>
       </c>
       <c r="P198" s="2">
-        <f>RATE(50,,J148,-'Real Returns 1792-2025'!$J198)</f>
+        <f>RATE(50,,J148,-'Real Returns 1792-2026'!$J198)</f>
         <v>6.8227204564705823E-2</v>
       </c>
       <c r="Q198" s="2">
-        <f>RATE(50,,K148,-'Real Returns 1792-2025'!$K198)</f>
+        <f>RATE(50,,K148,-'Real Returns 1792-2026'!$K198)</f>
         <v>1.3874927826759899E-3</v>
       </c>
       <c r="R198" s="2">
-        <f>RATE(100,,J98,-'Real Returns 1792-2025'!$J198)</f>
+        <f>RATE(100,,J98,-'Real Returns 1792-2026'!$J198)</f>
         <v>6.0466574726361424E-2</v>
       </c>
       <c r="S198" s="2">
-        <f>RATE(100,,K98,-'Real Returns 1792-2025'!$K198)</f>
+        <f>RATE(100,,K98,-'Real Returns 1792-2026'!$K198)</f>
         <v>2.0079478766608417E-2</v>
       </c>
     </row>
@@ -14966,35 +14966,35 @@
         <v>1973.906220939904</v>
       </c>
       <c r="L199" s="2">
-        <f>RATE(10,,J189,-'Real Returns 1792-2025'!$J199)</f>
+        <f>RATE(10,,J189,-'Real Returns 1792-2026'!$J199)</f>
         <v>9.7076757782356374E-2</v>
       </c>
       <c r="M199" s="2">
-        <f>RATE(10,,K189,-'Real Returns 1792-2025'!$K199)</f>
+        <f>RATE(10,,K189,-'Real Returns 1792-2026'!$K199)</f>
         <v>4.7074356294295162E-2</v>
       </c>
       <c r="N199" s="2">
-        <f>RATE(30,,J169,-'Real Returns 1792-2025'!$J199)</f>
+        <f>RATE(30,,J169,-'Real Returns 1792-2026'!$J199)</f>
         <v>4.7963576891836557E-2</v>
       </c>
       <c r="O199" s="2">
-        <f>RATE(30,,K169,-'Real Returns 1792-2025'!$K199)</f>
+        <f>RATE(30,,K169,-'Real Returns 1792-2026'!$K199)</f>
         <v>9.9147129540513891E-3</v>
       </c>
       <c r="P199" s="2">
-        <f>RATE(50,,J149,-'Real Returns 1792-2025'!$J199)</f>
+        <f>RATE(50,,J149,-'Real Returns 1792-2026'!$J199)</f>
         <v>6.6963785440129819E-2</v>
       </c>
       <c r="Q199" s="2">
-        <f>RATE(50,,K149,-'Real Returns 1792-2025'!$K199)</f>
+        <f>RATE(50,,K149,-'Real Returns 1792-2026'!$K199)</f>
         <v>8.4391359272668214E-4</v>
       </c>
       <c r="R199" s="2">
-        <f>RATE(100,,J99,-'Real Returns 1792-2025'!$J199)</f>
+        <f>RATE(100,,J99,-'Real Returns 1792-2026'!$J199)</f>
         <v>6.1539918993455553E-2</v>
       </c>
       <c r="S199" s="2">
-        <f>RATE(100,,K99,-'Real Returns 1792-2025'!$K199)</f>
+        <f>RATE(100,,K99,-'Real Returns 1792-2026'!$K199)</f>
         <v>1.9519292676302074E-2</v>
       </c>
     </row>
@@ -15029,35 +15029,35 @@
         <v>2096.8336541105186</v>
       </c>
       <c r="L200" s="2">
-        <f>RATE(10,,J190,-'Real Returns 1792-2025'!$J200)</f>
+        <f>RATE(10,,J190,-'Real Returns 1792-2026'!$J200)</f>
         <v>9.2630242618488665E-2</v>
       </c>
       <c r="M200" s="2">
-        <f>RATE(10,,K190,-'Real Returns 1792-2025'!$K200)</f>
+        <f>RATE(10,,K190,-'Real Returns 1792-2026'!$K200)</f>
         <v>8.0956591627223171E-2</v>
       </c>
       <c r="N200" s="2">
-        <f>RATE(30,,J170,-'Real Returns 1792-2025'!$J200)</f>
+        <f>RATE(30,,J170,-'Real Returns 1792-2026'!$J200)</f>
         <v>4.9069219662112418E-2</v>
       </c>
       <c r="O200" s="2">
-        <f>RATE(30,,K170,-'Real Returns 1792-2025'!$K200)</f>
+        <f>RATE(30,,K170,-'Real Returns 1792-2026'!$K200)</f>
         <v>1.3008613574669262E-2</v>
       </c>
       <c r="P200" s="2">
-        <f>RATE(50,,J150,-'Real Returns 1792-2025'!$J200)</f>
+        <f>RATE(50,,J150,-'Real Returns 1792-2026'!$J200)</f>
         <v>6.6955331497414755E-2</v>
       </c>
       <c r="Q200" s="2">
-        <f>RATE(50,,K150,-'Real Returns 1792-2025'!$K200)</f>
+        <f>RATE(50,,K150,-'Real Returns 1792-2026'!$K200)</f>
         <v>1.4187647140494867E-3</v>
       </c>
       <c r="R200" s="2">
-        <f>RATE(100,,J100,-'Real Returns 1792-2025'!$J200)</f>
+        <f>RATE(100,,J100,-'Real Returns 1792-2026'!$J200)</f>
         <v>6.1153985989033453E-2</v>
       </c>
       <c r="S200" s="2">
-        <f>RATE(100,,K100,-'Real Returns 1792-2025'!$K200)</f>
+        <f>RATE(100,,K100,-'Real Returns 1792-2026'!$K200)</f>
         <v>1.9465827929624806E-2</v>
       </c>
     </row>
@@ -15092,35 +15092,35 @@
         <v>2192.9599182728321</v>
       </c>
       <c r="L201" s="2">
-        <f>RATE(10,,J191,-'Real Returns 1792-2025'!$J201)</f>
+        <f>RATE(10,,J191,-'Real Returns 1792-2026'!$J201)</f>
         <v>8.5236772404853042E-2</v>
       </c>
       <c r="M201" s="2">
-        <f>RATE(10,,K191,-'Real Returns 1792-2025'!$K201)</f>
+        <f>RATE(10,,K191,-'Real Returns 1792-2026'!$K201)</f>
         <v>9.5205229044231454E-2</v>
       </c>
       <c r="N201" s="2">
-        <f>RATE(30,,J171,-'Real Returns 1792-2025'!$J201)</f>
+        <f>RATE(30,,J171,-'Real Returns 1792-2026'!$J201)</f>
         <v>4.4784909266117133E-2</v>
       </c>
       <c r="O201" s="2">
-        <f>RATE(30,,K171,-'Real Returns 1792-2025'!$K201)</f>
+        <f>RATE(30,,K171,-'Real Returns 1792-2026'!$K201)</f>
         <v>1.207303987862245E-2</v>
       </c>
       <c r="P201" s="2">
-        <f>RATE(50,,J151,-'Real Returns 1792-2025'!$J201)</f>
+        <f>RATE(50,,J151,-'Real Returns 1792-2026'!$J201)</f>
         <v>6.9365202887231803E-2</v>
       </c>
       <c r="Q201" s="2">
-        <f>RATE(50,,K151,-'Real Returns 1792-2025'!$K201)</f>
+        <f>RATE(50,,K151,-'Real Returns 1792-2026'!$K201)</f>
         <v>1.5750050883724304E-3</v>
       </c>
       <c r="R201" s="2">
-        <f>RATE(100,,J101,-'Real Returns 1792-2025'!$J201)</f>
+        <f>RATE(100,,J101,-'Real Returns 1792-2026'!$J201)</f>
         <v>6.1697216653398258E-2</v>
       </c>
       <c r="S201" s="2">
-        <f>RATE(100,,K101,-'Real Returns 1792-2025'!$K201)</f>
+        <f>RATE(100,,K101,-'Real Returns 1792-2026'!$K201)</f>
         <v>1.9663267929367609E-2</v>
       </c>
     </row>
@@ -15155,35 +15155,35 @@
         <v>2480.9396867271735</v>
       </c>
       <c r="L202" s="2">
-        <f>RATE(10,,J192,-'Real Returns 1792-2025'!$J202)</f>
+        <f>RATE(10,,J192,-'Real Returns 1792-2026'!$J202)</f>
         <v>0.1207685050125868</v>
       </c>
       <c r="M202" s="2">
-        <f>RATE(10,,K192,-'Real Returns 1792-2025'!$K202)</f>
+        <f>RATE(10,,K192,-'Real Returns 1792-2026'!$K202)</f>
         <v>0.11915212042501028</v>
       </c>
       <c r="N202" s="2">
-        <f>RATE(30,,J172,-'Real Returns 1792-2025'!$J202)</f>
+        <f>RATE(30,,J172,-'Real Returns 1792-2026'!$J202)</f>
         <v>4.7646279889313019E-2</v>
       </c>
       <c r="O202" s="2">
-        <f>RATE(30,,K172,-'Real Returns 1792-2025'!$K202)</f>
+        <f>RATE(30,,K172,-'Real Returns 1792-2026'!$K202)</f>
         <v>1.5579564964137477E-2</v>
       </c>
       <c r="P202" s="2">
-        <f>RATE(50,,J152,-'Real Returns 1792-2025'!$J202)</f>
+        <f>RATE(50,,J152,-'Real Returns 1792-2026'!$J202)</f>
         <v>7.7469391310935151E-2</v>
       </c>
       <c r="Q202" s="2">
-        <f>RATE(50,,K152,-'Real Returns 1792-2025'!$K202)</f>
+        <f>RATE(50,,K152,-'Real Returns 1792-2026'!$K202)</f>
         <v>5.5134892578245576E-3</v>
       </c>
       <c r="R202" s="2">
-        <f>RATE(100,,J102,-'Real Returns 1792-2025'!$J202)</f>
+        <f>RATE(100,,J102,-'Real Returns 1792-2026'!$J202)</f>
         <v>6.2383754982508741E-2</v>
       </c>
       <c r="S202" s="2">
-        <f>RATE(100,,K102,-'Real Returns 1792-2025'!$K202)</f>
+        <f>RATE(100,,K102,-'Real Returns 1792-2026'!$K202)</f>
         <v>2.0390870602893123E-2</v>
       </c>
     </row>
@@ -15218,35 +15218,35 @@
         <v>2741.4764742940101</v>
       </c>
       <c r="L203" s="2">
-        <f>RATE(10,,J193,-'Real Returns 1792-2025'!$J203)</f>
+        <f>RATE(10,,J193,-'Real Returns 1792-2026'!$J203)</f>
         <v>0.10425062871433385</v>
       </c>
       <c r="M203" s="2">
-        <f>RATE(10,,K193,-'Real Returns 1792-2025'!$K203)</f>
+        <f>RATE(10,,K193,-'Real Returns 1792-2026'!$K203)</f>
         <v>9.4597886752574856E-2</v>
       </c>
       <c r="N203" s="2">
-        <f>RATE(30,,J173,-'Real Returns 1792-2025'!$J203)</f>
+        <f>RATE(30,,J173,-'Real Returns 1792-2026'!$J203)</f>
         <v>5.1255800568892951E-2</v>
       </c>
       <c r="O203" s="2">
-        <f>RATE(30,,K173,-'Real Returns 1792-2025'!$K203)</f>
+        <f>RATE(30,,K173,-'Real Returns 1792-2026'!$K203)</f>
         <v>1.6772870980784945E-2</v>
       </c>
       <c r="P203" s="2">
-        <f>RATE(50,,J153,-'Real Returns 1792-2025'!$J203)</f>
+        <f>RATE(50,,J153,-'Real Returns 1792-2026'!$J203)</f>
         <v>7.5867754319597719E-2</v>
       </c>
       <c r="Q203" s="2">
-        <f>RATE(50,,K153,-'Real Returns 1792-2025'!$K203)</f>
+        <f>RATE(50,,K153,-'Real Returns 1792-2026'!$K203)</f>
         <v>7.9947342621128469E-3</v>
       </c>
       <c r="R203" s="2">
-        <f>RATE(100,,J103,-'Real Returns 1792-2025'!$J203)</f>
+        <f>RATE(100,,J103,-'Real Returns 1792-2026'!$J203)</f>
         <v>6.2500974984922894E-2</v>
       </c>
       <c r="S203" s="2">
-        <f>RATE(100,,K103,-'Real Returns 1792-2025'!$K203)</f>
+        <f>RATE(100,,K103,-'Real Returns 1792-2026'!$K203)</f>
         <v>2.0922890031330497E-2</v>
       </c>
     </row>
@@ -15281,35 +15281,35 @@
         <v>3012.3610298496192</v>
       </c>
       <c r="L204" s="2">
-        <f>RATE(10,,J194,-'Real Returns 1792-2025'!$J204)</f>
+        <f>RATE(10,,J194,-'Real Returns 1792-2026'!$J204)</f>
         <v>0.10361059547505323</v>
       </c>
       <c r="M204" s="2">
-        <f>RATE(10,,K194,-'Real Returns 1792-2025'!$K204)</f>
+        <f>RATE(10,,K194,-'Real Returns 1792-2026'!$K204)</f>
         <v>9.8820559487636475E-2</v>
       </c>
       <c r="N204" s="2">
-        <f>RATE(30,,J174,-'Real Returns 1792-2025'!$J204)</f>
+        <f>RATE(30,,J174,-'Real Returns 1792-2026'!$J204)</f>
         <v>4.9674933164110986E-2</v>
       </c>
       <c r="O204" s="2">
-        <f>RATE(30,,K174,-'Real Returns 1792-2025'!$K204)</f>
+        <f>RATE(30,,K174,-'Real Returns 1792-2026'!$K204)</f>
         <v>1.9909926215378824E-2</v>
       </c>
       <c r="P204" s="2">
-        <f>RATE(50,,J154,-'Real Returns 1792-2025'!$J204)</f>
+        <f>RATE(50,,J154,-'Real Returns 1792-2026'!$J204)</f>
         <v>7.4548087181688052E-2</v>
       </c>
       <c r="Q204" s="2">
-        <f>RATE(50,,K154,-'Real Returns 1792-2025'!$K204)</f>
+        <f>RATE(50,,K154,-'Real Returns 1792-2026'!$K204)</f>
         <v>8.9630173545385845E-3</v>
       </c>
       <c r="R204" s="2">
-        <f>RATE(100,,J104,-'Real Returns 1792-2025'!$J204)</f>
+        <f>RATE(100,,J104,-'Real Returns 1792-2026'!$J204)</f>
         <v>6.5476025881013519E-2</v>
       </c>
       <c r="S204" s="2">
-        <f>RATE(100,,K104,-'Real Returns 1792-2025'!$K204)</f>
+        <f>RATE(100,,K104,-'Real Returns 1792-2026'!$K204)</f>
         <v>2.1127093498683597E-2</v>
       </c>
     </row>
@@ -15344,35 +15344,35 @@
         <v>2775.9935566997287</v>
       </c>
       <c r="L205" s="2">
-        <f>RATE(10,,J195,-'Real Returns 1792-2025'!$J205)</f>
+        <f>RATE(10,,J195,-'Real Returns 1792-2026'!$J205)</f>
         <v>8.8502328145559875E-2</v>
       </c>
       <c r="M205" s="2">
-        <f>RATE(10,,K195,-'Real Returns 1792-2025'!$K205)</f>
+        <f>RATE(10,,K195,-'Real Returns 1792-2026'!$K205)</f>
         <v>7.6185506978670062E-2</v>
       </c>
       <c r="N205" s="2">
-        <f>RATE(30,,J175,-'Real Returns 1792-2025'!$J205)</f>
+        <f>RATE(30,,J175,-'Real Returns 1792-2026'!$J205)</f>
         <v>4.27044482820257E-2</v>
       </c>
       <c r="O205" s="2">
-        <f>RATE(30,,K175,-'Real Returns 1792-2025'!$K205)</f>
+        <f>RATE(30,,K175,-'Real Returns 1792-2026'!$K205)</f>
         <v>1.6301430535305569E-2</v>
       </c>
       <c r="P205" s="2">
-        <f>RATE(50,,J155,-'Real Returns 1792-2025'!$J205)</f>
+        <f>RATE(50,,J155,-'Real Returns 1792-2026'!$J205)</f>
         <v>6.9849777432751892E-2</v>
       </c>
       <c r="Q205" s="2">
-        <f>RATE(50,,K155,-'Real Returns 1792-2025'!$K205)</f>
+        <f>RATE(50,,K155,-'Real Returns 1792-2026'!$K205)</f>
         <v>6.4472447697292868E-3</v>
       </c>
       <c r="R205" s="2">
-        <f>RATE(100,,J105,-'Real Returns 1792-2025'!$J205)</f>
+        <f>RATE(100,,J105,-'Real Returns 1792-2026'!$J205)</f>
         <v>6.4339618916203767E-2</v>
       </c>
       <c r="S205" s="2">
-        <f>RATE(100,,K105,-'Real Returns 1792-2025'!$K205)</f>
+        <f>RATE(100,,K105,-'Real Returns 1792-2026'!$K205)</f>
         <v>1.9301339444911112E-2</v>
       </c>
     </row>
@@ -15407,35 +15407,35 @@
         <v>3356.3039596615067</v>
       </c>
       <c r="L206" s="2">
-        <f>RATE(10,,J196,-'Real Returns 1792-2025'!$J206)</f>
+        <f>RATE(10,,J196,-'Real Returns 1792-2026'!$J206)</f>
         <v>0.10199736212644862</v>
       </c>
       <c r="M206" s="2">
-        <f>RATE(10,,K196,-'Real Returns 1792-2025'!$K206)</f>
+        <f>RATE(10,,K196,-'Real Returns 1792-2026'!$K206)</f>
         <v>7.536662893676957E-2</v>
       </c>
       <c r="N206" s="2">
-        <f>RATE(30,,J176,-'Real Returns 1792-2025'!$J206)</f>
+        <f>RATE(30,,J176,-'Real Returns 1792-2026'!$J206)</f>
         <v>4.9549557092435963E-2</v>
       </c>
       <c r="O206" s="2">
-        <f>RATE(30,,K176,-'Real Returns 1792-2025'!$K206)</f>
+        <f>RATE(30,,K176,-'Real Returns 1792-2026'!$K206)</f>
         <v>2.3670796465194658E-2</v>
       </c>
       <c r="P206" s="2">
-        <f>RATE(50,,J156,-'Real Returns 1792-2025'!$J206)</f>
+        <f>RATE(50,,J156,-'Real Returns 1792-2026'!$J206)</f>
         <v>6.8498869565996434E-2</v>
       </c>
       <c r="Q206" s="2">
-        <f>RATE(50,,K156,-'Real Returns 1792-2025'!$K206)</f>
+        <f>RATE(50,,K156,-'Real Returns 1792-2026'!$K206)</f>
         <v>9.4733452194154938E-3</v>
       </c>
       <c r="R206" s="2">
-        <f>RATE(100,,J106,-'Real Returns 1792-2025'!$J206)</f>
+        <f>RATE(100,,J106,-'Real Returns 1792-2026'!$J206)</f>
         <v>6.6699142671185194E-2</v>
       </c>
       <c r="S206" s="2">
-        <f>RATE(100,,K106,-'Real Returns 1792-2025'!$K206)</f>
+        <f>RATE(100,,K106,-'Real Returns 1792-2026'!$K206)</f>
         <v>2.0773530312806703E-2</v>
       </c>
     </row>
@@ -15470,35 +15470,35 @@
         <v>3288.9536329151483</v>
       </c>
       <c r="L207" s="2">
-        <f>RATE(10,,J197,-'Real Returns 1792-2025'!$J207)</f>
+        <f>RATE(10,,J197,-'Real Returns 1792-2026'!$J207)</f>
         <v>9.5973561981866018E-2</v>
       </c>
       <c r="M207" s="2">
-        <f>RATE(10,,K197,-'Real Returns 1792-2025'!$K207)</f>
+        <f>RATE(10,,K197,-'Real Returns 1792-2026'!$K207)</f>
         <v>5.3682194123027521E-2</v>
       </c>
       <c r="N207" s="2">
-        <f>RATE(30,,J177,-'Real Returns 1792-2025'!$J207)</f>
+        <f>RATE(30,,J177,-'Real Returns 1792-2026'!$J207)</f>
         <v>5.8026147242571033E-2</v>
       </c>
       <c r="O207" s="2">
-        <f>RATE(30,,K177,-'Real Returns 1792-2025'!$K207)</f>
+        <f>RATE(30,,K177,-'Real Returns 1792-2026'!$K207)</f>
         <v>2.3601939633799675E-2</v>
       </c>
       <c r="P207" s="2">
-        <f>RATE(50,,J157,-'Real Returns 1792-2025'!$J207)</f>
+        <f>RATE(50,,J157,-'Real Returns 1792-2026'!$J207)</f>
         <v>7.8544924130439051E-2</v>
       </c>
       <c r="Q207" s="2">
-        <f>RATE(50,,K157,-'Real Returns 1792-2025'!$K207)</f>
+        <f>RATE(50,,K157,-'Real Returns 1792-2026'!$K207)</f>
         <v>1.2512741954287292E-2</v>
       </c>
       <c r="R207" s="2">
-        <f>RATE(100,,J107,-'Real Returns 1792-2025'!$J207)</f>
+        <f>RATE(100,,J107,-'Real Returns 1792-2026'!$J207)</f>
         <v>6.856785153735459E-2</v>
       </c>
       <c r="S207" s="2">
-        <f>RATE(100,,K107,-'Real Returns 1792-2025'!$K207)</f>
+        <f>RATE(100,,K107,-'Real Returns 1792-2026'!$K207)</f>
         <v>1.991686443917311E-2</v>
       </c>
     </row>
@@ -15533,35 +15533,35 @@
         <v>3717.9004939654192</v>
       </c>
       <c r="L208" s="2">
-        <f>RATE(10,,J198,-'Real Returns 1792-2025'!$J208)</f>
+        <f>RATE(10,,J198,-'Real Returns 1792-2026'!$J208)</f>
         <v>0.12939515570681678</v>
       </c>
       <c r="M208" s="2">
-        <f>RATE(10,,K198,-'Real Returns 1792-2025'!$K208)</f>
+        <f>RATE(10,,K198,-'Real Returns 1792-2026'!$K208)</f>
         <v>6.8099642035387209E-2</v>
       </c>
       <c r="N208" s="2">
-        <f>RATE(30,,J178,-'Real Returns 1792-2025'!$J208)</f>
+        <f>RATE(30,,J178,-'Real Returns 1792-2026'!$J208)</f>
         <v>6.1753522826289653E-2</v>
       </c>
       <c r="O208" s="2">
-        <f>RATE(30,,K178,-'Real Returns 1792-2025'!$K208)</f>
+        <f>RATE(30,,K178,-'Real Returns 1792-2026'!$K208)</f>
         <v>3.1929914287594847E-2</v>
       </c>
       <c r="P208" s="2">
-        <f>RATE(50,,J158,-'Real Returns 1792-2025'!$J208)</f>
+        <f>RATE(50,,J158,-'Real Returns 1792-2026'!$J208)</f>
         <v>8.5438170332031577E-2</v>
       </c>
       <c r="Q208" s="2">
-        <f>RATE(50,,K158,-'Real Returns 1792-2025'!$K208)</f>
+        <f>RATE(50,,K158,-'Real Returns 1792-2026'!$K208)</f>
         <v>1.8177937288109847E-2</v>
       </c>
       <c r="R208" s="2">
-        <f>RATE(100,,J108,-'Real Returns 1792-2025'!$J208)</f>
+        <f>RATE(100,,J108,-'Real Returns 1792-2026'!$J208)</f>
         <v>6.8685053858020109E-2</v>
       </c>
       <c r="S208" s="2">
-        <f>RATE(100,,K108,-'Real Returns 1792-2025'!$K208)</f>
+        <f>RATE(100,,K108,-'Real Returns 1792-2026'!$K208)</f>
         <v>2.0042522751322386E-2</v>
       </c>
     </row>
@@ -15596,35 +15596,35 @@
         <v>4044.51917239043</v>
       </c>
       <c r="L209" s="2">
-        <f>RATE(10,,J199,-'Real Returns 1792-2025'!$J209)</f>
+        <f>RATE(10,,J199,-'Real Returns 1792-2026'!$J209)</f>
         <v>0.13862726460345703</v>
       </c>
       <c r="M209" s="2">
-        <f>RATE(10,,K199,-'Real Returns 1792-2025'!$K209)</f>
+        <f>RATE(10,,K199,-'Real Returns 1792-2026'!$K209)</f>
         <v>7.4370409153438288E-2</v>
       </c>
       <c r="N209" s="2">
-        <f>RATE(30,,J179,-'Real Returns 1792-2025'!$J209)</f>
+        <f>RATE(30,,J179,-'Real Returns 1792-2026'!$J209)</f>
         <v>6.5224651217974855E-2</v>
       </c>
       <c r="O209" s="2">
-        <f>RATE(30,,K179,-'Real Returns 1792-2025'!$K209)</f>
+        <f>RATE(30,,K179,-'Real Returns 1792-2026'!$K209)</f>
         <v>3.6438262626545592E-2</v>
       </c>
       <c r="P209" s="2">
-        <f>RATE(50,,J159,-'Real Returns 1792-2025'!$J209)</f>
+        <f>RATE(50,,J159,-'Real Returns 1792-2026'!$J209)</f>
         <v>8.9078877682734883E-2</v>
       </c>
       <c r="Q209" s="2">
-        <f>RATE(50,,K159,-'Real Returns 1792-2025'!$K209)</f>
+        <f>RATE(50,,K159,-'Real Returns 1792-2026'!$K209)</f>
         <v>1.8954543642170189E-2</v>
       </c>
       <c r="R209" s="2">
-        <f>RATE(100,,J109,-'Real Returns 1792-2025'!$J209)</f>
+        <f>RATE(100,,J109,-'Real Returns 1792-2026'!$J209)</f>
         <v>6.8223154109443282E-2</v>
       </c>
       <c r="S209" s="2">
-        <f>RATE(100,,K109,-'Real Returns 1792-2025'!$K209)</f>
+        <f>RATE(100,,K109,-'Real Returns 1792-2026'!$K209)</f>
         <v>1.9811060524449777E-2</v>
       </c>
     </row>
@@ -15659,35 +15659,35 @@
         <v>3591.42035957182</v>
       </c>
       <c r="L210" s="2">
-        <f>RATE(10,,J200,-'Real Returns 1792-2025'!$J210)</f>
+        <f>RATE(10,,J200,-'Real Returns 1792-2026'!$J210)</f>
         <v>0.14516997384962019</v>
       </c>
       <c r="M210" s="2">
-        <f>RATE(10,,K200,-'Real Returns 1792-2025'!$K210)</f>
+        <f>RATE(10,,K200,-'Real Returns 1792-2026'!$K210)</f>
         <v>5.5286120523646766E-2</v>
       </c>
       <c r="N210" s="2">
-        <f>RATE(30,,J180,-'Real Returns 1792-2025'!$J210)</f>
+        <f>RATE(30,,J180,-'Real Returns 1792-2026'!$J210)</f>
         <v>7.8231777118767998E-2</v>
       </c>
       <c r="O210" s="2">
-        <f>RATE(30,,K180,-'Real Returns 1792-2025'!$K210)</f>
+        <f>RATE(30,,K180,-'Real Returns 1792-2026'!$K210)</f>
         <v>3.7683040830861353E-2</v>
       </c>
       <c r="P210" s="2">
-        <f>RATE(50,,J160,-'Real Returns 1792-2025'!$J210)</f>
+        <f>RATE(50,,J160,-'Real Returns 1792-2026'!$J210)</f>
         <v>8.6930691151268849E-2</v>
       </c>
       <c r="Q210" s="2">
-        <f>RATE(50,,K160,-'Real Returns 1792-2025'!$K210)</f>
+        <f>RATE(50,,K160,-'Real Returns 1792-2026'!$K210)</f>
         <v>1.4792955237088052E-2</v>
       </c>
       <c r="R210" s="2">
-        <f>RATE(100,,J110,-'Real Returns 1792-2025'!$J210)</f>
+        <f>RATE(100,,J110,-'Real Returns 1792-2026'!$J210)</f>
         <v>6.9148077756872844E-2</v>
       </c>
       <c r="S210" s="2">
-        <f>RATE(100,,K110,-'Real Returns 1792-2025'!$K210)</f>
+        <f>RATE(100,,K110,-'Real Returns 1792-2026'!$K210)</f>
         <v>1.8370889850210365E-2</v>
       </c>
     </row>
@@ -15722,35 +15722,35 @@
         <v>4056.0413001941833</v>
       </c>
       <c r="L211" s="2">
-        <f>RATE(10,,J201,-'Real Returns 1792-2025'!$J211)</f>
+        <f>RATE(10,,J201,-'Real Returns 1792-2026'!$J211)</f>
         <v>0.13620650838141488</v>
       </c>
       <c r="M211" s="2">
-        <f>RATE(10,,K201,-'Real Returns 1792-2025'!$K211)</f>
+        <f>RATE(10,,K201,-'Real Returns 1792-2026'!$K211)</f>
         <v>6.3425738390481906E-2</v>
       </c>
       <c r="N211" s="2">
-        <f>RATE(30,,J181,-'Real Returns 1792-2025'!$J211)</f>
+        <f>RATE(30,,J181,-'Real Returns 1792-2026'!$J211)</f>
         <v>7.2793494045964011E-2</v>
       </c>
       <c r="O211" s="2">
-        <f>RATE(30,,K181,-'Real Returns 1792-2025'!$K211)</f>
+        <f>RATE(30,,K181,-'Real Returns 1792-2026'!$K211)</f>
         <v>3.6978566748531866E-2</v>
       </c>
       <c r="P211" s="2">
-        <f>RATE(50,,J161,-'Real Returns 1792-2025'!$J211)</f>
+        <f>RATE(50,,J161,-'Real Returns 1792-2026'!$J211)</f>
         <v>8.0354286341037084E-2</v>
       </c>
       <c r="Q211" s="2">
-        <f>RATE(50,,K161,-'Real Returns 1792-2025'!$K211)</f>
+        <f>RATE(50,,K161,-'Real Returns 1792-2026'!$K211)</f>
         <v>1.8161900518143863E-2</v>
       </c>
       <c r="R211" s="2">
-        <f>RATE(100,,J111,-'Real Returns 1792-2025'!$J211)</f>
+        <f>RATE(100,,J111,-'Real Returns 1792-2026'!$J211)</f>
         <v>6.6463642041944895E-2</v>
       </c>
       <c r="S211" s="2">
-        <f>RATE(100,,K111,-'Real Returns 1792-2025'!$K211)</f>
+        <f>RATE(100,,K111,-'Real Returns 1792-2026'!$K211)</f>
         <v>1.8994399380029472E-2</v>
       </c>
     </row>
@@ -15785,35 +15785,35 @@
         <v>4358.4126241668946</v>
       </c>
       <c r="L212" s="2">
-        <f>RATE(10,,J202,-'Real Returns 1792-2025'!$J212)</f>
+        <f>RATE(10,,J202,-'Real Returns 1792-2026'!$J212)</f>
         <v>9.1534200051453268E-2</v>
       </c>
       <c r="M212" s="2">
-        <f>RATE(10,,K202,-'Real Returns 1792-2025'!$K212)</f>
+        <f>RATE(10,,K202,-'Real Returns 1792-2026'!$K212)</f>
         <v>5.7964788794201756E-2</v>
       </c>
       <c r="N212" s="2">
-        <f>RATE(30,,J182,-'Real Returns 1792-2025'!$J212)</f>
+        <f>RATE(30,,J182,-'Real Returns 1792-2026'!$J212)</f>
         <v>6.278810621981265E-2</v>
       </c>
       <c r="O212" s="2">
-        <f>RATE(30,,K182,-'Real Returns 1792-2025'!$K212)</f>
+        <f>RATE(30,,K182,-'Real Returns 1792-2026'!$K212)</f>
         <v>3.8486921601727911E-2</v>
       </c>
       <c r="P212" s="2">
-        <f>RATE(50,,J162,-'Real Returns 1792-2025'!$J212)</f>
+        <f>RATE(50,,J162,-'Real Returns 1792-2026'!$J212)</f>
         <v>7.4033422647194355E-2</v>
       </c>
       <c r="Q212" s="2">
-        <f>RATE(50,,K162,-'Real Returns 1792-2025'!$K212)</f>
+        <f>RATE(50,,K162,-'Real Returns 1792-2026'!$K212)</f>
         <v>2.111259613874961E-2</v>
       </c>
       <c r="R212" s="2">
-        <f>RATE(100,,J112,-'Real Returns 1792-2025'!$J212)</f>
+        <f>RATE(100,,J112,-'Real Returns 1792-2026'!$J212)</f>
         <v>6.2741961495203044E-2</v>
       </c>
       <c r="S212" s="2">
-        <f>RATE(100,,K112,-'Real Returns 1792-2025'!$K212)</f>
+        <f>RATE(100,,K112,-'Real Returns 1792-2026'!$K212)</f>
         <v>1.9325482378219492E-2</v>
       </c>
     </row>
@@ -15848,35 +15848,35 @@
         <v>4867.015068372868</v>
       </c>
       <c r="L213" s="2">
-        <f>RATE(10,,J203,-'Real Returns 1792-2025'!$J213)</f>
+        <f>RATE(10,,J203,-'Real Returns 1792-2026'!$J213)</f>
         <v>5.5534920025182802E-2</v>
       </c>
       <c r="M213" s="2">
-        <f>RATE(10,,K203,-'Real Returns 1792-2025'!$K213)</f>
+        <f>RATE(10,,K203,-'Real Returns 1792-2026'!$K213)</f>
         <v>5.9077683271976322E-2</v>
       </c>
       <c r="N213" s="2">
-        <f>RATE(30,,J183,-'Real Returns 1792-2025'!$J213)</f>
+        <f>RATE(30,,J183,-'Real Returns 1792-2026'!$J213)</f>
         <v>5.098150974729266E-2</v>
       </c>
       <c r="O213" s="2">
-        <f>RATE(30,,K183,-'Real Returns 1792-2025'!$K213)</f>
+        <f>RATE(30,,K183,-'Real Returns 1792-2026'!$K213)</f>
         <v>4.1421451595557685E-2</v>
       </c>
       <c r="P213" s="2">
-        <f>RATE(50,,J163,-'Real Returns 1792-2025'!$J213)</f>
+        <f>RATE(50,,J163,-'Real Returns 1792-2026'!$J213)</f>
         <v>6.6119590306475406E-2</v>
       </c>
       <c r="Q213" s="2">
-        <f>RATE(50,,K163,-'Real Returns 1792-2025'!$K213)</f>
+        <f>RATE(50,,K163,-'Real Returns 1792-2026'!$K213)</f>
         <v>2.3042189040424002E-2</v>
       </c>
       <c r="R213" s="2">
-        <f>RATE(100,,J113,-'Real Returns 1792-2025'!$J213)</f>
+        <f>RATE(100,,J113,-'Real Returns 1792-2026'!$J213)</f>
         <v>5.9247988900664156E-2</v>
       </c>
       <c r="S213" s="2">
-        <f>RATE(100,,K113,-'Real Returns 1792-2025'!$K213)</f>
+        <f>RATE(100,,K113,-'Real Returns 1792-2026'!$K213)</f>
         <v>2.0425775728835666E-2</v>
       </c>
     </row>
@@ -15911,35 +15911,35 @@
         <v>5110.0722857507526</v>
       </c>
       <c r="L214" s="2">
-        <f>RATE(10,,J204,-'Real Returns 1792-2025'!$J214)</f>
+        <f>RATE(10,,J204,-'Real Returns 1792-2026'!$J214)</f>
         <v>7.7978055401617938E-2</v>
       </c>
       <c r="M214" s="2">
-        <f>RATE(10,,K204,-'Real Returns 1792-2025'!$K214)</f>
+        <f>RATE(10,,K204,-'Real Returns 1792-2026'!$K214)</f>
         <v>5.4270373264703194E-2</v>
       </c>
       <c r="N214" s="2">
-        <f>RATE(30,,J184,-'Real Returns 1792-2025'!$J214)</f>
+        <f>RATE(30,,J184,-'Real Returns 1792-2026'!$J214)</f>
         <v>7.1450702706407576E-2</v>
       </c>
       <c r="O214" s="2">
-        <f>RATE(30,,K184,-'Real Returns 1792-2025'!$K214)</f>
+        <f>RATE(30,,K184,-'Real Returns 1792-2026'!$K214)</f>
         <v>4.5861721970272697E-2</v>
       </c>
       <c r="P214" s="2">
-        <f>RATE(50,,J164,-'Real Returns 1792-2025'!$J214)</f>
+        <f>RATE(50,,J164,-'Real Returns 1792-2026'!$J214)</f>
         <v>7.1847056962223835E-2</v>
       </c>
       <c r="Q214" s="2">
-        <f>RATE(50,,K164,-'Real Returns 1792-2025'!$K214)</f>
+        <f>RATE(50,,K164,-'Real Returns 1792-2026'!$K214)</f>
         <v>2.3247475321913756E-2</v>
       </c>
       <c r="R214" s="2">
-        <f>RATE(100,,J114,-'Real Returns 1792-2025'!$J214)</f>
+        <f>RATE(100,,J114,-'Real Returns 1792-2026'!$J214)</f>
         <v>6.4762649755020107E-2</v>
       </c>
       <c r="S214" s="2">
-        <f>RATE(100,,K114,-'Real Returns 1792-2025'!$K214)</f>
+        <f>RATE(100,,K114,-'Real Returns 1792-2026'!$K214)</f>
         <v>2.1010622001205112E-2</v>
       </c>
     </row>
@@ -15974,35 +15974,35 @@
         <v>5443.1642320675746</v>
       </c>
       <c r="L215" s="2">
-        <f>RATE(10,,J205,-'Real Returns 1792-2025'!$J215)</f>
+        <f>RATE(10,,J205,-'Real Returns 1792-2026'!$J215)</f>
         <v>8.7647569276004936E-2</v>
       </c>
       <c r="M215" s="2">
-        <f>RATE(10,,K205,-'Real Returns 1792-2025'!$K215)</f>
+        <f>RATE(10,,K205,-'Real Returns 1792-2026'!$K215)</f>
         <v>6.9653947968473393E-2</v>
       </c>
       <c r="N215" s="2">
-        <f>RATE(30,,J185,-'Real Returns 1792-2025'!$J215)</f>
+        <f>RATE(30,,J185,-'Real Returns 1792-2026'!$J215)</f>
         <v>8.418557214508253E-2</v>
       </c>
       <c r="O215" s="2">
-        <f>RATE(30,,K185,-'Real Returns 1792-2025'!$K215)</f>
+        <f>RATE(30,,K185,-'Real Returns 1792-2026'!$K215)</f>
         <v>5.0844950354156468E-2</v>
       </c>
       <c r="P215" s="2">
-        <f>RATE(50,,J165,-'Real Returns 1792-2025'!$J215)</f>
+        <f>RATE(50,,J165,-'Real Returns 1792-2026'!$J215)</f>
         <v>6.4841679731771767E-2</v>
       </c>
       <c r="Q215" s="2">
-        <f>RATE(50,,K165,-'Real Returns 1792-2025'!$K215)</f>
+        <f>RATE(50,,K165,-'Real Returns 1792-2026'!$K215)</f>
         <v>2.384994853068096E-2</v>
       </c>
       <c r="R215" s="2">
-        <f>RATE(100,,J115,-'Real Returns 1792-2025'!$J215)</f>
+        <f>RATE(100,,J115,-'Real Returns 1792-2026'!$J215)</f>
         <v>6.2307477053059931E-2</v>
       </c>
       <c r="S215" s="2">
-        <f>RATE(100,,K115,-'Real Returns 1792-2025'!$K215)</f>
+        <f>RATE(100,,K115,-'Real Returns 1792-2026'!$K215)</f>
         <v>2.0491064810646234E-2</v>
       </c>
     </row>
@@ -16037,35 +16037,35 @@
         <v>5342.4130287238604</v>
       </c>
       <c r="L216" s="2">
-        <f>RATE(10,,J206,-'Real Returns 1792-2025'!$J216)</f>
+        <f>RATE(10,,J206,-'Real Returns 1792-2026'!$J216)</f>
         <v>6.7371929532916083E-2</v>
       </c>
       <c r="M216" s="2">
-        <f>RATE(10,,K206,-'Real Returns 1792-2025'!$K216)</f>
+        <f>RATE(10,,K206,-'Real Returns 1792-2026'!$K216)</f>
         <v>4.7581010946829691E-2</v>
       </c>
       <c r="N216" s="2">
-        <f>RATE(30,,J186,-'Real Returns 1792-2025'!$J216)</f>
+        <f>RATE(30,,J186,-'Real Returns 1792-2026'!$J216)</f>
         <v>7.910039077644361E-2</v>
       </c>
       <c r="O216" s="2">
-        <f>RATE(30,,K186,-'Real Returns 1792-2025'!$K216)</f>
+        <f>RATE(30,,K186,-'Real Returns 1792-2026'!$K216)</f>
         <v>4.9057843179039481E-2</v>
       </c>
       <c r="P216" s="2">
-        <f>RATE(50,,J166,-'Real Returns 1792-2025'!$J216)</f>
+        <f>RATE(50,,J166,-'Real Returns 1792-2026'!$J216)</f>
         <v>6.2931843063518358E-2</v>
       </c>
       <c r="Q216" s="2">
-        <f>RATE(50,,K166,-'Real Returns 1792-2025'!$K216)</f>
+        <f>RATE(50,,K166,-'Real Returns 1792-2026'!$K216)</f>
         <v>2.3157674850399827E-2</v>
       </c>
       <c r="R216" s="2">
-        <f>RATE(100,,J116,-'Real Returns 1792-2025'!$J216)</f>
+        <f>RATE(100,,J116,-'Real Returns 1792-2026'!$J216)</f>
         <v>6.1311523937018622E-2</v>
       </c>
       <c r="S216" s="2">
-        <f>RATE(100,,K116,-'Real Returns 1792-2025'!$K216)</f>
+        <f>RATE(100,,K116,-'Real Returns 1792-2026'!$K216)</f>
         <v>1.9949781790068569E-2</v>
       </c>
     </row>
@@ -16100,35 +16100,35 @@
         <v>5426.0253837182327</v>
       </c>
       <c r="L217" s="2">
-        <f>RATE(10,,J207,-'Real Returns 1792-2025'!$J217)</f>
+        <f>RATE(10,,J207,-'Real Returns 1792-2026'!$J217)</f>
         <v>5.9205781803927188E-2</v>
       </c>
       <c r="M217" s="2">
-        <f>RATE(10,,K207,-'Real Returns 1792-2025'!$K217)</f>
+        <f>RATE(10,,K207,-'Real Returns 1792-2026'!$K217)</f>
         <v>5.1338108939511164E-2</v>
       </c>
       <c r="N217" s="2">
-        <f>RATE(30,,J187,-'Real Returns 1792-2025'!$J217)</f>
+        <f>RATE(30,,J187,-'Real Returns 1792-2026'!$J217)</f>
         <v>8.1941342799733294E-2</v>
       </c>
       <c r="O217" s="2">
-        <f>RATE(30,,K187,-'Real Returns 1792-2025'!$K217)</f>
+        <f>RATE(30,,K187,-'Real Returns 1792-2026'!$K217)</f>
         <v>4.7128848987350487E-2</v>
       </c>
       <c r="P217" s="2">
-        <f>RATE(50,,J167,-'Real Returns 1792-2025'!$J217)</f>
+        <f>RATE(50,,J167,-'Real Returns 1792-2026'!$J217)</f>
         <v>6.4225956842684812E-2</v>
       </c>
       <c r="Q217" s="2">
-        <f>RATE(50,,K167,-'Real Returns 1792-2025'!$K217)</f>
+        <f>RATE(50,,K167,-'Real Returns 1792-2026'!$K217)</f>
         <v>2.5565758460535475E-2</v>
       </c>
       <c r="R217" s="2">
-        <f>RATE(100,,J117,-'Real Returns 1792-2025'!$J217)</f>
+        <f>RATE(100,,J117,-'Real Returns 1792-2026'!$J217)</f>
         <v>6.2762346404908256E-2</v>
       </c>
       <c r="S217" s="2">
-        <f>RATE(100,,K117,-'Real Returns 1792-2025'!$K217)</f>
+        <f>RATE(100,,K117,-'Real Returns 1792-2026'!$K217)</f>
         <v>2.0382922215621917E-2</v>
       </c>
     </row>
@@ -16163,35 +16163,35 @@
         <v>5374.5068489739469</v>
       </c>
       <c r="L218" s="2">
-        <f>RATE(10,,J208,-'Real Returns 1792-2025'!$J218)</f>
+        <f>RATE(10,,J208,-'Real Returns 1792-2026'!$J218)</f>
         <v>3.232738506434675E-2</v>
       </c>
       <c r="M218" s="2">
-        <f>RATE(10,,K208,-'Real Returns 1792-2025'!$K218)</f>
+        <f>RATE(10,,K208,-'Real Returns 1792-2026'!$K218)</f>
         <v>3.7538176960251766E-2</v>
       </c>
       <c r="N218" s="2">
-        <f>RATE(30,,J188,-'Real Returns 1792-2025'!$J218)</f>
+        <f>RATE(30,,J188,-'Real Returns 1792-2026'!$J218)</f>
         <v>8.4140215333752613E-2</v>
       </c>
       <c r="O218" s="2">
-        <f>RATE(30,,K188,-'Real Returns 1792-2025'!$K218)</f>
+        <f>RATE(30,,K188,-'Real Returns 1792-2026'!$K218)</f>
         <v>4.7750950678095462E-2</v>
       </c>
       <c r="P218" s="2">
-        <f>RATE(50,,J168,-'Real Returns 1792-2025'!$J218)</f>
+        <f>RATE(50,,J168,-'Real Returns 1792-2026'!$J218)</f>
         <v>6.4409454539645736E-2</v>
       </c>
       <c r="Q218" s="2">
-        <f>RATE(50,,K168,-'Real Returns 1792-2025'!$K218)</f>
+        <f>RATE(50,,K168,-'Real Returns 1792-2026'!$K218)</f>
         <v>2.5043802034117567E-2</v>
       </c>
       <c r="R218" s="2">
-        <f>RATE(100,,J118,-'Real Returns 1792-2025'!$J218)</f>
+        <f>RATE(100,,J118,-'Real Returns 1792-2026'!$J218)</f>
         <v>6.5272968752001073E-2</v>
       </c>
       <c r="S218" s="2">
-        <f>RATE(100,,K118,-'Real Returns 1792-2025'!$K218)</f>
+        <f>RATE(100,,K118,-'Real Returns 1792-2026'!$K218)</f>
         <v>2.0807644550679193E-2</v>
       </c>
     </row>
@@ -16226,35 +16226,35 @@
         <v>5281.3930615474837</v>
       </c>
       <c r="L219" s="2">
-        <f>RATE(10,,J209,-'Real Returns 1792-2025'!$J219)</f>
+        <f>RATE(10,,J209,-'Real Returns 1792-2026'!$J219)</f>
         <v>-3.8984943726188541E-2</v>
       </c>
       <c r="M219" s="2">
-        <f>RATE(10,,K209,-'Real Returns 1792-2025'!$K219)</f>
+        <f>RATE(10,,K209,-'Real Returns 1792-2026'!$K219)</f>
         <v>2.7041893935272506E-2</v>
       </c>
       <c r="N219" s="2">
-        <f>RATE(30,,J189,-'Real Returns 1792-2025'!$J219)</f>
+        <f>RATE(30,,J189,-'Real Returns 1792-2026'!$J219)</f>
         <v>6.2795226233282306E-2</v>
       </c>
       <c r="O219" s="2">
-        <f>RATE(30,,K189,-'Real Returns 1792-2025'!$K219)</f>
+        <f>RATE(30,,K189,-'Real Returns 1792-2026'!$K219)</f>
         <v>4.9316673162157605E-2</v>
       </c>
       <c r="P219" s="2">
-        <f>RATE(50,,J169,-'Real Returns 1792-2025'!$J219)</f>
+        <f>RATE(50,,J169,-'Real Returns 1792-2026'!$J219)</f>
         <v>4.7201045804010994E-2</v>
       </c>
       <c r="Q219" s="2">
-        <f>RATE(50,,K169,-'Real Returns 1792-2025'!$K219)</f>
+        <f>RATE(50,,K169,-'Real Returns 1792-2026'!$K219)</f>
         <v>2.5933613180003135E-2</v>
       </c>
       <c r="R219" s="2">
-        <f>RATE(100,,J119,-'Real Returns 1792-2025'!$J219)</f>
+        <f>RATE(100,,J119,-'Real Returns 1792-2026'!$J219)</f>
         <v>5.6308239779982755E-2</v>
       </c>
       <c r="S219" s="2">
-        <f>RATE(100,,K119,-'Real Returns 1792-2025'!$K219)</f>
+        <f>RATE(100,,K119,-'Real Returns 1792-2026'!$K219)</f>
         <v>1.9277759299647198E-2</v>
       </c>
     </row>
@@ -16289,35 +16289,35 @@
         <v>5913.0895633047594</v>
       </c>
       <c r="L220" s="2">
-        <f>RATE(10,,J210,-'Real Returns 1792-2025'!$J220)</f>
+        <f>RATE(10,,J210,-'Real Returns 1792-2026'!$J220)</f>
         <v>-2.2610657455776603E-2</v>
       </c>
       <c r="M220" s="2">
-        <f>RATE(10,,K210,-'Real Returns 1792-2025'!$K220)</f>
+        <f>RATE(10,,K210,-'Real Returns 1792-2026'!$K220)</f>
         <v>5.1126104130944192E-2</v>
       </c>
       <c r="N220" s="2">
-        <f>RATE(30,,J190,-'Real Returns 1792-2025'!$J220)</f>
+        <f>RATE(30,,J190,-'Real Returns 1792-2026'!$J220)</f>
         <v>6.9391980304522552E-2</v>
       </c>
       <c r="O220" s="2">
-        <f>RATE(30,,K190,-'Real Returns 1792-2025'!$K220)</f>
+        <f>RATE(30,,K190,-'Real Returns 1792-2026'!$K220)</f>
         <v>6.2374816786071985E-2</v>
       </c>
       <c r="P220" s="2">
-        <f>RATE(50,,J170,-'Real Returns 1792-2025'!$J220)</f>
+        <f>RATE(50,,J170,-'Real Returns 1792-2026'!$J220)</f>
         <v>5.2616072839671187E-2</v>
       </c>
       <c r="Q220" s="2">
-        <f>RATE(50,,K170,-'Real Returns 1792-2025'!$K220)</f>
+        <f>RATE(50,,K170,-'Real Returns 1792-2026'!$K220)</f>
         <v>2.8899349085599029E-2</v>
       </c>
       <c r="R220" s="2">
-        <f>RATE(100,,J120,-'Real Returns 1792-2025'!$J220)</f>
+        <f>RATE(100,,J120,-'Real Returns 1792-2026'!$J220)</f>
         <v>5.7875829402793635E-2</v>
       </c>
       <c r="S220" s="2">
-        <f>RATE(100,,K120,-'Real Returns 1792-2025'!$K220)</f>
+        <f>RATE(100,,K120,-'Real Returns 1792-2026'!$K220)</f>
         <v>2.0251462402244465E-2</v>
       </c>
     </row>
@@ -16352,35 +16352,35 @@
         <v>6351.564660465694</v>
       </c>
       <c r="L221" s="2">
-        <f>RATE(10,,J211,-'Real Returns 1792-2025'!$J221)</f>
+        <f>RATE(10,,J211,-'Real Returns 1792-2026'!$J221)</f>
         <v>5.0810507754376752E-3</v>
       </c>
       <c r="M221" s="2">
-        <f>RATE(10,,K211,-'Real Returns 1792-2025'!$K221)</f>
+        <f>RATE(10,,K211,-'Real Returns 1792-2026'!$K221)</f>
         <v>4.5870312472837571E-2</v>
       </c>
       <c r="N221" s="2">
-        <f>RATE(30,,J191,-'Real Returns 1792-2025'!$J221)</f>
+        <f>RATE(30,,J191,-'Real Returns 1792-2026'!$J221)</f>
         <v>7.4140156643686853E-2</v>
       </c>
       <c r="O221" s="2">
-        <f>RATE(30,,K191,-'Real Returns 1792-2025'!$K221)</f>
+        <f>RATE(30,,K191,-'Real Returns 1792-2026'!$K221)</f>
         <v>6.7972747565251901E-2</v>
       </c>
       <c r="P221" s="2">
-        <f>RATE(50,,J171,-'Real Returns 1792-2025'!$J221)</f>
+        <f>RATE(50,,J171,-'Real Returns 1792-2026'!$J221)</f>
         <v>5.4260187105124064E-2</v>
       </c>
       <c r="Q221" s="2">
-        <f>RATE(50,,K171,-'Real Returns 1792-2025'!$K221)</f>
+        <f>RATE(50,,K171,-'Real Returns 1792-2026'!$K221)</f>
         <v>2.8878552499406983E-2</v>
       </c>
       <c r="R221" s="2">
-        <f>RATE(100,,J121,-'Real Returns 1792-2025'!$J221)</f>
+        <f>RATE(100,,J121,-'Real Returns 1792-2026'!$J221)</f>
         <v>6.0671107184200816E-2</v>
       </c>
       <c r="S221" s="2">
-        <f>RATE(100,,K121,-'Real Returns 1792-2025'!$K221)</f>
+        <f>RATE(100,,K121,-'Real Returns 1792-2026'!$K221)</f>
         <v>2.0888584048290821E-2</v>
       </c>
     </row>
@@ -16415,35 +16415,35 @@
         <v>7570.0147620579783</v>
       </c>
       <c r="L222" s="2">
-        <f>RATE(10,,J212,-'Real Returns 1792-2025'!$J222)</f>
+        <f>RATE(10,,J212,-'Real Returns 1792-2026'!$J222)</f>
         <v>2.3333244163560758E-2</v>
       </c>
       <c r="M222" s="2">
-        <f>RATE(10,,K212,-'Real Returns 1792-2025'!$K222)</f>
+        <f>RATE(10,,K212,-'Real Returns 1792-2026'!$K222)</f>
         <v>5.6761148647739706E-2</v>
       </c>
       <c r="N222" s="2">
-        <f>RATE(30,,J192,-'Real Returns 1792-2025'!$J222)</f>
+        <f>RATE(30,,J192,-'Real Returns 1792-2026'!$J222)</f>
         <v>7.7763445605825654E-2</v>
       </c>
       <c r="O222" s="2">
-        <f>RATE(30,,K192,-'Real Returns 1792-2025'!$K222)</f>
+        <f>RATE(30,,K192,-'Real Returns 1792-2026'!$K222)</f>
         <v>7.7570577342452263E-2</v>
       </c>
       <c r="P222" s="2">
-        <f>RATE(50,,J172,-'Real Returns 1792-2025'!$J222)</f>
+        <f>RATE(50,,J172,-'Real Returns 1792-2026'!$J222)</f>
         <v>5.1331534552603697E-2</v>
       </c>
       <c r="Q222" s="2">
-        <f>RATE(50,,K172,-'Real Returns 1792-2025'!$K222)</f>
+        <f>RATE(50,,K172,-'Real Returns 1792-2026'!$K222)</f>
         <v>3.2090980077451682E-2</v>
       </c>
       <c r="R222" s="2">
-        <f>RATE(100,,J122,-'Real Returns 1792-2025'!$J222)</f>
+        <f>RATE(100,,J122,-'Real Returns 1792-2026'!$J222)</f>
         <v>6.035080587821702E-2</v>
       </c>
       <c r="S222" s="2">
-        <f>RATE(100,,K122,-'Real Returns 1792-2025'!$K222)</f>
+        <f>RATE(100,,K122,-'Real Returns 1792-2026'!$K222)</f>
         <v>2.2354441888928905E-2</v>
       </c>
     </row>
@@ -16478,35 +16478,35 @@
         <v>7836.1397681875769</v>
       </c>
       <c r="L223" s="2">
-        <f>RATE(10,,J213,-'Real Returns 1792-2025'!$J223)</f>
+        <f>RATE(10,,J213,-'Real Returns 1792-2026'!$J223)</f>
         <v>6.4836396173182778E-2</v>
       </c>
       <c r="M223" s="2">
-        <f>RATE(10,,K213,-'Real Returns 1792-2025'!$K223)</f>
+        <f>RATE(10,,K213,-'Real Returns 1792-2026'!$K223)</f>
         <v>4.877891671510743E-2</v>
       </c>
       <c r="N223" s="2">
-        <f>RATE(30,,J193,-'Real Returns 1792-2025'!$J223)</f>
+        <f>RATE(30,,J193,-'Real Returns 1792-2026'!$J223)</f>
         <v>7.4668161635674232E-2</v>
       </c>
       <c r="O223" s="2">
-        <f>RATE(30,,K193,-'Real Returns 1792-2025'!$K223)</f>
+        <f>RATE(30,,K193,-'Real Returns 1792-2026'!$K223)</f>
         <v>6.7305604944530861E-2</v>
       </c>
       <c r="P223" s="2">
-        <f>RATE(50,,J173,-'Real Returns 1792-2025'!$J223)</f>
+        <f>RATE(50,,J173,-'Real Returns 1792-2026'!$J223)</f>
         <v>5.4814622394088526E-2</v>
       </c>
       <c r="Q223" s="2">
-        <f>RATE(50,,K173,-'Real Returns 1792-2025'!$K223)</f>
+        <f>RATE(50,,K173,-'Real Returns 1792-2026'!$K223)</f>
         <v>3.1470289479261677E-2</v>
       </c>
       <c r="R223" s="2">
-        <f>RATE(100,,J123,-'Real Returns 1792-2025'!$J223)</f>
+        <f>RATE(100,,J123,-'Real Returns 1792-2026'!$J223)</f>
         <v>6.1231006333418027E-2</v>
       </c>
       <c r="S223" s="2">
-        <f>RATE(100,,K123,-'Real Returns 1792-2025'!$K223)</f>
+        <f>RATE(100,,K123,-'Real Returns 1792-2026'!$K223)</f>
         <v>2.264982475801872E-2</v>
       </c>
     </row>
@@ -16541,35 +16541,35 @@
         <v>7645.5001955644411</v>
       </c>
       <c r="L224" s="2">
-        <f>RATE(10,,J214,-'Real Returns 1792-2025'!$J224)</f>
+        <f>RATE(10,,J214,-'Real Returns 1792-2026'!$J224)</f>
         <v>4.9360784602620757E-2</v>
       </c>
       <c r="M224" s="2">
-        <f>RATE(10,,K214,-'Real Returns 1792-2025'!$K224)</f>
+        <f>RATE(10,,K214,-'Real Returns 1792-2026'!$K224)</f>
         <v>4.1113039859621468E-2</v>
       </c>
       <c r="N224" s="2">
-        <f>RATE(30,,J194,-'Real Returns 1792-2025'!$J224)</f>
+        <f>RATE(30,,J194,-'Real Returns 1792-2026'!$J224)</f>
         <v>7.6754934045151324E-2</v>
       </c>
       <c r="O224" s="2">
-        <f>RATE(30,,K194,-'Real Returns 1792-2025'!$K224)</f>
+        <f>RATE(30,,K194,-'Real Returns 1792-2026'!$K224)</f>
         <v>6.4450707592137849E-2</v>
       </c>
       <c r="P224" s="2">
-        <f>RATE(50,,J174,-'Real Returns 1792-2025'!$J224)</f>
+        <f>RATE(50,,J174,-'Real Returns 1792-2026'!$J224)</f>
         <v>5.5212302004634471E-2</v>
       </c>
       <c r="Q224" s="2">
-        <f>RATE(50,,K174,-'Real Returns 1792-2025'!$K224)</f>
+        <f>RATE(50,,K174,-'Real Returns 1792-2026'!$K224)</f>
         <v>3.0924993760049427E-2</v>
       </c>
       <c r="R224" s="2">
-        <f>RATE(100,,J124,-'Real Returns 1792-2025'!$J224)</f>
+        <f>RATE(100,,J124,-'Real Returns 1792-2026'!$J224)</f>
         <v>6.3754652887050137E-2</v>
       </c>
       <c r="S224" s="2">
-        <f>RATE(100,,K124,-'Real Returns 1792-2025'!$K224)</f>
+        <f>RATE(100,,K124,-'Real Returns 1792-2026'!$K224)</f>
         <v>2.2502818677476576E-2</v>
       </c>
     </row>
@@ -16604,35 +16604,35 @@
         <v>9206.8658182796789</v>
       </c>
       <c r="L225" s="2">
-        <f>RATE(10,,J215,-'Real Returns 1792-2025'!$J225)</f>
+        <f>RATE(10,,J215,-'Real Returns 1792-2026'!$J225)</f>
         <v>5.5726530638785986E-2</v>
       </c>
       <c r="M225" s="2">
-        <f>RATE(10,,K215,-'Real Returns 1792-2025'!$K225)</f>
+        <f>RATE(10,,K215,-'Real Returns 1792-2026'!$K225)</f>
         <v>5.3964632258628346E-2</v>
       </c>
       <c r="N225" s="2">
-        <f>RATE(30,,J195,-'Real Returns 1792-2025'!$J225)</f>
+        <f>RATE(30,,J195,-'Real Returns 1792-2026'!$J225)</f>
         <v>7.7183429161287093E-2</v>
       </c>
       <c r="O225" s="2">
-        <f>RATE(30,,K195,-'Real Returns 1792-2025'!$K225)</f>
+        <f>RATE(30,,K195,-'Real Returns 1792-2026'!$K225)</f>
         <v>6.6560490474893291E-2</v>
       </c>
       <c r="P225" s="2">
-        <f>RATE(50,,J175,-'Real Returns 1792-2025'!$J225)</f>
+        <f>RATE(50,,J175,-'Real Returns 1792-2026'!$J225)</f>
         <v>5.4155457782744512E-2</v>
       </c>
       <c r="Q225" s="2">
-        <f>RATE(50,,K175,-'Real Returns 1792-2025'!$K225)</f>
+        <f>RATE(50,,K175,-'Real Returns 1792-2026'!$K225)</f>
         <v>3.4254428944105818E-2</v>
       </c>
       <c r="R225" s="2">
-        <f>RATE(100,,J125,-'Real Returns 1792-2025'!$J225)</f>
+        <f>RATE(100,,J125,-'Real Returns 1792-2026'!$J225)</f>
         <v>6.5597897121402557E-2</v>
       </c>
       <c r="S225" s="2">
-        <f>RATE(100,,K125,-'Real Returns 1792-2025'!$K225)</f>
+        <f>RATE(100,,K125,-'Real Returns 1792-2026'!$K225)</f>
         <v>2.4361885595765374E-2</v>
       </c>
     </row>
@@ -16667,35 +16667,35 @@
         <v>8539.2044760528661</v>
       </c>
       <c r="L226" s="2">
-        <f>RATE(10,,J216,-'Real Returns 1792-2025'!$J226)</f>
+        <f>RATE(10,,J216,-'Real Returns 1792-2026'!$J226)</f>
         <v>3.9027589099144555E-2</v>
       </c>
       <c r="M226" s="2">
-        <f>RATE(10,,K216,-'Real Returns 1792-2025'!$K226)</f>
+        <f>RATE(10,,K216,-'Real Returns 1792-2026'!$K226)</f>
         <v>4.8016198311006862E-2</v>
       </c>
       <c r="N226" s="2">
-        <f>RATE(30,,J196,-'Real Returns 1792-2025'!$J226)</f>
+        <f>RATE(30,,J196,-'Real Returns 1792-2026'!$J226)</f>
         <v>6.915614695955366E-2</v>
       </c>
       <c r="O226" s="2">
-        <f>RATE(30,,K196,-'Real Returns 1792-2025'!$K226)</f>
+        <f>RATE(30,,K196,-'Real Returns 1792-2026'!$K226)</f>
         <v>5.6908496783210763E-2</v>
       </c>
       <c r="P226" s="2">
-        <f>RATE(50,,J176,-'Real Returns 1792-2025'!$J226)</f>
+        <f>RATE(50,,J176,-'Real Returns 1792-2026'!$J226)</f>
         <v>5.0970053029214792E-2</v>
       </c>
       <c r="Q226" s="2">
-        <f>RATE(50,,K176,-'Real Returns 1792-2025'!$K226)</f>
+        <f>RATE(50,,K176,-'Real Returns 1792-2026'!$K226)</f>
         <v>3.3254512973881975E-2</v>
       </c>
       <c r="R226" s="2">
-        <f>RATE(100,,J126,-'Real Returns 1792-2025'!$J226)</f>
+        <f>RATE(100,,J126,-'Real Returns 1792-2026'!$J226)</f>
         <v>6.2342903616341851E-2</v>
       </c>
       <c r="S226" s="2">
-        <f>RATE(100,,K126,-'Real Returns 1792-2025'!$K226)</f>
+        <f>RATE(100,,K126,-'Real Returns 1792-2026'!$K226)</f>
         <v>2.3128715677074963E-2</v>
       </c>
     </row>
@@ -16730,35 +16730,35 @@
         <v>8811.4629568058299</v>
       </c>
       <c r="L227" s="2">
-        <f>RATE(10,,J217,-'Real Returns 1792-2025'!$J227)</f>
+        <f>RATE(10,,J217,-'Real Returns 1792-2026'!$J227)</f>
         <v>4.5890856303677591E-2</v>
       </c>
       <c r="M227" s="2">
-        <f>RATE(10,,K217,-'Real Returns 1792-2025'!$K227)</f>
+        <f>RATE(10,,K217,-'Real Returns 1792-2026'!$K227)</f>
         <v>4.96792685843103E-2</v>
       </c>
       <c r="N227" s="2">
-        <f>RATE(30,,J197,-'Real Returns 1792-2025'!$J227)</f>
+        <f>RATE(30,,J197,-'Real Returns 1792-2026'!$J227)</f>
         <v>6.6814546676893252E-2</v>
       </c>
       <c r="O227" s="2">
-        <f>RATE(30,,K197,-'Real Returns 1792-2025'!$K227)</f>
+        <f>RATE(30,,K197,-'Real Returns 1792-2026'!$K227)</f>
         <v>5.1565241946935174E-2</v>
       </c>
       <c r="P227" s="2">
-        <f>RATE(50,,J177,-'Real Returns 1792-2025'!$J227)</f>
+        <f>RATE(50,,J177,-'Real Returns 1792-2026'!$J227)</f>
         <v>5.5823155010653679E-2</v>
       </c>
       <c r="Q227" s="2">
-        <f>RATE(50,,K177,-'Real Returns 1792-2025'!$K227)</f>
+        <f>RATE(50,,K177,-'Real Returns 1792-2026'!$K227)</f>
         <v>3.4280806661804608E-2</v>
       </c>
       <c r="R227" s="2">
-        <f>RATE(100,,J127,-'Real Returns 1792-2025'!$J227)</f>
+        <f>RATE(100,,J127,-'Real Returns 1792-2026'!$J227)</f>
         <v>6.4524704956186077E-2</v>
       </c>
       <c r="S227" s="2">
-        <f>RATE(100,,K127,-'Real Returns 1792-2025'!$K227)</f>
+        <f>RATE(100,,K127,-'Real Returns 1792-2026'!$K227)</f>
         <v>2.4063338914533699E-2</v>
       </c>
     </row>
@@ -16793,35 +16793,35 @@
         <v>9474.1085944286206</v>
       </c>
       <c r="L228" s="2">
-        <f>RATE(10,,J218,-'Real Returns 1792-2025'!$J228)</f>
+        <f>RATE(10,,J218,-'Real Returns 1792-2026'!$J228)</f>
         <v>7.2357446487603755E-2</v>
       </c>
       <c r="M228" s="2">
-        <f>RATE(10,,K218,-'Real Returns 1792-2025'!$K228)</f>
+        <f>RATE(10,,K218,-'Real Returns 1792-2026'!$K228)</f>
         <v>5.8327238330599718E-2</v>
       </c>
       <c r="N228" s="2">
-        <f>RATE(30,,J198,-'Real Returns 1792-2025'!$J228)</f>
+        <f>RATE(30,,J198,-'Real Returns 1792-2026'!$J228)</f>
         <v>7.7294179913099323E-2</v>
       </c>
       <c r="O228" s="2">
-        <f>RATE(30,,K198,-'Real Returns 1792-2025'!$K228)</f>
+        <f>RATE(30,,K198,-'Real Returns 1792-2026'!$K228)</f>
         <v>5.4577763552951901E-2</v>
       </c>
       <c r="P228" s="2">
-        <f>RATE(50,,J178,-'Real Returns 1792-2025'!$J228)</f>
+        <f>RATE(50,,J178,-'Real Returns 1792-2026'!$J228)</f>
         <v>5.7902468230188839E-2</v>
       </c>
       <c r="Q228" s="2">
-        <f>RATE(50,,K178,-'Real Returns 1792-2025'!$K228)</f>
+        <f>RATE(50,,K178,-'Real Returns 1792-2026'!$K228)</f>
         <v>3.8281063492258863E-2</v>
       </c>
       <c r="R228" s="2">
-        <f>RATE(100,,J128,-'Real Returns 1792-2025'!$J228)</f>
+        <f>RATE(100,,J128,-'Real Returns 1792-2026'!$J228)</f>
         <v>7.0557477346676681E-2</v>
       </c>
       <c r="S228" s="2">
-        <f>RATE(100,,K128,-'Real Returns 1792-2025'!$K228)</f>
+        <f>RATE(100,,K128,-'Real Returns 1792-2026'!$K228)</f>
         <v>2.7671332814234041E-2</v>
       </c>
     </row>
@@ -16856,35 +16856,35 @@
         <v>9361.1907221541423</v>
       </c>
       <c r="L229" s="2">
-        <f>RATE(10,,J219,-'Real Returns 1792-2025'!$J229)</f>
+        <f>RATE(10,,J219,-'Real Returns 1792-2026'!$J229)</f>
         <v>0.12206197848743676</v>
       </c>
       <c r="M229" s="2">
-        <f>RATE(10,,K219,-'Real Returns 1792-2025'!$K229)</f>
+        <f>RATE(10,,K219,-'Real Returns 1792-2026'!$K229)</f>
         <v>5.8908075353364849E-2</v>
       </c>
       <c r="N229" s="2">
-        <f>RATE(30,,J199,-'Real Returns 1792-2025'!$J229)</f>
+        <f>RATE(30,,J199,-'Real Returns 1792-2026'!$J229)</f>
         <v>7.0802900806194072E-2</v>
       </c>
       <c r="O229" s="2">
-        <f>RATE(30,,K199,-'Real Returns 1792-2025'!$K229)</f>
+        <f>RATE(30,,K199,-'Real Returns 1792-2026'!$K229)</f>
         <v>5.3254894367013549E-2</v>
       </c>
       <c r="P229" s="2">
-        <f>RATE(50,,J179,-'Real Returns 1792-2025'!$J229)</f>
+        <f>RATE(50,,J179,-'Real Returns 1792-2026'!$J229)</f>
         <v>5.4421208263923326E-2</v>
       </c>
       <c r="Q229" s="2">
-        <f>RATE(50,,K179,-'Real Returns 1792-2025'!$K229)</f>
+        <f>RATE(50,,K179,-'Real Returns 1792-2026'!$K229)</f>
         <v>3.8999518960413919E-2</v>
       </c>
       <c r="R229" s="2">
-        <f>RATE(100,,J129,-'Real Returns 1792-2025'!$J229)</f>
+        <f>RATE(100,,J129,-'Real Returns 1792-2026'!$J229)</f>
         <v>7.0159938520797605E-2</v>
       </c>
       <c r="S229" s="2">
-        <f>RATE(100,,K129,-'Real Returns 1792-2025'!$K229)</f>
+        <f>RATE(100,,K129,-'Real Returns 1792-2026'!$K229)</f>
         <v>2.8453320524215824E-2</v>
       </c>
     </row>
@@ -16919,35 +16919,35 @@
         <v>11295.425842151299</v>
       </c>
       <c r="L230" s="2">
-        <f>RATE(10,,J220,-'Real Returns 1792-2025'!$J230)</f>
+        <f>RATE(10,,J220,-'Real Returns 1792-2026'!$J230)</f>
         <v>0.10771644772629367</v>
       </c>
       <c r="M230" s="2">
-        <f>RATE(10,,K220,-'Real Returns 1792-2025'!$K230)</f>
+        <f>RATE(10,,K220,-'Real Returns 1792-2026'!$K230)</f>
         <v>6.6863396923449919E-2</v>
       </c>
       <c r="N230" s="2">
-        <f>RATE(30,,J200,-'Real Returns 1792-2025'!$J230)</f>
+        <f>RATE(30,,J200,-'Real Returns 1792-2026'!$J230)</f>
         <v>7.4291283370987699E-2</v>
       </c>
       <c r="O230" s="2">
-        <f>RATE(30,,K200,-'Real Returns 1792-2025'!$K230)</f>
+        <f>RATE(30,,K200,-'Real Returns 1792-2026'!$K230)</f>
         <v>5.7737628253876148E-2</v>
       </c>
       <c r="P230" s="2">
-        <f>RATE(50,,J180,-'Real Returns 1792-2025'!$J230)</f>
+        <f>RATE(50,,J180,-'Real Returns 1792-2026'!$J230)</f>
         <v>6.2983484301702836E-2</v>
       </c>
       <c r="Q230" s="2">
-        <f>RATE(50,,K180,-'Real Returns 1792-2025'!$K230)</f>
+        <f>RATE(50,,K180,-'Real Returns 1792-2026'!$K230)</f>
         <v>4.614421725565053E-2</v>
       </c>
       <c r="R230" s="2">
-        <f>RATE(100,,J130,-'Real Returns 1792-2025'!$J230)</f>
+        <f>RATE(100,,J130,-'Real Returns 1792-2026'!$J230)</f>
         <v>7.1688445499826892E-2</v>
       </c>
       <c r="S230" s="2">
-        <f>RATE(100,,K130,-'Real Returns 1792-2025'!$K230)</f>
+        <f>RATE(100,,K130,-'Real Returns 1792-2026'!$K230)</f>
         <v>3.2266074292474772E-2</v>
       </c>
     </row>
@@ -16982,35 +16982,35 @@
         <v>11811.425052162303</v>
       </c>
       <c r="L231" s="2">
-        <f>RATE(10,,J221,-'Real Returns 1792-2025'!$J231)</f>
+        <f>RATE(10,,J221,-'Real Returns 1792-2026'!$J231)</f>
         <v>0.10445856389252098</v>
       </c>
       <c r="M231" s="2">
-        <f>RATE(10,,K221,-'Real Returns 1792-2025'!$K231)</f>
+        <f>RATE(10,,K221,-'Real Returns 1792-2026'!$K231)</f>
         <v>6.4001297318338937E-2</v>
       </c>
       <c r="N231" s="2">
-        <f>RATE(30,,J201,-'Real Returns 1792-2025'!$J231)</f>
+        <f>RATE(30,,J201,-'Real Returns 1792-2026'!$J231)</f>
         <v>8.0444828084418815E-2</v>
       </c>
       <c r="O231" s="2">
-        <f>RATE(30,,K201,-'Real Returns 1792-2025'!$K231)</f>
+        <f>RATE(30,,K201,-'Real Returns 1792-2026'!$K231)</f>
         <v>5.7732186833306158E-2</v>
       </c>
       <c r="P231" s="2">
-        <f>RATE(50,,J181,-'Real Returns 1792-2025'!$J231)</f>
+        <f>RATE(50,,J181,-'Real Returns 1792-2026'!$J231)</f>
         <v>6.5073995142221411E-2</v>
       </c>
       <c r="Q231" s="2">
-        <f>RATE(50,,K181,-'Real Returns 1792-2025'!$K231)</f>
+        <f>RATE(50,,K181,-'Real Returns 1792-2026'!$K231)</f>
         <v>4.4109065727762228E-2</v>
       </c>
       <c r="R231" s="2">
-        <f>RATE(100,,J131,-'Real Returns 1792-2025'!$J231)</f>
+        <f>RATE(100,,J131,-'Real Returns 1792-2026'!$J231)</f>
         <v>7.5041560504752858E-2</v>
       </c>
       <c r="S231" s="2">
-        <f>RATE(100,,K131,-'Real Returns 1792-2025'!$K231)</f>
+        <f>RATE(100,,K131,-'Real Returns 1792-2026'!$K231)</f>
         <v>3.2095733407139643E-2</v>
       </c>
     </row>
@@ -17045,35 +17045,35 @@
         <v>10553.504451469051</v>
       </c>
       <c r="L232" s="2">
-        <f>RATE(10,,J222,-'Real Returns 1792-2025'!$J232)</f>
+        <f>RATE(10,,J222,-'Real Returns 1792-2026'!$J232)</f>
         <v>0.11590119434846485</v>
       </c>
       <c r="M232" s="2">
-        <f>RATE(10,,K222,-'Real Returns 1792-2025'!$K232)</f>
+        <f>RATE(10,,K222,-'Real Returns 1792-2026'!$K232)</f>
         <v>3.3784454343198531E-2</v>
       </c>
       <c r="N232" s="2">
-        <f>RATE(30,,J202,-'Real Returns 1792-2025'!$J232)</f>
+        <f>RATE(30,,J202,-'Real Returns 1792-2026'!$J232)</f>
         <v>7.6200999315481507E-2</v>
       </c>
       <c r="O232" s="2">
-        <f>RATE(30,,K202,-'Real Returns 1792-2025'!$K232)</f>
+        <f>RATE(30,,K202,-'Real Returns 1792-2026'!$K232)</f>
         <v>4.944419528511379E-2</v>
       </c>
       <c r="P232" s="2">
-        <f>RATE(50,,J182,-'Real Returns 1792-2025'!$J232)</f>
+        <f>RATE(50,,J182,-'Real Returns 1792-2026'!$J232)</f>
         <v>6.5115185139465653E-2</v>
       </c>
       <c r="Q232" s="2">
-        <f>RATE(50,,K182,-'Real Returns 1792-2025'!$K232)</f>
+        <f>RATE(50,,K182,-'Real Returns 1792-2026'!$K232)</f>
         <v>4.1170815167807795E-2</v>
       </c>
       <c r="R232" s="2">
-        <f>RATE(100,,J132,-'Real Returns 1792-2025'!$J232)</f>
+        <f>RATE(100,,J132,-'Real Returns 1792-2026'!$J232)</f>
         <v>7.387382728920526E-2</v>
       </c>
       <c r="S232" s="2">
-        <f>RATE(100,,K132,-'Real Returns 1792-2025'!$K232)</f>
+        <f>RATE(100,,K132,-'Real Returns 1792-2026'!$K232)</f>
         <v>2.8167301661538507E-2</v>
       </c>
     </row>
@@ -17108,35 +17108,35 @@
         <v>8374.9465307550745</v>
       </c>
       <c r="L233" s="2">
-        <f>RATE(10,,J223,-'Real Returns 1792-2025'!$J233)</f>
+        <f>RATE(10,,J223,-'Real Returns 1792-2026'!$J233)</f>
         <v>8.50480543147734E-2</v>
       </c>
       <c r="M233" s="2">
-        <f>RATE(10,,K223,-'Real Returns 1792-2025'!$K233)</f>
+        <f>RATE(10,,K223,-'Real Returns 1792-2026'!$K233)</f>
         <v>6.6719949189227665E-3</v>
       </c>
       <c r="N233" s="2">
-        <f>RATE(30,,J203,-'Real Returns 1792-2025'!$J233)</f>
+        <f>RATE(30,,J203,-'Real Returns 1792-2026'!$J233)</f>
         <v>6.8402318186620278E-2</v>
       </c>
       <c r="O233" s="2">
-        <f>RATE(30,,K203,-'Real Returns 1792-2025'!$K233)</f>
+        <f>RATE(30,,K203,-'Real Returns 1792-2026'!$K233)</f>
         <v>3.7926460875903796E-2</v>
       </c>
       <c r="P233" s="2">
-        <f>RATE(50,,J183,-'Real Returns 1792-2025'!$J233)</f>
+        <f>RATE(50,,J183,-'Real Returns 1792-2026'!$J233)</f>
         <v>6.0482282486123667E-2</v>
       </c>
       <c r="Q233" s="2">
-        <f>RATE(50,,K183,-'Real Returns 1792-2025'!$K233)</f>
+        <f>RATE(50,,K183,-'Real Returns 1792-2026'!$K233)</f>
         <v>3.5834325452568719E-2</v>
       </c>
       <c r="R233" s="2">
-        <f>RATE(100,,J133,-'Real Returns 1792-2025'!$J233)</f>
+        <f>RATE(100,,J133,-'Real Returns 1792-2026'!$J233)</f>
         <v>6.9452462317650912E-2</v>
       </c>
       <c r="S233" s="2">
-        <f>RATE(100,,K133,-'Real Returns 1792-2025'!$K233)</f>
+        <f>RATE(100,,K133,-'Real Returns 1792-2026'!$K233)</f>
         <v>2.4928438835601412E-2</v>
       </c>
     </row>
@@ -17169,35 +17169,35 @@
         <v>8321.0005548674781</v>
       </c>
       <c r="L234" s="2">
-        <f>RATE(10,,J224,-'Real Returns 1792-2025'!$J234)</f>
+        <f>RATE(10,,J224,-'Real Returns 1792-2026'!$J234)</f>
         <v>8.2679962418073197E-2</v>
       </c>
       <c r="M234" s="2">
-        <f>RATE(10,,K224,-'Real Returns 1792-2025'!$K234)</f>
+        <f>RATE(10,,K224,-'Real Returns 1792-2026'!$K234)</f>
         <v>8.5024665353047816E-3</v>
       </c>
       <c r="N234" s="2">
-        <f>RATE(30,,J204,-'Real Returns 1792-2025'!$J234)</f>
+        <f>RATE(30,,J204,-'Real Returns 1792-2026'!$J234)</f>
         <v>6.9904341433805403E-2</v>
       </c>
       <c r="O234" s="2">
-        <f>RATE(30,,K204,-'Real Returns 1792-2025'!$K234)</f>
+        <f>RATE(30,,K204,-'Real Returns 1792-2026'!$K234)</f>
         <v>3.4448682966345082E-2</v>
       </c>
       <c r="P234" s="2">
-        <f>RATE(50,,J184,-'Real Returns 1792-2025'!$J234)</f>
+        <f>RATE(50,,J184,-'Real Returns 1792-2026'!$J234)</f>
         <v>6.9223024683182616E-2</v>
       </c>
       <c r="Q234" s="2">
-        <f>RATE(50,,K184,-'Real Returns 1792-2025'!$K234)</f>
+        <f>RATE(50,,K184,-'Real Returns 1792-2026'!$K234)</f>
         <v>3.7336193725611533E-2</v>
       </c>
       <c r="R234" s="2">
-        <f>RATE(100,,J134,-'Real Returns 1792-2025'!$J234)</f>
+        <f>RATE(100,,J134,-'Real Returns 1792-2026'!$J234)</f>
         <v>7.0752039479677134E-2</v>
       </c>
       <c r="S234" s="2">
-        <f>RATE(100,,K134,-'Real Returns 1792-2025'!$K234)</f>
+        <f>RATE(100,,K134,-'Real Returns 1792-2026'!$K234)</f>
         <v>2.4767309890629093E-2</v>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       <c r="A235">
         <v>2025</v>
       </c>
-      <c r="D235" s="43">
+      <c r="D235">
         <v>317.67099999999999</v>
       </c>
       <c r="E235">
@@ -17230,39 +17230,99 @@
         <v>8021.9793865564288</v>
       </c>
       <c r="L235" s="2">
-        <f>RATE(10,,J225,-'Real Returns 1792-2025'!$J235)</f>
+        <f>RATE(10,,J225,-'Real Returns 1792-2026'!$J235)</f>
         <v>9.3462586164452369E-2</v>
       </c>
       <c r="M235" s="2">
-        <f>RATE(10,,K225,-'Real Returns 1792-2025'!$K235)</f>
+        <f>RATE(10,,K225,-'Real Returns 1792-2026'!$K235)</f>
         <v>-1.3681968531945338E-2</v>
       </c>
       <c r="N235" s="2">
-        <f>RATE(30,,J205,-'Real Returns 1792-2025'!$J235)</f>
+        <f>RATE(30,,J205,-'Real Returns 1792-2026'!$J235)</f>
         <v>7.8817176125844851E-2</v>
       </c>
       <c r="O235" s="2">
-        <f>RATE(30,,K205,-'Real Returns 1792-2025'!$K235)</f>
+        <f>RATE(30,,K205,-'Real Returns 1792-2026'!$K235)</f>
         <v>3.6005599976797545E-2</v>
       </c>
       <c r="P235" s="2">
-        <f>RATE(50,,J185,-'Real Returns 1792-2025'!$J235)</f>
+        <f>RATE(50,,J185,-'Real Returns 1792-2026'!$J235)</f>
         <v>8.027231653985574E-2</v>
       </c>
       <c r="Q235" s="2">
-        <f>RATE(50,,K185,-'Real Returns 1792-2025'!$K235)</f>
+        <f>RATE(50,,K185,-'Real Returns 1792-2026'!$K235)</f>
         <v>3.8225728588419883E-2</v>
       </c>
       <c r="R235" s="2">
-        <f>RATE(100,,J135,-'Real Returns 1792-2025'!$J235)</f>
+        <f>RATE(100,,J135,-'Real Returns 1792-2026'!$J235)</f>
         <v>7.0375376549018182E-2</v>
       </c>
       <c r="S235" s="2">
-        <f>RATE(100,,K135,-'Real Returns 1792-2025'!$K235)</f>
+        <f>RATE(100,,K135,-'Real Returns 1792-2026'!$K235)</f>
         <v>2.3562057936181387E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>2026</v>
+      </c>
+      <c r="D236">
+        <v>325.25200000000001</v>
+      </c>
+      <c r="E236">
+        <v>1.0238643124490432</v>
+      </c>
+      <c r="F236">
+        <v>0.15451346114449982</v>
+      </c>
+      <c r="G236">
+        <v>0.12760396773958171</v>
+      </c>
+      <c r="H236">
+        <v>7.2361579936954357E-2</v>
+      </c>
+      <c r="I236">
+        <v>4.7366889243270593E-2</v>
+      </c>
+      <c r="J236">
+        <v>1233143.9285310188</v>
+      </c>
+      <c r="K236">
+        <v>8401.9555956712502</v>
+      </c>
+      <c r="L236" s="2">
+        <f>RATE(10,,J226,-'Real Returns 1792-2026'!$J236)</f>
+        <v>0.11353701375774819</v>
+      </c>
+      <c r="M236" s="2">
+        <f>RATE(10,,K226,-'Real Returns 1792-2026'!$K236)</f>
+        <v>-1.6190242651311735E-3</v>
+      </c>
+      <c r="N236" s="2">
+        <f>RATE(30,,J206,-'Real Returns 1792-2026'!$J236)</f>
+        <v>7.2875113286192034E-2</v>
+      </c>
+      <c r="O236" s="2">
+        <f>RATE(30,,K206,-'Real Returns 1792-2026'!$K236)</f>
+        <v>3.1060074003160781E-2</v>
+      </c>
+      <c r="P236" s="2">
+        <f>RATE(50,,J186,-'Real Returns 1792-2026'!$J236)</f>
+        <v>7.7713832973548683E-2</v>
+      </c>
+      <c r="Q236" s="2">
+        <f>RATE(50,,K186,-'Real Returns 1792-2026'!$K236)</f>
+        <v>3.8514391978695252E-2</v>
+      </c>
+      <c r="R236" s="2">
+        <f>RATE(100,,J136,-'Real Returns 1792-2026'!$J236)</f>
+        <v>6.9570515384623346E-2</v>
+      </c>
+      <c r="S236" s="2">
+        <f>RATE(100,,K136,-'Real Returns 1792-2026'!$K236)</f>
+        <v>2.3589771940061125E-2</v>
+      </c>
+    </row>
     <row r="237" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="238" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="239" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -18106,14 +18166,14 @@
         <v>-7.6413390766475131E-2</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C235" si="1">(1+B4)*C3</f>
+        <f t="shared" ref="C4:C236" si="1">(1+B4)*C3</f>
         <v>0.92358660923352487</v>
       </c>
       <c r="D4" s="1">
         <v>-7.2395008687413762E-2</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E235" si="2">(1+D4)*E3</f>
+        <f t="shared" ref="E4:E236" si="2">(1+D4)*E3</f>
         <v>0.92760499131258622</v>
       </c>
       <c r="F4" s="1">
@@ -25174,7 +25234,37 @@
         <v>19.580416520490381</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>2026</v>
+      </c>
+      <c r="B236" s="35">
+        <v>0.15451346114449982</v>
+      </c>
+      <c r="C236" s="1">
+        <f t="shared" si="1"/>
+        <v>41230593.047638185</v>
+      </c>
+      <c r="D236" s="35">
+        <v>7.2361579936954357E-2</v>
+      </c>
+      <c r="E236" s="1">
+        <f t="shared" si="2"/>
+        <v>280922.28648614918</v>
+      </c>
+      <c r="F236" s="1">
+        <f t="shared" ref="F236" si="8">C236/E236</f>
+        <v>146.7686795638802</v>
+      </c>
+      <c r="G236" s="1">
+        <f t="shared" ref="G236" si="9">E236/C236</f>
+        <v>6.8134427792869512E-3</v>
+      </c>
+      <c r="H236" s="8">
+        <f t="shared" ref="H236" si="10">(C236-C206)/C206</f>
+        <v>16.379921937662502</v>
+      </c>
+    </row>
     <row r="237" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="238" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="239" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -26016,7 +26106,7 @@
         <v>0.10929547698755715</v>
       </c>
       <c r="I2" s="1">
-        <f t="shared" ref="I2:I12" si="1">(1+G2)/(1+F2)-1</f>
+        <f t="shared" ref="I2:I13" si="1">(1+G2)/(1+F2)-1</f>
         <v>0.10929547698755715</v>
       </c>
       <c r="J2" s="1">
@@ -26210,7 +26300,7 @@
         <v>0.23662630929759287</v>
       </c>
       <c r="K7" s="12">
-        <f t="shared" ref="K7:K12" si="2">(1+J7)/(1+F7)-1</f>
+        <f t="shared" ref="K7:K13" si="2">(1+J7)/(1+F7)-1</f>
         <v>0.20662276599274976</v>
       </c>
       <c r="L7" s="12">
@@ -26432,6 +26522,49 @@
       <c r="M12" s="12">
         <f t="shared" si="4"/>
         <v>8021.9793865564288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="12">
+        <v>325.25200000000001</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" ref="E13" si="10">1+(D13-D12)/D12</f>
+        <v>1.0238643124490432</v>
+      </c>
+      <c r="F13" s="12">
+        <f t="shared" ref="F13" si="11">E13-1</f>
+        <v>2.386431244904319E-2</v>
+      </c>
+      <c r="G13" s="22">
+        <f>VTI!E85-1</f>
+        <v>0.15451346114449982</v>
+      </c>
+      <c r="H13" s="22">
+        <v>0.12760396773958171</v>
+      </c>
+      <c r="I13" s="12">
+        <f t="shared" si="1"/>
+        <v>0.12760396773958171</v>
+      </c>
+      <c r="J13" s="30">
+        <f>VCLT!E110-1</f>
+        <v>7.2361579936954357E-2</v>
+      </c>
+      <c r="K13" s="12">
+        <f t="shared" si="2"/>
+        <v>4.7366889243270593E-2</v>
+      </c>
+      <c r="L13" s="12">
+        <f t="shared" ref="L13" si="12">L12*(1+H13)</f>
+        <v>1233143.9285310188</v>
+      </c>
+      <c r="M13" s="12">
+        <f t="shared" ref="M13" si="13">M12*(1+K13)</f>
+        <v>8401.9555956712466</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -28596,7 +28729,7 @@
       </c>
       <c r="E51" s="19"/>
       <c r="F51" s="21">
-        <f t="shared" ref="F51:F73" si="1">F50*D51</f>
+        <f t="shared" ref="F51:F85" si="1">F50*D51</f>
         <v>15796.951654159999</v>
       </c>
       <c r="G51" s="20">
@@ -29100,7 +29233,7 @@
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="D73" s="23">
-        <f t="shared" ref="D73" si="2">1+C73</f>
+        <f t="shared" ref="D73:D85" si="2">1+C73</f>
         <v>1.0303</v>
       </c>
       <c r="E73" s="23">
@@ -29115,29 +29248,285 @@
         <v>3.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>2025</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74" s="43">
+        <v>-1.89E-2</v>
+      </c>
+      <c r="D74" s="43">
+        <f t="shared" si="2"/>
+        <v>0.98109999999999997</v>
+      </c>
+      <c r="F74" s="21">
+        <f t="shared" si="1"/>
+        <v>23252.397658336406</v>
+      </c>
+      <c r="G74">
+        <v>-1.89E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>2025</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
+      </c>
+      <c r="C75" s="43">
+        <v>-5.8500000000000003E-2</v>
+      </c>
+      <c r="D75" s="43">
+        <f t="shared" si="2"/>
+        <v>0.9415</v>
+      </c>
+      <c r="F75" s="21">
+        <f t="shared" si="1"/>
+        <v>21892.132395323726</v>
+      </c>
+      <c r="G75">
+        <v>-5.8500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>2025</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
+      </c>
+      <c r="C76" s="43">
+        <v>-7.3000000000000001E-3</v>
+      </c>
+      <c r="D76" s="43">
+        <f t="shared" si="2"/>
+        <v>0.99270000000000003</v>
+      </c>
+      <c r="F76" s="21">
+        <f t="shared" si="1"/>
+        <v>21732.319828837863</v>
+      </c>
+      <c r="G76">
+        <v>-7.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>2025</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+      <c r="C77" s="43">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D77" s="43">
+        <f t="shared" si="2"/>
+        <v>1.0625</v>
+      </c>
+      <c r="F77" s="21">
+        <f t="shared" si="1"/>
+        <v>23090.58981814023</v>
+      </c>
+      <c r="G77">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>2025</v>
+      </c>
+      <c r="B78">
+        <v>6</v>
+      </c>
+      <c r="C78" s="43">
+        <v>5.16E-2</v>
+      </c>
+      <c r="D78" s="43">
+        <f t="shared" si="2"/>
+        <v>1.0516000000000001</v>
+      </c>
+      <c r="F78" s="21">
+        <f t="shared" si="1"/>
+        <v>24282.064252756267</v>
+      </c>
+      <c r="G78">
+        <v>5.16E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>2025</v>
+      </c>
+      <c r="B79">
+        <v>7</v>
+      </c>
+      <c r="C79" s="43">
+        <v>2.29E-2</v>
+      </c>
+      <c r="D79" s="43">
+        <f t="shared" si="2"/>
+        <v>1.0228999999999999</v>
+      </c>
+      <c r="F79" s="21">
+        <f t="shared" si="1"/>
+        <v>24838.123524144383</v>
+      </c>
+      <c r="G79">
+        <v>2.29E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>2025</v>
+      </c>
+      <c r="B80">
+        <v>8</v>
+      </c>
+      <c r="C80" s="43">
+        <v>2.35E-2</v>
+      </c>
+      <c r="D80" s="43">
+        <f t="shared" si="2"/>
+        <v>1.0235000000000001</v>
+      </c>
+      <c r="F80" s="21">
+        <f t="shared" si="1"/>
+        <v>25421.819426961778</v>
+      </c>
+      <c r="G80">
+        <v>2.35E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>2025</v>
+      </c>
+      <c r="B81">
+        <v>9</v>
+      </c>
+      <c r="C81" s="43">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="D81" s="43">
+        <f t="shared" si="2"/>
+        <v>1.0342</v>
+      </c>
+      <c r="F81" s="21">
+        <f t="shared" si="1"/>
+        <v>26291.245651363872</v>
+      </c>
+      <c r="G81">
+        <v>3.4200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>2025</v>
+      </c>
+      <c r="B82">
+        <v>10</v>
+      </c>
+      <c r="C82" s="43">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="D82" s="43">
+        <f t="shared" si="2"/>
+        <v>1.0221</v>
+      </c>
+      <c r="F82" s="21">
+        <f t="shared" si="1"/>
+        <v>26872.282180259015</v>
+      </c>
+      <c r="G82">
+        <v>2.2100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>2025</v>
+      </c>
+      <c r="B83">
+        <v>11</v>
+      </c>
+      <c r="C83" s="43">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="D83" s="43">
+        <f t="shared" si="2"/>
+        <v>1.0026999999999999</v>
+      </c>
+      <c r="F83" s="21">
+        <f t="shared" si="1"/>
+        <v>26944.837342145711</v>
+      </c>
+      <c r="G83">
+        <v>2.7000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>2025</v>
+      </c>
+      <c r="B84">
+        <v>12</v>
+      </c>
+      <c r="C84" s="43">
+        <v>-2.9999999999999997E-4</v>
+      </c>
+      <c r="D84" s="43">
+        <f t="shared" si="2"/>
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="F84" s="21">
+        <f t="shared" si="1"/>
+        <v>26936.75389094307</v>
+      </c>
+      <c r="G84">
+        <v>-2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" s="22" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="22">
+        <v>2026</v>
+      </c>
+      <c r="B85" s="22">
+        <v>1</v>
+      </c>
+      <c r="C85" s="23">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="D85" s="23">
+        <f t="shared" si="2"/>
+        <v>1.0158</v>
+      </c>
+      <c r="E85" s="23">
+        <f>PRODUCT(D74:D85)</f>
+        <v>1.1545134611444998</v>
+      </c>
+      <c r="F85" s="24">
+        <f t="shared" si="1"/>
+        <v>27362.354602419971</v>
+      </c>
+      <c r="G85" s="22">
+        <v>1.5800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -31794,7 +32183,7 @@
       </c>
       <c r="E76" s="19"/>
       <c r="F76" s="26">
-        <f t="shared" ref="F76:F98" si="1">F75*D76</f>
+        <f t="shared" ref="F76:F110" si="1">F75*D76</f>
         <v>11316.371586756</v>
       </c>
       <c r="G76" s="19">
@@ -32302,18 +32691,286 @@
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>2025</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99" s="19">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="D99" s="15">
+        <f>C99+1</f>
+        <v>1.0343</v>
+      </c>
+      <c r="F99" s="26">
+        <f t="shared" si="1"/>
+        <v>12084.324560730243</v>
+      </c>
+      <c r="G99" s="19">
+        <f>D99-1</f>
+        <v>3.4299999999999997E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>2025</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="C100" s="19">
+        <v>-1.43E-2</v>
+      </c>
+      <c r="D100" s="15">
+        <f>C100+1</f>
+        <v>0.98570000000000002</v>
+      </c>
+      <c r="F100" s="26">
+        <f t="shared" si="1"/>
+        <v>11911.518719511801</v>
+      </c>
+      <c r="G100" s="19">
+        <f t="shared" ref="G100:G110" si="3">D100-1</f>
+        <v>-1.4299999999999979E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>2025</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101" s="19">
+        <v>-1.3899999999999999E-2</v>
+      </c>
+      <c r="D101" s="15">
+        <f>C101+1</f>
+        <v>0.98609999999999998</v>
+      </c>
+      <c r="F101" s="26">
+        <f t="shared" si="1"/>
+        <v>11745.948609310588</v>
+      </c>
+      <c r="G101" s="19">
+        <f t="shared" si="3"/>
+        <v>-1.3900000000000023E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>2025</v>
+      </c>
+      <c r="B102">
+        <v>5</v>
+      </c>
+      <c r="C102" s="19">
+        <v>-1.1999999999999999E-3</v>
+      </c>
+      <c r="D102" s="15">
+        <f>C102+1</f>
+        <v>0.99880000000000002</v>
+      </c>
+      <c r="F102" s="26">
+        <f t="shared" si="1"/>
+        <v>11731.853470979415</v>
+      </c>
+      <c r="G102" s="19">
+        <f t="shared" si="3"/>
+        <v>-1.1999999999999789E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>2025</v>
+      </c>
+      <c r="B103">
+        <v>6</v>
+      </c>
+      <c r="C103" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="D103" s="15">
+        <f>C103+1</f>
+        <v>1.03</v>
+      </c>
+      <c r="F103" s="26">
+        <f t="shared" si="1"/>
+        <v>12083.809075108798</v>
+      </c>
+      <c r="G103" s="19">
+        <f t="shared" si="3"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>2025</v>
+      </c>
+      <c r="B104">
+        <v>7</v>
+      </c>
+      <c r="C104" s="19">
+        <v>-2.0999999999999999E-3</v>
+      </c>
+      <c r="D104" s="15">
+        <f>C104+1</f>
+        <v>0.99790000000000001</v>
+      </c>
+      <c r="F104" s="26">
+        <f t="shared" si="1"/>
+        <v>12058.433076051069</v>
+      </c>
+      <c r="G104" s="19">
+        <f t="shared" si="3"/>
+        <v>-2.0999999999999908E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>2025</v>
+      </c>
+      <c r="B105">
+        <v>8</v>
+      </c>
+      <c r="C105" s="19">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="D105" s="15">
+        <f>C105+1</f>
+        <v>1.0071000000000001</v>
+      </c>
+      <c r="F105" s="26">
+        <f t="shared" si="1"/>
+        <v>12144.047950891034</v>
+      </c>
+      <c r="G105" s="19">
+        <f t="shared" si="3"/>
+        <v>7.1000000000001062E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>2025</v>
+      </c>
+      <c r="B106">
+        <v>9</v>
+      </c>
+      <c r="C106" s="19">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="D106" s="15">
+        <f>C106+1</f>
+        <v>1.0328999999999999</v>
+      </c>
+      <c r="F106" s="26">
+        <f t="shared" si="1"/>
+        <v>12543.587128475348</v>
+      </c>
+      <c r="G106" s="19">
+        <f t="shared" si="3"/>
+        <v>3.2899999999999929E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>2025</v>
+      </c>
+      <c r="B107">
+        <v>10</v>
+      </c>
+      <c r="C107" s="19">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="D107" s="15">
+        <f>C107+1</f>
+        <v>1.0013000000000001</v>
+      </c>
+      <c r="F107" s="26">
+        <f t="shared" si="1"/>
+        <v>12559.893791742368</v>
+      </c>
+      <c r="G107" s="19">
+        <f t="shared" si="3"/>
+        <v>1.3000000000000789E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>2025</v>
+      </c>
+      <c r="B108">
+        <v>11</v>
+      </c>
+      <c r="C108" s="19">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="D108" s="15">
+        <f>C108+1</f>
+        <v>1.0082</v>
+      </c>
+      <c r="F108" s="26">
+        <f t="shared" si="1"/>
+        <v>12662.884920834655</v>
+      </c>
+      <c r="G108" s="19">
+        <f t="shared" si="3"/>
+        <v>8.1999999999999851E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>2025</v>
+      </c>
+      <c r="B109">
+        <v>12</v>
+      </c>
+      <c r="C109" s="19">
+        <v>-1.52E-2</v>
+      </c>
+      <c r="D109" s="15">
+        <f>C109+1</f>
+        <v>0.98480000000000001</v>
+      </c>
+      <c r="F109" s="26">
+        <f t="shared" si="1"/>
+        <v>12470.409070037967</v>
+      </c>
+      <c r="G109" s="19">
+        <f t="shared" si="3"/>
+        <v>-1.5199999999999991E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" s="22" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="22">
+        <v>2026</v>
+      </c>
+      <c r="B110" s="22">
+        <v>1</v>
+      </c>
+      <c r="C110" s="25">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="D110" s="27">
+        <f>C110+1</f>
+        <v>1.0046999999999999</v>
+      </c>
+      <c r="E110" s="23">
+        <f>PRODUCT(D99:D110)</f>
+        <v>1.0723615799369544</v>
+      </c>
+      <c r="F110" s="28">
+        <f t="shared" si="1"/>
+        <v>12529.019992667145</v>
+      </c>
+      <c r="G110" s="25">
+        <f t="shared" si="3"/>
+        <v>4.6999999999999265E-3</v>
+      </c>
+    </row>
     <row r="111" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
